--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-13 · 共 60 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-14 · 共 60 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,29 +633,29 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Egonex-AI/Understand-Anything</t>
+          <t>HKUDS/DeepTutor</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>82338</v>
+        <v>39536</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>3166.9</v>
+        <v>1064.4</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>将代码转换为可交互的知识图谱，支持多种代码和工具的集成。
-【原文】Graphs that teach &gt; graphs that impress. Turn any code into an interactive knowledge graph you can explore, search, and ask questions about. Works with Claude Code, Codex, Cursor, Copilot, Gemini CLI, and more.</t>
+          <t>终身个性化辅导系统
+【原文】DeepTutor: Lifelong Personalized Tutoring. https://deeptutor.info/.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Egonex-AI/Understand-Anything</t>
+          <t>https://github.com/HKUDS/DeepTutor</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>452.41</v>
+        <v>152.06</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -703,21 +703,21 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>antigravity-skills, business-knowledge, claude-code, claude-skills, codebase-analysis, codex, codex-skills, developer-tools-ai-agent, gemini-cli-skills, karpathy-llm-wiki, knowledge-base, knowledge-graph</t>
+          <t>ai-agents, ai-tutor, clawdbot, cli-tool, deepresearch, interactive-learning, large-language-models, multi-agent-systems, rag</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>182</v>
+        <v>260</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -729,36 +729,36 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>XiaoDuoYa/codex-with-chatgpt</t>
+          <t>totec448-spec/chat-on-steroids</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4134</v>
+        <v>2368</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1808.7</v>
+        <v>720.7</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>结合ChatGPT和Codex的MCP服务，用于文本处理和代码生成
-【原文】ChatGPT thinks. Codex works. Use ChatGPT as the planning brain while keeping the Codex harness.</t>
+          <t>为 ChatGPT 提供跨平台的本地 MCP 功能，包括 Chrome 集成、多代理工作流等。
+【原文】Cross-platform local MCP capabilities for ChatGPT with Chrome integration, Goal, Compact &amp; Resume, and durable multi-agent workflows.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/XiaoDuoYa/codex-with-chatgpt</t>
+          <t>https://github.com/totec448-spec/chat-on-steroids</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>258.38</v>
+        <v>102.96</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, chatgpt, codex, mcp, model-context-protocol, oauth</t>
+          <t>automation, chatgpt, chrome-extension, electron, linux, local-first, macos, mcp, multi-agent, windows</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
@@ -832,37 +832,36 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-14</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>eternityspring/reelbench-skills</t>
+          <t>RyanCodrai/turbovec</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>371</v>
+        <v>17104</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1298.5</v>
+        <v>696.1</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 视频学习笔记和工具
-【原文】Learning notes and tooling skills for AI video - AI 视频相关的学习与工具 skill
-【依据】topics: ai-video, claude-code, claude-skills, ffmpeg, shot-analysis, video-analysis</t>
+          <t>基于TurboQuant的向量索引
+【原文】A vector index built on TurboQuant, written in Rust with Python bindings</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -877,7 +876,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/eternityspring/reelbench-skills</t>
+          <t>https://github.com/RyanCodrai/turbovec</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -886,16 +885,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>185.5</v>
+        <v>99.44</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -910,12 +909,12 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>ai-video, claude-code, claude-skills, ffmpeg, shot-analysis, video-analysis</t>
+          <t>ann, avx512, embedding, embeddings, faiss, nearest-neighbor, neon, python, quant, quantization, rag, rust</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -924,7 +923,7 @@
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>2</v>
+        <v>172</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -936,25 +935,27 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>mizzlelover/gongwen-gbt9704-skill</t>
+          <t>AgriciDaniel/claude-obsidian</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>548</v>
+        <v>14882</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>959</v>
+        <v>651.1</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>信息安全提醒：请勿上传企业禁止对外公开的文件；可在本地或企业内网部署大模型后使用。中文公文排版 Skill：按 GB/T 9704-2012 生成可编辑 DOCX。配套 CEB：https://github.com/mizzlelover/CEB</t>
+          <t>为 Obsidian 和 Claude Code 提供自组织的 AI 第二大脑。
+【原文】Self-organizing AI second brain for Obsidian + Claude Code. Drop any source and Claude reads, links, and files it into one connected knowledge graph of plain Markdown you own. AI note-taking, personal knowledge management (PKM), and an open-source Notion alternative. Based on Karpathy's LLM Wiki pattern.
+【依据】Obsidian + Claude Code 的 AI 第二大脑。</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -979,7 +980,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mizzlelover/gongwen-gbt9704-skill</t>
+          <t>https://github.com/AgriciDaniel/claude-obsidian</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -988,7 +989,7 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>137</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -997,7 +998,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1007,26 +1008,26 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>ai-skill, ceb, chinese-official-document, claude-code, cross-platform, document-formatting, docx, gbt-9704-2012, kimi, opencode, trae-code, traework</t>
+          <t>agent-skills, ai-note-taking, ai-second-brain, claude-code, claude-code-skill, claude-memory, claude-plugin, karpathy-llm-wiki, knowledge-graph, knowledge-management, note-taking, notion-alternative</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1038,25 +1039,26 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>jtydhr88/screenwriting-skills</t>
+          <t>larashero3-dotcom/lieflat-charts</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>915</v>
+        <v>5321</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>915</v>
+        <v>620.8</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>(无描述)</t>
+          <t>面向 AI Agents 的数据可视化 Skill，生成 HTML 图表
+【原文】Data visualization Skill for AI Agents, turning data into polished, interactive HTML charts. 面向 AI Agents 的数据可视化 Skill，将数据快速生成精致、可交互的 HTML 图表。</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1066,12 +1068,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1081,7 +1083,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jtydhr88/screenwriting-skills</t>
+          <t>https://github.com/larashero3-dotcom/lieflat-charts</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1090,16 +1092,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>130.71</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1109,22 +1111,26 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, charts, claude-code, codex, data-visualization, html, moxt, svg</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1136,36 +1142,36 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
+          <t>agent skill in:name,description stars:&gt;300 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>VectifyAI/PageIndex</t>
+          <t>alibaba/zvec</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>35628</v>
+        <v>15913</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>470.5</v>
+        <v>393.6</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供基于向量的文档索引，用于推理增强生成。
-【原文】📑 PageIndex: Document Index for Vectorless, Reasoning-based RAG</t>
+          <t>轻量级、快速的内进程向量数据库
+【原文】A lightweight, lightning-fast, in-process vector database</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1180,7 +1186,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/VectifyAI/PageIndex</t>
+          <t>https://github.com/alibaba/zvec</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1189,16 +1195,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>67.22</v>
+        <v>56.23</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1213,24 +1219,24 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, agents, ai, ai-agents, context-engineering, information-retrieval, llm, rag, reasoning, retrieval, retrieval-augmented-generation, vector-database</t>
+          <t>agent-skills, db, embedded, faiss, fts, fulltext-search, hnsw, llm-memory, local, rag, search-engine, semantic-search</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>530</v>
+        <v>283</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
@@ -1239,26 +1245,26 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>tradecatlabs/vibe-coding-cn</t>
+          <t>Tiger3807861189/J-Space-Cognition-Suite</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>16183</v>
+        <v>3009</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>385.3</v>
+        <v>390</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 编程教程和结对编程工作流
-【原文】Vibe Coding 从入门到精通教程｜AI 结对编程工作流｜Prompt、Skill、Workflow、上下文管理、codex实战指南</t>
+          <t>提供模型无关的推理时控制套件，用于深度推理、长期工作、验证和恢复。
+【原文】J-Space Cognition Suite — a model-agnostic inference-time control suite for deep reasoning, long-horizon work, verification, and recovery. Based on Anthropic's J-space global workspace research. | 哔哩哔哩：Tiger380 — https://space.bilibili.com/3494375382321675</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1268,7 +1274,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1283,7 +1289,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tradecatlabs/vibe-coding-cn</t>
+          <t>https://github.com/Tiger3807861189/J-Space-Cognition-Suite</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1292,11 +1298,11 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>55.04</v>
+        <v>55.72</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1316,52 +1322,52 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agent, ai-agents, ai-coding, ai-programming, chinese, claude-code, codex, cursor, developer-tools, gemini-cli, glue-coding</t>
+          <t>agent-skills, ai, ai-agent, ai-agents, claude-code, codex, cognitive-enhancement, deepseek, deepseek-harness, developer-tools, dsh, dsh-plugin</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>294</v>
+        <v>54</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-14</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Fosowl/agenticSeek</t>
+          <t>lewislulu/html-ppt-skill</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>27200</v>
+        <v>8347</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>333.5</v>
+        <v>384.4</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供本地化的 AI 代理，无需 API 和月费。
-【原文】Fully Local Manus AI. No APIs, No $200 monthly bills. Enjoy an autonomous agent that thinks, browses the web, and code for the sole cost of electricity.</t>
+          <t>构建专业HTML演示文稿的智能体技能
+【原文】HTML PPT Studio — AgentSkill with 24 themes, 31 layouts, 20+ animations for building professional HTML presentations</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1371,12 +1377,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1386,7 +1392,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Fosowl/agenticSeek</t>
+          <t>https://github.com/lewislulu/html-ppt-skill</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1395,16 +1401,16 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>47.64</v>
+        <v>54.91</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1417,26 +1423,22 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>agentic-ai, agents, ai, autonomous-agents, deepseek-r1, llm, llm-agents, voice-assistant</t>
-        </is>
-      </c>
+      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>571</v>
+        <v>152</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
@@ -1445,42 +1447,42 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
+          <t>skill in:name stars:&gt;500 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>SenteLabsAI/OpenExecutive</t>
+          <t>huggingface/agents-course</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4137</v>
+        <v>32493</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>308.1</v>
+        <v>375.3</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 虚拟执行团队
-【原文】AI-powered virtual executive team — a single coherent executive persona backed by 8 specialist agents (FastAPI + Next.js).
-【依据】topics: ai, anthropic, claude, fastapi, llm, multi-agent, nextjs, python, rag, typescript</t>
+          <t>包含 Hugging Face 代理课程的资源库。
+【原文】This repository contains the Hugging Face Agents Course.
+【依据】Hugging Face 代理课程。</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1490,7 +1492,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SenteLabsAI/OpenExecutive</t>
+          <t>https://github.com/huggingface/agents-course</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1499,16 +1501,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>44.01</v>
+        <v>53.62</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>MDX</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1523,21 +1525,21 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai, anthropic, claude, fastapi, llm, multi-agent, nextjs, python, rag, typescript</t>
+          <t>agentic-ai, agents, course, huggingface, langchain, llamaindex, smolagents</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>94</v>
+        <v>606</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1549,26 +1551,27 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>corsairdev/corsair</t>
+          <t>microsoft/agent-lightning</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>11293</v>
+        <v>18087</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>236.7</v>
+        <v>279.5</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>连接用户到他们的应用程序，支持 API 集成和功能调用。
-【原文】Connect your users to their apps</t>
+          <t>训练 AI 代理的绝对训练器。
+【原文】The absolute trainer to light up AI agents.
+【依据】AI 代理的训练器。</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1583,7 +1586,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1593,7 +1596,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/corsairdev/corsair</t>
+          <t>https://github.com/microsoft/agent-lightning</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1602,16 +1605,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>33.81</v>
+        <v>39.93</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1626,24 +1629,24 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, agents, ai, ai-agents, aiagents, api-integration, corsair, developer-tools, function-calling, integrations, javascript, llm</t>
+          <t>agent, agentic-ai, llm, mlops, reinforcement-learning</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>334</v>
+        <v>453</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
@@ -1652,35 +1655,36 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Adkid-Zephyr/anti-defensive-writing-Skill</t>
+          <t>microsoft/graphrag</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>932</v>
+        <v>35964</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>197.7</v>
+        <v>279.4</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>极致轻量｜阻止论文的防御性写作 | Anti-defensive writing for academic papers — 学术写作原则 Skill + prompt pack (CN/EN)</t>
+          <t>基于图检索增强的生成系统
+【原文】A modular graph-based Retrieval-Augmented Generation (RAG) system</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1695,7 +1699,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Adkid-Zephyr/anti-defensive-writing-Skill</t>
+          <t>https://github.com/microsoft/graphrag</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1704,14 +1708,18 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>28.24</v>
+        <v>39.92</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1719,26 +1727,26 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>academic-writing, ai-writing, claude-skill, paper-writing, prompt</t>
+          <t>gpt, gpt-4, gpt4, graphrag, llm, llms, rag</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>33</v>
+        <v>901</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1750,26 +1758,27 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Ar9av/obsidian-wiki</t>
+          <t>eigent-ai/eigent</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>3398</v>
+        <v>15269</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>148.7</v>
+        <v>259.4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>通过 Obsidian Wiki 构建和维护 AI 代理的数字大脑
-【原文】Framework for AI agents to build and maintain a digital brain through Obsidian wiki</t>
+          <t>开源协同桌面应用，替代 Claude Cowork 和 Codex。
+【原文】Eigent: The Open Source Cowork Desktop - Local and Free Alternative to Claude Cowork and Codex
+【依据】替代 Claude Cowork 和 Codex 的协同桌面应用。</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1794,7 +1803,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Ar9av/obsidian-wiki</t>
+          <t>https://github.com/eigent-ai/eigent</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1803,16 +1812,16 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>21.24</v>
+        <v>37.06</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1827,21 +1836,21 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, brain, knowledge-base, knowledge-graph, llm-tools, memory, obsidian, obsidian-brain, wiki</t>
+          <t>agent-framework, agent-skills, agentic-ai, agentic-workflow, claude-cowork, claude-cowork-alternative, claude-cowork-free, desktop-agent, multi-agent-systems</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>160</v>
+        <v>412</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1853,26 +1862,27 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GetStream/Vision-Agents</t>
+          <t>ParthJadhav/app-store-screenshots</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>8119</v>
+        <v>6885</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>142.8</v>
+        <v>252.3</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>构建语音和视觉代理的快速工具，使用Stream的边缘网络实现超低延迟
-【原文】Open Vision Agents by Stream. Build voice and vision agents quickly with any model or video provider. Uses Stream's edge network for ultra-low latency.</t>
+          <t>使用AI自动化生成应用商店截图
+【原文】end to end app store screenshot creation using AI
+【依据】end to end app store screenshot creation using AI.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1882,7 +1892,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1897,7 +1907,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/GetStream/Vision-Agents</t>
+          <t>https://github.com/ParthJadhav/app-store-screenshots</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1906,16 +1916,16 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>20.4</v>
+        <v>36.05</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1930,21 +1940,21 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, agents, ai, ai-agents, realtime, stt, tts, video-agents, video-ai, vision-ai, voice-ai</t>
+          <t>agentic-ai, apple, appstore, automate, claude, cursor, design, generate, ios, ios-app, marketing, screenshot</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>398</v>
+        <v>191</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1956,26 +1966,26 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MrLesk/Backlog.md</t>
+          <t>eugeniughelbur/obsidian-second-brain</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>6717</v>
+        <v>4443</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>100.9</v>
+        <v>178.7</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>用于在 git 生态系统中管理项目协作和任务管理的工具。
-【原文】Backlog.md - A tool for managing project collaboration between humans and AI Agents in a git ecosystem</t>
+          <t>为 Claude Code 和其他 CLI 代理提供持久化记忆存储，以 Markdown 格式保存在 Obsidian 仓库中。
+【原文】Persistent memory for Claude Code and 6 other CLI agents, stored as plain markdown in your Obsidian vault. Stop re-explaining your projects, decisions and people every session. 45 commands: hybrid semantic search, self-rewriting notes, key-less web research, and scheduled agents that maintain the vault while you sleep.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1985,7 +1995,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2000,7 +2010,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MrLesk/Backlog.md</t>
+          <t>https://github.com/eugeniughelbur/obsidian-second-brain</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2009,7 +2019,7 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>14.41</v>
+        <v>25.53</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -2018,7 +2028,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2033,21 +2043,21 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, management, markdown, project, task-manager, tasks</t>
+          <t>agent-skills, ai-agents, ai-note-taking, ai-second-brain, anthropic, claude, claude-code, claude-code-skill, claude-memory, claude-plugin, claude-skill, karpathy-llm-wiki</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>466</v>
+        <v>174</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2059,42 +2069,41 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>arc53/DocsGPT</t>
+          <t>yaojingang/GEOFlow</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>18260</v>
+        <v>3628</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>164.9</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 代理和搜索平台
-【原文】Private AI platform for agents, assistants and enterprise search. Built-in Agent Builder, Deep research, Document analysis, Multi-model support, and API connectivity for agents.
-【依据】topics: agent-builder, agents, ai, chatgpt, docsgpt, hacktoberfest, hacktoberfest2026, information-retrieval, language-m</t>
+          <t>开源 GEO 内容工程和多站分布平台，具有 AI 质量检查和辅助发布功能
+【原文】Open-source GEO content engineering and multi-site distribution platform with AI quality inspection, illustrated admin help, hosted sites, browser-assisted publishing, and signed updates.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/RAG检索线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2104,7 +2113,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/arc53/DocsGPT</t>
+          <t>https://github.com/yaojingang/GEOFlow</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2113,16 +2122,16 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>13.84</v>
+        <v>23.56</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2137,21 +2146,21 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>agent-builder, agents, ai, chatgpt, docsgpt, hacktoberfest, hacktoberfest2026, information-retrieval, language-model, llm, machine-learning, natural-language-processing</t>
+          <t>ai, chrome-extension, cms, content-automation, generative-engine-optimization, geo, laravel, multi-site, openai-compatible, php, postgresql, pwa</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>1319</v>
+        <v>154</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
@@ -2163,36 +2172,36 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>charmbracelet/vhs</t>
+          <t>PleasePrompto/notebooklm-skill</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>20880</v>
+        <v>7772</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>96.3</v>
+        <v>164.8</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>命令行视频录制工具，支持GIF和终端录制
-【原文】Your CLI home video recorder 📼</t>
+          <t>使Claude Code与Google NotebookLM笔记本直接通信的技能
+【原文】Use this skill to enable Claude Code to communicate directly with your Google NotebookLM notebooks. Query your uploaded documents and get source-grounded, citation-backed answers from Gemini. Features browser automation, library management, persistent authentication, and answers exclusively from your own knowledge base.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2207,7 +2216,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/charmbracelet/vhs</t>
+          <t>https://github.com/PleasePrompto/notebooklm-skill</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2216,7 +2225,7 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>13.76</v>
+        <v>23.55</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2234,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2238,23 +2247,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>ascii, cli, command-line, gif, recording, terminal, vhs, video</t>
-        </is>
-      </c>
+      <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>1517</v>
+        <v>330</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
@@ -2266,26 +2271,26 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-15</t>
+          <t>skill in:name stars:&gt;500 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>iFurySt/open-codex-computer-use</t>
+          <t>ScrapeCreators/social-media-research-skills</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2043</v>
+        <v>2320</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>96</v>
+        <v>162.4</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>提供 Codex 计算机使用的开源替代方案
-【原文】👾 Open Computer Use – Open-Source Alternative to Codex Computer Use</t>
+          <t>社交媒体研究 AI agent 技能
+【原文】AI agent skills for social media research. Outlier posts, comment mining, competitor teardowns, ad libraries &amp; trends across TikTok, Instagram, YouTube, Reddit, X, LinkedIn &amp; more. Powered by ScrapeCreators. Works with Claude Code, Cursor, Codex, Gemini CLI.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -2295,7 +2300,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2310,7 +2315,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/iFurySt/open-codex-computer-use</t>
+          <t>https://github.com/ScrapeCreators/social-media-research-skills</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2319,7 +2324,7 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>13.71</v>
+        <v>23.2</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2328,7 +2333,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2343,53 +2348,52 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>accessibility, ai-agent, ai-agents, claude-code, codex, codex-computer-use, computer-use, computer-use-agent, cross-platform, cua, desktop-automation, gemini-cli</t>
+          <t>agent-skills, ai-agents, claude-code, claude-skills, competitor-analysis, content-marketing, cursor, influencer-marketing, market-research, social-media, social-media-research, workflow-automation</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-14</t>
+          <t>skills in:name stars:&gt;500 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>yaklang/hack-skills</t>
+          <t>logseq/logseq</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2182</v>
+        <v>44893</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>96</v>
+        <v>136.4</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>帮助 AI 代理成为黑客
-【原文】Helping AI Agent become an awesome practical hacker!
-【依据】topics: -</t>
+          <t>提供隐私优先的开源知识管理和协作平台，支持 Clojure 和 ClojureScript。
+【原文】A privacy-first, open-source platform for knowledge management and collaboration. Download link:  http://github.com/logseq/logseq/releases. roadmap: https://logseq.io/p/NX4mc_ggEV</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2399,12 +2403,12 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>可部署服务/代码库</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -2414,7 +2418,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yaklang/hack-skills</t>
+          <t>https://github.com/logseq/logseq</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2423,16 +2427,16 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>13.72</v>
+        <v>19.48</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>Clojure</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2445,22 +2449,26 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P20" s="6" t="inlineStr"/>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>clojure, clojurescript, git, graph, knowledge-base, knowledge-graph, local-first, markdown, note-taking, org-mode, pkm</t>
+        </is>
+      </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2020-05-23</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>159</v>
+        <v>2305</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
@@ -2469,26 +2477,26 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>RLinf/RLinf</t>
+          <t>abhisheknaiidu/awesome-github-profile-readme</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>5180</v>
+        <v>31051</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>91.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>提供强化学习基础设施，用于具身和代理式 AI。
-【原文】RLinf: Reinforcement Learning Infrastructure for Embodied and Agentic AI</t>
+          <t>GitHub Profile 的 curated list
+【原文】😎 A curated list of awesome GitHub Profile which updates in real time</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2513,7 +2521,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/RLinf/RLinf</t>
+          <t>https://github.com/abhisheknaiidu/awesome-github-profile-readme</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2522,18 +2530,14 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>13.11</v>
+        <v>13.77</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2546,21 +2550,21 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, embodied-ai, reinforcement-learning, rl-infra, rlinf, vla-rl</t>
+          <t>awesome, awesome-list, github, github-profile-readme, github-readme, portfolio, profile-readme</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2020-07-12</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>395</v>
+        <v>2255</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
@@ -2572,27 +2576,26 @@
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>langbot-app/LangBot</t>
+          <t>zenstory-ai/oh-story-dsh</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>17756</v>
+        <v>341</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>90.3</v>
+        <v>91.8</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>提供生产级智能机器人开发平台
-【原文】Production-grade platform for building agentic IM bots - 生产级多平台智能机器人开发平台/ Agent、知识库编排、插件系统 / Bots for Discord / Slack / LINE / Telegram / WeChat(企业微信, 企微智能机器人, 公众号) / 飞书 / 钉钉 / QQ / Matrix e.g. Integrated with ChatGPT(GPT), DeepSeek, Dify, n8n, Langflow, Coze, Claude, Gemini, GLM, Ollama, SiliconFlow, Moonshot, openclaw / hermes agent, deerflow
-【依据】topics: agent, coze, deepseek, dify, dingtalk, discord, feishu, kook, langbot, lark, line, llm</t>
+          <t>提供 DeepSeek 写网文/小说的工作流插件，包括小说、短剧、游戏和视频解说工作台。
+【原文】DeepSeek 写网文/小说的工作流插件：DeepSeek Harness 社区插件，内置小说、短剧、游戏、视频解说四个工作台 | Community DeepSeek Harness plugin with novel, short-drama, game and video-recap workbenches. Not affiliated with DeepSeek.</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2602,7 +2605,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2617,7 +2620,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/langbot-app/LangBot</t>
+          <t>https://github.com/zenstory-ai/oh-story-dsh</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2626,11 +2629,11 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>12.9</v>
+        <v>13.12</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2650,62 +2653,62 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>agent, coze, deepseek, dify, dingtalk, discord, feishu, kook, langbot, lark, line, llm</t>
+          <t>agent-skills, ai-agents, ai-novel-writing, ai-writing, claude-code, creative-writing, deepseek, deepseek-harness, drama-skills, dsh-plugin, fiction-writing, novel-writing</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1376</v>
+        <v>26</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Evil0ctal/Douyin_TikTok_Download_API</t>
+          <t>dataelement/bisheng</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>20081</v>
+        <v>11957</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>79.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>抖音和TikTok爬虫和视频下载API，支持MCP服务器和CLI
-【原文】🚀 Self-hosted TikTok &amp; Douyin scraper and no-watermark video downloader — async REST API, MCP server, CLI and web console for posts, profiles, comments and playlists. Self-healing identity pool, PostgreSQL archive, one docker compose up. 抖音、TikTok 数据采集与无水印视频下载 API，自托管，支持 MCP 调用与 Docker 一键部署。</t>
+          <t>提供下一代企业AI应用的LLM开发平台
+【原文】BISHENG is an open LLM devops platform for next generation Enterprise AI applications. Powerful and comprehensive features include: GenAI workflow, RAG, Agent, Unified model management, Evaluation, SFT, Dataset Management, Enterprise-level System Management, Observability and more.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库</t>
+          <t>MCP服务/技能包/架构参考</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2720,7 +2723,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Evil0ctal/Douyin_TikTok_Download_API</t>
+          <t>https://github.com/dataelement/bisheng</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2729,7 +2732,7 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>11.34</v>
+        <v>10.74</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
@@ -2753,24 +2756,24 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>asyncio, crawler, data-collection, douyin, douyin-api, downloader, fastapi, mcp-server, model-context-protocol, openapi, rest-api, scraper</t>
+          <t>agent, ai, chatbot, enterprise, finetune, genai, gpt, langchian, llama, llm, llmdevops, llmops</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2021-11-07</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1771</v>
+        <v>1113</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
@@ -2779,26 +2782,25 @@
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-15</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>oomol-lab/pdf-craft</t>
+          <t>BZDmathclub/bzd-math-modeling-skills</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>6293</v>
+        <v>337</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>76.2</v>
+        <v>73.7</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>将PDF文件转换为其他格式，专注于处理扫描书籍的PDF文件
-【原文】PDF craft can convert PDF files into various other formats. This project will focus on processing PDF files of scanned books.</t>
+          <t>数学建模竞赛论文智能评审 Skill</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2808,12 +2810,12 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -2823,7 +2825,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/oomol-lab/pdf-craft</t>
+          <t>https://github.com/BZDmathclub/bzd-math-modeling-skills</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2832,16 +2834,16 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>10.89</v>
+        <v>10.53</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2854,23 +2856,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>deepseek-ocr, document, ocr, pdf</t>
-        </is>
-      </c>
+      <c r="P24" s="6" t="inlineStr"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>578</v>
+        <v>32</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>1</v>
@@ -2882,36 +2880,36 @@
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>keploy/keploy</t>
+          <t>KartikLabhshetwar/better-shot</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>18451</v>
+        <v>2296</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>开源平台，用于创建安全的 API、集成和端到端测试沙盒。
-【原文】Open-source platform for creating safe, isolated production sandboxes for API, integration, and E2E testing.</t>
+          <t>提供macOS上的截图、屏幕录制和视频编辑工具
+【原文】Screenshot, screen recording, and video editor for macOS. Native SwiftUI app with capture deck, 75+ customizable shortcuts, URL scheme automation, and self-hosted cloud sharing. Open-source alternative to CleanShot X and Loom.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2926,7 +2924,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/keploy/keploy</t>
+          <t>https://github.com/KartikLabhshetwar/better-shot</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2935,16 +2933,16 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>10.87</v>
+        <v>9.33</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Swift</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2959,21 +2957,21 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, ai-testing-tool, api-testing, code-quality, mock, mock-data-generator, mock-framework, test-automation, test-automation-framework, test-generation, testing, testing-library</t>
+          <t>annotation-tool, automation, capture-tool, cleanshot-alternative, cloudflare-r2, loom-alternative, macos, macos-app, native-macos, ocr, open-source, privacy</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2022-01-19</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>1698</v>
+        <v>246</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>1</v>
@@ -2985,41 +2983,41 @@
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>HIllya51/LunaTranslator</t>
+          <t>makenotion/notion-mcp-server</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>13151</v>
+        <v>4632</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>63.6</v>
+        <v>58.7</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>视觉小说翻译器，支持OCR和反向工程
-【原文】视觉小说翻译器 / Visual Novel Translator</t>
+          <t>官方 Notion MCP 服务器
+【原文】Official Notion MCP Server</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>MCP服务</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -3029,7 +3027,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/HIllya51/LunaTranslator</t>
+          <t>https://github.com/makenotion/notion-mcp-server</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3038,16 +3036,16 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>9.09</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -3060,14 +3058,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>galgame, ocr, reverse-engineering, translator, visual-novel, win32</t>
-        </is>
-      </c>
+      <c r="P26" s="6" t="inlineStr"/>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
@@ -3076,7 +3070,7 @@
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>1446</v>
+        <v>553</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>1</v>
@@ -3088,37 +3082,37 @@
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>HelixDB/helix-db</t>
+          <t>icip-cas/PPTAgent</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>5900</v>
+        <v>5025</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>62.6</v>
+        <v>56.9</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>提供 OLTP 图数据库
-【原文】HelixDB is an OLTP graph database with native vector and full-text search built in Rust on Object Storage.
-【依据】topics: ai, cli, database, databases, graph-database, helix, helixdb, rag, rust, rust-crate, rust-lang, vector</t>
+          <t>用于生成反思性演示文稿的代理框架
+【原文】An Agentic Framework for Reflective PowerPoint Generation
+【依据】An Agentic Framework for Reflective PowerPoint Generation.</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>MCP服务/技能包</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3133,7 +3127,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/HelixDB/helix-db</t>
+          <t>https://github.com/icip-cas/PPTAgent</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3142,16 +3136,16 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>8.949999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -3166,21 +3160,21 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>ai, cli, database, databases, graph-database, helix, helixdb, rag, rust, rust-crate, rust-lang, vector</t>
+          <t>agent, agentic-ai, llm, mcp, openclaw, presentation, slide</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>659</v>
+        <v>618</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>1</v>
@@ -3192,31 +3186,32 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="28" ht="150" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>bluenviron/mediamtx</t>
+          <t>potpie-ai/potpie</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>20111</v>
+        <v>5719</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>57.5</v>
+        <v>52.5</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>支持多种媒体协议的实时媒体服务器和代理
-【原文】Ready-to-use Media-over-QUIC / SRT / WebRTC / RTSP / RTMP / LL-HLS / MPEG-TS / RTP live media server and media proxy that allows to read, publish, proxy, record and playback real-time video and audio streams.</t>
+          <t>为 AI 本地 SDLC 提供上下文图框架。
+【原文】Context Graph for AI Native SDLC
+【依据】AI 本地 SDLC 的上下文图框架。</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -3236,7 +3231,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/bluenviron/mediamtx</t>
+          <t>https://github.com/potpie-ai/potpie</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3245,16 +3240,16 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>8.210000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -3269,24 +3264,24 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>go, golang, hls, media-over-quic, media-server, moq, obs-studio, rtcp, rtmp, rtmp-proxy, rtmp-server, rtp</t>
+          <t>agents, ai-agents, ai-agents-framework, artificial-intelligence, context-graph, developer-tools, devtools, generative-ai, knowledge-graph, rag</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>2019-12-28</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2451</v>
+        <v>763</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
@@ -3295,36 +3290,37 @@
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-15</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MemMachine/MemMachine</t>
+          <t>ocrmypdf/OCRmyPDF</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>3219</v>
+        <v>34759</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>57.2</v>
+        <v>52.3</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>为 AI 代理提供通用内存层，用于状态管理和自主系统。
-【原文】Universal memory layer for AI Agents. It provides scalable, extensible, and interoperable memory storage and retrieval to streamline AI agent state management for next-generation autonomous systems.</t>
+          <t>为扫描PDF文件添加OCR文本层
+【原文】OCRmyPDF adds an OCR text layer to scanned PDF files, allowing them to be searched
+【依据】OCRmyPDF adds an OCR text layer to scanned PDF files.</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -3339,7 +3335,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MemMachine/MemMachine</t>
+          <t>https://github.com/ocrmypdf/OCRmyPDF</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3348,11 +3344,11 @@
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>8.17</v>
+        <v>7.47</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MPL-2.0</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -3372,21 +3368,21 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, agents, agents-sdk, ai, ai-agents, chatbots, conversational-agents, conversational-ai, genai, knowledge-graph, llm</t>
+          <t>image-processing, ocr, pdf, python, tesseract</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2013-12-20</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S29" s="3" t="n">
-        <v>394</v>
+        <v>4651</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>1</v>
@@ -3398,26 +3394,26 @@
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="30" ht="150" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Zleap-AI/SAG</t>
+          <t>FrancyJGLisboa/agent-skills-platform</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2482</v>
+        <v>2384</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>56.1</v>
+        <v>50.4</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>提供 RAG 检索架构和开源知识库
-【原文】A new SOTA for RAG — an original retrieval architecture and an open-source knowledge base for humans and agents.</t>
+          <t>构建和治理智能体技能的平台
+【原文】Build tested agent skills and govern their lifecycle through a user-defined marketplace: evidence, discovery, updates, rollback, quarantine, and 17-platform distribution.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3427,7 +3423,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3442,7 +3438,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Zleap-AI/SAG</t>
+          <t>https://github.com/FrancyJGLisboa/agent-skills-platform</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3451,7 +3447,7 @@
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>8.01</v>
+        <v>7.2</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
@@ -3475,24 +3471,24 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>agent, ai, data-engineering, graphrag, knowledge-base, knowledge-graph, knowledge-graphs, llm, rag, sag, vector-search</t>
+          <t>agent-skills, ai-agents, claude-code, codex, cursor, developer-tools, evals, github-copilot, governance, skill-marketplace</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S30" s="3" t="n">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
@@ -3501,27 +3497,26 @@
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="31" ht="150" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>rothgar/awesome-tuis</t>
+          <t>DaoYiSec/SecSkills</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>20575</v>
+        <v>1006</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>52.9</v>
+        <v>42.9</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>提供终端用户界面项目列表
-【原文】List of projects that provide terminal user interfaces
-【依据】topics: -</t>
+          <t>收集网络安全相关技能和MCP
+【原文】收集整理渗透测试、漏洞扫描、代码审计、CTF、逆向、安全研究 等网络安全相关的 Skills和MCP</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -3531,12 +3526,12 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -3546,7 +3541,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rothgar/awesome-tuis</t>
+          <t>https://github.com/DaoYiSec/SecSkills</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -3555,11 +3550,11 @@
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>7.56</v>
+        <v>6.13</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr"/>
@@ -3576,16 +3571,16 @@
       <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>2019-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S31" s="3" t="n">
-        <v>2723</v>
+        <v>164</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>1</v>
@@ -3597,42 +3592,41 @@
       </c>
       <c r="V31" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-14</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="32" ht="150" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>genkit-ai/genkit</t>
+          <t>Marker-Inc-Korea/AutoRAG</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>6433</v>
+        <v>5071</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>51.9</v>
+        <v>36.3</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>提供构建代理应用的框架
-【原文】Open-source framework for building agentic apps in JavaScript, Go, Dart, and Python, built and used in production by Google
-【依据】topics: agents, ai, embedders, genkit, llm, multimodal, rag, vector-database</t>
+          <t>AutoRAG：使代理能够找到计算机中的任何内容，使用频率越高越智能
+【原文】AutoRAG: Now your agent can find anything in your computer. It gets smarter if you are using it frequently.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/RAG检索线</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -3642,7 +3636,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/genkit-ai/genkit</t>
+          <t>https://github.com/Marker-Inc-Korea/AutoRAG</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -3651,11 +3645,11 @@
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>7.42</v>
+        <v>5.19</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -3675,21 +3669,21 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>agents, ai, embedders, genkit, llm, multimodal, rag, vector-database</t>
+          <t>analysis, automl, benchmarking, document-parser, embeddings, evaluation, llm, llm-evaluation, llm-ops, open-source, ops, optimization</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S32" s="3" t="n">
-        <v>867</v>
+        <v>978</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>1</v>
@@ -3701,25 +3695,26 @@
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="33" ht="150" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>T8mars/minimax-h3-prompt-skill-T8</t>
+          <t>jwangkun/hermes-agent-guide</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>222</v>
+        <v>698</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>44.4</v>
+        <v>33.7</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Creative DNA video prompt cases and installable Skills for MiniMax H3 and Seedance 2.0, with an Electron video viewer.</t>
+          <t>提供 Hermes Agent 的系统化中文指南，涵盖从安装部署到高阶开发的完整知识图谱。
+【原文】Hermes Agent 是目前开源社区最具潜力的 AI Agent 框架之一。它继承了 OpenClaw 的优秀基因，在架构设计、记忆系统、技能生态和自动化能力上实现全面升级。但 Hermes 的文档分散在多个仓库和平台，缺乏一本系统性的中文指南。  本书填补的正是这个空白。全书 16 册、30 万+ 字，覆盖从安装部署到高阶开发、从个人玩赚到企业服务、从单 Agent 操控到多 Agent 编排的完整知识图谱。</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -3729,12 +3724,12 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>架构参考/代码库</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -3744,7 +3739,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/T8mars/minimax-h3-prompt-skill-T8</t>
+          <t>https://github.com/jwangkun/hermes-agent-guide</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -3753,16 +3748,16 @@
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>6.34</v>
+        <v>4.81</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3772,67 +3767,63 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>ai-video, codex-skills, creative-dna, electron, minimax-h3, prompt-engineering, seedance-2-0, video-generation</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr"/>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S33" s="3" t="n">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
+          <t>知识图谱 in:name,description stars:&gt;200 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="34" ht="150" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>robert-mcdermott/ai-knowledge-graph</t>
+          <t>agentscope-ai/ReMe</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>3075</v>
+        <v>3450</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>40</v>
+        <v>32.3</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>生成 AI 驱动的知识图谱
-【原文】AI Powered Knowledge Graph Generator</t>
+          <t>为代理提供记忆管理工具包，帮助代理记住和改进
+【原文】ReMe: Memory Management Kit for Agents - Remember Me, Refine Me.</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -3847,7 +3838,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/robert-mcdermott/ai-knowledge-graph</t>
+          <t>https://github.com/agentscope-ai/ReMe</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -3856,7 +3847,7 @@
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>5.71</v>
+        <v>4.62</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
@@ -3880,21 +3871,21 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>artificial-intelligence, knowledge-distillation, knowledge-graph, llm, networkx, pyvis, visualization</t>
+          <t>agent, ai-agents, dsh-plugin, memory, memoryscope, rag, reme</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S34" s="3" t="n">
-        <v>539</v>
+        <v>746</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>1</v>
@@ -3906,26 +3897,27 @@
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="35" ht="150" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>dgraph-io/dgraph</t>
+          <t>study8677/repobrain</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>21796</v>
+        <v>1325</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>37.8</v>
+        <v>31</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>提供高性能的图数据库，适用于实时用例。
-【原文】high-performance graph database for real-time use cases</t>
+          <t>为代码库提供智能助手，支持多种代码编辑器。
+【原文】🧠 RepoBrain (formerly Antigravity) — Give your repo a brain. ChatGPT for your codebase: works in Claude Code, Cursor, Codex, Windsurf &amp; more.
+【依据】为代码库提供智能助手，支持 Claude Code、Cursor 等。</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -3950,7 +3942,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dgraph-io/dgraph</t>
+          <t>https://github.com/study8677/repobrain</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -3959,16 +3951,16 @@
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>5.4</v>
+        <v>4.43</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -3983,21 +3975,21 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>database, distributed, go, knowledge-graph</t>
+          <t>agents-sdk, ai-agent, claude-code, code-intelligence, code-search, codebase-qa, codex-cli, copilot, cursor, developer-tools, ide-plugin, knowledge-graph</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>2015-08-25</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S35" s="3" t="n">
-        <v>4037</v>
+        <v>299</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>1</v>
@@ -4009,26 +4001,26 @@
       </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="36" ht="150" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>kaomei/hand-drawn-video-prompts</t>
+          <t>88lin/computer-repair-skill</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>将中文口播稿转换为手绘视频提示词
-【原文】将中文口播稿转换为 9:16 Q版手绘视频提示词，并把马斯克、黄仁勋、扎克伯格等科技人物转成非写实Q版角色｜Turn Chinese scripts into hand-drawn video prompts for Flow and Nano Banana.</t>
+          <t>让 AI 代理成为跨平台电脑维修助手，提供诊断、清理、性能等维护工具
+【原文】让 Codex、Claude Code 等 AI Agent 成为你的跨平台电脑维修助手：64 个按需加载的 Playbook，覆盖诊断、清理、性能、网络与安全维护——C 盘爆满、电脑卡顿、流氓软件、应用迁移、数据恢复都能直接问；先取证、再计划，确认后修改。</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -4038,12 +4030,12 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -4053,7 +4045,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kaomei/hand-drawn-video-prompts</t>
+          <t>https://github.com/88lin/computer-repair-skill</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4062,14 +4054,18 @@
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr"/>
+          <t>AGPL-3.0</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4082,51 +4078,52 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>ai-video, b-roll, flow, nano-banana, prompt-engineering, storyboard</t>
+          <t>agent-skills, claude-code, codex, computer-diagnostics, linux, macos, windows</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S36" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-15</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="37" ht="150" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>microsoft/work-iq</t>
+          <t>skills-directory/skill-codex</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>1002</v>
+        <v>1434</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>29.8</v>
+        <v>30.6</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>MCP Server and CLI for accessing Work IQ</t>
+          <t>将提示委托给Codex的Claude代码技能
+【原文】A claude code skill to delegate prompts to codex</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4136,12 +4133,12 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -4151,7 +4148,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/work-iq</t>
+          <t>https://github.com/skills-directory/skill-codex</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -4160,18 +4157,14 @@
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>4.25</v>
+        <v>4.37</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>PowerShell</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4179,22 +4172,26 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P37" s="6" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>claude, claude-code, codex</t>
+        </is>
+      </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S37" s="3" t="n">
-        <v>236</v>
+        <v>328</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>1</v>
@@ -4206,27 +4203,27 @@
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-14</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="38" ht="150" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>xushengfeng/eSearch</t>
+          <t>kedro-org/kedro</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>7114</v>
+        <v>10995</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>27.7</v>
+        <v>28.4</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>提供截图、OCR搜索、翻译、图像编辑等功能
-【原文】截屏 离线OCR 搜索翻译 以图搜图 贴图 录屏 万向滚动截屏 屏幕翻译   Screenshot  Offline OCR   Search   Translate   Search for picture   Paste the picture on the screen   Screen recorder   Omnidirectional scrolling screenshot   Screen translator  支持Windows Linux macOS
-【依据】Screenshot Offline OCR Search Translate Search for picture Paste the picture on the screen Screen recorder Omnidirection</t>
+          <t>用于生产就绪数据科学的工具箱，支持数据工程和科学管道。
+【原文】Kedro is a toolbox for production-ready data science. It uses software engineering best practices to help you create data engineering and data science pipelines that are reproducible, maintainable, and modular.
+【依据】生产就绪数据科学的工具箱。</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -4239,9 +4236,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -4251,7 +4248,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/xushengfeng/eSearch</t>
+          <t>https://github.com/kedro-org/kedro</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4260,16 +4257,16 @@
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>3.95</v>
+        <v>4.06</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -4284,21 +4281,21 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>clipboard, color-picker, cross-platform, electron, image-editing, image-editor, linux, live-text, macos, ocr, paddleocr, recorder</t>
+          <t>agentic-ai, agentic-workflow, data-pipelines, hacktoberfest, kedro, machine-learning, machine-learning-engineering, mlops, python</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2019-04-18</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S38" s="3" t="n">
-        <v>1803</v>
+        <v>2706</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>1</v>
@@ -4310,26 +4307,26 @@
       </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="39" ht="150" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>onestardao/WFGY</t>
+          <t>fenixsoft/awesome-fenix</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>1789</v>
+        <v>9445</v>
       </c>
       <c r="C39" s="5" t="n">
         <v>26.9</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 推理、RAG 和代理的开放源代码库，包括问题地图、全局调试卡等工具。
-【原文】WFGY is heading toward WFGY 5.0 Polaris Protocol, a major open-source release for AI reasoning, RAG, agents, and real-world workflows. Includes Problem Map, Global Debug Card, WFGY 4.0, and the CFV Easter Egg.</t>
+          <t>讨论如何构建可靠的大型分布式系统
+【原文】讨论如何构建一套可靠的大型分布式系统</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4339,12 +4336,12 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>架构参考</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -4354,7 +4351,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/onestardao/WFGY</t>
+          <t>https://github.com/fenixsoft/awesome-fenix</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4367,12 +4364,12 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Vue</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -4387,21 +4384,21 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, alignment, debugging, evaluation, graphrag, hallucination, information-retrieval, knowledge-graph, llm, rag, reasoning, retrieval-augmented-generation</t>
+          <t>architecture, cloud-native, istio, kubernetes, microservice, springcloud</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2019-12-23</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S39" s="3" t="n">
-        <v>466</v>
+        <v>2457</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>1</v>
@@ -4413,37 +4410,37 @@
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="40" ht="150" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>gptme/gptme</t>
+          <t>icereed/paperless-gpt</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>4411</v>
+        <v>2685</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>24.4</v>
+        <v>26</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>提供终端 AI 助手
-【原文】Your agent in your terminal, equipped with local tools: writes code, uses the terminal, browses the web. Make your own persistent autonomous agent on top!
-【依据】topics: agent, agents, ai-agents, ai-assistant, anthropic, chatbot, chatgpt, cli, code-generation, llamacpp, llm, llm-ag</t>
+          <t>使用LLM和LLM Vision (OCR)处理无纸化文档
+【原文】Use LLMs and LLM Vision (OCR) to handle paperless-ngx - Document Digitalization powered by AI
+【依据】Use LLMs and LLM Vision (OCR) to handle paperless-ngx - Document Digitalization powered by AI.</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -4458,7 +4455,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/gptme/gptme</t>
+          <t>https://github.com/icereed/paperless-gpt</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4467,7 +4464,7 @@
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>3.48</v>
+        <v>3.72</v>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
@@ -4476,7 +4473,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -4491,12 +4488,12 @@
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>agent, agents, ai-agents, ai-assistant, anthropic, chatbot, chatgpt, cli, code-generation, llamacpp, llm, llm-agent</t>
+          <t>ai, chatgpt, llm, mistral, ocr, ollama, paperless, paperless-ngx</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
@@ -4505,7 +4502,7 @@
         </is>
       </c>
       <c r="S40" s="3" t="n">
-        <v>1269</v>
+        <v>721</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>1</v>
@@ -4517,25 +4514,26 @@
       </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="41" ht="150" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>langroid/langroid</t>
+          <t>samchon/typia</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>4102</v>
+        <v>5905</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>23</v>
+        <v>25.7</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Harness LLMs with Multi-Agent Programming</t>
+          <t>提供快速/简单的运行时验证器和序列化器。
+【原文】Super-fast/easy runtime validators and serializers via transformation</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4560,7 +4558,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/langroid/langroid</t>
+          <t>https://github.com/samchon/typia</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -4569,7 +4567,7 @@
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>3.29</v>
+        <v>3.67</v>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
@@ -4578,7 +4576,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -4588,26 +4586,26 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>agents, ai, chatgpt, function-calling, gpt, gpt-4, gpt4, information-retrieval, language-model, llama, llm, llm-agent</t>
+          <t>agentic-ai, ajv, checker, fast, generator, hacktoberfest, json, json-schema, llm-function-calling, openapi, protobuf, random</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2022-04-18</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S41" s="3" t="n">
-        <v>1246</v>
+        <v>1610</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>1</v>
@@ -4619,41 +4617,41 @@
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="42" ht="150" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>shunbao-p/OneCue</t>
+          <t>zamesin/Next-Move-Theory-Canon-and-Skills</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>104</v>
+        <v>370</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>22.8</v>
+        <v>24.6</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>生成高质量视频、图像和音频内容
-【原文】只需要一台能跑 codex 的电脑，一句话直接可以生成可用的高质量视频，图像音频等一站式搞定。目前使用 mac-codex 中，使用流程：调用短视频导演 技能，告诉 codex 要做什么主题内容可选提交相关素材，然后等待即可直接得到成品，允许审阅后微调。</t>
+          <t>Claude Code 技能，用于产品市场研究、价值主张、PRD 和上市策略
+【原文】Claude Code skills for product market research, value props, PRDs, and go-to-market — plus the open Next Move Theory (based on AJTBD) canon and a product advisor you can /ask-nmt</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -4663,7 +4661,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/shunbao-p/OneCue</t>
+          <t>https://github.com/zamesin/Next-Move-Theory-Canon-and-Skills</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -4672,16 +4670,16 @@
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>PowerShell</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -4697,62 +4695,62 @@
       <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S42" s="3" t="n">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-15</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="43" ht="150" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MontageAI/niwo-render-everything</t>
+          <t>yzhao062/pyod</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>108</v>
+        <v>10001</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>22.3</v>
+        <v>21.4</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>将任意内容转换为短视频的技能
-【原文】把任意内容做成短视频 · Niwo Agent Skill</t>
+          <t>提供跨多种数据类型的异常检测库
+【原文】A Python library for anomaly detection across tabular, time series, graph, text, image, and audio data. 60+ detectors, benchmark-backed ADEngine orchestration, and an agentic workflow for AI agents.</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -4762,7 +4760,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MontageAI/niwo-render-everything</t>
+          <t>https://github.com/yzhao062/pyod</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -4771,11 +4769,11 @@
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>3.18</v>
+        <v>3.06</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>BSD-2-Clause</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -4793,50 +4791,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P43" s="6" t="inlineStr"/>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>agentic-ai, anomaly-detection, data-mining, data-science, deep-learning, foundation-models, fraud-detection, graph-anomaly-detection, image-anomaly-detection, machine-learning, multimodal, nlp-anomaly-detection</t>
+        </is>
+      </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S43" s="3" t="n">
-        <v>34</v>
+        <v>3268</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V43" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-15</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="44" ht="150" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>dmMaze/BallonsTranslator</t>
+          <t>lllllllama/RigorPilot-Skills</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>5117</v>
+        <v>487</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>22.1</v>
+        <v>20.3</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>深度学习辅助漫画翻译工具，支持一键机翻和图像/文本编辑
-【原文】深度学习辅助漫画翻译工具, 支持一键机翻和简单的图像/文本编辑 | Yet another computer-aided comic/manga translation tool powered by deeplearning</t>
+          <t>研究复现技能，带有执行限制、可审计证据和字节保留的 README 注释
+【原文】README-first research reproduction skills with bounded execution, auditable evidence, and byte-preserving README annotations.</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -4846,12 +4848,12 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
@@ -4861,7 +4863,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dmMaze/BallonsTranslator</t>
+          <t>https://github.com/lllllllama/RigorPilot-Skills</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -4870,11 +4872,11 @@
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -4894,21 +4896,21 @@
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>auto-translation, chinese-translation, comics, computer-aided-translation, computer-vision, deep-learning, inpainting, manga, ocr, pyqt, pyqt6, pytorch</t>
+          <t>agent-skills, ai-agents, deep-learning, reproducibility, research-tools</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S44" s="3" t="n">
-        <v>1618</v>
+        <v>168</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>1</v>
@@ -4920,27 +4922,26 @@
       </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="45" ht="150" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>rothgar/awesome-tmux</t>
+          <t>shiyutim/tickets</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>10336</v>
+        <v>3278</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>提供 tmux 资源列表
-【原文】A list of awesome resources for tmux
-【依据】topics: awesome, awesome-list, tmux</t>
+          <t>为大麦网和 B 站会员购演唱会提供抢票软件，监控余票并支持微信通知。
+【原文】大麦网(大麦）、bilibili(B站)会员购 演唱会调用接口的抢票软件，余票监控，微信通知。</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -4950,12 +4951,12 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务/代码库</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -4965,7 +4966,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rothgar/awesome-tmux</t>
+          <t>https://github.com/shiyutim/tickets</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -4974,14 +4975,18 @@
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4994,12 +4999,12 @@
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, tmux</t>
+          <t>bilibili, damai, rust, tauri, vue</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>2016-04-04</t>
+          <t>2023-06-04</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -5008,53 +5013,54 @@
         </is>
       </c>
       <c r="S45" s="3" t="n">
-        <v>3814</v>
+        <v>1198</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V45" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-14</t>
+          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="46" ht="150" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>vastsa/PI-Desktop</t>
+          <t>Physton/sd-webui-prompt-all-in-one</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>3140</v>
+        <v>3233</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>17.3</v>
+        <v>18.5</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>本地优先的AI编码代理桌面应用，支持插件安装
-【原文】Local-first AI coding agent desktop: Electron + Rust host core + pi Agent Harness + user-installable plugins</t>
+          <t>增强 sd-webui 的提示输入框体验，提供自动翻译功能。
+【原文】This is an extension based on sd-webui, aimed at improving the user experience of the prompt/negative prompt input box. It has a more intuitive and powerful input interface function, and provides automatic translation, history record, and bookmarking functions.    这是一个基于 sd-webui 的扩展，旨在提高提示词/反向提示词输入框的使用体验。它拥有更直观、强大的输入界面功能，它提供了自动翻译、历史记录和收藏等功能。
+【依据】sd-webui 的扩展，提供更直观的输入界面功能。</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -5064,7 +5070,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vastsa/PI-Desktop</t>
+          <t>https://github.com/Physton/sd-webui-prompt-all-in-one</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5073,16 +5079,16 @@
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>LGPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -5095,14 +5101,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>ai-agent, coding-agent, desktop-app, electron, global, i18n, local-first, mcp, pi, pi-agent, pi-desktop, plugins</t>
-        </is>
-      </c>
+      <c r="P46" s="6" t="inlineStr"/>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
@@ -5111,52 +5113,53 @@
         </is>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1271</v>
+        <v>1225</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V46" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-14</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="47" ht="150" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>donghuixin/AI-Vibe-Writing-Skills</t>
+          <t>software-mansion/react-native-executorch</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>492</v>
+        <v>1734</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Using AI for high quality writing</t>
+          <t>为 React Native 提供高性能、隐私优先的设备端 AI 推理库
+【原文】High-performance, privacy-first on-device AI inference library for React Native, powered by PyTorch's ExecuTorch runtime</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -5166,7 +5169,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/donghuixin/AI-Vibe-Writing-Skills</t>
+          <t>https://github.com/software-mansion/react-native-executorch</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -5175,16 +5178,16 @@
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -5194,22 +5197,26 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P47" s="6" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>ai, computer-vision, executorch, llm-inference, mobile-inference, object-detection, ocr, on-device-ai, react-native-ai, speech-to-text, text-to-speech, vlm</t>
+        </is>
+      </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S47" s="3" t="n">
-        <v>207</v>
+        <v>698</v>
       </c>
       <c r="T47" s="3" t="n">
         <v>1</v>
@@ -5221,36 +5228,36 @@
       </c>
       <c r="V47" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="48" ht="150" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>j3ssie/osmedeus</t>
+          <t>TheJoeFin/Text-Grab</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>6561</v>
+        <v>5003</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>现代安全编排引擎，用于安全攻击面管理和渗透测试
-【原文】A Modern Orchestration Engine for Security</t>
+          <t>提供Windows平台上的OCR工具
+【原文】Use OCR in Windows quickly and easily with Text Grab. With optional background process and notifications.</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -5265,7 +5272,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/j3ssie/osmedeus</t>
+          <t>https://github.com/TheJoeFin/Text-Grab</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5274,7 +5281,7 @@
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
@@ -5283,7 +5290,7 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -5298,21 +5305,21 @@
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, attack-surface-management, bugbounty, go, hacking, hacking-tool, llm, osint, penetration-testing, pentesting, reconnaissance, security</t>
+          <t>dotnet, local-ai, msix, ocr, window-10, windows, windows-11, wpf</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>2018-11-10</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S48" s="3" t="n">
-        <v>2864</v>
+        <v>2113</v>
       </c>
       <c r="T48" s="3" t="n">
         <v>1</v>
@@ -5324,41 +5331,41 @@
       </c>
       <c r="V48" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="49" ht="150" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>iwe-org/iwe</t>
+          <t>kotaro-kinoshita/yomitoku</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>1639</v>
+        <v>1591</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>提供 Markdown 知识图谱和 CLI + MCP 内存
-【原文】Markdown knowledge graph — LSP for your editor, CLI + MCP memory for your AI agents</t>
+          <t>提供针对日语文档的AI图像分析包
+【原文】YomiTokuはAIを活用した日本語文書解析エンジンを提供するPythonパッケージです。 Yomitoku is an AI-powered document image analysis package designed specifically for the Japanese language.</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -5368,7 +5375,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/iwe-org/iwe</t>
+          <t>https://github.com/kotaro-kinoshita/yomitoku</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5377,16 +5384,16 @@
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -5401,21 +5408,21 @@
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, ai-memory, cli, helix, knowledge-graph, knowledge-management, language-server, local-first, lsp, markdown, mcp, neovim</t>
+          <t>deep-learning, layout-analysis, ocr, python, pytorch</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S49" s="3" t="n">
-        <v>723</v>
+        <v>684</v>
       </c>
       <c r="T49" s="3" t="n">
         <v>1</v>
@@ -5427,25 +5434,26 @@
       </c>
       <c r="V49" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="50" ht="150" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>hemansnation/AI-Engineer-Headquarters</t>
+          <t>getopenpost/openpost</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>3683</v>
+        <v>404</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>A collection of scientific methods, processes, algorithms, and systems to build stories &amp; models.</t>
+          <t>创建、调整、安排和跟踪社交媒体帖子，支持自托管和托管选项。
+【原文】Create, adapt, schedule, and track social posts. Open-source, hosted or self-hosted.</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -5455,12 +5463,12 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
+          <t>可部署服务/代码库</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -5470,7 +5478,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/hemansnation/AI-Engineer-Headquarters</t>
+          <t>https://github.com/getopenpost/openpost</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5479,16 +5487,16 @@
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -5498,56 +5506,57 @@
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agents, aiengineering, data-structures-and-algorithms, deep-learning, langchain, langgraph, llm, llm-evaluation, llm-inference, llm-security, machine-learning</t>
+          <t>automation, buffer-alternative, content-creation, cross-posting, golang, mcp-server, self-hosted, single-binary, social-media, social-media-automation, social-media-management, social-media-scheduler</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>2022-03-29</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S50" s="3" t="n">
-        <v>1629</v>
+        <v>177</v>
       </c>
       <c r="T50" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U50" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
+          <t>topic:social-media-automation stars:&gt;300 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="51" ht="150" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>bostrot/wsl2-distro-manager</t>
+          <t>brootware/awesome-cyber-security-university</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>3998</v>
+        <v>3523</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>GUI for the Windows Subsystem for Linux — and native Linux/macOS VMs on Mac. Install, back up, move and configure distros without CLI flags; AI assistant with tools, MCP server for agents, remote WSL over SSH.</t>
+          <t>提供网络安全大学课程和资源的列表
+【原文】🎓 Because Education should be free. Contributions welcome! 🕵️</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -5557,12 +5566,12 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -5572,7 +5581,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/bostrot/wsl2-distro-manager</t>
+          <t>https://github.com/brootware/awesome-cyber-security-university</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -5581,18 +5590,14 @@
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>Dart</t>
-        </is>
-      </c>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -5600,26 +5605,26 @@
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>ai, developer-tools, docker, flutter, gui, llm, macos, mcp, model-context-protocol, rootfs, turnkey, virtual-machine</t>
+          <t>awesome, awesome-list, courses, curriculum, cyber-security, cybersecurity, education, educational-project, free, hacking, learning-by-doing</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S51" s="3" t="n">
-        <v>1822</v>
+        <v>1628</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>1</v>
@@ -5631,35 +5636,37 @@
       </c>
       <c r="V51" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-14</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="52" ht="150" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>ratatui/awesome-ratatui</t>
+          <t>robertknight/ocrs</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2001</v>
+        <v>1885</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>A curated list of TUI apps and libraries built with Ratatui</t>
+          <t>提供OCR的Rust库和CLI工具
+【原文】Rust library and CLI tool for OCR (extracting text from images)
+【依据】Rust library and CLI tool for OCR (extracting text from images).</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -5674,7 +5681,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ratatui/awesome-ratatui</t>
+          <t>https://github.com/robertknight/ocrs</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -5683,14 +5690,18 @@
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M52" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -5698,26 +5709,26 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, ratatui, rust, tui</t>
+          <t>computer-vision, machine-learning, ocr</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S52" s="3" t="n">
-        <v>1012</v>
+        <v>986</v>
       </c>
       <c r="T52" s="3" t="n">
         <v>1</v>
@@ -5729,36 +5740,36 @@
       </c>
       <c r="V52" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-14</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="53" ht="150" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Dest1ny-Sec/Des-CTF-Knowledge</t>
+          <t>vespa-engine/vespa</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>202</v>
+        <v>7082</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>CTF知识库，包含漏洞文章、脚本和AI/RAG知识库
-【原文】2026最新CTF知识库：12大Web漏洞深度文章+1156篇历年大赛WP+50+脚本+Payload速查 +AI/RAG离线在线知识库</t>
+          <t>AI 搜索平台，提供搜索、推荐等功能
+【原文】The AI search platform</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>AI免费池/RAG检索线</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -5773,7 +5784,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Dest1ny-Sec/Des-CTF-Knowledge</t>
+          <t>https://github.com/vespa-engine/vespa</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -5782,16 +5793,16 @@
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -5806,52 +5817,51 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>ai, ctf, ctf-challenges, ctf-writeups, knowledge-base, networking-security, rag-chatbot</t>
+          <t>ai, big-data, java, machine-learning, rag, search, search-engine, server, serving-recommendation, tensor, vector, vector-database</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2016-06-03</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S53" s="3" t="n">
-        <v>106</v>
+        <v>3755</v>
       </c>
       <c r="T53" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U53" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V53" s="6" t="inlineStr">
         <is>
-          <t>RAG 知识库 in:name,description stars:&gt;200</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="54" ht="150" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>zclucas/RMT</t>
+          <t>wmariuss/awesome-devops</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>1114</v>
+        <v>4357</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>基于AHKv2的免费开源宏工具，用于自动化和图像识别
-【原文】RMT (RuoMengTu) is a free, open-source macro tool built on AHKv2. Let the code handle the tedious work—you have more meaningful things to do.</t>
+          <t>curated list of awesome DevOps platforms, tools, practices and resources</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -5864,9 +5874,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -5876,7 +5886,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zclucas/RMT</t>
+          <t>https://github.com/wmariuss/awesome-devops</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -5885,16 +5895,16 @@
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>CC0-1.0</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>AutoHotkey</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -5909,12 +5919,12 @@
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>ahk, autohotkey, automation, gamepad-macros, image-recognition, key-macros, menu-macros, ocr, timed-macros</t>
+          <t>awesome, awesome-list, collections, development, devops, production, productivity, resources, sre, tools</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2019-11-19</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
@@ -5923,7 +5933,7 @@
         </is>
       </c>
       <c r="S54" s="3" t="n">
-        <v>614</v>
+        <v>2491</v>
       </c>
       <c r="T54" s="3" t="n">
         <v>1</v>
@@ -5935,26 +5945,26 @@
       </c>
       <c r="V54" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="55" ht="150" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>xianyu110/awesome-gptimage2</t>
+          <t>qmonnet/awesome-ebpf</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>267</v>
+        <v>5163</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>12.5</v>
+        <v>11.2</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>提供 GPT Image 2 中文提示词实战手册
-【原文】GPT Image 2 中文提示词实战手册（本站）。最新 Images 2.5 玩法请看 awesome-gpt-image2.5：https://xianyu110.github.io/awesome-gpt-image2.5/</t>
+          <t>eBPF相关项目列表
+【原文】A curated list of awesome projects related to eBPF.</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -5964,12 +5974,12 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -5979,7 +5989,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/xianyu110/awesome-gptimage2</t>
+          <t>https://github.com/qmonnet/awesome-ebpf</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -5988,18 +5998,14 @@
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M55" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6012,67 +6018,67 @@
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>chatgpt, gpt, gptimage, gptimage2</t>
+          <t>awesome, awesome-list, bcc, bpf, ebpf, xdp</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2017-11-05</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S55" s="3" t="n">
-        <v>150</v>
+        <v>3235</v>
       </c>
       <c r="T55" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U55" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V55" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-15</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="56" ht="150" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>fluxions-ai/vui</t>
+          <t>apecloud/ApeRAG</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>762</v>
+        <v>1315</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>提供实时文本到语音转换模型，支持CPU推理和边缘AI
-【原文】Vui Nano — a small, context-aware text-to-speech model trained on real conversations. 219M active params (305M total), Apache 2.0, voice cloning, streaming, runs on CPU (dependency-free C build). Ships with a full real-time voice assistant: WebRTC, ASR, local LLM, OpenAI Realtime API compatible.</t>
+          <t>提供生产就绪的 GraphRAG，支持多模态索引、AI 代理、MCP 支持和可扩展的 K8s 部署。
+【原文】ApeRAG: Production-ready GraphRAG with multi-modal indexing, AI agents, MCP support, and scalable K8s deployment</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务/代码库</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -6082,7 +6088,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/fluxions-ai/vui</t>
+          <t>https://github.com/apecloud/ApeRAG</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6091,11 +6097,11 @@
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -6115,12 +6121,12 @@
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>conversational-ai, conversational-speech, cpu-inference, edge-ai, lightweight, multi-speaker, on-device, openai-realtime, pytorch, realtime-api, realtime-tts, speech-synthesis</t>
+          <t>agents, context-engineering, graphrag, knowledge-graph, mcp</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
@@ -6129,7 +6135,7 @@
         </is>
       </c>
       <c r="S56" s="3" t="n">
-        <v>465</v>
+        <v>1182</v>
       </c>
       <c r="T56" s="3" t="n">
         <v>1</v>
@@ -6141,41 +6147,41 @@
       </c>
       <c r="V56" s="6" t="inlineStr">
         <is>
-          <t>free llm api in:name,description stars:&gt;200 pushed:&gt;2026-06-15</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="57" ht="150" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>skrstop/MCPHub-Desktop</t>
+          <t>awesome-mlss/awesome-mlss</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>215</v>
+        <v>3033</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>10.4</v>
+        <v>7.5</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>桌面客户端，用于管理MCP服务器、Skills和RAG知识库
-【原文】MCPHub Desktop 是一款基于 Tauri 2 构建的桌面客户端，用于在个人电脑上统一管理 MCP服务器、Skills、RAG 知识库。所有进程、配置、密钥与向量数据都运行/保存在用户自己的机器上，不依赖任何远端服务。</t>
+          <t>机器学习夏季学校的指南
+【原文】🤖 Machine Learning Summer School Guide</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -6185,7 +6191,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/skrstop/MCPHub-Desktop</t>
+          <t>https://github.com/awesome-mlss/awesome-mlss</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -6194,16 +6200,16 @@
         </is>
       </c>
       <c r="K57" s="5" t="n">
-        <v>1.48</v>
+        <v>1.07</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -6216,50 +6222,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P57" s="6" t="inlineStr"/>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>artificial-intelligence, deep-learning, machine-learning, reinforcement-learning, summer-school, summer-schools</t>
+        </is>
+      </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2018-12-01</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S57" s="3" t="n">
-        <v>145</v>
+        <v>2844</v>
       </c>
       <c r="T57" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V57" s="6" t="inlineStr">
         <is>
-          <t>RAG 知识库 in:name,description stars:&gt;200</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="58" ht="150" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>SnapXL/SnapX</t>
+          <t>yvoronoy/awesome-english</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>1028</v>
+        <v>4010</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>跨平台屏幕捕获和录制工具，支持上传图像、视频、文本等
-【原文】SnapX is a free, open-source, cross-platform tool that lets you capture or record any area of your screen and instantly share it with a single keypress. Upload images, videos, text, and more to multiple supported destinations—all with ease. ShareX fork</t>
+          <t>英语学习资源集合
+【原文】A collection of awesome study resources for learners of English.</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -6272,9 +6282,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -6284,7 +6294,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SnapXL/SnapX</t>
+          <t>https://github.com/yvoronoy/awesome-english</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -6293,16 +6303,16 @@
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>CC0-1.0</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -6317,12 +6327,12 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>avalonia, csharp, dotnet, ftp, gif, imgur, linux, macos, ocr, productivity, screen-capture, screenshot</t>
+          <t>awesome, awesome-list, english, english-resources, esl, learn-english</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2016-05-07</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
@@ -6331,7 +6341,7 @@
         </is>
       </c>
       <c r="S58" s="3" t="n">
-        <v>771</v>
+        <v>3782</v>
       </c>
       <c r="T58" s="3" t="n">
         <v>1</v>
@@ -6343,27 +6353,26 @@
       </c>
       <c r="V58" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="59" ht="150" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>scambier/obsidian-omnisearch</t>
+          <t>naodeng/awesome-qa-skills</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>2140</v>
+        <v>211</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Obsidian的搜索引擎，支持OCR和PDF索引
-【原文】A search engine that "just works" for Obsidian. Supports OCR and PDF indexing.
-【依据】A search engine that 'just works' for Obsidian. Supports OCR and PDF indexing.</t>
+          <t>开源 AI-native 质量工程技能系统，帮助团队提升软件质量
+【原文】Awesome QA Skills is an open-source AI-native Quality Engineering skill system that helps engineering teams reason about, design, execute, evaluate, and continuously improve software quality across the entire SDLC.</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -6373,12 +6382,12 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -6388,7 +6397,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/scambier/obsidian-omnisearch</t>
+          <t>https://github.com/naodeng/awesome-qa-skills</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -6397,16 +6406,16 @@
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>1.32</v>
+        <v>0.95</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -6421,21 +6430,21 @@
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>minisearch, obsidian, obsidian-md, obsidian-plugin, ocr, pdf, search</t>
+          <t>agent-skills, ai-qa, ai-skills, ai-testing, ai-tools, awesome-list, prompt-engineering, qa, qa-skills, skills</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S59" s="3" t="n">
-        <v>1617</v>
+        <v>222</v>
       </c>
       <c r="T59" s="3" t="n">
         <v>1</v>
@@ -6447,26 +6456,27 @@
       </c>
       <c r="V59" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="60" ht="150" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>eikek/docspell</t>
+          <t>tiddly-gittly/TidGi-Desktop</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>2324</v>
+        <v>2002</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>6.2</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>文档管理系统，帮助组织来自扫描仪、电子邮件等来源的文档
-【原文】Assist in organizing your piles of documents, resulting from scanners, e-mails and other sources with miminal effort.</t>
+          <t>基于 Tiddlywiki 的知识管理桌面应用，支持 REST API 和 Anki 连接。
+【原文】TidGi is an privacy-in-mind, automated, auto-git-backup, freely-deployed knowledge management Desktop note app, based on Tiddlywiki, with REST API for web-clipping and Anki connect. 「 太记 」是一个基于「 太微 TiddlyWiki 」的知识管理桌面应用，能保护隐私内容、高级自动化、自动Git云备份、部署为博客，且可通过RESTAPI与Anki等应用连接。（迭代开发中欢迎试用，开发进度见下方链接）(Under active development, see website below for details)
+【依据】基于 Tiddlywiki，提供知识管理和笔记功能。</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -6479,9 +6489,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G60" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -6491,7 +6501,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/eikek/docspell</t>
+          <t>https://github.com/tiddly-gittly/TidGi-Desktop</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -6500,16 +6510,16 @@
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>MPL-2.0</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>Elm</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -6524,21 +6534,21 @@
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>dms, docspell, document, document-management, document-management-system, edms, elm, nlp, ocr, pdf, personal-document-system, scala</t>
+          <t>all-in-one, anki, backlinks, electron, evernote, knowledge-graph, knowledge-management, linux, local-first, macos, note-taking, notebook</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S60" s="3" t="n">
-        <v>2616</v>
+        <v>2285</v>
       </c>
       <c r="T60" s="3" t="n">
         <v>1</v>
@@ -6550,26 +6560,26 @@
       </c>
       <c r="V60" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="61" ht="150" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>silexlabs/Silex</t>
+          <t>AI-Efficiency/Awesome-Model-Quantization</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>2964</v>
+        <v>2440</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>在线工具，用于可视创建静态网站，支持动态数据
-【原文】Silex is an online tool for visually creating static sites with dynamic data. With the free/libre spirit of internet, together.</t>
+          <t>模型量化相关论文、基准、调查和工具的 curated collection
+【原文】A curated collection of papers, benchmarks, surveys, and tools for model quantization, covering low-bit networks, LLMs, multimodal and generative models, vector and lattice quantization, and efficient deployment.</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -6582,9 +6592,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -6594,7 +6604,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/silexlabs/Silex</t>
+          <t>https://github.com/AI-Efficiency/Awesome-Model-Quantization</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -6603,18 +6613,14 @@
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6627,12 +6633,12 @@
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>composable, design, grapesjs, jamstack, javascript, mcp, mcp-server, no-code, nocode, nodejs, saas, silex</t>
+          <t>awesome, awesome-list, awesome-lists, binarization, binary-neural-networks, data-free-quantization, diffusion-models, efficient-inference, kv-cache, kv-cache-quantization, large-language-models, large-language-models-llms</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>2013-09-29</t>
+          <t>2018-10-18</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
@@ -6641,38 +6647,38 @@
         </is>
       </c>
       <c r="S61" s="3" t="n">
-        <v>4732</v>
+        <v>2888</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U61" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V61" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp-server stars:&gt;1000 pushed:&gt;2026-08-14</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="62" ht="150" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>toki-plus/ai-highlight-clip</t>
+          <t>totogo/awesome-knowledge-graph</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>101</v>
+        <v>1889</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>自动剪辑长视频为短视频，并生成标题和评分
-【原文】AI驱动的长视频高光剪辑工具，自动将数小时的课程、访谈、直播回放转化为数十个爆款短视频。内置Whisper语音识别、大模型(LLM)智能评分与标题生成。 video-processing, ai-content-creation, nlp, openai-whisper, llm, automation, pyqt5, ffmpeg, bot.</t>
+          <t>提供知识图谱相关学习材料、数据库、工具和其他资源的精选列表。
+【原文】A curated list of Knowledge Graph related learning materials, databases, tools and other resources</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -6682,12 +6688,12 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -6697,7 +6703,7 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/toki-plus/ai-highlight-clip</t>
+          <t>https://github.com/totogo/awesome-knowledge-graph</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -6706,18 +6712,14 @@
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6730,33 +6732,33 @@
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>ai-content-creation, automation, content-creation, ffmpeg, llm, nlp, openai-whisper, pyqt5, python, short-video, video-editing, video-processing</t>
+          <t>awesome-list, graph, graph-database, knowledge-graph, nlp</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2019-02-03</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S62" s="3" t="n">
-        <v>277</v>
+        <v>2780</v>
       </c>
       <c r="T62" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U62" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V62" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-15</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
         </is>
       </c>
     </row>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -113,10 +113,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V62"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-14 · 共 60 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-15 · 共 51 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,44 +633,44 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>HKUDS/DeepTutor</t>
+          <t>qingjian-team/qingjian</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>39536</v>
+        <v>773</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1064.4</v>
+        <v>676.3</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>终身个性化辅导系统
-【原文】DeepTutor: Lifelong Personalized Tutoring. https://deeptutor.info/.</t>
+          <t>Rust 编写的拼音输入法，支持多语言学习
+【原文】青简 Qingjian：用 Rust 写的拼音输入法，候选词旁多一条正在学的语言的译词</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/HKUDS/DeepTutor</t>
+          <t>https://github.com/qingjian-team/qingjian</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>152.06</v>
+        <v>96.62</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -703,77 +703,68 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, ai-tutor, clawdbot, cli-tool, deepresearch, interactive-learning, large-language-models, multi-agent-systems, rag</t>
+          <t>chinese, chinese-input-method, english-learning, ime, input-method, japanese-learning, language-learning, language-model, macos, offline, pinyin, rust</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>260</v>
+        <v>8</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>totec448-spec/chat-on-steroids</t>
+          <t>StarTrail-org/PixelRAG</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2368</v>
+        <v>9959</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>720.7</v>
+        <v>639.6</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>为 ChatGPT 提供跨平台的本地 MCP 功能，包括 Chrome 集成、多代理工作流等。
-【原文】Cross-platform local MCP capabilities for ChatGPT with Chrome integration, Goal, Compact &amp; Resume, and durable multi-agent workflows.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>技能包/代码库</t>
-        </is>
-      </c>
+          <t>https://arxiv.org/abs/2606.28344. The end of web parsing. The beginning of scalable pixel-native search. link: https://pixelrag.ai/</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/totec448-spec/chat-on-steroids</t>
+          <t>https://github.com/StarTrail-org/PixelRAG</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,16 +773,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>102.96</v>
+        <v>91.37</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -801,17 +792,17 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>automation, chatgpt, chrome-extension, electron, linux, local-first, macos, mcp, multi-agent, windows</t>
+          <t>agent, ai, memory, multimodal, rag, search, searchengine, vision, vlm</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -820,63 +811,54 @@
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-15</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>RyanCodrai/turbovec</t>
+          <t>opendataloader-project/opendataloader-pdf</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>17104</v>
+        <v>29183</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>696.1</v>
+        <v>416.9</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>基于TurboQuant的向量索引
-【原文】A vector index built on TurboQuant, written in Rust with Python bindings</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
+          <t>PDF Parser for AI-ready data. Automate PDF accessibility. Open-source.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/RyanCodrai/turbovec</t>
+          <t>https://github.com/opendataloader-project/opendataloader-pdf</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -885,16 +867,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>99.44</v>
+        <v>59.56</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -904,29 +886,29 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>ann, avx512, embedding, embeddings, faiss, nearest-neighbor, neon, python, quant, quantization, rag, rust</t>
+          <t>a11y, accessibility, ai, bounding-box, document-parsing, eaa, html, json, markdown, ocr, ocr-recognition, pdf</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>172</v>
+        <v>490</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
@@ -935,52 +917,42 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>AgriciDaniel/claude-obsidian</t>
+          <t>mem0ai/mem0</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>14882</v>
+        <v>65303</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>651.1</v>
+        <v>386.4</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>为 Obsidian 和 Claude Code 提供自组织的 AI 第二大脑。
-【原文】Self-organizing AI second brain for Obsidian + Claude Code. Drop any source and Claude reads, links, and files it into one connected knowledge graph of plain Markdown you own. AI note-taking, personal knowledge management (PKM), and an open-source Notion alternative. Based on Karpathy's LLM Wiki pattern.
-【依据】Obsidian + Claude Code 的 AI 第二大脑。</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
+          <t>The Memory Layer for AI Agents - Drop-in memory infrastructure for AI agents and apps. Context that persists. Built for production.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/AgriciDaniel/claude-obsidian</t>
+          <t>https://github.com/mem0ai/mem0</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -989,11 +961,11 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>93.01000000000001</v>
+        <v>55.2</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1008,26 +980,26 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-note-taking, ai-second-brain, claude-code, claude-code-skill, claude-memory, claude-plugin, karpathy-llm-wiki, knowledge-graph, knowledge-management, note-taking, notion-alternative</t>
+          <t>agentic-memory, agentic-memory-system, agents, ai, ai-agents, chatgpt, genai, llm, long-term-memory, memory, memory-management, python</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>160</v>
+        <v>1183</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1039,51 +1011,42 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>larashero3-dotcom/lieflat-charts</t>
+          <t>cloudflare/security-audit-skill</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>5321</v>
+        <v>4152</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>620.8</v>
+        <v>326.6</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>面向 AI Agents 的数据可视化 Skill，生成 HTML 图表
-【原文】Data visualization Skill for AI Agents, turning data into polished, interactive HTML charts. 面向 AI Agents 的数据可视化 Skill，将数据快速生成精致、可交互的 HTML 图表。</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
+          <t>A coding-agent skill for multi-phase security audits with independently verified, machine-readable findings</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/larashero3-dotcom/lieflat-charts</t>
+          <t>https://github.com/cloudflare/security-audit-skill</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1092,16 +1055,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>88.68000000000001</v>
+        <v>46.65</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1111,29 +1074,25 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, charts, claude-code, codex, data-visualization, html, moxt, svg</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
@@ -1142,51 +1101,42 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>agent skill in:name,description stars:&gt;300 pushed:&gt;2026-06-16</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>alibaba/zvec</t>
+          <t>elayadesign/ai-design-skills</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>15913</v>
+        <v>2229</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>393.6</v>
+        <v>325.1</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>轻量级、快速的内进程向量数据库
-【原文】A lightweight, lightning-fast, in-process vector database</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
+          <t>(无描述)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/alibaba/zvec</t>
+          <t>https://github.com/elayadesign/ai-design-skills</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1195,18 +1145,14 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>56.23</v>
+        <v>46.44</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>C++</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1214,26 +1160,22 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, db, embedded, faiss, fts, fulltext-search, hnsw, llm-memory, local, rag, search-engine, semantic-search</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>283</v>
+        <v>48</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1245,51 +1187,42 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
+          <t>skills in:name stars:&gt;500 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Tiger3807861189/J-Space-Cognition-Suite</t>
+          <t>getzep/graphiti</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>3009</v>
+        <v>30880</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>390</v>
+        <v>281.5</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>提供模型无关的推理时控制套件，用于深度推理、长期工作、验证和恢复。
-【原文】J-Space Cognition Suite — a model-agnostic inference-time control suite for deep reasoning, long-horizon work, verification, and recovery. Based on Anthropic's J-space global workspace research. | 哔哩哔哩：Tiger380 — https://space.bilibili.com/3494375382321675</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>技能包/代码库</t>
-        </is>
-      </c>
+          <t>Build Real-Time Knowledge Graphs for AI Agents</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Tiger3807861189/J-Space-Cognition-Suite</t>
+          <t>https://github.com/getzep/graphiti</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1298,7 +1231,7 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>55.72</v>
+        <v>40.21</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1317,82 +1250,73 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai, ai-agent, ai-agents, claude-code, codex, cognitive-enhancement, deepseek, deepseek-harness, developer-tools, dsh, dsh-plugin</t>
+          <t>agents, graph, llms, rag</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>54</v>
+        <v>768</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-15</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>lewislulu/html-ppt-skill</t>
+          <t>ykdojo/claude-code-tips</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>8347</v>
+        <v>10087</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>384.4</v>
+        <v>242.6</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>构建专业HTML演示文稿的智能体技能
-【原文】HTML PPT Studio — AgentSkill with 24 themes, 31 layouts, 20+ animations for building professional HTML presentations</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
+          <t>45+ tips for getting the most out of Claude Code, from basics to advanced - includes a custom status line script and Claude Code running itself in a container. Also includes the dx plugin: skills for everyday dev workflows.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lewislulu/html-ppt-skill</t>
+          <t>https://github.com/ykdojo/claude-code-tips</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1401,11 +1325,11 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>54.91</v>
+        <v>34.66</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1420,25 +1344,29 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>agentic, agentic-ai, agentic-coding, agentic-workflow, ai, claude, claude-ai, claude-code, cli, developer-tools, productivity, tips-and-tricks</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>152</v>
+        <v>291</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
@@ -1447,52 +1375,42 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;500 pushed:&gt;2026-06-16</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>huggingface/agents-course</t>
+          <t>zai-org/GLM-5</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>32493</v>
+        <v>7185</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>375.3</v>
+        <v>230.7</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>包含 Hugging Face 代理课程的资源库。
-【原文】This repository contains the Hugging Face Agents Course.
-【依据】Hugging Face 代理课程。</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
+          <t>GLM-5: From Vibe Coding to Agentic Engineering</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/huggingface/agents-course</t>
+          <t>https://github.com/zai-org/GLM-5</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1501,18 +1419,14 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>53.62</v>
+        <v>32.96</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>MDX</t>
-        </is>
-      </c>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1520,26 +1434,26 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, agents, course, huggingface, langchain, llamaindex, smolagents</t>
+          <t>agentic-ai, coding, llm, long-horizon</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>606</v>
+        <v>218</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1551,27 +1465,26 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>microsoft/agent-lightning</t>
+          <t>TencentCloud/Octop</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>18087</v>
+        <v>2208</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>279.5</v>
+        <v>224</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>训练 AI 代理的绝对训练器。
-【原文】The absolute trainer to light up AI agents.
-【依据】AI 代理的训练器。</t>
+          <t>多用户、多代理的自托管 AI 助手
+【原文】A smarter, self-hosted AI assistant — multi-user, multi-agent.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1581,7 +1494,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1589,14 +1502,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/agent-lightning</t>
+          <t>https://github.com/TencentCloud/Octop</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1605,7 +1518,7 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>39.93</v>
+        <v>32</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -1629,12 +1542,12 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, llm, mlops, reinforcement-learning</t>
+          <t>agent, agentic-ai, ai, ai-agent, ai-agents, local-first, long-term-memory</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1643,63 +1556,54 @@
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>microsoft/graphrag</t>
+          <t>FlowElement-xinliuyuansu/m_flow</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>35964</v>
+        <v>4499</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>279.4</v>
+        <v>187.5</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>基于图检索增强的生成系统
-【原文】A modular graph-based Retrieval-Augmented Generation (RAG) system</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>RAG检索线</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
+          <t>A bio-inspired cognitive memory engine — a new paradigm for Graph RAG.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/graphrag</t>
+          <t>https://github.com/FlowElement-xinliuyuansu/m_flow</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1708,11 +1612,11 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>39.92</v>
+        <v>26.78</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1727,26 +1631,26 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>gpt, gpt-4, gpt4, graphrag, llm, llms, rag</t>
+          <t>agent-memory, agentic-ai, ai-reasoning, episodic-memory, graph-database, knowledge-graph, llm, long-term-memory, mcp, memory-engine, python, rag</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>901</v>
+        <v>168</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1758,52 +1662,42 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>eigent-ai/eigent</t>
+          <t>SteveTheKiller/KillerPDF</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>15269</v>
+        <v>3851</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>259.4</v>
+        <v>177.4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>开源协同桌面应用，替代 Claude Cowork 和 Codex。
-【原文】Eigent: The Open Source Cowork Desktop - Local and Free Alternative to Claude Cowork and Codex
-【依据】替代 Claude Cowork 和 Codex 的协同桌面应用。</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
+          <t>Free and open-source PDF editor for Windows with a built-in PDF 2.0 engine. View, annotate, OCR, merge, split, crop, rotate, compare, edit text, draw, sign, fill forms, print, flatten, and open password-protected PDFs without a subscription.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/eigent-ai/eigent</t>
+          <t>https://github.com/SteveTheKiller/KillerPDF</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1812,16 +1706,16 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>37.06</v>
+        <v>25.34</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1831,26 +1725,26 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>agent-framework, agent-skills, agentic-ai, agentic-workflow, claude-cowork, claude-cowork-alternative, claude-cowork-free, desktop-agent, multi-agent-systems</t>
+          <t>csharp, dotnet, dotnet-core, fast, gplv3, ocr, open-source, opensource, pdf, pdf-2-0, pdf-annotator, pdf-editor</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>412</v>
+        <v>152</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1862,52 +1756,42 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>ParthJadhav/app-store-screenshots</t>
+          <t>conorbronsdon/avoid-ai-writing</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>6885</v>
+        <v>4383</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>252.3</v>
+        <v>159</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>使用AI自动化生成应用商店截图
-【原文】end to end app store screenshot creation using AI
-【依据】end to end app store screenshot creation using AI.</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
+          <t>Skill that audits and rewrites content to remove AI writing patterns. Use it with your favorite agents including Claude Code, OpenClaw, Codex, and Hermes.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ParthJadhav/app-store-screenshots</t>
+          <t>https://github.com/conorbronsdon/avoid-ai-writing</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1916,7 +1800,7 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>36.05</v>
+        <v>22.71</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -1925,7 +1809,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1935,26 +1819,26 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, apple, appstore, automate, claude, cursor, design, generate, ios, ios-app, marketing, screenshot</t>
+          <t>ai-writing, claude, claude-code, llm, prompt-engineering, skill, writing</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1966,51 +1850,42 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
+          <t>agent skill in:name,description stars:&gt;300 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>eugeniughelbur/obsidian-second-brain</t>
+          <t>CortexReach/memory-lancedb-pro</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>4443</v>
+        <v>4458</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>178.7</v>
+        <v>153.7</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>为 Claude Code 和其他 CLI 代理提供持久化记忆存储，以 Markdown 格式保存在 Obsidian 仓库中。
-【原文】Persistent memory for Claude Code and 6 other CLI agents, stored as plain markdown in your Obsidian vault. Stop re-explaining your projects, decisions and people every session. 45 commands: hybrid semantic search, self-rewriting notes, key-less web research, and scheduled agents that maintain the vault while you sleep.</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>技能包/代码库</t>
-        </is>
-      </c>
+          <t>Enhanced LanceDB memory plugin for OpenClaw — Hybrid Retrieval (Vector + BM25), Cross-Encoder Rerank, Multi-Scope Isolation, Management CLI</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/eugeniughelbur/obsidian-second-brain</t>
+          <t>https://github.com/CortexReach/memory-lancedb-pro</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2019,16 +1894,16 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>25.53</v>
+        <v>21.96</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2038,17 +1913,17 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, ai-note-taking, ai-second-brain, anthropic, claude, claude-code, claude-code-skill, claude-memory, claude-plugin, claude-skill, karpathy-llm-wiki</t>
+          <t>lancedb, memory, openclaw, openclaw-agent, openclaw-plugin, rag</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -2057,7 +1932,7 @@
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2069,51 +1944,51 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>yaojingang/GEOFlow</t>
+          <t>rlaope/oh-my-hermes</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>3628</v>
+        <v>2186</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>164.9</v>
+        <v>147.1</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>开源 GEO 内容工程和多站分布平台，具有 AI 质量检查和辅助发布功能
-【原文】Open-source GEO content engineering and multi-site distribution platform with AI quality inspection, illustrated admin help, hosted sites, browser-assisted publishing, and signed updates.</t>
+          <t>Hermes Agent 插件，提供编码智能和模型优化工作流程
+【原文】All in one plugin for Hermes Agent ⚚ the coding intelligence, a long-term memory system and model optimized workflow packages</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
+          <t>技能包/代码库</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yaojingang/GEOFlow</t>
+          <t>https://github.com/rlaope/oh-my-hermes</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2122,16 +1997,16 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>23.56</v>
+        <v>21.02</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2146,62 +2021,62 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>ai, chrome-extension, cms, content-automation, generative-engine-optimization, geo, laravel, multi-site, openai-compatible, php, postgresql, pwa</t>
+          <t>agent, ai, ai-agent, ai-tools, claude-code, codex, hermes-agent, hermes-skill, skills</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>PleasePrompto/notebooklm-skill</t>
+          <t>melgarafael/DeskcommCRM</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>7772</v>
+        <v>2565</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>164.8</v>
+        <v>128.2</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>使Claude Code与Google NotebookLM笔记本直接通信的技能
-【原文】Use this skill to enable Claude Code to communicate directly with your Google NotebookLM notebooks. Query your uploaded documents and get source-grounded, citation-backed answers from Gemini. Features browser automation, library management, persistent authentication, and answers exclusively from your own knowledge base.</t>
+          <t>开源 AI 销售操作系统，内置 AI 代理和 WhatsApp 支持
+【原文】Open-source AI sales OS — self-hosted CRM with native AI agents + WhatsApp (WAHA). Open alternative to Kommo, Octadesk &amp; Intercom for any business that sells by chat. MCP-ready, multi-tenant, LGPD.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/图文产线</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>可部署服务/技能包</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2209,14 +2084,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/PleasePrompto/notebooklm-skill</t>
+          <t>https://github.com/melgarafael/DeskcommCRM</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2225,7 +2100,7 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>23.55</v>
+        <v>18.32</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2109,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2247,75 +2122,70 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>ai, ai-agents, chatbot, crm, customer-support, ecommerce, lgpd, mcp, multi-tenant, nextjs, nuvemshop, open-source</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>330</v>
+        <v>140</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;500 pushed:&gt;2026-06-16</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>ScrapeCreators/social-media-research-skills</t>
+          <t>eosphoros-ai/DB-GPT</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2320</v>
+        <v>19960</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>162.4</v>
+        <v>111.7</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>社交媒体研究 AI agent 技能
-【原文】AI agent skills for social media research. Outlier posts, comment mining, competitor teardowns, ad libraries &amp; trends across TikTok, Instagram, YouTube, Reddit, X, LinkedIn &amp; more. Powered by ScrapeCreators. Works with Claude Code, Cursor, Codex, Gemini CLI.</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
+          <t>open-source agentic AI data assistant for the next generation of AI + Data products.</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ScrapeCreators/social-media-research-skills</t>
+          <t>https://github.com/eosphoros-ai/DB-GPT</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2324,7 +2194,7 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>23.2</v>
+        <v>15.96</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2343,26 +2213,26 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, claude-code, claude-skills, competitor-analysis, content-marketing, cursor, influencer-marketing, market-research, social-media, social-media-research, workflow-automation</t>
+          <t>agents, bgi, database, deepseek, gpt, gpt-4, hacktoberfest, llm, private, rag, security, vicuna</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>100</v>
+        <v>1251</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
@@ -2374,51 +2244,42 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>skills in:name stars:&gt;500 pushed:&gt;2026-06-16</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>logseq/logseq</t>
+          <t>Orkas-AI/Orkas</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>44893</v>
+        <v>2005</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>136.4</v>
+        <v>100.9</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>提供隐私优先的开源知识管理和协作平台，支持 Clojure 和 ClojureScript。
-【原文】A privacy-first, open-source platform for knowledge management and collaboration. Download link:  http://github.com/logseq/logseq/releases. roadmap: https://logseq.io/p/NX4mc_ggEV</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务/代码库</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
+          <t>Orkas is an open-source, local-first AI desktop app: a commander LLM directs specialist sub-agents, and runs your installed coding CLIs — Claude Code, Codex, OpenCode, OpenClaw, Hermes — as local sessions. Agents self-evolve via reflection and skill crystallization. BYO keys. macOS / Windows / Linux.</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/logseq/logseq</t>
+          <t>https://github.com/Orkas-AI/Orkas</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2427,16 +2288,16 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>19.48</v>
+        <v>14.42</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>Clojure</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2446,82 +2307,73 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>clojure, clojurescript, git, graph, knowledge-base, knowledge-graph, local-first, markdown, note-taking, org-mode, pkm</t>
+          <t>agent-collaboration, agent-orchestration, agent-team, agentic-ai, ai-agents, ai-assistant, ai-team, ai-workflow, autonomous-agents, byo-llm, cross-platform, desktop-app</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2020-05-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>2305</v>
+        <v>139</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>abhisheknaiidu/awesome-github-profile-readme</t>
+          <t>CaviraOSS/LongMemory</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>31051</v>
+        <v>4498</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>96.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>GitHub Profile 的 curated list
-【原文】😎 A curated list of awesome GitHub Profile which updates in real time</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
+          <t>Local persistent memory store for LLM applications including claude desktop, github copilot, codex, antigravity, etc.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/abhisheknaiidu/awesome-github-profile-readme</t>
+          <t>https://github.com/CaviraOSS/LongMemory</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2530,14 +2382,18 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>13.77</v>
+        <v>13.59</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2545,26 +2401,26 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, github, github-profile-readme, github-readme, portfolio, profile-readme</t>
+          <t>ai, ai-agents, ai-infrastructure, ai-memory, artificial-intelligence, cognitive-architecture, embeddings, gemini, llm, long-term-memory, memory, memory-engine</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>2255</v>
+        <v>331</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
@@ -2576,51 +2432,42 @@
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>zenstory-ai/oh-story-dsh</t>
+          <t>wxyhgk/retain-pdf</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>341</v>
+        <v>2278</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>91.8</v>
+        <v>93.8</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>提供 DeepSeek 写网文/小说的工作流插件，包括小说、短剧、游戏和视频解说工作台。
-【原文】DeepSeek 写网文/小说的工作流插件：DeepSeek Harness 社区插件，内置小说、短剧、游戏、视频解说四个工作台 | Community DeepSeek Harness plugin with novel, short-drama, game and video-recap workbenches. Not affiliated with DeepSeek.</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>技能包/代码库</t>
-        </is>
-      </c>
+          <t>在保留版面、公式与结构的前提下进行 PDF 翻译，适用于科研与技术文档</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zenstory-ai/oh-story-dsh</t>
+          <t>https://github.com/wxyhgk/retain-pdf</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2629,7 +2476,7 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>13.12</v>
+        <v>13.4</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -2648,82 +2495,73 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, ai-novel-writing, ai-writing, claude-code, creative-writing, deepseek, deepseek-harness, drama-skills, dsh-plugin, fiction-writing, novel-writing</t>
+          <t>document-ai, document-processing, layout-preserving, ocr, pdf, scientific-papers, translation, typst</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>dataelement/bisheng</t>
+          <t>Kulaxyz/self-learning-skills</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>11957</v>
+        <v>954</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>75.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>提供下一代企业AI应用的LLM开发平台
-【原文】BISHENG is an open LLM devops platform for next generation Enterprise AI applications. Powerful and comprehensive features include: GenAI workflow, RAG, Agent, Unified model management, Evaluation, SFT, Dataset Management, Enterprise-level System Management, Observability and more.</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>MCP服务/技能包/架构参考</t>
-        </is>
-      </c>
+          <t>A self-improving skill for AI coding agents (Claude Code, Cursor, AGENTS.md): recognize a hard-won golden path in a session and harvest it into a reusable skill/rule for next time.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dataelement/bisheng</t>
+          <t>https://github.com/Kulaxyz/self-learning-skills</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2732,18 +2570,14 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>10.74</v>
+        <v>12.08</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr"/>
       <c r="N23" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2751,17 +2585,13 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>agent, ai, chatbot, enterprise, finetune, genai, gpt, langchian, llama, llm, llmdevops, llmops</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
@@ -2770,10 +2600,10 @@
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1113</v>
+        <v>79</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
@@ -2782,50 +2612,42 @@
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>BZDmathclub/bzd-math-modeling-skills</t>
+          <t>NirDiamant/Agent_Memory_Techniques</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>337</v>
+        <v>1058</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>73.7</v>
+        <v>55.6</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>数学建模竞赛论文智能评审 Skill</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
+          <t>Agent memory for LLMs: 30 runnable Jupyter notebooks covering conversation buffers, vector stores, knowledge graphs, episodic and semantic memory, MemGPT, Mem0, Letta, Zep, Graphiti, LoCoMo benchmarks, and production patterns.</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/BZDmathclub/bzd-math-modeling-skills</t>
+          <t>https://github.com/NirDiamant/Agent_Memory_Techniques</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2834,16 +2656,16 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>10.53</v>
+        <v>7.95</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2853,22 +2675,26 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>agent-memory, ai-agents, anthropic, episodic-memory, generative-ai, graphiti, knowledge-graph, langchain, letta, llm, llm-agents, llm-memory</t>
+        </is>
+      </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>1</v>
@@ -2880,36 +2706,36 @@
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>KartikLabhshetwar/better-shot</t>
+          <t>crmne/ruby_llm</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2296</v>
+        <v>4365</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>65.3</v>
+        <v>51.5</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>提供macOS上的截图、屏幕录制和视频编辑工具
-【原文】Screenshot, screen recording, and video editor for macOS. Native SwiftUI app with capture deck, 75+ customizable shortcuts, URL scheme automation, and self-hosted cloud sharing. Open-source alternative to CleanShot X and Loom.</t>
+          <t>提供 Ruby-native AI 框架，支持多模态内容生成
+【原文】The Ruby-native AI framework. Chats, agents, tools, images, audio, and video through one consistent API, in plain Ruby or Rails.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>视频产线/图文产线</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2917,14 +2743,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/KartikLabhshetwar/better-shot</t>
+          <t>https://github.com/crmne/ruby_llm</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2933,16 +2759,16 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>9.33</v>
+        <v>7.36</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>BSD-3-Clause</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2957,24 +2783,24 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>annotation-tool, automation, capture-tool, cleanshot-alternative, cloudflare-r2, loom-alternative, macos, macos-app, native-macos, ocr, open-source, privacy</t>
+          <t>agents, ai, ai-framework, anthropic, embeddings, gemini, image-generation, llm, multimodal, ocr, ollama, openai</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>246</v>
+        <v>593</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
@@ -2983,51 +2809,42 @@
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>makenotion/notion-mcp-server</t>
+          <t>any4ai/AnyCrawl</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>4632</v>
+        <v>3455</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>58.7</v>
+        <v>45.4</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>官方 Notion MCP 服务器
-【原文】Official Notion MCP Server</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>MCP服务</t>
-        </is>
-      </c>
+          <t>AnyCrawl 🚀: A Node.js/TypeScript crawler that turns websites into LLM-ready data and extracts structured SERP results from Google/Bing/Baidu/etc. Native multi-threading for bulk processing.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/makenotion/notion-mcp-server</t>
+          <t>https://github.com/any4ai/AnyCrawl</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3036,7 +2853,7 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>8.380000000000001</v>
+        <v>6.48</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
@@ -3055,22 +2872,26 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P26" s="6" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>ai-scraping, aitools, crawl, data, html-to-markdown, rag, scrape, scraping, serp, webscraper</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>1</v>
@@ -3082,52 +2903,42 @@
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-15</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>icip-cas/PPTAgent</t>
+          <t>GH05TCREW/pentestagent</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>5025</v>
+        <v>3077</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>56.9</v>
+        <v>44.2</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>用于生成反思性演示文稿的代理框架
-【原文】An Agentic Framework for Reflective PowerPoint Generation
-【依据】An Agentic Framework for Reflective PowerPoint Generation.</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>MCP服务/技能包</t>
-        </is>
-      </c>
+          <t>PentestAgent is an AI agent framework for black-box security testing, supporting bug bounty, red-team, and penetration testing workflows.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/icip-cas/PPTAgent</t>
+          <t>https://github.com/GH05TCREW/pentestagent</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3136,7 +2947,7 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>6.31</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -3155,17 +2966,17 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, llm, mcp, openclaw, presentation, slide</t>
+          <t>ai, ai-agents, ai-assistant, ai-cybersecurity, ai-hacking, ai-security-tool, blackbox-testing, ctf-tools, knowledge-graph, llm, mcp-tools, penetration-testing</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
@@ -3174,7 +2985,7 @@
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>618</v>
+        <v>488</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>1</v>
@@ -3186,52 +2997,42 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="28" ht="150" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>potpie-ai/potpie</t>
+          <t>jonyzhang2023/awesome-embodied-vla-va-vln</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>5719</v>
+        <v>3528</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>52.5</v>
+        <v>40.7</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>为 AI 本地 SDLC 提供上下文图框架。
-【原文】Context Graph for AI Native SDLC
-【依据】AI 本地 SDLC 的上下文图框架。</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
+          <t>A curated list of state-of-the-art research in embodied AI, focusing on vision-language-action (VLA) models, vision-language navigation (VLN), and related multimodal learning approaches.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/potpie-ai/potpie</t>
+          <t>https://github.com/jonyzhang2023/awesome-embodied-vla-va-vln</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3240,18 +3041,14 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>7.5</v>
+        <v>5.81</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr"/>
       <c r="N28" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3259,29 +3056,25 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>agents, ai-agents, ai-agents-framework, artificial-intelligence, context-graph, developer-tools, devtools, generative-ai, knowledge-graph, rag</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr"/>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S28" s="3" t="n">
-        <v>763</v>
+        <v>607</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
@@ -3290,52 +3083,42 @@
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>ocrmypdf/OCRmyPDF</t>
+          <t>neuml/txtai</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>34759</v>
+        <v>12948</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>52.3</v>
+        <v>40.7</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>为扫描PDF文件添加OCR文本层
-【原文】OCRmyPDF adds an OCR text layer to scanned PDF files, allowing them to be searched
-【依据】OCRmyPDF adds an OCR text layer to scanned PDF files.</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>古籍OCR线</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
+          <t>💡 All-in-one AI framework for semantic search, LLM orchestration and language model workflows</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ocrmypdf/OCRmyPDF</t>
+          <t>https://github.com/neuml/txtai</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3344,11 +3127,11 @@
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>7.47</v>
+        <v>5.81</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>MPL-2.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -3363,26 +3146,26 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>image-processing, ocr, pdf, python, tesseract</t>
+          <t>agents, ai, ai-agents, embeddings, information-retrieval, language-model, large-language-models, llm, nlp, python, rag, retrieval-augmented-generation</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>2013-12-20</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S29" s="3" t="n">
-        <v>4651</v>
+        <v>2228</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>1</v>
@@ -3394,36 +3177,36 @@
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="30" ht="150" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>FrancyJGLisboa/agent-skills-platform</t>
+          <t>neo4j-labs/llm-graph-builder</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2384</v>
+        <v>5249</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>50.4</v>
+        <v>37.6</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>构建和治理智能体技能的平台
-【原文】Build tested agent skills and govern their lifecycle through a user-defined marketplace: evidence, discovery, updates, rollback, quarantine, and 17-platform distribution.</t>
+          <t>使用 LLM 从非结构化数据构建 Neo4j 图
+【原文】Neo4j graph construction from unstructured data using LLMs</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>可部署服务/代码库</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3431,14 +3214,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/FrancyJGLisboa/agent-skills-platform</t>
+          <t>https://github.com/neo4j-labs/llm-graph-builder</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3447,16 +3230,16 @@
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>7.2</v>
+        <v>5.37</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -3471,21 +3254,21 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, claude-code, codex, cursor, developer-tools, evals, github-copilot, governance, skill-marketplace</t>
+          <t>data-import, genai, graph, graph-rag, graph-search, graphdb, graphrag, knowledge-graph, langchain, neo4j, rag, unstructured-data</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S30" s="3" t="n">
-        <v>331</v>
+        <v>978</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>2</v>
@@ -3497,51 +3280,42 @@
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="31" ht="150" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>DaoYiSec/SecSkills</t>
+          <t>us/crw</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>42.9</v>
+        <v>36.1</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>收集网络安全相关技能和MCP
-【原文】收集整理渗透测试、漏洞扫描、代码审计、CTF、逆向、安全研究 等网络安全相关的 Skills和MCP</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
+          <t>Fast, lightweight Firecrawl/Tavily alternative in Rust. Web scraper, crawler &amp; search API with MCP server for AI agents. Drop-in Firecrawl-compatible API (/scrape, /crawl, /search). 2.3x faster than Tavily, 1.5x faster than Firecrawl in 1K-URL benchmarks. 6 MB RAM, single binary. Self-host or use managed cloud.</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/DaoYiSec/SecSkills</t>
+          <t>https://github.com/us/crw</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -3550,14 +3324,18 @@
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>6.13</v>
+        <v>5.15</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr"/>
+          <t>AGPL-3.0</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3565,13 +3343,17 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P31" s="6" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>ai, ai-agents, crawler, data-extraction, docker, firecrawl-alternative, html-to-markdown, llm, markdown, mcp, mcp-server, rust</t>
+        </is>
+      </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
@@ -3580,7 +3362,7 @@
         </is>
       </c>
       <c r="S31" s="3" t="n">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>1</v>
@@ -3592,51 +3374,42 @@
       </c>
       <c r="V31" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="32" ht="150" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Marker-Inc-Korea/AutoRAG</t>
+          <t>Ramakm/ai-hands-on</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>5071</v>
+        <v>1443</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>36.3</v>
+        <v>34.2</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>AutoRAG：使代理能够找到计算机中的任何内容，使用频率越高越智能
-【原文】AutoRAG: Now your agent can find anything in your computer. It gets smarter if you are using it frequently.</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>RAG检索线</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
+          <t>A group of notebooks  and other files which can help you learn AI from scratch.</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Marker-Inc-Korea/AutoRAG</t>
+          <t>https://github.com/Ramakm/ai-hands-on</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -3645,16 +3418,16 @@
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>5.19</v>
+        <v>4.89</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3664,26 +3437,26 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>analysis, automl, benchmarking, document-parser, embeddings, evaluation, llm, llm-evaluation, llm-ops, open-source, ops, optimization</t>
+          <t>ai, artificial-intelligence, books, chatbot, machine-learning, math, ml, mlmodel, neural-network, ocr, pytorch, rag</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S32" s="3" t="n">
-        <v>978</v>
+        <v>295</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>1</v>
@@ -3695,51 +3468,42 @@
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="33" ht="150" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>jwangkun/hermes-agent-guide</t>
+          <t>thetahealth/mirobody</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>698</v>
+        <v>1307</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>33.7</v>
+        <v>31.6</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>提供 Hermes Agent 的系统化中文指南，涵盖从安装部署到高阶开发的完整知识图谱。
-【原文】Hermes Agent 是目前开源社区最具潜力的 AI Agent 框架之一。它继承了 OpenClaw 的优秀基因，在架构设计、记忆系统、技能生态和自动化能力上实现全面升级。但 Hermes 的文档分散在多个仓库和平台，缺乏一本系统性的中文指南。  本书填补的正是这个空白。全书 16 册、30 万+ 字，覆盖从安装部署到高阶开发、从个人玩赚到企业服务、从单 Agent 操控到多 Agent 编排的完整知识图谱。</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>架构参考/代码库</t>
-        </is>
-      </c>
+          <t>The AI-native health data engine — collect, translate, and reason over labs, wearables &amp; genomics.</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jwangkun/hermes-agent-guide</t>
+          <t>https://github.com/thetahealth/mirobody</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -3748,11 +3512,11 @@
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>4.81</v>
+        <v>4.51</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -3767,13 +3531,17 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>ai-agents, apple-health, digital-health, ehr, fhir, garmin, health, health-data, healthcare, healthcare-ai, lab-reports, loinc</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
@@ -3782,63 +3550,54 @@
         </is>
       </c>
       <c r="S33" s="3" t="n">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>知识图谱 in:name,description stars:&gt;200 pushed:&gt;2026-06-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="34" ht="150" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>agentscope-ai/ReMe</t>
+          <t>supercorp-ai/supergateway</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>3450</v>
+        <v>2844</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>32.3</v>
+        <v>31.4</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>为代理提供记忆管理工具包，帮助代理记住和改进
-【原文】ReMe: Memory Management Kit for Agents - Remember Me, Refine Me.</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>RAG检索线</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
+          <t>Run MCP stdio servers over SSE and SSE over stdio. AI gateway.</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/ReMe</t>
+          <t>https://github.com/supercorp-ai/supergateway</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -3847,16 +3606,16 @@
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>4.62</v>
+        <v>4.49</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3866,26 +3625,22 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>agent, ai-agents, dsh-plugin, memory, memoryscope, rag, reme</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr"/>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S34" s="3" t="n">
-        <v>746</v>
+        <v>633</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>1</v>
@@ -3897,27 +3652,26 @@
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="35" ht="150" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>study8677/repobrain</t>
+          <t>wanshuiyin/ARIS-in-AI-Offer</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>1325</v>
+        <v>512</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>31</v>
+        <v>30.1</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>为代码库提供智能助手，支持多种代码编辑器。
-【原文】🧠 RepoBrain (formerly Antigravity) — Give your repo a brain. ChatGPT for your codebase: works in Claude Code, Cursor, Codex, Windsurf &amp; more.
-【依据】为代码库提供智能助手，支持 Claude Code、Cursor 等。</t>
+          <t>提供双语 AI 面试技巧和简历信息检查工具
+【原文】Bilingual (中文+EN) ML / LLM / diffusion / agent interview cheat sheets for AI 秋招 — generated by ARIS /interview-cheatsheet, rendered by /render-html into single-file HTML, reads anywhere — plus a CV→DBLP-fact-checked academic homepage generator and hand-authored long-form blogs 🌱</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -3927,7 +3681,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3935,14 +3689,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/study8677/repobrain</t>
+          <t>https://github.com/wanshuiyin/ARIS-in-AI-Offer</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -3951,7 +3705,7 @@
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>4.43</v>
+        <v>4.3</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
@@ -3975,52 +3729,52 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>agents-sdk, ai-agent, claude-code, code-intelligence, code-search, codebase-qa, codex-cli, copilot, cursor, developer-tools, ide-plugin, knowledge-graph</t>
+          <t>ai-interview, aris, autumn-recruiting, cheatsheet, chinese, claude-code, deep-learning, diffusion, flow-matching, interview-prep, llm, machine-learning</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S35" s="3" t="n">
-        <v>299</v>
+        <v>119</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="36" ht="150" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>88lin/computer-repair-skill</t>
+          <t>vesoft-inc/nebula</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>220</v>
+        <v>12387</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>30.8</v>
+        <v>29.5</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>让 AI 代理成为跨平台电脑维修助手，提供诊断、清理、性能等维护工具
-【原文】让 Codex、Claude Code 等 AI Agent 成为你的跨平台电脑维修助手：64 个按需加载的 Playbook，覆盖诊断、清理、性能、网络与安全维护——C 盘爆满、电脑卡顿、流氓软件、应用迁移、数据恢复都能直接问；先取证、再计划，确认后修改。</t>
+          <t>分布式、快速的开源图数据库，支持横向扩展和高可用性
+【原文】A distributed, fast open-source graph database featuring horizontal scalability and high availability</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -4030,22 +3784,22 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
+          <t>可部署服务/代码库</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/88lin/computer-repair-skill</t>
+          <t>https://github.com/vesoft-inc/nebula</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4054,16 +3808,16 @@
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>4.4</v>
+        <v>4.21</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -4078,21 +3832,21 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, claude-code, codex, computer-diagnostics, linux, macos, windows</t>
+          <t>big-data, cpp, database, distributed, distributed-systems, graph, graph-database, graphdb, graphrag, hacktoberfest, knowledge-base, knowledge-graph</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S36" s="3" t="n">
-        <v>50</v>
+        <v>2940</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>1</v>
@@ -4104,51 +3858,42 @@
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="37" ht="150" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>skills-directory/skill-codex</t>
+          <t>Affitor/affiliate-skills</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>1434</v>
+        <v>661</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>30.6</v>
+        <v>25.1</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>将提示委托给Codex的Claude代码技能
-【原文】A claude code skill to delegate prompts to codex</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
+          <t>50 AI agent skills for affiliate marketing. Research trending content, write data-backed posts, generate infographics, build landing pages, deploy — full flywheel with social intelligence. Works with Claude Code, Pi, ChatGPT, Gemini, Cursor, Windsurf, any AI.</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/skills-directory/skill-codex</t>
+          <t>https://github.com/Affitor/affiliate-skills</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -4157,14 +3902,18 @@
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>4.37</v>
+        <v>3.59</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4172,26 +3921,26 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>claude, claude-code, codex</t>
+          <t>affiliate-marketing, agent-skills, ai, ai-agents, chatgpt, claude, claude-code, content-marketing, cursor, gemini, influencer, llm</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S37" s="3" t="n">
-        <v>328</v>
+        <v>184</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>1</v>
@@ -4203,37 +3952,36 @@
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="38" ht="150" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>kedro-org/kedro</t>
+          <t>gzxx-2025/aid-server</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>10995</v>
+        <v>194</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>28.4</v>
+        <v>23.4</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>用于生产就绪数据科学的工具箱，支持数据工程和科学管道。
-【原文】Kedro is a toolbox for production-ready data science. It uses software engineering best practices to help you create data engineering and data science pipelines that are reproducible, maintainable, and modular.
-【依据】生产就绪数据科学的工具箱。</t>
+          <t>一站式 AI 漫剧、漫画、动态漫、短剧与视频创作平台
+【原文】AID 是一套全开源、可私有化部署、可直接运营的一站式 AI 漫剧、AI 漫画、AI 动态漫、AI 短剧与 AI 视频创作平台。支持 AI 剧本创作、角色/道具/场景管理、AI 智能分镜、AI 文生图、AI 图生视频、AI 配音及项目管理，并提供多模型多厂商接入、任务调度、用户权限、积分计费、充值支付和运营后台。</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务/技能包</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -4241,14 +3989,14 @@
           <t>未知·需人工确认</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kedro-org/kedro</t>
+          <t>https://github.com/gzxx-2025/aid-server</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4257,7 +4005,7 @@
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>4.06</v>
+        <v>3.34</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -4266,7 +4014,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -4281,77 +4029,68 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, agentic-workflow, data-pipelines, hacktoberfest, kedro, machine-learning, machine-learning-engineering, mlops, python</t>
+          <t>ai-animation, ai-anime, ai-comic, ai-drama, ai-manga, ai-short-drama, ai-storyboard, ai-storytelling, aigc, animated-comic, character-consistency, comic-generator</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>2019-04-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S38" s="3" t="n">
-        <v>2706</v>
+        <v>58</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="39" ht="150" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>fenixsoft/awesome-fenix</t>
+          <t>katanaml/sparrow</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>9445</v>
+        <v>5219</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>26.9</v>
+        <v>21.3</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>讨论如何构建可靠的大型分布式系统
-【原文】讨论如何构建一套可靠的大型分布式系统</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>架构参考</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
+          <t>Structured data extraction, instruction calling and agentic workflows with ML, LLM and Vision LLM</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/fenixsoft/awesome-fenix</t>
+          <t>https://github.com/katanaml/sparrow</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4360,16 +4099,16 @@
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>3.84</v>
+        <v>3.05</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -4379,17 +4118,17 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>architecture, cloud-native, istio, kubernetes, microservice, springcloud</t>
+          <t>agentic-ai, computer-vision, documentai, huggingface-transformers, llm, machinelearning, vllm</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>2019-12-23</t>
+          <t>2022-01-08</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
@@ -4398,7 +4137,7 @@
         </is>
       </c>
       <c r="S39" s="3" t="n">
-        <v>2457</v>
+        <v>1711</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>1</v>
@@ -4410,52 +4149,42 @@
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="40" ht="150" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>icereed/paperless-gpt</t>
+          <t>AdrienTorris/awesome-blazor</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2685</v>
+        <v>9377</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>26</v>
+        <v>21.2</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>使用LLM和LLM Vision (OCR)处理无纸化文档
-【原文】Use LLMs and LLM Vision (OCR) to handle paperless-ngx - Document Digitalization powered by AI
-【依据】Use LLMs and LLM Vision (OCR) to handle paperless-ngx - Document Digitalization powered by AI.</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>古籍OCR线</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
+          <t>Resources for Blazor, a .NET web framework using C#/Razor and HTML that runs in the browser with WebAssembly.</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/icereed/paperless-gpt</t>
+          <t>https://github.com/AdrienTorris/awesome-blazor</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4464,18 +4193,14 @@
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>3.72</v>
+        <v>3.03</v>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>Go</t>
-        </is>
-      </c>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4483,26 +4208,26 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>ai, chatgpt, llm, mistral, ocr, ollama, paperless, paperless-ngx</t>
+          <t>asp-net-core, aspnetcore, awesome, awesome-list, blazor, blazor-application, blazor-component, blazor-crud, blazor-interop, blazor-master, blazor-port, blazor-sample</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2018-03-29</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S40" s="3" t="n">
-        <v>721</v>
+        <v>3092</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>1</v>
@@ -4514,51 +4239,42 @@
       </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="41" ht="150" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>samchon/typia</t>
+          <t>SenmuuuuW/universal-diagnostic-tutor-skill</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>5905</v>
+        <v>208</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>25.7</v>
+        <v>18</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>提供快速/简单的运行时验证器和序列化器。
-【原文】Super-fast/easy runtime validators and serializers via transformation</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
+          <t>One diagnosis-first AI tutor for STEM, AI/CS, and beyond — no mode or command menu. It decides the next useful teaching step, checks understanding, and builds mastery.</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/samchon/typia</t>
+          <t>https://github.com/SenmuuuuW/universal-diagnostic-tutor-skill</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -4567,18 +4283,14 @@
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>3.67</v>
+        <v>2.57</v>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>Go</t>
-        </is>
-      </c>
+      <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4586,26 +4298,26 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, ajv, checker, fast, generator, hacktoberfest, json, json-schema, llm-function-calling, openapi, protobuf, random</t>
+          <t>ai-education, ai-tutor, codex, codex-skill, computer-science, diagnostics, learning-assistant, math, skill, stem, tutoring</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>2022-04-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S41" s="3" t="n">
-        <v>1610</v>
+        <v>81</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>1</v>
@@ -4617,51 +4329,42 @@
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="42" ht="150" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>zamesin/Next-Move-Theory-Canon-and-Skills</t>
+          <t>modelcontextprotocol/ext-skills</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>370</v>
+        <v>536</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>24.6</v>
+        <v>16.6</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Claude Code 技能，用于产品市场研究、价值主张、PRD 和上市策略
-【原文】Claude Code skills for product market research, value props, PRDs, and go-to-market — plus the open Next Move Theory (based on AJTBD) canon and a product advisor you can /ask-nmt</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
+          <t>Experimental exploration of skills discovery and distribution through MCP primitives. Maintained by the Skills Over MCP Working Group.</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zamesin/Next-Move-Theory-Canon-and-Skills</t>
+          <t>https://github.com/modelcontextprotocol/ext-skills</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -4670,16 +4373,16 @@
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>3.52</v>
+        <v>2.37</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>PowerShell</t>
+          <t>MDX</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -4689,22 +4392,22 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S42" s="3" t="n">
-        <v>105</v>
+        <v>226</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>1</v>
@@ -4716,51 +4419,42 @@
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="43" ht="150" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>yzhao062/pyod</t>
+          <t>lignertys/reddit-research-skills</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>10001</v>
+        <v>532</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>21.4</v>
+        <v>16.2</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>提供跨多种数据类型的异常检测库
-【原文】A Python library for anomaly detection across tabular, time series, graph, text, image, and audio data. 60+ detectors, benchmark-backed ADEngine orchestration, and an agentic workflow for AI agents.</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
+          <t>Reddit research skills for Claude Code and AI agents</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yzhao062/pyod</t>
+          <t>https://github.com/lignertys/reddit-research-skills</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -4769,11 +4463,11 @@
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>3.06</v>
+        <v>2.32</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>BSD-2-Clause</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -4788,26 +4482,26 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, anomaly-detection, data-mining, data-science, deep-learning, foundation-models, fraud-detection, graph-anomaly-detection, image-anomaly-detection, machine-learning, multimodal, nlp-anomaly-detection</t>
+          <t>agent-skills, claude-code, claude-skill, gemini-cli-extension, skills</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>2017-10-03</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S43" s="3" t="n">
-        <v>3268</v>
+        <v>229</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>1</v>
@@ -4819,51 +4513,42 @@
       </c>
       <c r="V43" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-15</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="44" ht="150" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>lllllllama/RigorPilot-Skills</t>
+          <t>kitspace/awesome-electronics</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>487</v>
+        <v>8120</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>20.3</v>
+        <v>15.3</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>研究复现技能，带有执行限制、可审计证据和字节保留的 README 注释
-【原文】README-first research reproduction skills with bounded execution, auditable evidence, and byte-preserving README annotations.</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
+          <t>A curated list of awesome resources for Electronic Engineers and hobbyists</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lllllllama/RigorPilot-Skills</t>
+          <t>https://github.com/kitspace/awesome-electronics</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -4872,18 +4557,14 @@
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>2.9</v>
+        <v>2.19</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4891,26 +4572,26 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, deep-learning, reproducibility, research-tools</t>
+          <t>altium, awesome, eagle, electronics, gerber, hardware, kicad, pcb</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2016-07-26</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S44" s="3" t="n">
-        <v>168</v>
+        <v>3703</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>1</v>
@@ -4922,51 +4603,42 @@
       </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="45" ht="150" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>shiyutim/tickets</t>
+          <t>pymupdf/PyMuPDF</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>3278</v>
+        <v>10714</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>19.2</v>
+        <v>14.7</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>为大麦网和 B 站会员购演唱会提供抢票软件，监控余票并支持微信通知。
-【原文】大麦网(大麦）、bilibili(B站)会员购 演唱会调用接口的抢票软件，余票监控，微信通知。</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务/代码库</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
+          <t>PyMuPDF is a high performance Python library for data extraction, analysis, conversion &amp; manipulation of PDF (and other) documents.</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/shiyutim/tickets</t>
+          <t>https://github.com/pymupdf/PyMuPDF</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -4975,16 +4647,16 @@
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -4994,83 +4666,73 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>bilibili, damai, rust, tauri, vue</t>
+          <t>data-science, epub, extract-data, font, mupdf, ocr, pdf, pdf-documents, pymupdf, python, table-extraction, tesseract</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2012-10-06</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S45" s="3" t="n">
-        <v>1198</v>
+        <v>5092</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V45" s="6" t="inlineStr">
         <is>
-          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-06-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="46" ht="150" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Physton/sd-webui-prompt-all-in-one</t>
+          <t>InternScience/GraphGen</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>3233</v>
+        <v>1220</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>18.5</v>
+        <v>13.9</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>增强 sd-webui 的提示输入框体验，提供自动翻译功能。
-【原文】This is an extension based on sd-webui, aimed at improving the user experience of the prompt/negative prompt input box. It has a more intuitive and powerful input interface function, and provides automatic translation, history record, and bookmarking functions.    这是一个基于 sd-webui 的扩展，旨在提高提示词/反向提示词输入框的使用体验。它拥有更直观、强大的输入界面功能，它提供了自动翻译、历史记录和收藏等功能。
-【依据】sd-webui 的扩展，提供更直观的输入界面功能。</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
+          <t>GraphGen: Enhancing Supervised Fine-Tuning for LLMs with Knowledge-Driven Synthetic Data Generation</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Physton/sd-webui-prompt-all-in-one</t>
+          <t>https://github.com/InternScience/GraphGen</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5079,11 +4741,11 @@
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>2.64</v>
+        <v>1.98</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5098,78 +4760,73 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P46" s="6" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>ai4science, data-generation, data-synthesis, graphgen, knowledge-graph, llama-factory, llm, llm-training, pretrain, pretraining, qa, question-answering</t>
+        </is>
+      </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1225</v>
+        <v>615</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V46" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-16</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="47" ht="150" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>software-mansion/react-native-executorch</t>
+          <t>deepdoctection/deepdoctection</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>1734</v>
+        <v>3258</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>17.4</v>
+        <v>13.1</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>为 React Native 提供高性能、隐私优先的设备端 AI 推理库
-【原文】High-performance, privacy-first on-device AI inference library for React Native, powered by PyTorch's ExecuTorch runtime</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
+          <t>A Repo For Document AI</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/software-mansion/react-native-executorch</t>
+          <t>https://github.com/deepdoctection/deepdoctection</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -5178,16 +4835,16 @@
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>2.48</v>
+        <v>1.87</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -5197,26 +4854,26 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>ai, computer-vision, executorch, llm-inference, mobile-inference, object-detection, ocr, on-device-ai, react-native-ai, speech-to-text, text-to-speech, vlm</t>
+          <t>document-ai, document-image-analysis, document-layout-analysis, document-parser, document-understanding, layoutlm, nlp, ocr, publaynet, pubtabnet, python, pytorch</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S47" s="3" t="n">
-        <v>698</v>
+        <v>1741</v>
       </c>
       <c r="T47" s="3" t="n">
         <v>1</v>
@@ -5228,51 +4885,42 @@
       </c>
       <c r="V47" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="48" ht="150" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TheJoeFin/Text-Grab</t>
+          <t>jkf87/hwpx-skill</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>5003</v>
+        <v>249</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>16.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>提供Windows平台上的OCR工具
-【原文】Use OCR in Windows quickly and easily with Text Grab. With optional background process and notifications.</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>古籍OCR线</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
+          <t>AI 에이전트용 HWPX(.hwpx) 문서 생성 스킬 - 한컴오피스 한글 문서를 마크다운/텍스트/URL에서 자동 생성</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/TheJoeFin/Text-Grab</t>
+          <t>https://github.com/jkf87/hwpx-skill</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5281,16 +4929,16 @@
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>2.37</v>
+        <v>1.39</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -5300,26 +4948,22 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>dotnet, local-ai, msix, ocr, window-10, windows, windows-11, wpf</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P48" s="6" t="inlineStr"/>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S48" s="3" t="n">
-        <v>2113</v>
+        <v>179</v>
       </c>
       <c r="T48" s="3" t="n">
         <v>1</v>
@@ -5331,51 +4975,42 @@
       </c>
       <c r="V48" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="49" ht="150" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>kotaro-kinoshita/yomitoku</t>
+          <t>toolleeo/awesome-cli-apps-in-a-csv</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>1591</v>
+        <v>2616</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>16.3</v>
+        <v>5.5</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>提供针对日语文档的AI图像分析包
-【原文】YomiTokuはAIを活用した日本語文書解析エンジンを提供するPythonパッケージです。 Yomitoku is an AI-powered document image analysis package designed specifically for the Japanese language.</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>古籍OCR线</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
+          <t>The largest Awesome Curated list of command line programs (CLI/TUI) with source data organized into CSV files</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
           <t>无许可·不可用</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kotaro-kinoshita/yomitoku</t>
+          <t>https://github.com/toolleeo/awesome-cli-apps-in-a-csv</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5384,7 +5019,7 @@
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>2.33</v>
+        <v>0.78</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
@@ -5403,17 +5038,17 @@
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>deep-learning, layout-analysis, ocr, python, pytorch</t>
+          <t>awesome, awesome-list, cli, cli-apps, command-line, command-line-tool, linux, linux-command, resources, terminal-based, tui</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
@@ -5422,7 +5057,7 @@
         </is>
       </c>
       <c r="S49" s="3" t="n">
-        <v>684</v>
+        <v>3373</v>
       </c>
       <c r="T49" s="3" t="n">
         <v>1</v>
@@ -5434,26 +5069,26 @@
       </c>
       <c r="V49" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="50" ht="150" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>getopenpost/openpost</t>
+          <t>frutik/awesome-search</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>404</v>
+        <v>1562</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>创建、调整、安排和跟踪社交媒体帖子，支持自托管和托管选项。
-【原文】Create, adapt, schedule, and track social posts. Open-source, hosted or self-hosted.</t>
+          <t>关于搜索和其优点的资源集合，包括电商搜索
+【原文】Awesome Search - this is all about the (e-commerce, but not only) search and its awesomeness</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -5463,22 +5098,22 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/getopenpost/openpost</t>
+          <t>https://github.com/frutik/awesome-search</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5487,16 +5122,16 @@
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>2.28</v>
+        <v>0.61</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -5511,77 +5146,68 @@
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>automation, buffer-alternative, content-creation, cross-posting, golang, mcp-server, self-hosted, single-binary, social-media, social-media-automation, social-media-management, social-media-scheduler</t>
+          <t>autocomplete-suggestions, ecommerce-search, evaluating-search, knowledge-graph, learning-to-rank, natural-language-processing, query-understanding, ranking, relevance-algorithms, relevant-search, search, search-engine</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2019-09-09</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S50" s="3" t="n">
-        <v>177</v>
+        <v>2563</v>
       </c>
       <c r="T50" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U50" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>topic:social-media-automation stars:&gt;300 pushed:&gt;2026-06-16</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="51" ht="150" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>brootware/awesome-cyber-security-university</t>
+          <t>kmonkeyhead/MORT</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>3523</v>
+        <v>1753</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>15.1</v>
+        <v>3.3</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>提供网络安全大学课程和资源的列表
-【原文】🎓 Because Education should be free. Contributions welcome! 🕵️</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>数据集</t>
-        </is>
-      </c>
+          <t>MORT 번역기 프로젝트 - Real-time game translator with OCR</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/brootware/awesome-cyber-security-university</t>
+          <t>https://github.com/kmonkeyhead/MORT</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -5590,14 +5216,18 @@
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>2.16</v>
+        <v>0.47</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -5605,26 +5235,26 @@
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, courses, curriculum, cyber-security, cybersecurity, education, educational-project, free, hacking, learning-by-doing</t>
+          <t>auto-translation, game, game-translation, image-to-text, ocr, tesseract-ocr, translate, translation</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
+          <t>2016-06-09</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S51" s="3" t="n">
-        <v>1628</v>
+        <v>3750</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>1</v>
@@ -5636,52 +5266,42 @@
       </c>
       <c r="V51" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="52" ht="150" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>robertknight/ocrs</t>
+          <t>google/schema-dts</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>1885</v>
+        <v>1240</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>13.4</v>
+        <v>3.1</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>提供OCR的Rust库和CLI工具
-【原文】Rust library and CLI tool for OCR (extracting text from images)
-【依据】Rust library and CLI tool for OCR (extracting text from images).</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>古籍OCR线</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
+          <t>JSON-LD TypeScript types for Schema.org vocabulary</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/robertknight/ocrs</t>
+          <t>https://github.com/google/schema-dts</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -5690,7 +5310,7 @@
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>1.91</v>
+        <v>0.44</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
@@ -5699,7 +5319,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -5709,26 +5329,26 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>computer-vision, machine-learning, ocr</t>
+          <t>json-ld, knowledge-graph, linked-data, ontology, schema-org, schemaorg, semantic-web, typescript, typescript-definitions</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2018-11-29</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="S52" s="3" t="n">
-        <v>986</v>
+        <v>2847</v>
       </c>
       <c r="T52" s="3" t="n">
         <v>1</v>
@@ -5740,51 +5360,42 @@
       </c>
       <c r="V52" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-16</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="53" ht="150" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>vespa-engine/vespa</t>
+          <t>itsmostafa/aws-agent-skills</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>7082</v>
+        <v>1155</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>13.2</v>
+        <v>3</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>AI 搜索平台，提供搜索、推荐等功能
-【原文】The AI search platform</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池/RAG检索线</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
+          <t>AWS Skills for Agents</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vespa-engine/vespa</t>
+          <t>https://github.com/itsmostafa/aws-agent-skills</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -5793,16 +5404,16 @@
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>1.89</v>
+        <v>0.43</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -5812,26 +5423,26 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>ai, big-data, java, machine-learning, rag, search, search-engine, server, serving-recommendation, tensor, vector, vector-database</t>
+          <t>agent-skills, agentic-ai, aws, claude-code, claude-skills, codex, coding-agents</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>2016-06-03</t>
+          <t>2019-05-18</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S53" s="3" t="n">
-        <v>3755</v>
+        <v>2677</v>
       </c>
       <c r="T53" s="3" t="n">
         <v>1</v>
@@ -5843,927 +5454,12 @@
       </c>
       <c r="V53" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="150" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>wmariuss/awesome-devops</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>4357</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>curated list of awesome DevOps platforms, tools, practices and resources</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/wmariuss/awesome-devops</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N54" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, collections, development, devops, production, productivity, resources, sre, tools</t>
-        </is>
-      </c>
-      <c r="Q54" s="3" t="inlineStr">
-        <is>
-          <t>2019-11-19</t>
-        </is>
-      </c>
-      <c r="R54" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="S54" s="3" t="n">
-        <v>2491</v>
-      </c>
-      <c r="T54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V54" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="150" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>qmonnet/awesome-ebpf</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>5163</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>eBPF相关项目列表
-【原文】A curated list of awesome projects related to eBPF.</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/qmonnet/awesome-ebpf</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M55" s="3" t="inlineStr"/>
-      <c r="N55" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, bcc, bpf, ebpf, xdp</t>
-        </is>
-      </c>
-      <c r="Q55" s="3" t="inlineStr">
-        <is>
-          <t>2017-11-05</t>
-        </is>
-      </c>
-      <c r="R55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="S55" s="3" t="n">
-        <v>3235</v>
-      </c>
-      <c r="T55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V55" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="150" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>apecloud/ApeRAG</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>1315</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>提供生产就绪的 GraphRAG，支持多模态索引、AI 代理、MCP 支持和可扩展的 K8s 部署。
-【原文】ApeRAG: Production-ready GraphRAG with multi-modal indexing, AI agents, MCP support, and scalable K8s deployment</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池/未归类</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务/代码库</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/apecloud/ApeRAG</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N56" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>agents, context-engineering, graphrag, knowledge-graph, mcp</t>
-        </is>
-      </c>
-      <c r="Q56" s="3" t="inlineStr">
-        <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="R56" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="S56" s="3" t="n">
-        <v>1182</v>
-      </c>
-      <c r="T56" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V56" s="6" t="inlineStr">
-        <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="150" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>awesome-mlss/awesome-mlss</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>3033</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>机器学习夏季学校的指南
-【原文】🤖 Machine Learning Summer School Guide</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/awesome-mlss/awesome-mlss</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
-      <c r="N57" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>artificial-intelligence, deep-learning, machine-learning, reinforcement-learning, summer-school, summer-schools</t>
-        </is>
-      </c>
-      <c r="Q57" s="3" t="inlineStr">
-        <is>
-          <t>2018-12-01</t>
-        </is>
-      </c>
-      <c r="R57" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="S57" s="3" t="n">
-        <v>2844</v>
-      </c>
-      <c r="T57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V57" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="150" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>yvoronoy/awesome-english</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>4010</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>英语学习资源集合
-【原文】A collection of awesome study resources for learners of English.</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/yvoronoy/awesome-english</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, english, english-resources, esl, learn-english</t>
-        </is>
-      </c>
-      <c r="Q58" s="3" t="inlineStr">
-        <is>
-          <t>2016-05-07</t>
-        </is>
-      </c>
-      <c r="R58" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="S58" s="3" t="n">
-        <v>3782</v>
-      </c>
-      <c r="T58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U58" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V58" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="150" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>naodeng/awesome-qa-skills</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="n">
-        <v>211</v>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>开源 AI-native 质量工程技能系统，帮助团队提升软件质量
-【原文】Awesome QA Skills is an open-source AI-native Quality Engineering skill system that helps engineering teams reason about, design, execute, evaluate, and continuously improve software quality across the entire SDLC.</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/naodeng/awesome-qa-skills</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N59" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, ai-qa, ai-skills, ai-testing, ai-tools, awesome-list, prompt-engineering, qa, qa-skills, skills</t>
-        </is>
-      </c>
-      <c r="Q59" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="R59" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="S59" s="3" t="n">
-        <v>222</v>
-      </c>
-      <c r="T59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V59" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="150" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>tiddly-gittly/TidGi-Desktop</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>基于 Tiddlywiki 的知识管理桌面应用，支持 REST API 和 Anki 连接。
-【原文】TidGi is an privacy-in-mind, automated, auto-git-backup, freely-deployed knowledge management Desktop note app, based on Tiddlywiki, with REST API for web-clipping and Anki connect. 「 太记 」是一个基于「 太微 TiddlyWiki 」的知识管理桌面应用，能保护隐私内容、高级自动化、自动Git云备份、部署为博客，且可通过RESTAPI与Anki等应用连接。（迭代开发中欢迎试用，开发进度见下方链接）(Under active development, see website below for details)
-【依据】基于 Tiddlywiki，提供知识管理和笔记功能。</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/tiddly-gittly/TidGi-Desktop</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>MPL-2.0</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="N60" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>all-in-one, anki, backlinks, electron, evernote, knowledge-graph, knowledge-management, linux, local-first, macos, note-taking, notebook</t>
-        </is>
-      </c>
-      <c r="Q60" s="3" t="inlineStr">
-        <is>
-          <t>2020-06-12</t>
-        </is>
-      </c>
-      <c r="R60" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="S60" s="3" t="n">
-        <v>2285</v>
-      </c>
-      <c r="T60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U60" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V60" s="6" t="inlineStr">
-        <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="150" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>AI-Efficiency/Awesome-Model-Quantization</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="n">
-        <v>2440</v>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>模型量化相关论文、基准、调查和工具的 curated collection
-【原文】A curated collection of papers, benchmarks, surveys, and tools for model quantization, covering low-bit networks, LLMs, multimodal and generative models, vector and lattice quantization, and efficient deployment.</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/AI-Efficiency/Awesome-Model-Quantization</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="inlineStr"/>
-      <c r="N61" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, awesome-lists, binarization, binary-neural-networks, data-free-quantization, diffusion-models, efficient-inference, kv-cache, kv-cache-quantization, large-language-models, large-language-models-llms</t>
-        </is>
-      </c>
-      <c r="Q61" s="3" t="inlineStr">
-        <is>
-          <t>2018-10-18</t>
-        </is>
-      </c>
-      <c r="R61" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>2888</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V61" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="150" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>totogo/awesome-knowledge-graph</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>1889</v>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>提供知识图谱相关学习材料、数据库、工具和其他资源的精选列表。
-【原文】A curated list of Knowledge Graph related learning materials, databases, tools and other resources</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>数据集/代码库</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/totogo/awesome-knowledge-graph</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="inlineStr"/>
-      <c r="N62" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>awesome-list, graph, graph-database, knowledge-graph, nlp</t>
-        </is>
-      </c>
-      <c r="Q62" s="3" t="inlineStr">
-        <is>
-          <t>2019-02-03</t>
-        </is>
-      </c>
-      <c r="R62" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="S62" s="3" t="n">
-        <v>2780</v>
-      </c>
-      <c r="T62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U62" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V62" s="6" t="inlineStr">
-        <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-15</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V62"/>
+  <autoFilter ref="A2:V53"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -113,10 +113,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-15 · 共 51 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-16 · 共 38 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,44 +633,44 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>qingjian-team/qingjian</t>
+          <t>youngyangyang04/llm-master</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>773</v>
+        <v>505</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>676.3</v>
+        <v>883.8</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Rust 编写的拼音输入法，支持多语言学习
-【原文】青简 Qingjian：用 Rust 写的拼音输入法，候选词旁多一条正在学的语言的译词</t>
+          <t>提供大模型（LLM）全栈学习路线和中文教程，涵盖Prompt Engineering、RAG、AI Agent等。
+【原文】大模型（LLM）全栈学习路线与中文教程🔥：覆盖 Prompt Engineering、RAG、AI Agent、MCP、微调、模型部署、Transformer、AI 编程与大厂面试，从入门到生产实践。</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
+          <t>数据集/代码库</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/qingjian-team/qingjian</t>
+          <t>https://github.com/youngyangyang04/llm-master</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,18 +679,14 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>96.62</v>
+        <v>126.25</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Rust</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -703,21 +699,21 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>chinese, chinese-input-method, english-learning, ime, input-method, japanese-learning, language-learning, language-model, macos, offline, pinyin, rust</t>
+          <t>agent, large-language-models, llm, llm-learning, llm-tutorial, rag</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -729,42 +725,51 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-16</t>
+          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>StarTrail-org/PixelRAG</t>
+          <t>hypit-ai/hypit</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9959</v>
+        <v>4310</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>639.6</v>
+        <v>615.7</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2606.28344. The end of web parsing. The beginning of scalable pixel-native search. link: https://pixelrag.ai/</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+          <t>使用AI代理克隆病毒视频，包括人脸、文字和视频片段替换，批量生成变体视频。
+【原文】Clone any viral video with AI agents. Not just a script, the whole workflow: swap the face, the words, the B-roll, ship 100 variants in one command, and get your 100M views.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/StarTrail-org/PixelRAG</t>
+          <t>https://github.com/hypit-ai/hypit</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -773,16 +778,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>91.37</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -792,29 +797,29 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agent, ai, memory, multimodal, rag, search, searchengine, vision, vlm</t>
+          <t>agentic-ai, ai, ai-agents, ai-video, compiler, dsl, ffmpeg, generative-ai, llm, markup-language, modular, monorepo</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -823,42 +828,51 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
+          <t>topic:video-automation stars:&gt;2000 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>opendataloader-project/opendataloader-pdf</t>
+          <t>patchy631/ai-engineering-hub</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>29183</v>
+        <v>37557</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>416.9</v>
+        <v>378.3</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>PDF Parser for AI-ready data. Automate PDF accessibility. Open-source.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+          <t>关于 LLM、RAG 和 AI 代理应用的深入教程
+【原文】In-depth tutorials on LLMs, RAGs and real-world AI agent applications.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>RAG检索线</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>架构参考</t>
+        </is>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/opendataloader-project/opendataloader-pdf</t>
+          <t>https://github.com/patchy631/ai-engineering-hub</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -867,16 +881,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>59.56</v>
+        <v>54.04</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -886,29 +900,29 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>a11y, accessibility, ai, bounding-box, document-parsing, eaa, html, json, markdown, ocr, ocr-recognition, pdf</t>
+          <t>agents, ai, llms, machine-learning, mcp, rag</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>490</v>
+        <v>695</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
@@ -917,42 +931,51 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>mem0ai/mem0</t>
+          <t>yjz211/vivid-figures-skill</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>65303</v>
+        <v>245</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>386.4</v>
+        <v>285.8</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>The Memory Layer for AI Agents - Drop-in memory infrastructure for AI agents and apps. Context that persists. Built for production.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
+          <t>提供AI生成科研图表的配方
+【原文】让 AI 用你的数据生成科研图表：108 个配方，鲜艳与稳重两种风格，多套配色，交付图片与源码。仅限个人非商业使用。</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mem0ai/mem0</t>
+          <t>https://github.com/yjz211/vivid-figures-skill</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -961,16 +984,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>55.2</v>
+        <v>40.83</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -980,26 +1003,22 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>agentic-memory, agentic-memory-system, agents, ai, ai-agents, chatgpt, genai, llm, long-term-memory, memory, memory-management, python</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1183</v>
+        <v>6</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1011,42 +1030,51 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>cloudflare/security-audit-skill</t>
+          <t>NirDiamant/RAG_Techniques</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4152</v>
+        <v>29503</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>326.6</v>
+        <v>259.8</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>A coding-agent skill for multi-phase security audits with independently verified, machine-readable findings</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
+          <t>展示RAG系统的各种高级技术
+【原文】This repository showcases various advanced techniques for Retrieval-Augmented Generation (RAG) systems. Each technique has a detailed notebook tutorial.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>代码库/架构参考</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cloudflare/security-audit-skill</t>
+          <t>https://github.com/NirDiamant/RAG_Techniques</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1055,16 +1083,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>46.65</v>
+        <v>37.11</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1074,25 +1102,29 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>agentic-rag, ai, embeddings, generative-ai, gpt, langchain, llama-index, llm, llms, machine-learning, nlp, openai</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>89</v>
+        <v>795</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
@@ -1101,42 +1133,51 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>elayadesign/ai-design-skills</t>
+          <t>muxuuu/serenity-skill</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2229</v>
+        <v>3993</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>325.1</v>
+        <v>207.1</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>(无描述)</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
+          <t>用于供应链瓶颈股票研究的 Serenity 风格智能体技能
+【原文】Serenity-inspired Agent Skill for supply-chain bottleneck stock research</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/elayadesign/ai-design-skills</t>
+          <t>https://github.com/muxuuu/serenity-skill</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1145,14 +1186,18 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>46.44</v>
+        <v>29.58</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1160,22 +1205,26 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, ai-agents, claude-code, codex, investment-research, stock-research, supply-chain</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1187,42 +1236,52 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>skills in:name stars:&gt;500 pushed:&gt;2026-06-17</t>
+          <t>skill in:name stars:&gt;500 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>getzep/graphiti</t>
+          <t>tesseract-ocr/tesseract</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>30880</v>
+        <v>76507</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>281.5</v>
+        <v>121.2</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Build Real-Time Knowledge Graphs for AI Agents</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+          <t>开源的 OCR 引擎仓库
+【原文】Tesseract Open Source OCR Engine (main repository)
+【依据】topics: ocr, ocr-engine</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>古籍OCR线</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/getzep/graphiti</t>
+          <t>https://github.com/tesseract-ocr/tesseract</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1231,7 +1290,7 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>40.21</v>
+        <v>17.32</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1240,7 +1299,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1250,17 +1309,17 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>agents, graph, llms, rag</t>
+          <t>hacktoberfest, lstm, machine-learning, ocr, ocr-engine, tesseract, tesseract-ocr</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2014-08-12</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1269,7 +1328,7 @@
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>768</v>
+        <v>4418</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
@@ -1281,42 +1340,51 @@
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ykdojo/claude-code-tips</t>
+          <t>kunpengtalk/OmniStudio</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>10087</v>
+        <v>108</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>242.6</v>
+        <v>108</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>45+ tips for getting the most out of Claude Code, from basics to advanced - includes a custom status line script and Claude Code running itself in a container. Also includes the dx plugin: skills for everyday dev workflows.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
+          <t>提供本地大模型一体化桌面工作台，支持模型市集下载、推理管理、对话、语音合成等。
+【原文】OmniStudio 是一个本地大模型一体化桌面工作台，集模型市集下载、llama.cpp/vLLM/SGLang 三引擎推理管理，以及对话、语音合成、ASR语音识别、图片生成、视频生成、OCR 等多种大模型应用于一体，全程本地优先。</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ykdojo/claude-code-tips</t>
+          <t>https://github.com/kunpengtalk/OmniStudio</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1325,16 +1393,16 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>34.66</v>
+        <v>15.43</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1344,73 +1412,78 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>agentic, agentic-ai, agentic-coding, agentic-workflow, ai, claude, claude-ai, claude-code, cli, developer-tools, productivity, tips-and-tricks</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>291</v>
+        <v>7</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-16</t>
+          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>zai-org/GLM-5</t>
+          <t>LING71671/open-reverselab</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>7185</v>
+        <v>1137</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>230.7</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>GLM-5: From Vibe Coding to Agentic Engineering</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
+          <t>提供开源AI逆向工程平台和MCP服务器
+【原文】Open-source AI reverse-engineering agent platform and MCP server for Ghidra, Frida, x64dbg and Rizin — automated PE/APK/binary analysis, CTF and malware research, with 100+ MCP tools and a 194-article runnable knowledge base.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池/未归类</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务/代码库/可部署服务</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zai-org/GLM-5</t>
+          <t>https://github.com/LING71671/open-reverselab</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1419,14 +1492,18 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>32.96</v>
+        <v>12.49</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr"/>
+          <t>GPL-3.0</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1434,26 +1511,26 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, coding, llm, long-horizon</t>
+          <t>ai-agent, ai-reverse-engineering, android-reverse-engineering, binary-analysis, binary-reverse-engineering, claude-code, codex, ctf, frida, ghidra, ghidra-mcp, malware-analysis</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1465,36 +1542,36 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-16</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>TencentCloud/Octop</t>
+          <t>ATH-MaaS/ComfyUI-Copilot</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2208</v>
+        <v>5516</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>224</v>
+        <v>66.7</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>多用户、多代理的自托管 AI 助手
-【原文】A smarter, self-hosted AI assistant — multi-user, multi-agent.</t>
+          <t>为 ComfyUI 设计的 AI 辅助节点，增强工作流程自动化
+【原文】An AI-powered custom node for ComfyUI designed to enhance workflow automation and provide intelligent assistance</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1502,14 +1579,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/TencentCloud/Octop</t>
+          <t>https://github.com/ATH-MaaS/ComfyUI-Copilot</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1518,7 +1595,7 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>32</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -1527,7 +1604,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1542,68 +1619,78 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, ai, ai-agent, ai-agents, local-first, long-term-memory</t>
+          <t>agent, ai, comfy-ui, comfyui, comfyui-nodes, copilot, deepseek, deepseek-v3, flux, gpt-4, llm-agent, rag</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>69</v>
+        <v>579</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-16</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>FlowElement-xinliuyuansu/m_flow</t>
+          <t>umlx5h/LLPlayer</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>4499</v>
+        <v>4143</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>187.5</v>
+        <v>48.9</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>A bio-inspired cognitive memory engine — a new paradigm for Graph RAG.</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
+          <t>语言学习用媒体播放器，具有AI字幕和翻译功能
+【原文】The media player for language learning, with dual subtitles, AI-generated subtitles, real-time translation, and more!
+【依据】topics: video, video-player, ocr</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/FlowElement-xinliuyuansu/m_flow</t>
+          <t>https://github.com/umlx5h/LLPlayer</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1612,16 +1699,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>26.78</v>
+        <v>6.99</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1631,26 +1718,26 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>agent-memory, agentic-ai, ai-reasoning, episodic-memory, graph-database, knowledge-graph, llm, long-term-memory, mcp, memory-engine, python, rag</t>
+          <t>asr, csharp, flyleaf, language-learning, llm, media-player, ocr, ollama, player, video, video-player, whisper</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>168</v>
+        <v>593</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1662,42 +1749,51 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>SteveTheKiller/KillerPDF</t>
+          <t>Future-House/paper-qa</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>3851</v>
+        <v>9203</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>177.4</v>
+        <v>48.9</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Free and open-source PDF editor for Windows with a built-in PDF 2.0 engine. View, annotate, OCR, merge, split, crop, rotate, compare, edit text, draw, sign, fill forms, print, flatten, and open password-protected PDFs without a subscription.</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
+          <t>提供科学文档问答的RAG系统
+【原文】High accuracy RAG for answering questions from scientific documents with citations</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>RAG检索线</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SteveTheKiller/KillerPDF</t>
+          <t>https://github.com/Future-House/paper-qa</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1706,16 +1802,16 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>25.34</v>
+        <v>6.98</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1725,17 +1821,17 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>csharp, dotnet, dotnet-core, fast, gplv3, ocr, open-source, opensource, pdf, pdf-2-0, pdf-annotator, pdf-editor</t>
+          <t>ai, rag, science, search</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2023-02-05</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
@@ -1744,7 +1840,7 @@
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>152</v>
+        <v>1319</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1756,42 +1852,52 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>conorbronsdon/avoid-ai-writing</t>
+          <t>alibaba-flyai/flyai-skill</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>4383</v>
+        <v>1140</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>159</v>
+        <v>44.1</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Skill that audits and rewrites content to remove AI writing patterns. Use it with your favorite agents including Claude Code, OpenClaw, Codex, and Hermes.</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
+          <t>飞智AI代理技能
+【原文】fly ai agent skill
+【依据】topics: -</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/conorbronsdon/avoid-ai-writing</t>
+          <t>https://github.com/alibaba-flyai/flyai-skill</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1800,18 +1906,14 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>22.71</v>
+        <v>6.3</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
+      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1819,26 +1921,22 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>ai-writing, claude, claude-code, llm, prompt-engineering, skill, writing</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr"/>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1850,42 +1948,51 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>agent skill in:name,description stars:&gt;300 pushed:&gt;2026-06-17</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>CortexReach/memory-lancedb-pro</t>
+          <t>huangkiki/dailypaper-skills</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>4458</v>
+        <v>1232</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>153.7</v>
+        <v>42.7</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Enhanced LanceDB memory plugin for OpenClaw — Hybrid Retrieval (Vector + BM25), Cross-Encoder Rerank, Multi-Scope Isolation, Management CLI</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>用Agent skills打造论文流水线
+【原文】用Agent skills打造我的论文流水线</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/CortexReach/memory-lancedb-pro</t>
+          <t>https://github.com/huangkiki/dailypaper-skills</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1894,16 +2001,16 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>21.96</v>
+        <v>6.1</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1913,26 +2020,22 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>lancedb, memory, openclaw, openclaw-agent, openclaw-plugin, rag</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -1944,36 +2047,37 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>rlaope/oh-my-hermes</t>
+          <t>aiptimizer/TurboOCR</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2186</v>
+        <v>1075</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>147.1</v>
+        <v>41.8</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Hermes Agent 插件，提供编码智能和模型优化工作流程
-【原文】All in one plugin for Hermes Agent ⚚ the coding intelligence, a long-term memory system and model optimized workflow packages</t>
+          <t>快速文档解析和OCR工具
+【原文】TurboOCR, &gt;200 img/s OmnidocBench. TensorRT FP16, PP-OCRv6, HTTP + gRPC
+【依据】topics: document-ai, document-parsing, ocr</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1981,14 +2085,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rlaope/oh-my-hermes</t>
+          <t>https://github.com/aiptimizer/TurboOCR</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1997,7 +2101,7 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>21.02</v>
+        <v>5.97</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2006,7 +2110,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2021,62 +2125,63 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>agent, ai, ai-agent, ai-tools, claude-code, codex, hermes-agent, hermes-skill, skills</t>
+          <t>document-ai, document-parsing, easyocr, fastapi, fp16, gpu-ocr, grpc, inference-server, nvidia, ocr, paddleocr, pdf-extraction</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>melgarafael/DeskcommCRM</t>
+          <t>STranslate/STranslate</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2565</v>
+        <v>8022</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>128.2</v>
+        <v>41</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>开源 AI 销售操作系统，内置 AI 代理和 WhatsApp 支持
-【原文】Open-source AI sales OS — self-hosted CRM with native AI agents + WhatsApp (WAHA). Open alternative to Kommo, Octadesk &amp; Intercom for any business that sells by chat. MCP-ready, multi-tenant, LGPD.</t>
+          <t>基于WPF的即用即走的翻译和OCR工具
+【原文】A ready-to-go translation ocr tool developed with WPF/WPF 开发的一款即用即走的翻译、OCR工具
+【依据】topics: ocr, plugin</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>视频产线/图文产线</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/技能包</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2084,14 +2189,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/melgarafael/DeskcommCRM</t>
+          <t>https://github.com/STranslate/STranslate</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2100,7 +2205,7 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>18.32</v>
+        <v>5.86</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2109,7 +2214,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2124,68 +2229,77 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agents, chatbot, crm, customer-support, ecommerce, lgpd, mcp, multi-tenant, nextjs, nuvemshop, open-source</t>
+          <t>ocr, plugin, stranslate, translate, wpf</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2022-12-17</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>140</v>
+        <v>1369</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>eosphoros-ai/DB-GPT</t>
+          <t>carson-katri/dream-textures</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>19960</v>
+        <v>8202</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>111.7</v>
+        <v>39.1</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>open-source agentic AI data assistant for the next generation of AI + Data products.</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
+          <t>将Stable Diffusion集成到Blender中。
+【原文】Stable Diffusion built-in to Blender</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>图文产线</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/eosphoros-ai/DB-GPT</t>
+          <t>https://github.com/carson-katri/dream-textures</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2194,11 +2308,11 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>15.96</v>
+        <v>5.58</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -2213,26 +2327,26 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>agents, bgi, database, deepseek, gpt, gpt-4, hacktoberfest, llm, private, rag, security, vicuna</t>
+          <t>ai, blender, blender-addon, image-generation, stable-diffusion</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2023-04-13</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>1251</v>
+        <v>1469</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
@@ -2244,42 +2358,52 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
+          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Orkas-AI/Orkas</t>
+          <t>nanbingxyz/5ire</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2005</v>
+        <v>5348</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>100.9</v>
+        <v>38</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Orkas is an open-source, local-first AI desktop app: a commander LLM directs specialist sub-agents, and runs your installed coding CLIs — Claude Code, Codex, OpenCode, OpenClaw, Hermes — as local sessions. Agents self-evolve via reflection and skill crystallization. BYO keys. macOS / Windows / Linux.</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
+          <t>跨平台桌面 AI 助手，支持模型上下文协议
+【原文】5ire is a cross-platform desktop AI assistant, MCP client. It compatible with major service providers,  supports local knowledge base and  tools via model context protocol servers .
+【依据】5ire is a cross-platform desktop AI assistant, MCP client. It compatible with major service providers, supports local kn</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务/技能包</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Orkas-AI/Orkas</t>
+          <t>https://github.com/nanbingxyz/5ire</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2288,11 +2412,11 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>14.42</v>
+        <v>5.43</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -2307,73 +2431,82 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>agent-collaboration, agent-orchestration, agent-team, agentic-ai, ai-agents, ai-assistant, ai-team, ai-workflow, autonomous-agents, byo-llm, cross-platform, desktop-app</t>
+          <t>knowledge-base, llms, mcp, mcp-client, model-context-protocol</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>139</v>
+        <v>984</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-16</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>CaviraOSS/LongMemory</t>
+          <t>gzxx-2025/aid-studio</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>4498</v>
+        <v>314</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>95.09999999999999</v>
+        <v>37.2</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Local persistent memory store for LLM applications including claude desktop, github copilot, codex, antigravity, etc.</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
+          <t>开源AI漫剧、AI短剧、AI电影与AI漫画创作平台。
+【原文】开源AI漫剧、AI短剧、AI电影与AI漫画创作平台，支持剧本、角色场景、智能分镜、图片与视频生成、配音及成片预览，多模型接入，可自行部署，短剧。预：无限画布、导演台。</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/CaviraOSS/LongMemory</t>
+          <t>https://github.com/gzxx-2025/aid-studio</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2382,16 +2515,16 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>13.59</v>
+        <v>5.32</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -2401,73 +2534,82 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agents, ai-infrastructure, ai-memory, artificial-intelligence, cognitive-architecture, embeddings, gemini, llm, long-term-memory, memory, memory-engine</t>
+          <t>ai, ai-anime-art, ai-comic-creator, ai-comic-drama, ai-comics, ai-drama, ai-short-drama, ai-short-drama-agent, ai-storyboard, ai-video, ai-video-editing, ai-video-editor</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>331</v>
+        <v>59</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>wxyhgk/retain-pdf</t>
+          <t>oracle-devrel/oracle-ai-developer-hub</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2278</v>
+        <v>4376</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>93.8</v>
+        <v>31.4</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>在保留版面、公式与结构的前提下进行 PDF 翻译，适用于科研与技术文档</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
+          <t>提供Oracle AI开发者资源和工具
+【原文】Technical resources for AI developers to build applications, agents, and systems using Oracle AI Database and OCI services</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池/未归类</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>代码库/架构参考</t>
+        </is>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wxyhgk/retain-pdf</t>
+          <t>https://github.com/oracle-devrel/oracle-ai-developer-hub</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2476,16 +2618,16 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>13.4</v>
+        <v>4.49</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2495,17 +2637,17 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>document-ai, document-processing, layout-preserving, ocr, pdf, scientific-papers, translation, typst</t>
+          <t>agentmemory, agents, ai, ai-developer, artificial-intelligence, generative-ai, kubernetes, kustomize, oracle-database, oracleaidatabase, oraclejet, rag</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -2514,7 +2656,7 @@
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>170</v>
+        <v>974</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
@@ -2526,42 +2668,51 @@
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Kulaxyz/self-learning-skills</t>
+          <t>NVIDIA/GenerativeAIExamples</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>954</v>
+        <v>4183</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>84.59999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>A self-improving skill for AI coding agents (Claude Code, Cursor, AGENTS.md): recognize a hard-won golden path in a session and harvest it into a reusable skill/rule for next time.</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
+          <t>针对加速基础设施和微服务架构优化的生成式 AI 参考工作流程
+【原文】Generative AI reference workflows optimized for accelerated infrastructure and microservice architecture.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>RAG检索线</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>架构参考</t>
+        </is>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Kulaxyz/self-learning-skills</t>
+          <t>https://github.com/NVIDIA/GenerativeAIExamples</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2570,14 +2721,18 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>12.08</v>
+        <v>3.94</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Jupyter Notebook</t>
+        </is>
+      </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2585,22 +2740,26 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>gpu-acceleration, large-language-models, llm, llm-inference, microservice, nemo, rag, retrieval-augmented-generation, tensorrt, triton-inference-server</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>79</v>
+        <v>1063</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>1</v>
@@ -2612,42 +2771,51 @@
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>NirDiamant/Agent_Memory_Techniques</t>
+          <t>AnotiaWang/deep-research-web-ui</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1058</v>
+        <v>2209</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>55.6</v>
+        <v>26.5</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Agent memory for LLMs: 30 runnable Jupyter notebooks covering conversation buffers, vector stores, knowledge graphs, episodic and semantic memory, MemGPT, Mem0, Letta, Zep, Graphiti, LoCoMo benchmarks, and production patterns.</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
+          <t>提供AI深度研究代理，将问题转化为引用报告。
+【原文】AI deep-research agent that turns any question into a cited report: plans searches, reads real sources, verifies evidence. Self-hosted, multi-provider, Docker-ready.</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>RAG检索线</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/NirDiamant/Agent_Memory_Techniques</t>
+          <t>https://github.com/AnotiaWang/deep-research-web-ui</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2656,16 +2824,16 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>7.95</v>
+        <v>3.79</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2675,67 +2843,67 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>agent-memory, ai-agents, anthropic, episodic-memory, generative-ai, graphiti, knowledge-graph, langchain, letta, llm, llm-agents, llm-memory</t>
+          <t>ai-agent, citations, deep-research, docker, llm, nuxtjs, rag, research-assistant, self-hosted, web-search</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>133</v>
+        <v>583</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>crmne/ruby_llm</t>
+          <t>oil-oil/video-publisher-skill</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>4365</v>
+        <v>213</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>51.5</v>
+        <v>23.3</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>提供 Ruby-native AI 框架，支持多模态内容生成
-【原文】The Ruby-native AI framework. Chats, agents, tools, images, audio, and video through one consistent API, in plain Ruby or Rails.</t>
+          <t>准备视频、标题和封面为多平台草稿，支持恢复上传
+【原文】将视频、标题和封面准备为经过核验的多平台草稿，支持恢复上传，停在最终发布之前。</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>视频产线/图文产线</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2743,14 +2911,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/crmne/ruby_llm</t>
+          <t>https://github.com/oil-oil/video-publisher-skill</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2759,7 +2927,7 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>7.36</v>
+        <v>3.33</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -2768,7 +2936,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2781,26 +2949,22 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>agents, ai, ai-framework, anthropic, embeddings, gemini, image-generation, llm, multimodal, ocr, ollama, openai</t>
-        </is>
-      </c>
+      <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>593</v>
+        <v>64</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
@@ -2809,42 +2973,51 @@
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-17</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>any4ai/AnyCrawl</t>
+          <t>infiniflow/infinity</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>3455</v>
+        <v>4707</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>45.4</v>
+        <v>21.6</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>AnyCrawl 🚀: A Node.js/TypeScript crawler that turns websites into LLM-ready data and extracts structured SERP results from Google/Bing/Baidu/etc. Native multi-threading for bulk processing.</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
+          <t>为 LLM 应用构建的 AI 原生数据库，提供快速混合搜索
+【原文】The AI-native database built for LLM applications, providing incredibly fast hybrid search of dense vector, sparse vector, tensor (multi-vector), and full-text.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/any4ai/AnyCrawl</t>
+          <t>https://github.com/infiniflow/infinity</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2853,16 +3026,16 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>6.48</v>
+        <v>3.09</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2872,26 +3045,26 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>ai-scraping, aitools, crawl, data, html-to-markdown, rag, scrape, scraping, serp, webscraper</t>
+          <t>ai-native, approximate-nearest-neighbor-search, bm25, cpp20, cpp20-modules, embedding, full-text-search, hnsw, hybrid-search, information-retrival, multi-vector, nearest-neighbor-search</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2022-07-18</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>533</v>
+        <v>1521</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>1</v>
@@ -2903,42 +3076,52 @@
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>GH05TCREW/pentestagent</t>
+          <t>mindee/doctr</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>3077</v>
+        <v>6347</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>44.2</v>
+        <v>21.4</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>PentestAgent is an AI agent framework for black-box security testing, supporting bug bounty, red-team, and penetration testing workflows.</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
+          <t>提供深度学习驱动的文档文本识别库
+【原文】docTR (Document Text Recognition) - a seamless, high-performing &amp; accessible library for OCR-related tasks powered by Deep Learning. Ongoing development and maintenance by t2k.
+【依据】topics: document-recognition, ocr</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>古籍OCR线</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/GH05TCREW/pentestagent</t>
+          <t>https://github.com/mindee/doctr</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2947,11 +3130,11 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>6.31</v>
+        <v>3.06</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2966,26 +3149,26 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agents, ai-assistant, ai-cybersecurity, ai-hacking, ai-security-tool, blackbox-testing, ctf-tools, knowledge-graph, llm, mcp-tools, penetration-testing</t>
+          <t>deep-learning, document-recognition, ocr, optical-character-recognition, pytorch, tensorflow2, text-detection, text-detection-recognition, text-recognition</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2021-01-08</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>488</v>
+        <v>2077</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>1</v>
@@ -2997,42 +3180,52 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="28" ht="150" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>jonyzhang2023/awesome-embodied-vla-va-vln</t>
+          <t>ogkalu2/comic-translate</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>3528</v>
+        <v>2937</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>40.7</v>
+        <v>21.3</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>A curated list of state-of-the-art research in embodied AI, focusing on vision-language-action (VLA) models, vision-language navigation (VLN), and related multimodal learning approaches.</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
+          <t>自动翻译漫画和漫画的浏览器扩展/应用程序
+【原文】AI comic and manga translator app/browser extension for automatically translating comics, manga, manhwa, BDs, fumetti, and more in multiple languages and formats (Images, PDF, EPUB, CBR, CBZ etc).
+【依据】topics: ocr, machine-translation</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>古籍OCR线</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jonyzhang2023/awesome-embodied-vla-va-vln</t>
+          <t>https://github.com/ogkalu2/comic-translate</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3041,14 +3234,18 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>5.81</v>
+        <v>3.04</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3056,22 +3253,26 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P28" s="6" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>anime, comics, computer-vision, deep-learning, gui, inpainting, machine-translation, manga, manhua, manhwa, neural-network, ocr</t>
+        </is>
+      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S28" s="3" t="n">
-        <v>607</v>
+        <v>965</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>1</v>
@@ -3083,42 +3284,51 @@
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>neuml/txtai</t>
+          <t>x-hw/amazing-qr</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>12948</v>
+        <v>10816</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>40.7</v>
+        <v>20.6</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>💡 All-in-one AI framework for semantic search, LLM orchestration and language model workflows</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
+          <t>生成支持动态GIF的二维码。
+【原文】💮 amazing QRCode generator (supporting animated gif) - amazing 二维码生成器（支持 gif 动态图片二维码）</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>图文产线</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/neuml/txtai</t>
+          <t>https://github.com/x-hw/amazing-qr</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3127,11 +3337,11 @@
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>5.81</v>
+        <v>2.94</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -3146,67 +3356,68 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>agents, ai, ai-agents, embeddings, information-retrieval, language-model, large-language-models, llm, nlp, python, rag, retrieval-augmented-generation</t>
+          <t>amazing, gif, mcp, picture, qr, qr-code, qr-generator, qrcode, qrcode-generator, skills</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>2020-08-09</t>
+          <t>2016-08-25</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S29" s="3" t="n">
-        <v>2228</v>
+        <v>3674</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-16</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="30" ht="150" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>neo4j-labs/llm-graph-builder</t>
+          <t>seleniumbase/SeleniumBase</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>5249</v>
+        <v>13015</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>37.6</v>
+        <v>19.9</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>使用 LLM 从非结构化数据构建 Neo4j 图
-【原文】Neo4j graph construction from unstructured data using LLMs</t>
+          <t>浏览器自动化、网络抓取和测试工具
+【原文】Browser automation, web scraping, and testing. CDP Mode provides a Stealthy Chromium instance that bypasses bot-detection systems. Includes an MCP server.
+【依据】topics: anti-detection, bot-detection, selenium</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
+          <t>MCP服务</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3214,14 +3425,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/neo4j-labs/llm-graph-builder</t>
+          <t>https://github.com/seleniumbase/SeleniumBase</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3230,16 +3441,16 @@
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>5.37</v>
+        <v>2.84</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -3254,24 +3465,24 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>data-import, genai, graph, graph-rag, graph-search, graphdb, graphrag, knowledge-graph, langchain, neo4j, rag, unstructured-data</t>
+          <t>anti-detection, bot-detection, chromedriver, chromium, data, e2e-testing, end-to-end-testing, playwright, pytest, python, python-scraper, selenium</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2014-03-04</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S30" s="3" t="n">
-        <v>978</v>
+        <v>4579</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
@@ -3280,42 +3491,51 @@
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="31" ht="150" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>us/crw</t>
+          <t>partme-ai/full-stack-skills</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>1014</v>
+        <v>661</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>36.1</v>
+        <v>19</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Fast, lightweight Firecrawl/Tavily alternative in Rust. Web scraper, crawler &amp; search API with MCP server for AI agents. Drop-in Firecrawl-compatible API (/scrape, /crawl, /search). 2.3x faster than Tavily, 1.5x faster than Firecrawl in 1K-URL benchmarks. 6 MB RAM, single binary. Self-host or use managed cloud.</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
+          <t>提供免费的全栈开发AI技能市场
+【原文】这是一个免费的全栈开发所需的技能市场，提供各种实用的 AI 技能集合，支持多种平台。</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>技能包/代码库</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/us/crw</t>
+          <t>https://github.com/partme-ai/full-stack-skills</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -3324,18 +3544,14 @@
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>5.15</v>
+        <v>2.72</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>Rust</t>
-        </is>
-      </c>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3343,26 +3559,26 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agents, crawler, data-extraction, docker, firecrawl-alternative, html-to-markdown, llm, markdown, mcp, mcp-server, rust</t>
+          <t>agent-skills, claude-code, codebuddy, cursor, qoder, skills</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S31" s="3" t="n">
-        <v>197</v>
+        <v>243</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>1</v>
@@ -3374,42 +3590,51 @@
       </c>
       <c r="V31" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-16</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="32" ht="150" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Ramakm/ai-hands-on</t>
+          <t>adbar/trafilatura</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>1443</v>
+        <v>6825</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>34.2</v>
+        <v>17.6</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>A group of notebooks  and other files which can help you learn AI from scratch.</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr"/>
+          <t>从网络爬取文本和元数据，输出为多种格式
+【原文】Python &amp; Command-line tool to gather text and metadata on the Web: Crawling, scraping, extraction, output as CSV, JSON, HTML, MD, TXT, XML</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Ramakm/ai-hands-on</t>
+          <t>https://github.com/adbar/trafilatura</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -3418,16 +3643,16 @@
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>4.89</v>
+        <v>2.51</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3437,17 +3662,17 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>ai, artificial-intelligence, books, chatbot, machine-learning, math, ml, mlmodel, neural-network, ocr, pytorch, rag</t>
+          <t>article-extractor, corpus-builder, corpus-tools, crawler, html-to-markdown, html2text, llm, news-aggregator, news-crawler, nlp, rag, readability</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2019-04-08</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
@@ -3456,7 +3681,7 @@
         </is>
       </c>
       <c r="S32" s="3" t="n">
-        <v>295</v>
+        <v>2718</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>1</v>
@@ -3468,42 +3693,50 @@
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="33" ht="150" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>thetahealth/mirobody</t>
+          <t>wechatpay-apiv3/wechatpay-skills</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1307</v>
+        <v>352</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>31.6</v>
+        <v>13.9</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>The AI-native health data engine — collect, translate, and reason over labs, wearables &amp; genomics.</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
+          <t>提供微信支付Skills接口</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/thetahealth/mirobody</t>
+          <t>https://github.com/wechatpay-apiv3/wechatpay-skills</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -3512,11 +3745,11 @@
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>4.51</v>
+        <v>1.99</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -3531,26 +3764,22 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>ai-agents, apple-health, digital-health, ehr, fhir, garmin, health, health-data, healthcare, healthcare-ai, lab-reports, loinc</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr"/>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S33" s="3" t="n">
-        <v>290</v>
+        <v>177</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>1</v>
@@ -3562,42 +3791,52 @@
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="34" ht="150" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>supercorp-ai/supergateway</t>
+          <t>ballerine-io/ballerine</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2844</v>
+        <v>2430</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>31.4</v>
+        <v>11.8</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Run MCP stdio servers over SSE and SSE over stdio. AI gateway.</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
+          <t>风险决策的风险决策基础设施和数据编排平台
+【原文】Open-source infrastructure and data orchestration platform for risk decisioning
+【依据】topics: back-office, case-management, compliance</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>架构参考</t>
+        </is>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/supercorp-ai/supergateway</t>
+          <t>https://github.com/ballerine-io/ballerine</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -3606,11 +3845,11 @@
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>4.49</v>
+        <v>1.68</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -3625,22 +3864,26 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P34" s="6" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>back-office, case-management, compliance, dashboard, flow, fraud, id-card-camera, identity-verification, idv, know-your-customer, kyb, kyc</t>
+        </is>
+      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S34" s="3" t="n">
-        <v>633</v>
+        <v>1445</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>1</v>
@@ -3652,26 +3895,26 @@
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="35" ht="150" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>wanshuiyin/ARIS-in-AI-Offer</t>
+          <t>apify/awesome-skills</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>512</v>
+        <v>253</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>30.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>提供双语 AI 面试技巧和简历信息检查工具
-【原文】Bilingual (中文+EN) ML / LLM / diffusion / agent interview cheat sheets for AI 秋招 — generated by ARIS /interview-cheatsheet, rendered by /render-html into single-file HTML, reads anywhere — plus a CV→DBLP-fact-checked academic homepage generator and hand-authored long-form blogs 🌱</t>
+          <t>收集Apify AI编码助手技能
+【原文】Community collection of Apify agent skills for AI coding assistants</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -3681,7 +3924,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3689,14 +3932,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wanshuiyin/ARIS-in-AI-Offer</t>
+          <t>https://github.com/apify/awesome-skills</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -3705,11 +3948,11 @@
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>4.3</v>
+        <v>1.33</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3729,77 +3972,78 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>ai-interview, aris, autumn-recruiting, cheatsheet, chinese, claude-code, deep-learning, diffusion, flow-matching, interview-prep, llm, machine-learning</t>
+          <t>actor, agent-skills, ai-agents, apify, awesome-list, mcp</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S35" s="3" t="n">
-        <v>119</v>
+        <v>190</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-16</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="36" ht="150" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>vesoft-inc/nebula</t>
+          <t>dynobo/normcap</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>12387</v>
+        <v>2722</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>29.5</v>
+        <v>7.4</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>分布式、快速的开源图数据库，支持横向扩展和高可用性
-【原文】A distributed, fast open-source graph database featuring horizontal scalability and high availability</t>
+          <t>OCR功能的屏幕截图工具
+【原文】OCR powered screen-capture tool to capture information instead of images
+【依据】topics: ocr, screenshot</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vesoft-inc/nebula</t>
+          <t>https://github.com/dynobo/normcap</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -3808,16 +4052,16 @@
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>4.21</v>
+        <v>1.05</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -3832,21 +4076,21 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>big-data, cpp, database, distributed, distributed-systems, graph, graph-database, graphdb, graphrag, hacktoberfest, knowledge-base, knowledge-graph</t>
+          <t>multiplatform, ocr, python, screenshot, tesserocr, tool</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S36" s="3" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>1</v>
@@ -3858,42 +4102,52 @@
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="37" ht="150" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Affitor/affiliate-skills</t>
+          <t>FalkorDB/GraphRAG-SDK</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>661</v>
+        <v>1001</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>25.1</v>
+        <v>7.3</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>50 AI agent skills for affiliate marketing. Research trending content, write data-backed posts, generate infographics, build landing pages, deploy — full flywheel with social intelligence. Works with Claude Code, Pi, ChatGPT, Gemini, Cursor, Windsurf, any AI.</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
+          <t>使用GraphRAG SDK构建快速准确的GenAI应用程序。
+【原文】Build fast and accurate GenAI apps with GraphRAG SDK at scale  🌟
+【依据】Build fast and accurate GenAI apps with GraphRAG SDK at scale 🌟</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Affitor/affiliate-skills</t>
+          <t>https://github.com/FalkorDB/GraphRAG-SDK</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -3902,16 +4156,16 @@
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>3.59</v>
+        <v>1.04</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -3921,17 +4175,17 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>affiliate-marketing, agent-skills, ai, ai-agents, chatgpt, claude, claude-code, content-marketing, cursor, gemini, influencer, llm</t>
+          <t>falkordb, genai, graph-database, graphrag, knowledge-graph, llm, open-source, rag, sdk</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
@@ -3940,7 +4194,7 @@
         </is>
       </c>
       <c r="S37" s="3" t="n">
-        <v>184</v>
+        <v>965</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>1</v>
@@ -3952,51 +4206,51 @@
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="38" ht="150" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>gzxx-2025/aid-server</t>
+          <t>danjdewhurst/story-skills</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>23.4</v>
+        <v>7.3</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>一站式 AI 漫剧、漫画、动态漫、短剧与视频创作平台
-【原文】AID 是一套全开源、可私有化部署、可直接运营的一站式 AI 漫剧、AI 漫画、AI 动态漫、AI 短剧与 AI 视频创作平台。支持 AI 剧本创作、角色/道具/场景管理、AI 智能分镜、AI 文生图、AI 图生视频、AI 配音及项目管理，并提供多模型多厂商接入、任务调度、用户权限、积分计费、充值支付和运营后台。</t>
+          <t>提供故事写作的AI技能插件
+【原文】Agent Skills for end-to-end story writing in markdown, packaged as Codex and Claude Code plugins.</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/技能包</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/gzxx-2025/aid-server</t>
+          <t>https://github.com/danjdewhurst/story-skills</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4005,16 +4259,16 @@
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>3.34</v>
+        <v>1.04</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -4029,12 +4283,12 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>ai-animation, ai-anime, ai-comic, ai-drama, ai-manga, ai-short-drama, ai-storyboard, ai-storytelling, aigc, animated-comic, character-consistency, comic-generator</t>
+          <t>agent-skills, ai-agents, claude-code-plugin, codex, codex-plugin, creative-writing, fiction-writing, markdown, plot-structure, skill-md, storytelling, worldbuilding</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
@@ -4043,54 +4297,63 @@
         </is>
       </c>
       <c r="S38" s="3" t="n">
-        <v>58</v>
+        <v>216</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-17</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="39" ht="150" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>katanaml/sparrow</t>
+          <t>bangle-io/bangle-io</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>5219</v>
+        <v>1231</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>21.3</v>
+        <v>4.1</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Structured data extraction, instruction calling and agentic workflows with ML, LLM and Vision LLM</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="7" t="inlineStr">
+          <t>提供本地Markdown格式笔记记录应用。
+【原文】A web only WYSIWYG note taking app that saves notes locally in markdown format. v2: https://app.bangle.io/</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>传染·只能读架构</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/katanaml/sparrow</t>
+          <t>https://github.com/bangle-io/bangle-io</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4099,16 +4362,16 @@
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>3.05</v>
+        <v>0.59</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -4118,26 +4381,26 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, computer-vision, documentai, huggingface-transformers, llm, machinelearning, vllm</t>
+          <t>knowledge-graph, local-first, markdown, markdown-notes, note-taker, notes, pwa, react, webworkers, wysiwyg</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>2022-01-08</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S39" s="3" t="n">
-        <v>1711</v>
+        <v>2093</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>1</v>
@@ -4149,42 +4412,51 @@
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-16</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="40" ht="150" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>AdrienTorris/awesome-blazor</t>
+          <t>lucky-Luor/tcm-elderly-care-system</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>9377</v>
+        <v>0</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Resources for Blazor, a .NET web framework using C#/Razor and HTML that runs in the browser with WebAssembly.</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
+          <t>基于树莓派和大模型的中医居家健康养老系统。
+【原文】基于树莓派和大模型的中医居家健康养老系统 · 云端(Spring Boot 3 + Vue3)+ 树莓派边缘端(Python)</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/AdrienTorris/awesome-blazor</t>
+          <t>https://github.com/lucky-Luor/tcm-elderly-care-system</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4193,14 +4465,18 @@
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr"/>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4208,1258 +4484,39 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>asp-net-core, aspnetcore, awesome, awesome-list, blazor, blazor-application, blazor-component, blazor-crud, blazor-interop, blazor-master, blazor-port, blazor-sample</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr"/>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>2018-03-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S40" s="3" t="n">
-        <v>3092</v>
+        <v>1</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="150" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>SenmuuuuW/universal-diagnostic-tutor-skill</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>208</v>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>One diagnosis-first AI tutor for STEM, AI/CS, and beyond — no mode or command menu. It decides the next useful teaching step, checks understanding, and builds mastery.</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/SenmuuuuW/universal-diagnostic-tutor-skill</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>ai-education, ai-tutor, codex, codex-skill, computer-science, diagnostics, learning-assistant, math, skill, stem, tutoring</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V41" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="150" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>modelcontextprotocol/ext-skills</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>536</v>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Experimental exploration of skills discovery and distribution through MCP primitives. Maintained by the Skills Over MCP Working Group.</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/modelcontextprotocol/ext-skills</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>MDX</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P42" s="6" t="inlineStr"/>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>226</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V42" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="150" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>lignertys/reddit-research-skills</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>532</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Reddit research skills for Claude Code and AI agents</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/lignertys/reddit-research-skills</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, claude-code, claude-skill, gemini-cli-extension, skills</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V43" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="150" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>kitspace/awesome-electronics</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>8120</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of awesome resources for Electronic Engineers and hobbyists</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/kitspace/awesome-electronics</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr"/>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>altium, awesome, eagle, electronics, gerber, hardware, kicad, pcb</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>2016-07-26</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>3703</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V44" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="150" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>pymupdf/PyMuPDF</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>10714</v>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>PyMuPDF is a high performance Python library for data extraction, analysis, conversion &amp; manipulation of PDF (and other) documents.</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/pymupdf/PyMuPDF</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>AGPL-3.0</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>data-science, epub, extract-data, font, mupdf, ocr, pdf, pdf-documents, pymupdf, python, table-extraction, tesseract</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t>2012-10-06</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>5092</v>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V45" s="6" t="inlineStr">
-        <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="150" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>InternScience/GraphGen</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>GraphGen: Enhancing Supervised Fine-Tuning for LLMs with Knowledge-Driven Synthetic Data Generation</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/InternScience/GraphGen</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>ai4science, data-generation, data-synthesis, graphgen, knowledge-graph, llama-factory, llm, llm-training, pretrain, pretraining, qa, question-answering</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>2025-01-08</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>615</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V46" s="6" t="inlineStr">
-        <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="150" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>deepdoctection/deepdoctection</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>3258</v>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>A Repo For Document AI</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/deepdoctection/deepdoctection</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>document-ai, document-image-analysis, document-layout-analysis, document-parser, document-understanding, layoutlm, nlp, ocr, publaynet, pubtabnet, python, pytorch</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>2021-12-09</t>
-        </is>
-      </c>
-      <c r="R47" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="S47" s="3" t="n">
-        <v>1741</v>
-      </c>
-      <c r="T47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V47" s="6" t="inlineStr">
-        <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="150" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>jkf87/hwpx-skill</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>249</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>AI 에이전트용 HWPX(.hwpx) 문서 생성 스킬 - 한컴오피스 한글 문서를 마크다운/텍스트/URL에서 자동 생성</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/jkf87/hwpx-skill</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P48" s="6" t="inlineStr"/>
-      <c r="Q48" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="R48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="S48" s="3" t="n">
-        <v>179</v>
-      </c>
-      <c r="T48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V48" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="150" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>toolleeo/awesome-cli-apps-in-a-csv</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>2616</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>The largest Awesome Curated list of command line programs (CLI/TUI) with source data organized into CSV files</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/toolleeo/awesome-cli-apps-in-a-csv</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N49" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, cli, cli-apps, command-line, command-line-tool, linux, linux-command, resources, terminal-based, tui</t>
-        </is>
-      </c>
-      <c r="Q49" s="3" t="inlineStr">
-        <is>
-          <t>2017-06-21</t>
-        </is>
-      </c>
-      <c r="R49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="S49" s="3" t="n">
-        <v>3373</v>
-      </c>
-      <c r="T49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U49" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V49" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="150" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>frutik/awesome-search</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>1562</v>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>关于搜索和其优点的资源集合，包括电商搜索
-【原文】Awesome Search - this is all about the (e-commerce, but not only) search and its awesomeness</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/frutik/awesome-search</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
-      <c r="N50" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>autocomplete-suggestions, ecommerce-search, evaluating-search, knowledge-graph, learning-to-rank, natural-language-processing, query-understanding, ranking, relevance-algorithms, relevant-search, search, search-engine</t>
-        </is>
-      </c>
-      <c r="Q50" s="3" t="inlineStr">
-        <is>
-          <t>2019-09-09</t>
-        </is>
-      </c>
-      <c r="R50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="S50" s="3" t="n">
-        <v>2563</v>
-      </c>
-      <c r="T50" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V50" s="6" t="inlineStr">
-        <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="150" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>kmonkeyhead/MORT</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>1753</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>MORT 번역기 프로젝트 - Real-time game translator with OCR</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/kmonkeyhead/MORT</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>C#</t>
-        </is>
-      </c>
-      <c r="N51" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>auto-translation, game, game-translation, image-to-text, ocr, tesseract-ocr, translate, translation</t>
-        </is>
-      </c>
-      <c r="Q51" s="3" t="inlineStr">
-        <is>
-          <t>2016-06-09</t>
-        </is>
-      </c>
-      <c r="R51" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="S51" s="3" t="n">
-        <v>3750</v>
-      </c>
-      <c r="T51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V51" s="6" t="inlineStr">
-        <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="150" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>google/schema-dts</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>1240</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>JSON-LD TypeScript types for Schema.org vocabulary</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/google/schema-dts</t>
-        </is>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M52" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="N52" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>json-ld, knowledge-graph, linked-data, ontology, schema-org, schemaorg, semantic-web, typescript, typescript-definitions</t>
-        </is>
-      </c>
-      <c r="Q52" s="3" t="inlineStr">
-        <is>
-          <t>2018-11-29</t>
-        </is>
-      </c>
-      <c r="R52" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="S52" s="3" t="n">
-        <v>2847</v>
-      </c>
-      <c r="T52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V52" s="6" t="inlineStr">
-        <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="150" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>itsmostafa/aws-agent-skills</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>1155</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>AWS Skills for Agents</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/itsmostafa/aws-agent-skills</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N53" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, agentic-ai, aws, claude-code, claude-skills, codex, coding-agents</t>
-        </is>
-      </c>
-      <c r="Q53" s="3" t="inlineStr">
-        <is>
-          <t>2019-05-18</t>
-        </is>
-      </c>
-      <c r="R53" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="S53" s="3" t="n">
-        <v>2677</v>
-      </c>
-      <c r="T53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U53" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V53" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-16</t>
+          <t>中医 大模型 in:name,description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V53"/>
+  <autoFilter ref="A2:V40"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-16 · 共 38 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-17 · 共 28 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,34 +633,34 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>youngyangyang04/llm-master</t>
+          <t>deepseek-ai/awesome-deepseek-agent</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>505</v>
+        <v>6091</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>883.8</v>
+        <v>298.1</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>提供大模型（LLM）全栈学习路线和中文教程，涵盖Prompt Engineering、RAG、AI Agent等。
-【原文】大模型（LLM）全栈学习路线与中文教程🔥：覆盖 Prompt Engineering、RAG、AI Agent、MCP、微调、模型部署、Transformer、AI 编程与大厂面试，从入门到生产实践。</t>
+          <t>DeepSeek Agent开源列表
+【依据】描述中提到开源列表</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/youngyangyang04/llm-master</t>
+          <t>https://github.com/deepseek-ai/awesome-deepseek-agent</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,11 +679,11 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>126.25</v>
+        <v>42.59</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr"/>
@@ -697,69 +697,64 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>agent, large-language-models, llm, llm-learning, llm-tutorial, rag</t>
-        </is>
-      </c>
+      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>4</v>
+        <v>143</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-06-18</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>hypit-ai/hypit</t>
+          <t>browserbase/stagehand</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4310</v>
+        <v>24314</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>615.7</v>
+        <v>187.7</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>使用AI代理克隆病毒视频，包括人脸、文字和视频片段替换，批量生成变体视频。
-【原文】Clone any viral video with AI agents. Not just a script, the whole workflow: swap the face, the words, the B-roll, ship 100 variants in one command, and get your 100M views.</t>
+          <t>The SDK for browser agents. Interact, search, extract, and fetch any site reliably across the web</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/hypit-ai/hypit</t>
+          <t>https://github.com/browserbase/stagehand</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -778,11 +773,11 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>26.81</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -797,72 +792,71 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, ai, ai-agents, ai-video, compiler, dsl, ffmpeg, generative-ai, llm, markup-language, modular, monorepo</t>
+          <t>agents, ai, ai-agent, ai-agents, automation, browser, browser-agent, browser-automation, cdp, cloud-browser, data-extraction, harness</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>49</v>
+        <v>907</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:video-automation stars:&gt;2000 pushed:&gt;2026-06-18</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>patchy631/ai-engineering-hub</t>
+          <t>harvard-edge/cs249r_book</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>37557</v>
+        <v>28252</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>378.3</v>
+        <v>178.6</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>关于 LLM、RAG 和 AI 代理应用的深入教程
-【原文】In-depth tutorials on LLMs, RAGs and real-world AI agent applications.</t>
+          <t>Machine Learning Systems: Foundations, Scaling, Agentic AI, and Physical AI (Vols I–IV) • Harvard CS249r | https://mlsysbook.ai</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -872,7 +866,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/patchy631/ai-engineering-hub</t>
+          <t>https://github.com/harvard-edge/cs249r_book</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -881,16 +875,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>54.04</v>
+        <v>25.52</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -900,26 +894,26 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>agents, ai, llms, machine-learning, mcp, rag</t>
+          <t>agentic-ai, ai-agents, artificial-intelligence, cloud-ml, computer-systems, courseware, deep-learning, edge-machine-learning, embedded-ml, embodied-ai, machine-learning, machine-learning-systems</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>695</v>
+        <v>1107</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -931,26 +925,25 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>yjz211/vivid-figures-skill</t>
+          <t>liustack/modlens</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>245</v>
+        <v>3975</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>285.8</v>
+        <v>134.4</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供AI生成科研图表的配方
-【原文】让 AI 用你的数据生成科研图表：108 个配方，鲜艳与稳重两种风格，多套配色，交付图片与源码。仅限个人非商业使用。</t>
+          <t>The first vision plugin for DeepSeek Harness, and the vision bridge for every text-only coding agent. Paste an image, get structured JSON evidence (OCR, layout, semantics). | 全网最强 DeepSeek Harness 外挂视觉插件，为 DeepSeek、GLM 等纯文本模型外挂视觉能力，粘贴图片即得结构化 JSON 证据（OCR、版面、语义）。</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -960,12 +953,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -975,7 +968,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yjz211/vivid-figures-skill</t>
+          <t>https://github.com/liustack/modlens</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -984,16 +977,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>40.83</v>
+        <v>19.2</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1003,22 +996,26 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, claude-code, claude-skills, codex, cordis, deepseek, dsh, dsh-plugin, glm, harness, harness-engineering, hermes-agent</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>6</v>
+        <v>207</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1030,26 +1027,26 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NirDiamant/RAG_Techniques</t>
+          <t>vuejs/awesome-vue</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>29503</v>
+        <v>73544</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>259.8</v>
+        <v>129.2</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>展示RAG系统的各种高级技术
-【原文】This repository showcases various advanced techniques for Retrieval-Augmented Generation (RAG) systems. Each technique has a detailed notebook tutorial.</t>
+          <t>收集Vue.js相关资源列表
+【原文】🎉 A curated list of awesome things related to Vue.js</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1059,12 +1056,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>代码库/架构参考</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1074,7 +1071,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/NirDiamant/RAG_Techniques</t>
+          <t>https://github.com/vuejs/awesome-vue</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1083,18 +1080,14 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>37.11</v>
+        <v>18.46</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>Jupyter Notebook</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1105,23 +1098,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>agentic-rag, ai, embeddings, generative-ai, gpt, langchain, llama-index, llm, llms, machine-learning, nlp, openai</t>
-        </is>
-      </c>
+      <c r="P7" s="6" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2015-10-20</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>795</v>
+        <v>3985</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1133,26 +1122,26 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>muxuuu/serenity-skill</t>
+          <t>cookiy-ai/sell-sessions-skill</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3993</v>
+        <v>218</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>207.1</v>
+        <v>117.4</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>用于供应链瓶颈股票研究的 Serenity 风格智能体技能
-【原文】Serenity-inspired Agent Skill for supply-chain bottleneck stock research</t>
+          <t>销售会话技能
+【依据】描述中提到销售会话技能</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1162,7 +1151,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1177,7 +1166,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/muxuuu/serenity-skill</t>
+          <t>https://github.com/cookiy-ai/sell-sessions-skill</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1186,18 +1175,14 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>29.58</v>
+        <v>16.77</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1208,23 +1193,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, ai-agents, claude-code, codex, investment-research, stock-research, supply-chain</t>
-        </is>
-      </c>
+      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1236,42 +1217,42 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;500 pushed:&gt;2026-06-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>tesseract-ocr/tesseract</t>
+          <t>CVHub520/X-AnyLabeling</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>76507</v>
+        <v>10461</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>121.2</v>
+        <v>60.3</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>开源的 OCR 引擎仓库
-【原文】Tesseract Open Source OCR Engine (main repository)
-【依据】topics: ocr, ocr-engine</t>
+          <t>提供跨平台图像、文本、视频标注工具，结合AI模型和内置工具
+【原文】X-AnyLabeling: A lightweight, efficient, and unified cross-platform desktop application for annotating text, image, video, and multimodal data, combining versatile built-in tools with state-of-the-art AI models and flexible multi-format export.
+【依据】描述中提到标注图像、文本、视频</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>图文产线/视频产线</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1281,7 +1262,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tesseract-ocr/tesseract</t>
+          <t>https://github.com/CVHub520/X-AnyLabeling</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1290,16 +1271,16 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>17.32</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1314,21 +1295,21 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>hacktoberfest, lstm, machine-learning, ocr, ocr-engine, tesseract, tesseract-ocr</t>
+          <t>artificial-intelligence, clip, computer-vision, deep-learning, groundingdino, image-annotation-tool, image-classification, image-labeling-tool, image-matting, instance-segmentation, machine-learning, object-detection</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2014-08-12</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>4418</v>
+        <v>1213</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
@@ -1340,41 +1321,42 @@
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>kunpengtalk/OmniStudio</t>
+          <t>hgmzhn/manga-translator-ui</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>108</v>
+        <v>2793</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供本地大模型一体化桌面工作台，支持模型市集下载、推理管理、对话、语音合成等。
-【原文】OmniStudio 是一个本地大模型一体化桌面工作台，集模型市集下载、llama.cpp/vLLM/SGLang 三引擎推理管理，以及对话、语音合成、ASR语音识别、图片生成、视频生成、OCR 等多种大模型应用于一体，全程本地优先。</t>
+          <t>开源漫画AI翻译桌面工具，支持多种翻译引擎和OCR功能
+【原文】基于manga-image-translator 实现的开源漫画AI翻译桌面工具。支持日、韩、英文漫画自动处理，集成OpenAl、Gemini等多翻译引擎；实现OCR文字检测、原文擦除、AI翻译、图像修复、译文排版完整链路，自带可视化编辑器，支持自定义文本样式，一键部署开箱即用。
+【依据】描述中提到漫画图像翻译和OCR文字检测</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>图文产线/AI免费池</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1384,7 +1366,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kunpengtalk/OmniStudio</t>
+          <t>https://github.com/hgmzhn/manga-translator-ui</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1393,16 +1375,16 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>15.43</v>
+        <v>7.29</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1415,65 +1397,68 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>automated-translation, comic-translation, gemini, image-translator, machine-translation, manga-translato, ocr, openai, python, scanlation</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>7</v>
+        <v>383</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-06-18</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>LING71671/open-reverselab</t>
+          <t>Sumanth077/Hands-On-AI-Engineering</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1137</v>
+        <v>3628</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>44.5</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>提供开源AI逆向工程平台和MCP服务器
-【原文】Open-source AI reverse-engineering agent platform and MCP server for Ghidra, Frida, x64dbg and Rizin — automated PE/APK/binary analysis, CTF and malware research, with 100+ MCP tools and a 194-article runnable knowledge base.</t>
+          <t>A curated collection of practical AI projects implementing OCR systems, RAG, AI agents, and other AI use cases.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库/可部署服务</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1483,7 +1468,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LING71671/open-reverselab</t>
+          <t>https://github.com/Sumanth077/Hands-On-AI-Engineering</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1492,11 +1477,11 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>12.49</v>
+        <v>6.36</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1511,26 +1496,26 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, ai-reverse-engineering, android-reverse-engineering, binary-analysis, binary-reverse-engineering, claude-code, codex, ctf, frida, ghidra, ghidra-mcp, malware-analysis</t>
+          <t>agents, ai, ai-agents, ai-engineering, generative-ai, llms, mcp, ocr, python, rag</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>91</v>
+        <v>570</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1542,41 +1527,41 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-17</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>ATH-MaaS/ComfyUI-Copilot</t>
+          <t>irinabuht12-oss/marketing-skills</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>5516</v>
+        <v>1498</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>66.7</v>
+        <v>43.9</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>为 ComfyUI 设计的 AI 辅助节点，增强工作流程自动化
-【原文】An AI-powered custom node for ComfyUI designed to enhance workflow automation and provide intelligent assistance</t>
+          <t>提供48个免费Claude营销技能和Ryze MCP服务
+【原文】48 free Claude marketing skills (Google Ads, Meta Ads, SEO, AI visibility) + Ryze MCP: claude mcp add ryze --transport http https://connector.get-ryze.ai/mcp</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包/MCP服务</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1586,7 +1571,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ATH-MaaS/ComfyUI-Copilot</t>
+          <t>https://github.com/irinabuht12-oss/marketing-skills</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1595,18 +1580,14 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>9.529999999999999</v>
+        <v>6.27</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1619,21 +1600,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agent, ai, comfy-ui, comfyui, comfyui-nodes, copilot, deepseek, deepseek-v3, flux, gpt-4, llm-agent, rag</t>
+          <t>ai-visibility, claude-code, claude-plugin, claude-skills, cursor, geo, google-ads, marketing, mcp, mcp-server, meta-ads, seo</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>579</v>
+        <v>239</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1645,27 +1626,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>umlx5h/LLPlayer</t>
+          <t>feichanggege/ecommerce-visual-copywriting-skill</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>4143</v>
+        <v>770</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>48.9</v>
+        <v>34.8</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>语言学习用媒体播放器，具有AI字幕和翻译功能
-【原文】The media player for language learning, with dual subtitles, AI-generated subtitles, real-time translation, and more!
-【依据】topics: video, video-player, ocr</t>
+          <t>提供电商视觉文案设计SOP Skill，兼容多种AI工具
+【原文】电商视觉文案设计SOP Skill - 让电商设计小白也能一键做出5年资深设计经验的商品图片.兼容 Claude / Codex / Cursor / Workbuddy 等 SKILL.md Agent. AI-powered e-commerce visual strategy skill for main images, PDP/A+, copywriting, localization, evidence-aware compliance and image prompts.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1675,12 +1655,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1690,7 +1670,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/umlx5h/LLPlayer</t>
+          <t>https://github.com/feichanggege/ecommerce-visual-copywriting-skill</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1699,16 +1679,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>6.99</v>
+        <v>4.97</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1723,21 +1703,21 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>asr, csharp, flyleaf, language-learning, llm, media-player, ocr, ollama, player, video, video-player, whisper</t>
+          <t>agent-skills, ai-image-generation-api, amazon, copywriting, ecommerce, prompt-engineering, shopify, tiktok-shop-affiliate</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>593</v>
+        <v>155</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1749,41 +1729,40 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Future-House/paper-qa</t>
+          <t>datawhalechina/llms-from-scratch-cn</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9203</v>
+        <v>4367</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>48.9</v>
+        <v>32.8</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>提供科学文档问答的RAG系统
-【原文】High accuracy RAG for answering questions from scientific documents with citations</t>
+          <t>仅需Python基础，从0构建大语言模型；从0逐步构建GLM4\Llama3\RWKV6， 深入理解大模型原理</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1793,7 +1772,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Future-House/paper-qa</t>
+          <t>https://github.com/datawhalechina/llms-from-scratch-cn</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1802,16 +1781,16 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>6.98</v>
+        <v>4.69</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1821,58 +1800,56 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>ai, rag, science, search</t>
+          <t>glm, llama, llm, llms-from-scratch, rwkv</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2023-02-05</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>1319</v>
+        <v>932</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
+          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>alibaba-flyai/flyai-skill</t>
+          <t>vercel-labs/next-skills</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>1140</v>
+        <v>981</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>44.1</v>
+        <v>29</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>飞智AI代理技能
-【原文】fly ai agent skill
-【依据】topics: -</t>
+          <t>提供Next.js技能</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1882,12 +1859,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1897,7 +1874,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/alibaba-flyai/flyai-skill</t>
+          <t>https://github.com/vercel-labs/next-skills</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1906,11 +1883,11 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>6.3</v>
+        <v>4.14</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr"/>
@@ -1927,7 +1904,7 @@
       <c r="P15" s="6" t="inlineStr"/>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
@@ -1936,7 +1913,7 @@
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>181</v>
+        <v>237</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1948,31 +1925,32 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>huangkiki/dailypaper-skills</t>
+          <t>filtalgo/Filtmall-Shopping-Skill</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1232</v>
+        <v>348</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>42.7</v>
+        <v>21.8</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>用Agent skills打造论文流水线
-【原文】用Agent skills打造我的论文流水线</t>
+          <t>购物代理技能，提供价格验证和购物流程服务
+【原文】Agent-native shopping for extreme value: verifiable same-product price evidence, checkout, orders, delivery, and after-sales.
+【依据】描述中提到购物代理和价格验证</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1992,7 +1970,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/huangkiki/dailypaper-skills</t>
+          <t>https://github.com/filtalgo/Filtmall-Shopping-Skill</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2001,7 +1979,7 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>6.1</v>
+        <v>3.11</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -2010,7 +1988,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2023,19 +2001,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, ai-agent, claude-skills, ecommerce, filtalgo, filtmall, openclaw, product-search, shopping, skillsmp</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2047,37 +2029,35 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>aiptimizer/TurboOCR</t>
+          <t>Zchary1106/agent-interview-hub</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1075</v>
+        <v>510</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>41.8</v>
+        <v>20.5</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>快速文档解析和OCR工具
-【原文】TurboOCR, &gt;200 img/s OmnidocBench. TensorRT FP16, PP-OCRv6, HTTP + gRPC
-【依据】topics: document-ai, document-parsing, ocr</t>
+          <t>AI Agent 工程师面试资料库 - 国内大厂面经、岗位要求、高频面试题</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2092,7 +2072,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/aiptimizer/TurboOCR</t>
+          <t>https://github.com/Zchary1106/agent-interview-hub</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2101,7 +2081,7 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>5.97</v>
+        <v>2.93</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2110,7 +2090,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2120,68 +2100,67 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>document-ai, document-parsing, easyocr, fastapi, fp16, gpu-ocr, grpc, inference-server, nvidia, ocr, paddleocr, pdf-extraction</t>
+          <t>ai-agent, chinese, claude, interview, langchain, llm, machine-learning, mcp, prompt-engineering, rag</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>STranslate/STranslate</t>
+          <t>EpicGames/unreal-engine-skills-for-claude-code-plugin</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>8022</v>
+        <v>290</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>41</v>
+        <v>20.1</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>基于WPF的即用即走的翻译和OCR工具
-【原文】A ready-to-go translation ocr tool developed with WPF/WPF 开发的一款即用即走的翻译、OCR工具
-【依据】topics: ocr, plugin</t>
+          <t>Unreal Engine Claude Code插件技能
+【依据】描述中提到插件技能</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>架构参考</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2196,7 +2175,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/STranslate/STranslate</t>
+          <t>https://github.com/EpicGames/unreal-engine-skills-for-claude-code-plugin</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2205,7 +2184,7 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>5.86</v>
+        <v>2.87</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2214,7 +2193,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2227,23 +2206,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>ocr, plugin, stranslate, translate, wpf</t>
-        </is>
-      </c>
+      <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2022-12-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>1369</v>
+        <v>101</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
@@ -2255,41 +2230,41 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>carson-katri/dream-textures</t>
+          <t>qdrant/fastembed</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>8202</v>
+        <v>3204</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>39.1</v>
+        <v>19.3</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>将Stable Diffusion集成到Blender中。
-【原文】Stable Diffusion built-in to Blender</t>
+          <t>提供快速、精确、轻量级的Python库进行高级嵌入
+【原文】Fast, Accurate, Lightweight Python library to make State of the Art Embedding</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -2299,7 +2274,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/carson-katri/dream-textures</t>
+          <t>https://github.com/qdrant/fastembed</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2308,11 +2283,11 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>5.58</v>
+        <v>2.76</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -2332,21 +2307,21 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>ai, blender, blender-addon, image-generation, stable-diffusion</t>
+          <t>embeddings, openai, rag, retrieval, retrieval-augmented-generation, vector-search</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>1469</v>
+        <v>1161</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
@@ -2358,42 +2333,41 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-18</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>nanbingxyz/5ire</t>
+          <t>mattt/iMCP</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>5348</v>
+        <v>1549</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>38</v>
+        <v>19.3</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>跨平台桌面 AI 助手，支持模型上下文协议
-【原文】5ire is a cross-platform desktop AI assistant, MCP client. It compatible with major service providers,  supports local knowledge base and  tools via model context protocol servers .
-【依据】5ire is a cross-platform desktop AI assistant, MCP client. It compatible with major service providers, supports local kn</t>
+          <t>为MacOS提供MCP服务器
+【原文】A macOS app that provides an MCP server to your Messages, Contacts, Reminders and more</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包</t>
+          <t>架构参考</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -2403,7 +2377,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/nanbingxyz/5ire</t>
+          <t>https://github.com/mattt/iMCP</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2412,16 +2386,16 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>5.43</v>
+        <v>2.76</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Swift</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2436,21 +2410,21 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>knowledge-base, llms, mcp, mcp-client, model-context-protocol</t>
+          <t>macos, mcp</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>984</v>
+        <v>561</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
@@ -2462,26 +2436,26 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-17</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>gzxx-2025/aid-studio</t>
+          <t>smixs/visual-skills</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>314</v>
+        <v>389</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>37.2</v>
+        <v>18.9</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>开源AI漫剧、AI短剧、AI电影与AI漫画创作平台。
-【原文】开源AI漫剧、AI短剧、AI电影与AI漫画创作平台，支持剧本、角色场景、智能分镜、图片与视频生成、配音及成片预览，多模型接入，可自行部署，短剧。预：无限画布、导演台。</t>
+          <t>提供AI电影导演技能，用于生成视觉内容
+【原文】AI film director skills for agents: cinematic dramaturgy (Murch, blocking, montage) + exact prompt syntax for Seedance 2.5, Kling 3.0 Turbo/Omni, Veo 3.1, Nano Banana 2, GPT Image 2.5.</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2491,12 +2465,12 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2506,7 +2480,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/gzxx-2025/aid-studio</t>
+          <t>https://github.com/smixs/visual-skills</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2515,18 +2489,14 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>5.32</v>
+        <v>2.7</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2539,67 +2509,68 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-anime-art, ai-comic-creator, ai-comic-drama, ai-comics, ai-drama, ai-short-drama, ai-short-drama-agent, ai-storyboard, ai-video, ai-video-editing, ai-video-editor</t>
+          <t>ai-image-generation, ai-prompts, ai-video-generation, claude, claude-agent-sdk, claude-code, claude-skills, cline, creative-director, cursor, generative-ai, gpt-image</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>oracle-devrel/oracle-ai-developer-hub</t>
+          <t>sindresorhus/awesome-whisper</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>4376</v>
+        <v>2383</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>31.4</v>
+        <v>13.6</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>提供Oracle AI开发者资源和工具
-【原文】Technical resources for AI developers to build applications, agents, and systems using Oracle AI Database and OCI services</t>
+          <t>Whisper语音识别系统开源列表
+【原文】🔊 Awesome list for Whisper — an open-source AI-powered speech recognition system developed by OpenAI
+【依据】描述中提到Whisper语音识别系统</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>代码库/架构参考</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2609,7 +2580,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/oracle-devrel/oracle-ai-developer-hub</t>
+          <t>https://github.com/sindresorhus/awesome-whisper</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2618,18 +2589,14 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>4.49</v>
+        <v>1.94</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>Jupyter Notebook</t>
-        </is>
-      </c>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2642,21 +2609,21 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>agentmemory, agents, ai, ai-developer, artificial-intelligence, generative-ai, kubernetes, kustomize, oracle-database, oracleaidatabase, oraclejet, rag</t>
+          <t>ai, artificial-intelligence, awesome, awesome-list, gpt, openai, speech-to-text, transcription</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>974</v>
+        <v>1226</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
@@ -2668,36 +2635,35 @@
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA/GenerativeAIExamples</t>
+          <t>enoch3712/ExtractThinker</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>4183</v>
+        <v>1598</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>27.6</v>
+        <v>11.7</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>针对加速基础设施和微服务架构优化的生成式 AI 参考工作流程
-【原文】Generative AI reference workflows optimized for accelerated infrastructure and microservice architecture.</t>
+          <t>ExtractThinker is a Document Intelligence library for LLMs, offering ORM-style interaction for flexible and powerful document workflows.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2712,7 +2678,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA/GenerativeAIExamples</t>
+          <t>https://github.com/enoch3712/ExtractThinker</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2721,7 +2687,7 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>3.94</v>
+        <v>1.67</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
@@ -2730,7 +2696,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2740,26 +2706,26 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>gpu-acceleration, large-language-models, llm, llm-inference, microservice, nemo, rag, retrieval-augmented-generation, tensorrt, triton-inference-server</t>
+          <t>ai, document-image-analysis, document-intelligence, document-parsing, document-processing, langchain, llm, machine-learning, nlp, ocr, openai, pdf</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1063</v>
+        <v>959</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>1</v>
@@ -2771,41 +2737,42 @@
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>AnotiaWang/deep-research-web-ui</t>
+          <t>ciur/papermerge</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2209</v>
+        <v>2936</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>26.5</v>
+        <v>8.4</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>提供AI深度研究代理，将问题转化为引用报告。
-【原文】AI deep-research agent that turns any question into a cited report: plans searches, reads real sources, verifies evidence. Self-hosted, multi-provider, Docker-ready.</t>
+          <t>开源数字档案文档管理系统，支持扫描文档管理
+【原文】Open Source Document Management System for Digital Archives (Scanned Documents)
+【依据】描述中提到文档管理系统和OCR</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -2815,7 +2782,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/AnotiaWang/deep-research-web-ui</t>
+          <t>https://github.com/ciur/papermerge</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2824,16 +2791,16 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>3.79</v>
+        <v>1.2</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2848,67 +2815,68 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, citations, deep-research, docker, llm, nuxtjs, rag, research-assistant, self-hosted, web-search</t>
+          <t>archives, django, dms, document-management, ocr, paperless, pdf, scan, scanned-documents</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>583</v>
+        <v>2446</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-17</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>oil-oil/video-publisher-skill</t>
+          <t>awesome-devblog/awesome-devblog</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>213</v>
+        <v>3582</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>23.3</v>
+        <v>6.1</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>准备视频、标题和封面为多平台草稿，支持恢复上传
-【原文】将视频、标题和封面准备为经过核验的多平台草稿，支持恢复上传，停在最终发布之前。</t>
+          <t>韩国技术博客列表
+【原文】어썸데브블로그. 국내 개발/기술 블로그 모음(only 실명으로).
+【依据】描述中提到技术博客列表</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -2918,7 +2886,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/oil-oil/video-publisher-skill</t>
+          <t>https://github.com/awesome-devblog/awesome-devblog</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2927,18 +2895,14 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>3.33</v>
+        <v>0.87</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2949,19 +2913,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr"/>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>awesome, blogs, devblog, developer, korean, tech-blog</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2015-06-16</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>64</v>
+        <v>4111</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>1</v>
@@ -2973,26 +2941,25 @@
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>infiniflow/infinity</t>
+          <t>DerpZhenjun/Partlawyer-LAA</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>4707</v>
+        <v>144</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>21.6</v>
+        <v>4.9</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>为 LLM 应用构建的 AI 原生数据库，提供快速混合搜索
-【原文】The AI-native database built for LLM applications, providing incredibly fast hybrid search of dense vector, sparse vector, tensor (multi-vector), and full-text.</t>
+          <t>基于数字人与(微调)大模型的劳动仲裁辅助平台，支持辅助生成仲裁文书与法律咨询。</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3002,7 +2969,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3017,7 +2984,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/infiniflow/infinity</t>
+          <t>https://github.com/DerpZhenjun/Partlawyer-LAA</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3026,16 +2993,16 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>3.09</v>
+        <v>0.7</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -3045,68 +3012,68 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>ai-native, approximate-nearest-neighbor-search, bm25, cpp20, cpp20-modules, embedding, full-text-search, hnsw, hybrid-search, information-retrival, multi-vector, nearest-neighbor-search</t>
+          <t>digital-human, document-generation, labor-arbitration</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2022-07-18</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>1521</v>
+        <v>207</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
+          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>mindee/doctr</t>
+          <t>ttop32/MouseTooltipTranslator</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>6347</v>
+        <v>1317</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>21.4</v>
+        <v>4.4</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>提供深度学习驱动的文档文本识别库
-【原文】docTR (Document Text Recognition) - a seamless, high-performing &amp; accessible library for OCR-related tasks powered by Deep Learning. Ongoing development and maintenance by t2k.
-【依据】topics: document-recognition, ocr</t>
+          <t>Chrome扩展，支持多种语言翻译和OCR功能
+【原文】Mouseover Translate Any Language At Once - Chrome Extension: PDF Translator, EBOOK, EPUB, OCR, TTS, NETFLIX, YOUTUBE DUAL SUBTITLES, GOOGLE DOCS, AI, VIEWER, GMAIL, WRITING, IMAGE, DUAL SUBS, MANGA, HOVER, DICTIONARY, WEBTOON, EDGE, JAPANESE, ENGLISH
+【依据】描述中提到OCR和翻译功能</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>图文产线/AI免费池</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3121,7 +3088,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mindee/doctr</t>
+          <t>https://github.com/ttop32/MouseTooltipTranslator</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3130,16 +3097,16 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>3.06</v>
+        <v>0.63</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -3154,21 +3121,21 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>deep-learning, document-recognition, ocr, optical-character-recognition, pytorch, tensorflow2, text-detection, text-detection-recognition, text-recognition</t>
+          <t>browser-extension, chatgpt, chrome, chrome-extension, dictionaries, dictionary, dual, ebook, epub, extension, manifest-v3, ocr</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>2077</v>
+        <v>2093</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>1</v>
@@ -3180,32 +3147,31 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="28" ht="150" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>ogkalu2/comic-translate</t>
+          <t>Berserk-hub150/moodle-ai-skill-navigator</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2937</v>
+        <v>217</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>21.3</v>
+        <v>3.8</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>自动翻译漫画和漫画的浏览器扩展/应用程序
-【原文】AI comic and manga translator app/browser extension for automatically translating comics, manga, manhwa, BDs, fumetti, and more in multiple languages and formats (Images, PDF, EPUB, CBR, CBZ etc).
-【依据】topics: ocr, machine-translation</t>
+          <t>提供AI驱动的Moodle插件，用于教学和评估
+【原文】AI-powered Moodle plugin for tutoring, quizzes, mind maps, RAG course materials and more.</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -3213,9 +3179,9 @@
           <t>技能包</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -3225,7 +3191,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ogkalu2/comic-translate</t>
+          <t>https://github.com/Berserk-hub150/moodle-ai-skill-navigator</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3234,16 +3200,16 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>3.04</v>
+        <v>0.54</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -3258,21 +3224,21 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>anime, comics, computer-vision, deep-learning, gui, inpainting, machine-translation, manga, manhua, manhwa, neural-network, ocr</t>
+          <t>artificial-intelligence, beginner-friendly, contributions-welcome, digital-twin, e-learning, edtech, first-contributions, generative-ai, good-first-issue, help-wanted, learning-management-system, moodle</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S28" s="3" t="n">
-        <v>965</v>
+        <v>403</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>1</v>
@@ -3284,41 +3250,40 @@
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>x-hw/amazing-qr</t>
+          <t>Lance-myk/Traditional-Chinese-Medicine-nihaisha</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>10816</v>
+        <v>62</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>20.6</v>
+        <v>3.4</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>生成支持动态GIF的二维码。
-【原文】💮 amazing QRCode generator (supporting animated gif) - amazing 二维码生成器（支持 gif 动态图片二维码）</t>
+          <t>开源整理倪海厦全套高清教学视频、原版PDF讲义、课件笔记，涵盖人纪、天纪全套体系，纯公益开源分享，助力传统中医、国学文化普惠自学与数字化传承。</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -3328,7 +3293,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/x-hw/amazing-qr</t>
+          <t>https://github.com/Lance-myk/Traditional-Chinese-Medicine-nihaisha</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3337,18 +3302,14 @@
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>2.94</v>
+        <v>0.49</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr"/>
       <c r="N29" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3356,58 +3317,56 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>amazing, gif, mcp, picture, qr, qr-code, qr-generator, qrcode, qrcode-generator, skills</t>
+          <t>nihaisha, self-study-of-traditional-chinese-medicine, tcm</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>2016-08-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="S29" s="3" t="n">
-        <v>3674</v>
+        <v>127</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-17</t>
+          <t>中医 in:name,description stars:&gt;50</t>
         </is>
       </c>
     </row>
     <row r="30" ht="150" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>seleniumbase/SeleniumBase</t>
+          <t>zelon88/HRConvert2</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>13015</v>
+        <v>1369</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>19.9</v>
+        <v>3.1</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>浏览器自动化、网络抓取和测试工具
-【原文】Browser automation, web scraping, and testing. CDP Mode provides a Stealthy Chromium instance that bypasses bot-detection systems. Includes an MCP server.
-【依据】topics: anti-detection, bot-detection, selenium</t>
+          <t>A self-hosted, respource aware file conversion server supporting 488 formats in 26 languages.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3417,12 +3376,12 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>MCP服务</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -3432,7 +3391,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/seleniumbase/SeleniumBase</t>
+          <t>https://github.com/zelon88/HRConvert2</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3441,16 +3400,16 @@
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>2.84</v>
+        <v>0.44</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -3460,26 +3419,26 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>anti-detection, bot-detection, chromedriver, chromium, data, e2e-testing, end-to-end-testing, playwright, pytest, python, python-scraper, selenium</t>
+          <t>antivirus, archiver, bootable-iso, conversion, converter, document-conversion, ebook, extractor, file-converter, file-sharing, format, image</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>2014-03-04</t>
+          <t>2018-02-24</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S30" s="3" t="n">
-        <v>4579</v>
+        <v>3127</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>1</v>
@@ -3491,1032 +3450,12 @@
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="150" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>partme-ai/full-stack-skills</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>661</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>提供免费的全栈开发AI技能市场
-【原文】这是一个免费的全栈开发所需的技能市场，提供各种实用的 AI 技能集合，支持多种平台。</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>技能包/代码库</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/partme-ai/full-stack-skills</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, claude-code, codebuddy, cursor, qoder, skills</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V31" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="150" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>adbar/trafilatura</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>6825</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>从网络爬取文本和元数据，输出为多种格式
-【原文】Python &amp; Command-line tool to gather text and metadata on the Web: Crawling, scraping, extraction, output as CSV, JSON, HTML, MD, TXT, XML</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/adbar/trafilatura</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>article-extractor, corpus-builder, corpus-tools, crawler, html-to-markdown, html2text, llm, news-aggregator, news-crawler, nlp, rag, readability</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>2019-04-08</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>2718</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
-        <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="150" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>wechatpay-apiv3/wechatpay-skills</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>352</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>提供微信支付Skills接口</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/wechatpay-apiv3/wechatpay-skills</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr"/>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>177</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V33" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="150" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>ballerine-io/ballerine</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>2430</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>风险决策的风险决策基础设施和数据编排平台
-【原文】Open-source infrastructure and data orchestration platform for risk decisioning
-【依据】topics: back-office, case-management, compliance</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>架构参考</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/ballerine-io/ballerine</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>back-office, case-management, compliance, dashboard, flow, fraud, id-card-camera, identity-verification, idv, know-your-customer, kyb, kyc</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="n">
-        <v>1445</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V34" s="6" t="inlineStr">
-        <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="150" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>apify/awesome-skills</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>253</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>收集Apify AI编码助手技能
-【原文】Community collection of Apify agent skills for AI coding assistants</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>技能包/代码库</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/apify/awesome-skills</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>actor, agent-skills, ai-agents, apify, awesome-list, mcp</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V35" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="150" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>dynobo/normcap</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>2722</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>OCR功能的屏幕截图工具
-【原文】OCR powered screen-capture tool to capture information instead of images
-【依据】topics: ocr, screenshot</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>古籍OCR线</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/dynobo/normcap</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>multiplatform, ocr, python, screenshot, tesserocr, tool</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t>2019-08-14</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>2590</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V36" s="6" t="inlineStr">
-        <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="150" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>FalkorDB/GraphRAG-SDK</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>使用GraphRAG SDK构建快速准确的GenAI应用程序。
-【原文】Build fast and accurate GenAI apps with GraphRAG SDK at scale  🌟
-【依据】Build fast and accurate GenAI apps with GraphRAG SDK at scale 🌟</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/FalkorDB/GraphRAG-SDK</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>falkordb, genai, graph-database, graphrag, knowledge-graph, llm, open-source, rag, sdk</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t>2024-01-25</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>965</v>
-      </c>
-      <c r="T37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V37" s="6" t="inlineStr">
-        <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="150" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>danjdewhurst/story-skills</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>提供故事写作的AI技能插件
-【原文】Agent Skills for end-to-end story writing in markdown, packaged as Codex and Claude Code plugins.</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/danjdewhurst/story-skills</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, ai-agents, claude-code-plugin, codex, codex-plugin, creative-writing, fiction-writing, markdown, plot-structure, skill-md, storytelling, worldbuilding</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V38" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="150" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>bangle-io/bangle-io</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>1231</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>提供本地Markdown格式笔记记录应用。
-【原文】A web only WYSIWYG note taking app that saves notes locally in markdown format. v2: https://app.bangle.io/</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/bangle-io/bangle-io</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>AGPL-3.0</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>knowledge-graph, local-first, markdown, markdown-notes, note-taker, notes, pwa, react, webworkers, wysiwyg</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>2020-12-23</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>2093</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V39" s="6" t="inlineStr">
-        <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="150" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>lucky-Luor/tcm-elderly-care-system</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>基于树莓派和大模型的中医居家健康养老系统。
-【原文】基于树莓派和大模型的中医居家健康养老系统 · 云端(Spring Boot 3 + Vue3)+ 树莓派边缘端(Python)</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/lucky-Luor/tcm-elderly-care-system</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P40" s="6" t="inlineStr"/>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V40" s="6" t="inlineStr">
-        <is>
-          <t>中医 大模型 in:name,description</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V40"/>
+  <autoFilter ref="A2:V30"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-17 · 共 28 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-18 · 共 25 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,19 +633,19 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>deepseek-ai/awesome-deepseek-agent</t>
+          <t>yi1108/printfilm</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>6091</v>
+        <v>579</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>298.1</v>
+        <v>506.7</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>DeepSeek Agent开源列表
-【依据】描述中提到开源列表</t>
+          <t>提供 AI 视频获客与 AI 短剧创作平台
+【原文】PRINTFILM：AI 视频获客与 AI短剧创作平台</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/deepseek-ai/awesome-deepseek-agent</t>
+          <t>https://github.com/yi1108/printfilm</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,14 +679,18 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>42.59</v>
+        <v>72.38</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -700,7 +704,7 @@
       <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -709,37 +713,38 @@
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>143</v>
+        <v>8</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-18</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>browserbase/stagehand</t>
+          <t>MemoriLabs/Memori</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>24314</v>
+        <v>16789</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>187.7</v>
+        <v>279.2</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>The SDK for browser agents. Interact, search, extract, and fetch any site reliably across the web</t>
+          <t>提供企业级 AI 内存基础设施
+【原文】Memori is agent-native memory infrastructure. A LLM-agnostic layer that turns agent execution and conversation into structured, persistent state for production systems. Built for enterprise, Memori works with the data infrastructure you already run, no rip-and-replace, and deploys across managed cloud, single-tenant cloud, VPC, and on-premises.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -754,7 +759,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -764,7 +769,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/browserbase/stagehand</t>
+          <t>https://github.com/MemoriLabs/Memori</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -773,16 +778,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>26.81</v>
+        <v>39.88</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -792,56 +797,57 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agents, ai, ai-agent, ai-agents, automation, browser, browser-agent, browser-automation, cdp, cloud-browser, data-extraction, harness</t>
+          <t>agent, agent-memory, agenticai, ai, ai-memory, claude-code, enterprise, hermes, llm, long-short-term-memory, memory, memory-management</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>907</v>
+        <v>421</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-18</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>harvard-edge/cs249r_book</t>
+          <t>Jakeschincariol/linkedin-agent-skill</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>28252</v>
+        <v>298</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>178.6</v>
+        <v>189.6</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Machine Learning Systems: Foundations, Scaling, Agentic AI, and Physical AI (Vols I–IV) • Harvard CS249r | https://mlsysbook.ai</t>
+          <t>运行 LinkedIn 账户的 Claude 技能
+【原文】Eleven free Claude skills that run a LinkedIn account: posts off 21 hook formulas, comments, replies, profile score, weekly plan, and a humanizer that strips the AI fingerprint and scores the draft before it goes out.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -856,7 +862,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -866,7 +872,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/harvard-edge/cs249r_book</t>
+          <t>https://github.com/Jakeschincariol/linkedin-agent-skill</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -875,11 +881,11 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>25.52</v>
+        <v>27.09</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -894,17 +900,17 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, ai-agents, artificial-intelligence, cloud-ml, computer-systems, courseware, deep-learning, edge-machine-learning, embedded-ml, embodied-ai, machine-learning, machine-learning-systems</t>
+          <t>agent-skills, ai-humanizer, claude, claude-code, claude-skills, content-marketing, linkedin</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -913,7 +919,7 @@
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1107</v>
+        <v>11</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -925,25 +931,27 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>liustack/modlens</t>
+          <t>modelbus/one-api-pro</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3975</v>
+        <v>791</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>134.4</v>
+        <v>98.8</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>The first vision plugin for DeepSeek Harness, and the vision bridge for every text-only coding agent. Paste an image, get structured JSON evidence (OCR, layout, semantics). | 全网最强 DeepSeek Harness 外挂视觉插件，为 DeepSeek、GLM 等纯文本模型外挂视觉能力，粘贴图片即得结构化 JSON 证据（OCR、版面、语义）。</t>
+          <t>提供企业级 AI API 网关服务
+【原文】one-api-pro is an enterprise-grade AI API Gateway built on one-api（oneapi）. It has undergone a full architectural redesign, adding support for subscription plans, active-active clusters, precise billing. 本项目与new-api | sub2api不同之处是one-api-pro是面向企业AI网关的应用场景，并不适用于中转站
+【依据】topics: one-api, one-api-pro, oneapi, openai</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -958,7 +966,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -968,7 +976,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/liustack/modlens</t>
+          <t>https://github.com/modelbus/one-api-pro</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -977,16 +985,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>19.2</v>
+        <v>14.12</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -996,67 +1004,67 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, claude-code, claude-skills, codex, cordis, deepseek, dsh, dsh-plugin, glm, harness, harness-engineering, hermes-agent</t>
+          <t>one-api, one-api-pro, oneapi, openai</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>207</v>
+        <v>56</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
+          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>vuejs/awesome-vue</t>
+          <t>can4hou6joeng4/boss-agent-cli</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>73544</v>
+        <v>2002</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>129.2</v>
+        <v>77</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>收集Vue.js相关资源列表
-【原文】🎉 A curated list of awesome things related to Vue.js</t>
+          <t>提供本地 AI 代理的 CLI 工具
+【原文】🤖 Local-assist BOSS Zhipin CLI for AI agents — search, welfare filtering, shortlist, JSON-envelope output; low-risk &amp; compliant by default.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>MCP服务/技能包</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1071,7 +1079,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vuejs/awesome-vue</t>
+          <t>https://github.com/can4hou6joeng4/boss-agent-cli</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1080,14 +1088,18 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>18.46</v>
+        <v>11</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1098,50 +1110,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>agent-skill, agent-tools, ai-agent, boss-zhipin, claude, cli, command-line, job-hunting, job-search, mcp, model-context-protocol, python</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2015-10-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3985</v>
+        <v>182</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-18</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>cookiy-ai/sell-sessions-skill</t>
+          <t>Andonywang123/Epost</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>218</v>
+        <v>107</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>117.4</v>
+        <v>62.4</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>销售会话技能
-【依据】描述中提到销售会话技能</t>
+          <t>提供社交平台一键发布与管理工具
+【原文】海内外热门社交平台的一键发布与管理工具，支持自媒体创作者跨平台发布；自动完成语言翻译、字幕烧录和跨时区发布设置。 | One-click publishing and management for global social platforms, with translation, burned-in subtitles, and timezone-aware scheduling.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1156,7 +1172,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1166,7 +1182,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cookiy-ai/sell-sessions-skill</t>
+          <t>https://github.com/Andonywang123/Epost</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1175,14 +1191,18 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>16.77</v>
+        <v>8.92</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1196,63 +1216,63 @@
       <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
+          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>CVHub520/X-AnyLabeling</t>
+          <t>lzhgus/Capso</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>10461</v>
+        <v>1334</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>60.3</v>
+        <v>58</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>提供跨平台图像、文本、视频标注工具，结合AI模型和内置工具
-【原文】X-AnyLabeling: A lightweight, efficient, and unified cross-platform desktop application for annotating text, image, video, and multimodal data, combining versatile built-in tools with state-of-the-art AI models and flexible multi-format export.
-【依据】描述中提到标注图像、文本、视频</t>
+          <t>提供 macOS 的开源截图和屏幕录制工具
+【原文】Open-source screenshot and screen recording for macOS. The free, native alternative to CleanShot X. Built with Swift 6.0 and SwiftUI.
+【依据】topics: annotation, cleanshot-alternative, macos, ocr, open-source, screen-recording, screenshot, swift, swiftui</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>图文产线/视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1262,7 +1282,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/CVHub520/X-AnyLabeling</t>
+          <t>https://github.com/lzhgus/Capso</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1271,16 +1291,16 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>8.619999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Swift</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1295,21 +1315,21 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>artificial-intelligence, clip, computer-vision, deep-learning, groundingdino, image-annotation-tool, image-classification, image-labeling-tool, image-matting, instance-segmentation, machine-learning, object-detection</t>
+          <t>annotation, cleanshot-alternative, macos, ocr, open-source, screen-recording, screenshot, swift, swiftui</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1213</v>
+        <v>161</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
@@ -1321,42 +1341,41 @@
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>hgmzhn/manga-translator-ui</t>
+          <t>my-take-dev/inspired-mino-design-skills</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2793</v>
+        <v>336</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>51</v>
+        <v>36.2</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>开源漫画AI翻译桌面工具，支持多种翻译引擎和OCR功能
-【原文】基于manga-image-translator 实现的开源漫画AI翻译桌面工具。支持日、韩、英文漫画自动处理，集成OpenAl、Gemini等多翻译引擎；实现OCR文字检测、原文擦除、AI翻译、图像修复、译文排版完整链路，自带可视化编辑器，支持自定义文本样式，一键部署开箱即用。
-【依据】描述中提到漫画图像翻译和OCR文字检测</t>
+          <t>从资料中整理开发技能
+【原文】ミノ駆動氏のWebに掲載されている資料から作成した開発スキル</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>图文产线/AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1366,7 +1385,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/hgmzhn/manga-translator-ui</t>
+          <t>https://github.com/my-take-dev/inspired-mino-design-skills</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1375,11 +1394,11 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>7.29</v>
+        <v>5.17</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1397,23 +1416,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>automated-translation, comic-translation, gemini, image-translator, machine-translation, manga-translato, ocr, openai, python, scanlation</t>
-        </is>
-      </c>
+      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>383</v>
+        <v>65</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1425,25 +1440,26 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Sumanth077/Hands-On-AI-Engineering</t>
+          <t>BaYue-SYJ/shuixian-prompts</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>3628</v>
+        <v>230</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>44.5</v>
+        <v>33.5</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>A curated collection of practical AI projects implementing OCR systems, RAG, AI agents, and other AI use cases.</t>
+          <t>提供中文 AI 绘画提示词库
+【原文】水仙的AI提示词｜5,000+ 中文 AI 绘画提示词库：检索 / 分类 / 一键复制。提示词覆盖 ChatGPT、Grok、Gemini、Midjourney、Stable Diffusion、Flux、即梦、可灵、豆包、海螺、文心一格等主流生图模型。源码 + 数据集开源，图片走 R2。</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1458,7 +1474,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1468,7 +1484,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Sumanth077/Hands-On-AI-Engineering</t>
+          <t>https://github.com/BaYue-SYJ/shuixian-prompts</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1477,16 +1493,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>6.36</v>
+        <v>4.79</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1496,72 +1512,72 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>agents, ai, ai-agents, ai-engineering, generative-ai, llms, mcp, ocr, python, rag</t>
+          <t>ai-art, ai-drawing, aigc, chatgpt, chinese, dall-e, doubao, flux, gemini, grok, image-generation, jimeng</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>570</v>
+        <v>48</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>irinabuht12-oss/marketing-skills</t>
+          <t>landing-ai/ade-cli</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>1498</v>
+        <v>2417</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>43.9</v>
+        <v>30.4</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>提供48个免费Claude营销技能和Ryze MCP服务
-【原文】48 free Claude marketing skills (Google Ads, Meta Ads, SEO, AI visibility) + Ryze MCP: claude mcp add ryze --transport http https://connector.get-ryze.ai/mcp</t>
+          <t>提供文档解析和结构化数据提取的命令行工具
+【原文】The official CLI for Agentic Document Extraction (ADE) by LandingAI — parse documents and extract schema-shaped data from your terminal</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包/MCP服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1571,7 +1587,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/irinabuht12-oss/marketing-skills</t>
+          <t>https://github.com/landing-ai/ade-cli</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1580,14 +1596,18 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>6.27</v>
+        <v>4.35</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1600,21 +1620,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>ai-visibility, claude-code, claude-plugin, claude-skills, cursor, geo, google-ads, marketing, mcp, mcp-server, meta-ads, seo</t>
+          <t>agentic-document-extraction, cli, document-extraction, document-parsing, ocr, pdf</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>239</v>
+        <v>555</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1626,36 +1646,36 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>feichanggege/ecommerce-visual-copywriting-skill</t>
+          <t>spf13/go-skills</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>770</v>
+        <v>653</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>34.8</v>
+        <v>25.6</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供电商视觉文案设计SOP Skill，兼容多种AI工具
-【原文】电商视觉文案设计SOP Skill - 让电商设计小白也能一键做出5年资深设计经验的商品图片.兼容 Claude / Codex / Cursor / Workbuddy 等 SKILL.md Agent. AI-powered e-commerce visual strategy skill for main images, PDP/A+, copywriting, localization, evidence-aware compliance and image prompts.</t>
+          <t>提供 Go 语言技能库
+【依据】spf13/go-skills</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1670,7 +1690,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/feichanggege/ecommerce-visual-copywriting-skill</t>
+          <t>https://github.com/spf13/go-skills</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1679,18 +1699,14 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>4.97</v>
+        <v>3.65</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1701,23 +1717,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, ai-image-generation-api, amazon, copywriting, ecommerce, prompt-engineering, shopify, tiktok-shop-affiliate</t>
-        </is>
-      </c>
+      <c r="P13" s="6" t="inlineStr"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1729,25 +1741,26 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>datawhalechina/llms-from-scratch-cn</t>
+          <t>intercom/2x-skills</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>4367</v>
+        <v>240</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>32.8</v>
+        <v>21</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>仅需Python基础，从0构建大语言模型；从0逐步构建GLM4\Llama3\RWKV6， 深入理解大模型原理</t>
+          <t>收集和整理通用的 Claude 技能
+【原文】A collection of claude skills we think are generic enough to be useful to everyone</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1762,7 +1775,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1772,7 +1785,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/datawhalechina/llms-from-scratch-cn</t>
+          <t>https://github.com/intercom/2x-skills</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1781,16 +1794,16 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>4.69</v>
+        <v>3</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1800,17 +1813,13 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>glm, llama, llm, llms-from-scratch, rwkv</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
@@ -1819,37 +1828,38 @@
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>932</v>
+        <v>80</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>vercel-labs/next-skills</t>
+          <t>breezedeus/Pix2Text</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>981</v>
+        <v>3245</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>29</v>
+        <v>15.4</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>提供Next.js技能</t>
+          <t>提供图像中的布局、表格、公式和文本的识别工具
+【原文】An Open-Source Python3 tool with SMALL models for recognizing layouts, tables, math formulas (LaTeX), and text in images, converting them into Markdown format. A free alternative to Mathpix, empowering seamless conversion of visual content into text-based representations. 80+ languages are supported.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1864,7 +1874,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1874,7 +1884,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vercel-labs/next-skills</t>
+          <t>https://github.com/breezedeus/Pix2Text</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1883,14 +1893,18 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>4.14</v>
+        <v>2.2</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Jupyter Notebook</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1901,19 +1915,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>image-to-markdown, latex, latex-pdf, layout-analysis, math-formula, math-formula-recognition, math-ocr, mathpix, ocr, python, pytorch, table-ocr</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>237</v>
+        <v>1472</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1925,37 +1943,36 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>filtalgo/Filtmall-Shopping-Skill</t>
+          <t>benjaminasterA/antigravity-awesome-skills</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>348</v>
+        <v>298</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>21.8</v>
+        <v>10</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>购物代理技能，提供价格验证和购物流程服务
-【原文】Agent-native shopping for extreme value: verifiable same-product price evidence, checkout, orders, delivery, and after-sales.
-【依据】描述中提到购物代理和价格验证</t>
+          <t>提供 antigravity 技能
+【原文】antigravity-awesome-skills</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1970,7 +1987,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/filtalgo/Filtmall-Shopping-Skill</t>
+          <t>https://github.com/benjaminasterA/antigravity-awesome-skills</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1979,16 +1996,16 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>3.11</v>
+        <v>1.43</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2001,14 +2018,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, ai-agent, claude-skills, ecommerce, filtalgo, filtmall, openclaw, product-search, shopping, skillsmp</t>
-        </is>
-      </c>
+      <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -2017,7 +2030,7 @@
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>112</v>
+        <v>208</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2029,25 +2042,26 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Zchary1106/agent-interview-hub</t>
+          <t>akuity/awesome-argo</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>510</v>
+        <v>2490</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>20.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>AI Agent 工程师面试资料库 - 国内大厂面经、岗位要求、高频面试题</t>
+          <t>收集和整理与 Argo 相关的项目和资源
+【原文】A curated list of awesome projects and resources related to Argo (a CNCF graduated project)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2072,7 +2086,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Zchary1106/agent-interview-hub</t>
+          <t>https://github.com/akuity/awesome-argo</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2081,18 +2095,14 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>2.93</v>
+        <v>1.4</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2100,57 +2110,57 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, chinese, claude, interview, langchain, llm, machine-learning, mcp, prompt-engineering, rag</t>
+          <t>argo, argo-events, argo-rollouts, argo-workflows, argocd, awesome, awesome-list, awesome-lists, cloud-native, cncf, continuous-delivery, devops</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>174</v>
+        <v>1782</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-18</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>EpicGames/unreal-engine-skills-for-claude-code-plugin</t>
+          <t>dracohu2025-cloud/draco-skills-collection</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>290</v>
+        <v>226</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>20.1</v>
+        <v>9.5</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Unreal Engine Claude Code插件技能
-【依据】描述中提到插件技能</t>
+          <t>收集 Draco 技能
+【依据】draco-skills-collection</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2160,12 +2170,12 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -2175,7 +2185,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/EpicGames/unreal-engine-skills-for-claude-code-plugin</t>
+          <t>https://github.com/dracohu2025-cloud/draco-skills-collection</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2184,16 +2194,16 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>2.87</v>
+        <v>1.35</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2209,7 +2219,7 @@
       <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -2218,7 +2228,7 @@
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
@@ -2230,36 +2240,36 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>qdrant/fastembed</t>
+          <t>joe-shenouda/awesome-cyber-skills</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>3204</v>
+        <v>4678</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>19.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>提供快速、精确、轻量级的Python库进行高级嵌入
-【原文】Fast, Accurate, Lightweight Python library to make State of the Art Embedding</t>
+          <t>收集和整理合法安全地进行网络安全技能训练的环境
+【原文】A curated list of hacking environments where you can train your cyber skills legally and safely</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2274,7 +2284,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/qdrant/fastembed</t>
+          <t>https://github.com/joe-shenouda/awesome-cyber-skills</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2283,18 +2293,14 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>2.76</v>
+        <v>1.32</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2305,26 +2311,22 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>embeddings, openai, rag, retrieval, retrieval-augmented-generation, vector-search</t>
-        </is>
-      </c>
+      <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2017-01-04</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>1161</v>
+        <v>3544</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
@@ -2333,36 +2335,36 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-18</t>
+          <t>skills in:name stars:&gt;500 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>mattt/iMCP</t>
+          <t>yennanliu/InvestSkill</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1549</v>
+        <v>214</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>19.3</v>
+        <v>7</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>为MacOS提供MCP服务器
-【原文】A macOS app that provides an MCP server to your Messages, Contacts, Reminders and more</t>
+          <t>为 LLM 提供美国股市分析技能
+【原文】US stock analysis skills for LLMs (Claude code, Gemini ...)  | #AI</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2377,7 +2379,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mattt/iMCP</t>
+          <t>https://github.com/yennanliu/InvestSkill</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2386,7 +2388,7 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>2.76</v>
+        <v>1</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -2395,7 +2397,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2410,21 +2412,21 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>macos, mcp</t>
+          <t>agent, financial, financial-analysis, gemini, investment, llm, stock, stock-market, us-stock</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>561</v>
+        <v>214</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
@@ -2436,41 +2438,41 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>smixs/visual-skills</t>
+          <t>xiaofengShi/CHINESE-OCR</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>389</v>
+        <v>2956</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>18.9</v>
+        <v>6.7</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>提供AI电影导演技能，用于生成视觉内容
-【原文】AI film director skills for agents: cinematic dramaturgy (Murch, blocking, montage) + exact prompt syntax for Seedance 2.5, Kling 3.0 Turbo/Omni, Veo 3.1, Nano Banana 2, GPT Image 2.5.</t>
+          <t>提供端到端中文场景文本检测和识别功能
+【原文】End-to-end Chinese scene-text detection and recognition with CTPN, CRNN, and CTC (legacy project).</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2480,7 +2482,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/smixs/visual-skills</t>
+          <t>https://github.com/xiaofengShi/CHINESE-OCR</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2489,14 +2491,18 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>2.7</v>
+        <v>0.96</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr"/>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2509,21 +2515,21 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>ai-image-generation, ai-prompts, ai-video-generation, claude, claude-agent-sdk, claude-code, claude-skills, cline, creative-director, cursor, generative-ai, gpt-image</t>
+          <t>chinese-ocr, crnn, ctpn, keras-crnn, legacy-project, lstm-ctc, ocr, pytorch-crnn, scene-text-recognition, tensorflow</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2018-04-14</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>144</v>
+        <v>3079</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
@@ -2535,37 +2541,36 @@
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>sindresorhus/awesome-whisper</t>
+          <t>ab604/claude-code-r-skills</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2383</v>
+        <v>202</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>13.6</v>
+        <v>6.1</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Whisper语音识别系统开源列表
-【原文】🔊 Awesome list for Whisper — an open-source AI-powered speech recognition system developed by OpenAI
-【依据】描述中提到Whisper语音识别系统</t>
+          <t>提供 Claude Code R 开发配置
+【原文】Claude Code configurations for R development.</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2580,7 +2585,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sindresorhus/awesome-whisper</t>
+          <t>https://github.com/ab604/claude-code-r-skills</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2589,14 +2594,18 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1.94</v>
+        <v>0.87</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2607,14 +2616,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>ai, artificial-intelligence, awesome, awesome-list, gpt, openai, speech-to-text, transcription</t>
-        </is>
-      </c>
+      <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -2623,7 +2628,7 @@
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1226</v>
+        <v>232</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
@@ -2635,25 +2640,27 @@
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-18</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>enoch3712/ExtractThinker</t>
+          <t>Anil-matcha/awesome-vibecoded-saas</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1598</v>
+        <v>1013</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11.7</v>
+        <v>5.7</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>ExtractThinker is a Document Intelligence library for LLMs, offering ORM-style interaction for flexible and powerful document workflows.</t>
+          <t>提供开源的 SaaS 工具替代方案
+【原文】Open-source alternatives to the SaaS tools people pay for
+【依据】topics: ai-apps, ai-tools, awesome, awesome-list, content-creation, creative-tools, generative-ai, marketing-tools, open</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -2678,7 +2685,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/enoch3712/ExtractThinker</t>
+          <t>https://github.com/Anil-matcha/awesome-vibecoded-saas</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2687,11 +2694,11 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>1.67</v>
+        <v>0.82</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2706,68 +2713,68 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>ai, document-image-analysis, document-intelligence, document-parsing, document-processing, langchain, llm, machine-learning, nlp, ocr, openai, pdf</t>
+          <t>ai-apps, ai-tools, awesome, awesome-list, content-creation, creative-tools, generative-ai, marketing-tools, open-source, open-source-alternatives, open-source-apps, productivity-tools</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>959</v>
+        <v>1231</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
+          <t>topic:content-creation stars:&gt;1000 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>ciur/papermerge</t>
+          <t>robocorp/rpaframework</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2936</v>
+        <v>1563</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>开源数字档案文档管理系统，支持扫描文档管理
-【原文】Open Source Document Management System for Digital Archives (Scanned Documents)
-【依据】描述中提到文档管理系统和OCR</t>
+          <t>提供 RPA 工具和库集合
+【原文】Collection of open-source libraries and tools for Robotic Process Automation (RPA), designed to be used with both Robot Framework and Python
+【依据】topics: ai, automation, documentai, nlp, ocr, opencv, python, robocorp, robot, robotframework, rpa, rpa-robots</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2782,7 +2789,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ciur/papermerge</t>
+          <t>https://github.com/robocorp/rpaframework</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2791,7 +2798,7 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>1.2</v>
+        <v>0.64</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -2815,21 +2822,21 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>archives, django, dms, document-management, ocr, paperless, pdf, scan, scanned-documents</t>
+          <t>ai, automation, documentai, nlp, ocr, opencv, python, robocorp, robot, robotframework, rpa, rpa-robots</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2020-01-06</t>
+          <t>2020-01-02</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>2446</v>
+        <v>2451</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>1</v>
@@ -2841,27 +2848,26 @@
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>awesome-devblog/awesome-devblog</t>
+          <t>sismics/docs</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>3582</v>
+        <v>2564</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>韩国技术博客列表
-【原文】어썸데브블로그. 국내 개발/기술 블로그 모음(only 실명으로).
-【依据】描述中提到技术博客列表</t>
+          <t>提供轻量级文档管理系统，支持文件共享和文档管理
+【原文】Lightweight document management system packed with all the features you can expect from big expensive solutions</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -2871,12 +2877,12 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -2886,7 +2892,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/awesome-devblog/awesome-devblog</t>
+          <t>https://github.com/sismics/docs</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2895,14 +2901,18 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.87</v>
+        <v>0.53</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr"/>
+          <t>GPL-2.0</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2915,21 +2925,21 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>awesome, blogs, devblog, developer, korean, tech-blog</t>
+          <t>cloud, dms, docker, document, enterprise, file-sharing, java, javascript, ocr, open-source, self-hosting, sharing</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2015-06-16</t>
+          <t>2013-07-27</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>4111</v>
+        <v>4801</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>1</v>
@@ -2941,25 +2951,26 @@
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-18</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>DerpZhenjun/Partlawyer-LAA</t>
+          <t>zacharywhitley/awesome-ocr</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>144</v>
+        <v>1024</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>基于数字人与(微调)大模型的劳动仲裁辅助平台，支持辅助生成仲裁文书与法律咨询。</t>
+          <t>收集和整理 OCR 相关的资源和项目
+【依据】A curated list of awesome projects and resources related to OCR</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2974,7 +2985,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -2984,7 +2995,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/DerpZhenjun/Partlawyer-LAA</t>
+          <t>https://github.com/zacharywhitley/awesome-ocr</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2993,18 +3004,14 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.7</v>
+        <v>0.39</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr"/>
       <c r="N26" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3012,68 +3019,68 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>digital-human, document-generation, labor-arbitration</t>
+          <t>awesome, awesome-list, deep-learning, machine, machine-learning, ocr, ocr-recognition</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2019-07-23</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>207</v>
+        <v>2614</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-06-19</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>ttop32/MouseTooltipTranslator</t>
+          <t>mittagessen/kraken</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>1317</v>
+        <v>1070</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Chrome扩展，支持多种语言翻译和OCR功能
-【原文】Mouseover Translate Any Language At Once - Chrome Extension: PDF Translator, EBOOK, EPUB, OCR, TTS, NETFLIX, YOUTUBE DUAL SUBTITLES, GOOGLE DOCS, AI, VIEWER, GMAIL, WRITING, IMAGE, DUAL SUBS, MANGA, HOVER, DICTIONARY, WEBTOON, EDGE, JAPANESE, ENGLISH
-【依据】描述中提到OCR和翻译功能</t>
+          <t>提供多种语言的 OCR 引擎服务
+【原文】OCR engine for all the languages
+【依据】topics: alto-xml, handwritten-text-recognition, hocr, htr, layout-analysis, neural-networks, ocr, optical-character-reco</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>图文产线/AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3088,7 +3095,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ttop32/MouseTooltipTranslator</t>
+          <t>https://github.com/mittagessen/kraken</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3097,16 +3104,16 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.63</v>
+        <v>0.26</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -3121,21 +3128,21 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>browser-extension, chatgpt, chrome, chrome-extension, dictionaries, dictionary, dual, ebook, epub, extension, manifest-v3, ocr</t>
+          <t>alto-xml, handwritten-text-recognition, hocr, htr, layout-analysis, neural-networks, ocr, optical-character-recognition, page-xml</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2020-12-24</t>
+          <t>2015-05-19</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>2093</v>
+        <v>4140</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>1</v>
@@ -3147,315 +3154,12 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Berserk-hub150/moodle-ai-skill-navigator</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>217</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>提供AI驱动的Moodle插件，用于教学和评估
-【原文】AI-powered Moodle plugin for tutoring, quizzes, mind maps, RAG course materials and more.</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>RAG检索线</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/Berserk-hub150/moodle-ai-skill-navigator</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>GPL-3.0</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>PHP</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>artificial-intelligence, beginner-friendly, contributions-welcome, digital-twin, e-learning, edtech, first-contributions, generative-ai, good-first-issue, help-wanted, learning-management-system, moodle</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>403</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V28" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="150" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Lance-myk/Traditional-Chinese-Medicine-nihaisha</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>开源整理倪海厦全套高清教学视频、原版PDF讲义、课件笔记，涵盖人纪、天纪全套体系，纯公益开源分享，助力传统中医、国学文化普惠自学与数字化传承。</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/Lance-myk/Traditional-Chinese-Medicine-nihaisha</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>nihaisha, self-study-of-traditional-chinese-medicine, tcm</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V29" s="6" t="inlineStr">
-        <is>
-          <t>中医 in:name,description stars:&gt;50</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>zelon88/HRConvert2</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>1369</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>A self-hosted, respource aware file conversion server supporting 488 formats in 26 languages.</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/zelon88/HRConvert2</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>GPL-3.0</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>PHP</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>antivirus, archiver, bootable-iso, conversion, converter, document-conversion, ebook, extractor, file-converter, file-sharing, format, image</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t>2018-02-24</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>3127</v>
-      </c>
-      <c r="T30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V30" s="6" t="inlineStr">
-        <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-19</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V30"/>
+  <autoFilter ref="A2:V27"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-18 · 共 25 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-19 · 共 28 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,29 +633,29 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>yi1108/printfilm</t>
+          <t>modelscope/ms-cookbook</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>579</v>
+        <v>318</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>506.7</v>
+        <v>278.2</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 视频获客与 AI 短剧创作平台
-【原文】PRINTFILM：AI 视频获客与 AI短剧创作平台</t>
+          <t>提供模型应用实战指南，涵盖模型选型、推理等
+【原文】魔搭紫皮书｜ModelScope Cookbook：面向开发者的开源模型应用实战指南，覆盖模型选型、推理、微调、评测、RAG、Agent 与 AIGC，从跑通第一个模型到构建实际应用。</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/RAG检索线</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>MCP服务/代码库</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yi1108/printfilm</t>
+          <t>https://github.com/modelscope/ms-cookbook</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>72.38</v>
+        <v>39.75</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -701,15 +701,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>ai-agents, cookbook, diffusion-models, fine-tuning, generative-ai, llm, mcp, model-evaluation, modelscope, rag</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
@@ -725,41 +729,41 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-20</t>
+          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-06-21</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MemoriLabs/Memori</t>
+          <t>Pinvou/pinvou-agent</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>16789</v>
+        <v>2003</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>279.2</v>
+        <v>246</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>提供企业级 AI 内存基础设施
-【原文】Memori is agent-native memory infrastructure. A LLM-agnostic layer that turns agent execution and conversation into structured, persistent state for production systems. Built for enterprise, Memori works with the data infrastructure you already run, no rip-and-replace, and deploys across managed cloud, single-tenant cloud, VPC, and on-premises.</t>
+          <t>开源桌面AI代理，支持工具、文件、知识等
+【原文】Open-source desktop AI agent for tools, files, knowledge, workflows, and real deliverables.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>MCP服务/技能包/架构参考</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -769,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MemoriLabs/Memori</t>
+          <t>https://github.com/Pinvou/pinvou-agent</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -778,16 +782,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>39.88</v>
+        <v>35.14</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -802,62 +806,62 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agent, agent-memory, agenticai, ai, ai-memory, claude-code, enterprise, hermes, llm, long-short-term-memory, memory, memory-management</t>
+          <t>ai-agent, automation, desktop-app, llm, local-first, mcp, open-source, react, rust, tauri</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>421</v>
+        <v>57</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-19</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Jakeschincariol/linkedin-agent-skill</t>
+          <t>StarTrail-org/LEANN</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>298</v>
+        <v>12946</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>189.6</v>
+        <v>194</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>运行 LinkedIn 账户的 Claude 技能
-【原文】Eleven free Claude skills that run a LinkedIn account: posts off 21 hook formulas, comments, replies, profile score, weekly plan, and a humanizer that strips the AI fingerprint and scores the draft before it goes out.</t>
+          <t>提供基于LEANN的RAG应用，支持快速、准确和隐私保护
+【原文】[MLsys2026 Best Paper]: https://arxiv.org/abs/2506.08276. RAG on Everything with LEANN. Enjoy 97% storage savings while running a fast, accurate, and 100% private RAG application on your personal device.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Jakeschincariol/linkedin-agent-skill</t>
+          <t>https://github.com/StarTrail-org/LEANN</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -881,7 +885,7 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>27.09</v>
+        <v>27.72</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -905,21 +909,21 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-humanizer, claude, claude-code, claude-skills, content-marketing, linkedin</t>
+          <t>ai, faiss, gpt-oss, langchain, llama-index, llm, localstorage, offline-first, ollama, privacy, python, rag</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>11</v>
+        <v>467</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -931,27 +935,26 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>modelbus/one-api-pro</t>
+          <t>carnot-tech/consulting-pptx-skill</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>791</v>
+        <v>466</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>98.8</v>
+        <v>191.9</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供企业级 AI API 网关服务
-【原文】one-api-pro is an enterprise-grade AI API Gateway built on one-api（oneapi）. It has undergone a full architectural redesign, adding support for subscription plans, active-active clusters, precise billing. 本项目与new-api | sub2api不同之处是one-api-pro是面向企业AI网关的应用场景，并不适用于中转站
-【依据】topics: one-api, one-api-pro, oneapi, openai</t>
+          <t>AI 辅助生成 PPTX 的 Claude Code 技能
+【原文】AIにまじなPPTXを作らせるClaude Codeスキル — スライド規約＋62型スライド型カタログ（SlideSpec 36型＋自由記述27パーツ）＋生成パイプライン＋機械チェック</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -961,12 +964,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -976,7 +979,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/modelbus/one-api-pro</t>
+          <t>https://github.com/carnot-tech/consulting-pptx-skill</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -985,16 +988,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>14.12</v>
+        <v>27.41</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1007,14 +1010,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>one-api, one-api-pro, oneapi, openai</t>
-        </is>
-      </c>
+      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1023,48 +1022,48 @@
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-06-20</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>can4hou6joeng4/boss-agent-cli</t>
+          <t>frankbria/ralph-claude-code</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2002</v>
+        <v>9638</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>77</v>
+        <v>173.9</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供本地 AI 代理的 CLI 工具
-【原文】🤖 Local-assist BOSS Zhipin CLI for AI agents — search, welfare filtering, shortlist, JSON-envelope output; low-risk &amp; compliant by default.</t>
+          <t>Claude Code的自动AI开发循环工具
+【原文】Autonomous AI development loop for Claude Code with intelligent exit detection</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1079,7 +1078,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/can4hou6joeng4/boss-agent-cli</t>
+          <t>https://github.com/frankbria/ralph-claude-code</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1088,7 +1087,7 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>11</v>
+        <v>24.84</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -1097,7 +1096,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1112,24 +1111,24 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>agent-skill, agent-tools, ai-agent, boss-zhipin, claude, cli, command-line, job-hunting, job-search, mcp, model-context-protocol, python</t>
+          <t>ai, ai-agent, ai-agents, ai-development, ai-development-tools, claude-code, claude-code-cli, development-tools, development-workflow</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>182</v>
+        <v>388</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
@@ -1138,41 +1137,41 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-19</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Andonywang123/Epost</t>
+          <t>DenisSergeevitch/agents-best-practices</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>107</v>
+        <v>2337</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>62.4</v>
+        <v>128.8</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供社交平台一键发布与管理工具
-【原文】海内外热门社交平台的一键发布与管理工具，支持自媒体创作者跨平台发布；自动完成语言翻译、字幕烧录和跨时区发布设置。 | One-click publishing and management for global social platforms, with translation, burned-in subtitles, and timezone-aware scheduling.</t>
+          <t>提供Codex、Claude Code等代理技能
+【原文】Provider-neutral Agent Skill for Codex, Claude Code, and agentic harness design.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1182,7 +1181,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Andonywang123/Epost</t>
+          <t>https://github.com/DenisSergeevitch/agents-best-practices</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1191,18 +1190,14 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>8.92</v>
+        <v>18.4</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1213,66 +1208,69 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>agent-skill, agent-skills, agentic-workflows, agents, ai-agents, anthropic, claude, claude-code, codex, codex-skill, mcp, prompt-engineering</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-20</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>lzhgus/Capso</t>
+          <t>LetMeHappyCode/auto-video-agent</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1334</v>
+        <v>220</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>58</v>
+        <v>128.3</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>提供 macOS 的开源截图和屏幕录制工具
-【原文】Open-source screenshot and screen recording for macOS. The free, native alternative to CleanShot X. Built with Swift 6.0 and SwiftUI.
-【依据】topics: annotation, cleanshot-alternative, macos, ocr, open-source, screen-recording, screenshot, swift, swiftui</t>
+          <t>自动生成视频，包括分镜插画提示词、AI 生图和拼接成片
+【原文】自动流水线化生成成套「分镜插画提示词 → AI 生图 → 拼接成片」的视频，基于 Agent / Skill / Workflow 编排。</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1282,7 +1280,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lzhgus/Capso</t>
+          <t>https://github.com/LetMeHappyCode/auto-video-agent</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1291,16 +1289,16 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>8.289999999999999</v>
+        <v>18.33</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1313,69 +1311,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>annotation, cleanshot-alternative, macos, ocr, open-source, screen-recording, screenshot, swift, swiftui</t>
-        </is>
-      </c>
+      <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>161</v>
+        <v>12</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-21</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>my-take-dev/inspired-mino-design-skills</t>
+          <t>mukul975/cve-mcp-server</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>336</v>
+        <v>1578</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>36.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>从资料中整理开发技能
-【原文】ミノ駆動氏のWebに掲載されている資料から作成した開発スキル</t>
+          <t>提供 Claude 27 安全智能工具的生产级 MCP 服务器
+【原文】Production-grade MCP server giving Claude 27 security intelligence tools across 21 APIs — CVE lookup, EPSS scoring, CISA KEV, MITRE ATT&amp;CK, Shodan, VirusTotal, and more.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>MCP服务/技能包</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1385,7 +1379,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/my-take-dev/inspired-mino-design-skills</t>
+          <t>https://github.com/mukul975/cve-mcp-server</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1394,11 +1388,11 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5.17</v>
+        <v>9.99</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1416,19 +1410,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>cisa-kev, claude-ai, cve, cybersecurity, devsecops, epss, fastmcp, mcp, mitre-attack, model-context-protocol, nvd, osv</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1440,41 +1438,41 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>BaYue-SYJ/shuixian-prompts</t>
+          <t>feyninc/chonkie</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>230</v>
+        <v>4754</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>33.5</v>
+        <v>61.7</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>提供中文 AI 绘画提示词库
-【原文】水仙的AI提示词｜5,000+ 中文 AI 绘画提示词库：检索 / 分类 / 一键复制。提示词覆盖 ChatGPT、Grok、Gemini、Midjourney、Stable Diffusion、Flux、即梦、可灵、豆包、海螺、文心一格等主流生图模型。源码 + 数据集开源，图片走 R2。</t>
+          <t>用于快速、高效和稳健 RAG 管道的轻量级文档库
+【原文】🦛 CHONK docs with Chonkie ✨ — The lightweight ingestion library for fast, efficient and robust RAG pipelines</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1484,7 +1482,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/BaYue-SYJ/shuixian-prompts</t>
+          <t>https://github.com/feyninc/chonkie</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1493,16 +1491,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>4.79</v>
+        <v>8.82</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1517,12 +1515,12 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai-art, ai-drawing, aigc, chatgpt, chinese, dall-e, doubao, flux, gemini, grok, image-generation, jimeng</t>
+          <t>ai, chonkie, chunker, chunking-algorithm, llms, rag, retrieval-systems, semantic-chunker, similarity-search, splitting-algorithms, text-splitter</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1531,43 +1529,43 @@
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>48</v>
+        <v>539</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-20</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>landing-ai/ade-cli</t>
+          <t>zyddnys/manga-image-translator</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2417</v>
+        <v>10424</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>30.4</v>
+        <v>35.8</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>提供文档解析和结构化数据提取的命令行工具
-【原文】The official CLI for Agentic Document Extraction (ADE) by LandingAI — parse documents and extract schema-shaped data from your terminal</t>
+          <t>一键翻译图片内文字，包括漫画和图像
+【原文】Translate manga/image 一键翻译各类图片内文字 https://cotrans.touhou.ai/ (no longer working)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1575,9 +1573,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1587,7 +1585,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/landing-ai/ade-cli</t>
+          <t>https://github.com/zyddnys/manga-image-translator</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1596,11 +1594,11 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>4.35</v>
+        <v>5.11</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1620,21 +1618,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agentic-document-extraction, cli, document-extraction, document-parsing, ocr, pdf</t>
+          <t>anime, auto-translation, chinese-translation, deep-learning, image-processing, inpainting, japanese-translations, machine-translation, manga, neural-network, ocr, pytorch-implementation</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>555</v>
+        <v>2039</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1646,26 +1644,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>spf13/go-skills</t>
+          <t>ai-for-developers/awesome-ai-coding-tools</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>653</v>
+        <v>2082</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>25.6</v>
+        <v>32.5</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供 Go 语言技能库
-【依据】spf13/go-skills</t>
+          <t>收集AI编程工具的列表
+【原文】A curated list of AI-powered coding tools</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1690,7 +1688,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/spf13/go-skills</t>
+          <t>https://github.com/ai-for-developers/awesome-ai-coding-tools</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1699,7 +1697,7 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>3.65</v>
+        <v>4.64</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -1717,10 +1715,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>ai-code-generation, ai-code-generator, ai-coding, ai-coding-assistant, ai-coding-tools, ai-developer, ai-developer-tools, ai-development, ai-development-tools, ai-devtools, ai-ide, ai-security</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -1729,7 +1731,7 @@
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>179</v>
+        <v>449</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1741,26 +1743,26 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>intercom/2x-skills</t>
+          <t>WJZ-P/gemini-skill</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>240</v>
+        <v>831</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>21</v>
+        <v>30.4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>收集和整理通用的 Claude 技能
-【原文】A collection of claude skills we think are generic enough to be useful to everyone</t>
+          <t>Gemini 画图 MCP 和 skill，支持龙虾或任何 agent 使用
+【原文】gemini drawing MCP &amp; skill through browser, can be used in openclaw or any agent that supports MCP. Gemini画图 MCP和sill，支持龙虾或任何agent使用٩(๑&gt;◡&lt;๑)۶</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1770,7 +1772,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1785,7 +1787,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/intercom/2x-skills</t>
+          <t>https://github.com/WJZ-P/gemini-skill</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1794,7 +1796,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1803,7 +1805,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1816,19 +1818,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>automation, browser-automation, drawing, gemini, mcp, mcp-client, mcp-server, openclaw, openclaw-agent, openclaw-skills, openclawskill</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1840,26 +1846,26 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>breezedeus/Pix2Text</t>
+          <t>ayangweb/Awesome-BongoCat</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>3245</v>
+        <v>2005</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>15.4</v>
+        <v>29.3</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>提供图像中的布局、表格、公式和文本的识别工具
-【原文】An Open-Source Python3 tool with SMALL models for recognizing layouts, tables, math formulas (LaTeX), and text in images, converting them into Markdown format. A free alternative to Mathpix, empowering seamless conversion of visual content into text-based representations. 80+ languages are supported.</t>
+          <t>汇集第三方BongoCat模型
+【原文】🚀 汇聚优质的第三方 BongoCat 模型！</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1874,7 +1880,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1884,7 +1890,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/breezedeus/Pix2Text</t>
+          <t>https://github.com/ayangweb/Awesome-BongoCat</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1893,18 +1899,14 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>2.2</v>
+        <v>4.19</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Jupyter Notebook</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1917,21 +1919,21 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>image-to-markdown, latex, latex-pdf, layout-analysis, math-formula, math-formula-recognition, math-ocr, mathpix, ocr, python, pytorch, table-ocr</t>
+          <t>awesome-bongo-cat, awesome-bongocat, bongo-cat, bongocat</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>1472</v>
+        <v>478</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1943,26 +1945,26 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>benjaminasterA/antigravity-awesome-skills</t>
+          <t>beiyege-01/dsh-voice-ai-girlfriend</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>298</v>
+        <v>103</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>10</v>
+        <v>20.6</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>提供 antigravity 技能
-【原文】antigravity-awesome-skills</t>
+          <t>语音AI女友，支持语音输入和声音克隆
+【原文】语音 AI 女友（Voice AI girlfriend for DeepSeek Harness）：Whisper 语音输入 + Qwen3-TTS 声音克隆 + 句子级流式朗读 + 数字人动画窗。插话/排队双模式，说话即打断。</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1977,7 +1979,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1987,7 +1989,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/benjaminasterA/antigravity-awesome-skills</t>
+          <t>https://github.com/beiyege-01/dsh-voice-ai-girlfriend</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1996,16 +1998,16 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1.43</v>
+        <v>2.94</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2018,65 +2020,69 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>ai-girlfriend, companion, deepseek-harness, digital-human, dsh, dsh-plugin, speech-to-speech, tts, voice-assistant, voice-clone, whisper</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>208</v>
+        <v>35</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
+          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-06-21</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>akuity/awesome-argo</t>
+          <t>heshengtao/comfyui_LLM_party</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2490</v>
+        <v>2363</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>9.800000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>收集和整理与 Argo 相关的项目和资源
-【原文】A curated list of awesome projects and resources related to Argo (a CNCF graduated project)</t>
+          <t>提供LLM Agent框架，包括MCP服务器和多种功能节点
+【原文】LLM Agent Framework in ComfyUI includes MCP sever, Omost,GPT-sovits, ChatTTS,GOT-OCR2.0, and FLUX prompt nodes,access to Feishu,discord,and adapts to all llms with similar openai / aisuite interfaces, such as o1,ollama, gemini, grok, qwen, GLM, deepseek, kimi,doubao. Adapted to local llms, vlm, gguf such as llama-3.3 Janus-Pro, Linkage graphRAG</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>MCP服务/技能包/架构参考</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2086,7 +2092,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/akuity/awesome-argo</t>
+          <t>https://github.com/heshengtao/comfyui_LLM_party</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2095,14 +2101,18 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>1.4</v>
+        <v>2.66</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr"/>
+          <t>AGPL-3.0</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2115,21 +2125,21 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>argo, argo-events, argo-rollouts, argo-workflows, argocd, awesome, awesome-list, awesome-lists, cloud-native, cncf, continuous-delivery, devops</t>
+          <t>agent, comfyui, dify, flux, gemini, gguf, gpt-sovits, graphrag, janus-pro, linux, llama, mcp</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>1782</v>
+        <v>889</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
@@ -2141,26 +2151,26 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-19</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>dracohu2025-cloud/draco-skills-collection</t>
+          <t>mars-tw/open-seo-advisor-skill</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>9.5</v>
+        <v>18.6</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>收集 Draco 技能
-【依据】draco-skills-collection</t>
+          <t>全域 SEO 顧問技能，协助 SEO 健檢、修復、内容产出
+【原文】開源、可攜、不綁定單一廠商的全域 SEO 顧問技能 - 蒸餾 SEO 權威方法論，協助任何產業做 SEO 健檢、修復、內容產出</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2170,12 +2180,12 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -2185,7 +2195,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dracohu2025-cloud/draco-skills-collection</t>
+          <t>https://github.com/mars-tw/open-seo-advisor-skill</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2194,16 +2204,16 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>1.35</v>
+        <v>2.66</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2219,16 +2229,16 @@
       <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
@@ -2240,41 +2250,41 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>joe-shenouda/awesome-cyber-skills</t>
+          <t>Dicklesworthstone/llm_aided_ocr</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>4678</v>
+        <v>3001</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>收集和整理合法安全地进行网络安全技能训练的环境
-【原文】A curated list of hacking environments where you can train your cyber skills legally and safely</t>
+          <t>使用LLM增强Tesseract OCR输出，支持错误纠正
+【原文】Enhances Tesseract OCR output using LLMs (local or API) for error correction, smart chunking, and markdown formatting of scanned PDFs</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -2284,7 +2294,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/joe-shenouda/awesome-cyber-skills</t>
+          <t>https://github.com/Dicklesworthstone/llm_aided_ocr</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2293,14 +2303,18 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>1.32</v>
+        <v>2.61</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2311,22 +2325,26 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr"/>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>ai-assist, llama2, llm, ocr, ocr-correction, tesseract</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2017-01-04</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>3544</v>
+        <v>1151</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
@@ -2335,26 +2353,26 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>skills in:name stars:&gt;500 pushed:&gt;2026-06-20</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>yennanliu/InvestSkill</t>
+          <t>Prohao42/aimy-skill</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>7</v>
+        <v>12.9</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>为 LLM 提供美国股市分析技能
-【原文】US stock analysis skills for LLMs (Claude code, Gemini ...)  | #AI</t>
+          <t>轻量级 AI Agent 渗透测试辅助技能
+【原文】aimy-skill 是一个轻量级、可嵌入 AI Agent 的渗透测试辅助技能，专为授权环境下的自动化信息收集和基础漏洞探测设计。它可以被 AI 助手（如 AutoGPT、LangChain 应用）调用，也可以独立命令行运行。</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2364,7 +2382,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2379,7 +2397,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yennanliu/InvestSkill</t>
+          <t>https://github.com/Prohao42/aimy-skill</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2388,7 +2406,7 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1</v>
+        <v>1.84</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -2397,7 +2415,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2410,23 +2428,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>agent, financial, financial-analysis, gemini, investment, llm, stock, stock-market, us-stock</t>
-        </is>
-      </c>
+      <c r="P20" s="6" t="inlineStr"/>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>214</v>
+        <v>109</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
@@ -2438,41 +2452,41 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>xiaofengShi/CHINESE-OCR</t>
+          <t>Topdu/OpenOCR</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2956</v>
+        <v>1453</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>6.7</v>
+        <v>12.1</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>提供端到端中文场景文本检测和识别功能
-【原文】End-to-end Chinese scene-text detection and recognition with CTPN, CRNN, and CTC (legacy project).</t>
+          <t>开源OCR工具包，支持文档分析和处理
+【原文】OpenOCR: An Open-Source Toolkit for General-OCR Research and Applications, integrates a unified training and evaluation benchmark, commercial-grade OCR and Document Parsing systems, and faithful reproductions of the core implementations from a wide range of academic papers.</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2482,7 +2496,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/xiaofengShi/CHINESE-OCR</t>
+          <t>https://github.com/Topdu/OpenOCR</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2491,11 +2505,11 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.96</v>
+        <v>1.73</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2515,21 +2529,21 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>chinese-ocr, crnn, ctpn, keras-crnn, legacy-project, lstm-ctc, ocr, pytorch-crnn, scene-text-recognition, tensorflow</t>
+          <t>chineseocr, document-analysis, document-parsing, document-processing, ocr, ocr-pytorch, scene-text-detection, scene-text-recognition</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>3079</v>
+        <v>841</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
@@ -2541,26 +2555,26 @@
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ab604/claude-code-r-skills</t>
+          <t>ombulabs/claude-code_rails-upgrade-skill</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>202</v>
+        <v>386</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>6.1</v>
+        <v>11.6</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude Code R 开发配置
-【原文】Claude Code configurations for R development.</t>
+          <t>Rails 应用升级辅助技能
+【原文】🤖 The one and only Claude Code Skill to Upgrade Rails by FastRuby.io -- Based on 60,000 dev/hours of experience upgrading Rails from 2.3 all the way to 8.1. Dual boot your Rails application and gradually upgrade one minor version at a time.  🚀</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2570,7 +2584,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2585,7 +2599,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ab604/claude-code-r-skills</t>
+          <t>https://github.com/ombulabs/claude-code_rails-upgrade-skill</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2594,7 +2608,7 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.87</v>
+        <v>1.66</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2617,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2616,15 +2630,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P22" s="6" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>claude-code, claude-code-skill, claude-code-skills, ruby-on-rails, technical-debt</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
@@ -2640,32 +2658,31 @@
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-19</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Anil-matcha/awesome-vibecoded-saas</t>
+          <t>kha-white/manga-ocr</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1013</v>
+        <v>2781</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>5.7</v>
+        <v>11.4</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>提供开源的 SaaS 工具替代方案
-【原文】Open-source alternatives to the SaaS tools people pay for
-【依据】topics: ai-apps, ai-tools, awesome, awesome-list, content-creation, creative-tools, generative-ai, marketing-tools, open</t>
+          <t>进行日本漫画文本的光学字符识别
+【原文】Optical character recognition for Japanese text, with the main focus being Japanese manga</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -2685,7 +2702,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Anil-matcha/awesome-vibecoded-saas</t>
+          <t>https://github.com/kha-white/manga-ocr</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2694,11 +2711,11 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.82</v>
+        <v>1.63</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2718,53 +2735,52 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>ai-apps, ai-tools, awesome, awesome-list, content-creation, creative-tools, generative-ai, marketing-tools, open-source, open-source-alternatives, open-source-apps, productivity-tools</t>
+          <t>comics, computer-vision, deep-learning, japanese, manga, ocr, transformers</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
+          <t>2022-01-15</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1231</v>
+        <v>1708</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>topic:content-creation stars:&gt;1000 pushed:&gt;2026-06-20</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>robocorp/rpaframework</t>
+          <t>railwayapp/railway-skills</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1563</v>
+        <v>325</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>提供 RPA 工具和库集合
-【原文】Collection of open-source libraries and tools for Robotic Process Automation (RPA), designed to be used with both Robot Framework and Python
-【依据】topics: ai, automation, documentai, nlp, ocr, opencv, python, robocorp, robot, robotframework, rpa, rpa-robots</t>
+          <t>与 Railway 交互的 Agent 技能
+【原文】Agent skills for interacting with Railway</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2774,7 +2790,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2789,7 +2805,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/robocorp/rpaframework</t>
+          <t>https://github.com/railwayapp/railway-skills</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2798,11 +2814,11 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.64</v>
+        <v>1.26</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2822,21 +2838,21 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>ai, automation, documentai, nlp, ocr, opencv, python, robocorp, robot, robotframework, rpa, rpa-robots</t>
+          <t>agents, infrastructure, railway</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2020-01-02</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>2451</v>
+        <v>258</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>1</v>
@@ -2848,31 +2864,31 @@
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>sismics/docs</t>
+          <t>kha-white/mokuro</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2564</v>
+        <v>1725</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>3.7</v>
+        <v>7.5</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>提供轻量级文档管理系统，支持文件共享和文档管理
-【原文】Lightweight document management system packed with all the features you can expect from big expensive solutions</t>
+          <t>在浏览器中阅读日本漫画，支持文本选择
+【原文】Read Japanese manga inside browser with selectable text.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -2892,7 +2908,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sismics/docs</t>
+          <t>https://github.com/kha-white/mokuro</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2901,16 +2917,16 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.53</v>
+        <v>1.07</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>GPL-2.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2925,21 +2941,21 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>cloud, dms, docker, document, enterprise, file-sharing, java, javascript, ocr, open-source, self-hosting, sharing</t>
+          <t>comics, comics-reader, japanese, manga, manga-reader, ocr</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2013-07-27</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>4801</v>
+        <v>1617</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>1</v>
@@ -2951,26 +2967,26 @@
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
         </is>
       </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>zacharywhitley/awesome-ocr</t>
+          <t>amebalabs/TRex</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>1024</v>
+        <v>1909</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>收集和整理 OCR 相关的资源和项目
-【依据】A curated list of awesome projects and resources related to OCR</t>
+          <t>屏幕文字复制工具，支持文本识别和截图
+【原文】Copy any text on your screen, stop retyping.</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2985,7 +3001,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -2995,7 +3011,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zacharywhitley/awesome-ocr</t>
+          <t>https://github.com/amebalabs/TRex</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3004,14 +3020,18 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.39</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Swift</t>
+        </is>
+      </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3024,21 +3044,21 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, deep-learning, machine, machine-learning, ocr, ocr-recognition</t>
+          <t>macos, ocr, productivity, screenshot, swift, textrecognition, tools</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2019-07-23</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>2614</v>
+        <v>2038</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>1</v>
@@ -3050,27 +3070,26 @@
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
         </is>
       </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>mittagessen/kraken</t>
+          <t>ahkscript/awesome-AutoHotkey</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>1070</v>
+        <v>3087</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>提供多种语言的 OCR 引擎服务
-【原文】OCR engine for all the languages
-【依据】topics: alto-xml, handwritten-text-recognition, hocr, htr, layout-analysis, neural-networks, ocr, optical-character-reco</t>
+          <t>收集AutoHotkey库、脚本、工具和资源
+【原文】A curated list of awesome AutoHotkey libraries, library distributions, scripts, tools and resources.</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3085,7 +3104,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -3095,7 +3114,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mittagessen/kraken</t>
+          <t>https://github.com/ahkscript/awesome-AutoHotkey</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3104,18 +3123,14 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.26</v>
+        <v>0.7</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr"/>
       <c r="N27" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3126,23 +3141,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>alto-xml, handwritten-text-recognition, hocr, htr, layout-analysis, neural-networks, ocr, optical-character-recognition, page-xml</t>
-        </is>
-      </c>
+      <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2015-05-19</t>
+          <t>2014-08-04</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>4140</v>
+        <v>4429</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>1</v>
@@ -3154,12 +3165,313 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-20</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="150" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>sirfz/tesserocr</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>2172</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Tesseract OCR API的Python封装库
+【原文】A Python wrapper for the tesseract-ocr API</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>古籍OCR线</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/sirfz/tesserocr</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>cython, ocr, optical-character-recognition, python-library, tesseract</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>2015-12-17</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>3929</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V28" s="6" t="inlineStr">
+        <is>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>44bits/awesome-opensource-documents</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>2329</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>收集开源文档、指南和书籍的列表
+【原文】:blue_book: A curated list of awesome open source or open source licensed documents, guides, books.</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/44bits/awesome-opensource-documents</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>2015-05-14</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>4146</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V29" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>toki-plus/ai-video-workflow</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>全自动AI视频生成工作流，支持多种内容创作
+【原文】全自动AI原生视频生成工作流，集成文生图(LibLib)/图生视频(即梦)/文生音乐(即梦)和AI提示词生成(豆包)，一键创作AIGC短视频。generative-ai, text-to-video, image-to-video, text-to-music, aigc, automation, pyqt5.</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/toki-plus/ai-video-workflow</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>ai-content-creation, aigc, automation, bot, content-creation, ffmpeg, llm, pyqt5, python, short-video, tiktok, video-processing</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V30" s="6" t="inlineStr">
+        <is>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-21</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V27"/>
+  <autoFilter ref="A2:V30"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-19 · 共 28 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-20 · 共 27 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,29 +633,29 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>modelscope/ms-cookbook</t>
+          <t>liyupi/ai-model-world</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>318</v>
+        <v>123</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>278.2</v>
+        <v>287</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>提供模型应用实战指南，涵盖模型选型、推理等
-【原文】魔搭紫皮书｜ModelScope Cookbook：面向开发者的开源模型应用实战指南，覆盖模型选型、推理、微调、评测、RAG、Agent 与 AIGC，从跑通第一个模型到构建实际应用。</t>
+          <t>展示556个AI大模型的排行榜和可视化信息
+【原文】AI 大模型世界，把 556 个大模型拟人化成像素小人的可视化站点。进来就能看到此刻谁最聪明、谁最会写代码、谁最便宜、谁刚发布，往下是国内与国外分区的厂商广场、完整的发布时间线和多维排行榜。搜索认模型名、厂商和能力，输入「多模态」会直接列出全部多模态模型。数据取自 Epoch AI、models.dev、LiveBench 与 Hugging Face，每小时自动同步，所有文案由真实数据生成，不调用任何 LLM。Next.js 静态导出，零后端。</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/modelscope/ms-cookbook</t>
+          <t>https://github.com/liyupi/ai-model-world</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>39.75</v>
+        <v>41</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -703,21 +703,21 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, cookbook, diffusion-models, fine-tuning, generative-ai, llm, mcp, model-evaluation, modelscope, rag</t>
+          <t>ai, ai-models, benchmark, chinese, data-visualization, deepseek, large-language-models, leaderboard, llm, llm-benchmarks, llm-leaderboard, model-comparison</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -729,36 +729,36 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-06-21</t>
+          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Pinvou/pinvou-agent</t>
+          <t>HUANGCHIHHUNGLeo/claude-real-video</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2003</v>
+        <v>2163</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>246</v>
+        <v>184.7</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>开源桌面AI代理，支持工具、文件、知识等
-【原文】Open-source desktop AI agent for tools, files, knowledge, workflows, and real deliverables.</t>
+          <t>允许LLM观看视频，提取场景感知帧和转录本
+【原文】Let Claude (or any LLM) actually watch a video — scene-aware, deduplicated frames + transcript, from a URL or local file. Runs locally, MIT.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>视频产线/古籍OCR线</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Pinvou/pinvou-agent</t>
+          <t>https://github.com/HUANGCHIHHUNGLeo/claude-real-video</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>35.14</v>
+        <v>26.38</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, automation, desktop-app, llm, local-first, mcp, open-source, react, rust, tauri</t>
+          <t>claude, claude-code, cli, codex, codex-cli, ffmpeg, keyframe-extraction, llm, multimodal, ocr, openai-codex, python</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -820,53 +820,53 @@
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-20</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>StarTrail-org/LEANN</t>
+          <t>HRuiCcc/RuiC-card-skill</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>12946</v>
+        <v>342</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>194</v>
+        <v>184.2</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>提供基于LEANN的RAG应用，支持快速、准确和隐私保护
-【原文】[MLsys2026 Best Paper]: https://arxiv.org/abs/2506.08276. RAG on Everything with LEANN. Enjoy 97% storage savings while running a fast, accurate, and 100% private RAG application on your personal device.</t>
+          <t>生成3D全息闪卡网页的Agent Skill
+【原文】全息闪卡通用 Agent Skill：多模态模型都能用，不挑宿主——一句话生成可拖转、会流光、带层次景深的 3D 闪卡网页，附可编辑 Blender 工程</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>图文产线/AI免费池</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/StarTrail-org/LEANN</t>
+          <t>https://github.com/HRuiCcc/RuiC-card-skill</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>27.72</v>
+        <v>26.31</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -909,21 +909,21 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>ai, faiss, gpt-oss, langchain, llama-index, llm, localstorage, offline-first, ollama, privacy, python, rag</t>
+          <t>agent-skill, agent-skills, blender, collectible-card, holographic, multimodal, skills, threejs, webgl</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>467</v>
+        <v>13</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -935,41 +935,41 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-20</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>carnot-tech/consulting-pptx-skill</t>
+          <t>jingyunstudio/jingyun-dsh</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>191.9</v>
+        <v>146.7</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>AI 辅助生成 PPTX 的 Claude Code 技能
-【原文】AIにまじなPPTXを作らせるClaude Codeスキル — スライド規約＋62型スライド型カタログ（SlideSpec 36型＋自由記述27パーツ）＋生成パイプライン＋機械チェック</t>
+          <t>AI商业化桌面客户端，将AI智能体转化为商业产品
+【原文】基于 Jingyun Studio + DeepSeek Harness (DSH) 打造的一站式 AI 商业化桌面客户端，一个将 AI 智能体 / 技能 / 工作流转化为可交易商品的完整商业化平台客户端。  井云为 DSH 注入了完整的商业闭环：登录注册 → 会员体系 → 订阅支付 → 云端资产 → 多端同步，让 AI 开发者 30 分钟内将自己的智能体封装为独立的商业产品。</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>MCP服务/可部署服务</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/carnot-tech/consulting-pptx-skill</t>
+          <t>https://github.com/jingyunstudio/jingyun-dsh</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>27.41</v>
+        <v>20.96</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1010,60 +1010,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>deepseekharness, dsh, dsh-bundle, dsh-plugin, dsh-plugin-desktop, dsh-plugin-market, dsh-plugin-verify, dsh-plugins, dsh-skill</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>frankbria/ralph-claude-code</t>
+          <t>dexhunter/seedance2-skill</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9638</v>
+        <v>3812</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>173.9</v>
+        <v>120.8</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Claude Code的自动AI开发循环工具
-【原文】Autonomous AI development loop for Claude Code with intelligent exit detection</t>
+          <t>生成视频生成最佳提示词的技能
+【原文】skill to create best prompts for generating videos with seedance2.0
+【依据】topics: prompt, seedance, seedance-2, video-prompt</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1078,7 +1083,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/frankbria/ralph-claude-code</t>
+          <t>https://github.com/dexhunter/seedance2-skill</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1087,18 +1092,14 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>24.84</v>
+        <v>17.25</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1111,12 +1112,12 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agent, ai-agents, ai-development, ai-development-tools, claude-code, claude-code-cli, development-tools, development-workflow</t>
+          <t>prompt, seedance, seedance-2, video-prompt</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -1125,48 +1126,49 @@
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>388</v>
+        <v>221</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-20</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>DenisSergeevitch/agents-best-practices</t>
+          <t>Kappaemme-git/codex-first-customer-finder-skill</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2337</v>
+        <v>1048</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>128.8</v>
+        <v>104.8</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供Codex、Claude Code等代理技能
-【原文】Provider-neutral Agent Skill for Codex, Claude Code, and agentic harness design.</t>
+          <t>寻找潜在的首批客户
+【原文】A Codex skill that finds evidence-backed potential first customers from recent public signals.
+【依据】topics: codex, codex-skill, customer-discovery, early-adopters, prospecting, startup</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1181,7 +1183,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/DenisSergeevitch/agents-best-practices</t>
+          <t>https://github.com/Kappaemme-git/codex-first-customer-finder-skill</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1190,14 +1192,18 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>18.4</v>
+        <v>14.97</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1210,67 +1216,67 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>agent-skill, agent-skills, agentic-workflows, agents, ai-agents, anthropic, claude, claude-code, codex, codex-skill, mcp, prompt-engineering</t>
+          <t>codex, codex-skill, customer-discovery, early-adopters, prospecting, startup</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-20</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>LetMeHappyCode/auto-video-agent</t>
+          <t>pot-app/pot-desktop</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>220</v>
+        <v>19425</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>128.3</v>
+        <v>104.4</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>自动生成视频，包括分镜插画提示词、AI 生图和拼接成片
-【原文】自动流水线化生成成套「分镜插画提示词 → AI 生图 → 拼接成片」的视频，基于 Agent / Skill / Workflow 编排。</t>
+          <t>提供跨平台的划词翻译和OCR软件
+【原文】🌈一个跨平台的划词翻译和OCR软件 | A cross-platform software for text translation and recognition.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>图文产线/AI免费池/视频产线</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
+          <t>MCP服务/技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1280,7 +1286,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LetMeHappyCode/auto-video-agent</t>
+          <t>https://github.com/pot-app/pot-desktop</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1289,16 +1295,16 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>18.33</v>
+        <v>14.92</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1311,65 +1317,69 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>linux, macos, ocr, pot, pot-app, recognize, tauri, translate, translation, tts, windows</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>12</v>
+        <v>1302</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-21</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>mukul975/cve-mcp-server</t>
+          <t>AccumulateMore/CV</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1578</v>
+        <v>23767</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>101.9</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude 27 安全智能工具的生产级 MCP 服务器
-【原文】Production-grade MCP server giving Claude 27 security intelligence tools across 21 APIs — CVE lookup, EPSS scoring, CISA KEV, MITRE ATT&amp;CK, Shodan, VirusTotal, and more.</t>
+          <t>提供深度学习笔记资源集合
+【原文】✅（已完结）超级全面的 深度学习 笔记【土堆 Pytorch】【李沐 动手学深度学习】【吴恩达 深度学习】【大飞 大模型Agent】</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1379,7 +1389,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mukul975/cve-mcp-server</t>
+          <t>https://github.com/AccumulateMore/CV</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1388,16 +1398,16 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>9.99</v>
+        <v>14.55</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1412,62 +1422,62 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>cisa-kev, claude-ai, cve, cybersecurity, devsecops, epss, fastmcp, mcp, mitre-attack, model-context-protocol, nvd, osv</t>
+          <t>agent, agents, book, chinese, computer-vision, cv, deep-learning, jupyter-notebook, llm, llms, machine-learning, natural-language-processing</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>158</v>
+        <v>1634</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-20</t>
+          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>feyninc/chonkie</t>
+          <t>yuxino/kiri</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4754</v>
+        <v>454</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>61.7</v>
+        <v>60</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>用于快速、高效和稳健 RAG 管道的轻量级文档库
-【原文】🦛 CHONK docs with Chonkie ✨ — The lightweight ingestion library for fast, efficient and robust RAG pipelines</t>
+          <t>提供本地化截图、标注、OCR、录屏和视频剪辑功能
+【原文】Local-first screenshots, annotation, OCR, screen recording and video editing for macOS and Windows. 截图标注、文字识别、录屏与视频剪辑。</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>图文产线/AI免费池/视频产线</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>MCP服务/技能包/可部署服务</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1482,7 +1492,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/feyninc/chonkie</t>
+          <t>https://github.com/yuxino/kiri</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1491,7 +1501,7 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>8.82</v>
+        <v>8.57</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1500,7 +1510,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1515,57 +1525,57 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai, chonkie, chunker, chunking-algorithm, llms, rag, retrieval-systems, semantic-chunker, similarity-search, splitting-algorithms, text-splitter</t>
+          <t>annotation, desktop-app, image-annotation, local-first, macos, ocr, screen-capture, screen-recorder, screenshot, tauri, text-recognition, video-editing</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>539</v>
+        <v>53</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-20</t>
+          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>zyddnys/manga-image-translator</t>
+          <t>manyuegong33/r0crawl_skills</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>10424</v>
+        <v>232</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>35.8</v>
+        <v>36.1</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>一键翻译图片内文字，包括漫画和图像
-【原文】Translate manga/image 一键翻译各类图片内文字 https://cotrans.touhou.ai/ (no longer working)</t>
+          <t>提供逆向工程技能工具集
+【原文】r0crawl_skills is a massive reverse-engineering skill arsenal for web, Android, iOS, Frida, native binaries, protocols, malware, firmware, and anti-analysis—built for beginners, tuned for pros, and engineered for reproducible results.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1573,9 +1583,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1585,7 +1595,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zyddnys/manga-image-translator</t>
+          <t>https://github.com/manyuegong33/r0crawl_skills</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1594,16 +1604,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>5.11</v>
+        <v>5.16</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1616,23 +1626,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>anime, auto-translation, chinese-translation, deep-learning, image-processing, inpainting, japanese-translations, machine-translation, manga, neural-network, ocr, pytorch-implementation</t>
-        </is>
-      </c>
+      <c r="P12" s="6" t="inlineStr"/>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>2039</v>
+        <v>45</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1644,26 +1650,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ai-for-developers/awesome-ai-coding-tools</t>
+          <t>ramjke/Translumo</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2082</v>
+        <v>5771</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>32.5</v>
+        <v>33.9</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>收集AI编程工具的列表
-【原文】A curated list of AI-powered coding tools</t>
+          <t>提供游戏、视频、静态文本的实时屏幕翻译功能
+【原文】Advanced real-time screen translator for games, hardcoded subtitles in videos, static text and etc.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1688,7 +1694,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ai-for-developers/awesome-ai-coding-tools</t>
+          <t>https://github.com/ramjke/Translumo</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1697,14 +1703,18 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>4.64</v>
+        <v>4.84</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1717,21 +1727,21 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>ai-code-generation, ai-code-generator, ai-coding, ai-coding-assistant, ai-coding-tools, ai-developer, ai-developer-tools, ai-development, ai-development-tools, ai-devtools, ai-ide, ai-security</t>
+          <t>autotranslate, easyocr, game-translation, mlnet, ocr, translation</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>449</v>
+        <v>1192</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1743,31 +1753,31 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-20</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>WJZ-P/gemini-skill</t>
+          <t>renmu2017/Hell-Grind-AIGC-Skill</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>831</v>
+        <v>201</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Gemini 画图 MCP 和 skill，支持龙虾或任何 agent 使用
-【原文】gemini drawing MCP &amp; skill through browser, can be used in openclaw or any agent that supports MCP. Gemini画图 MCP和sill，支持龙虾或任何agent使用٩(๑&gt;◡&lt;๑)۶</t>
+          <t>AI故事片《Hell Grind》的AIGC视频生产工作流Skill
+【原文】Higgsfield 的 95 分钟 AI 故事片《Hell Grind》 全部提示词和制作方法抽取出来的Skill。这一套模型无关的 AIGC 视频生产工作流，将项目搭建、资产与镜头管理、图片/视频提示词生成与润色、生成记录、连续性检查和交付验收整合到一个 Skill 中。</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/AI免费池</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1787,7 +1797,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/WJZ-P/gemini-skill</t>
+          <t>https://github.com/renmu2017/Hell-Grind-AIGC-Skill</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1796,7 +1806,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1815,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1818,69 +1828,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>automation, browser-automation, drawing, gemini, mcp, mcp-client, mcp-server, openclaw, openclaw-agent, openclaw-skills, openclawskill</t>
-        </is>
-      </c>
+      <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>191</v>
+        <v>46</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>ayangweb/Awesome-BongoCat</t>
+          <t>jipraks/yt-short-clipper</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2005</v>
+        <v>1001</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>29.3</v>
+        <v>28.3</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>汇集第三方BongoCat模型
-【原文】🚀 汇聚优质的第三方 BongoCat 模型！</t>
+          <t>将长视频转换为短视频剪辑，具有AI高光检测、人脸追踪和字幕功能
+【原文】Windows desktop app that turns long-form YouTube videos into 9:16 short-form clips — AI highlight detection, face-tracking portrait reframe, and word-by-word captions.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1890,7 +1896,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ayangweb/Awesome-BongoCat</t>
+          <t>https://github.com/jipraks/yt-short-clipper</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1899,14 +1905,18 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>4.19</v>
+        <v>4.04</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1919,52 +1929,53 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>awesome-bongo-cat, awesome-bongocat, bongo-cat, bongocat</t>
+          <t>ai-video, content-creation, ffmpeg, instagram-reels, llm, mediapipe, python, react, rust, short-form-video, tauri, tauri-app</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>478</v>
+        <v>248</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-20</t>
+          <t>topic:content-creation stars:&gt;1000 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>beiyege-01/dsh-voice-ai-girlfriend</t>
+          <t>yunshu0909/yunshu_skillshub</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>103</v>
+        <v>760</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>20.6</v>
+        <v>21.8</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>语音AI女友，支持语音输入和声音克隆
-【原文】语音 AI 女友（Voice AI girlfriend for DeepSeek Harness）：Whisper 语音输入 + Qwen3-TTS 声音克隆 + 句子级流式朗读 + 数字人动画窗。插话/排队双模式，说话即打断。</t>
+          <t>提供 Claude Code Skills 集合
+【原文】云舒精选的 Claude Code Skills 集合，提升开发和产品管理效率
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1979,7 +1990,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1989,7 +2000,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/beiyege-01/dsh-voice-ai-girlfriend</t>
+          <t>https://github.com/yunshu0909/yunshu_skillshub</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1998,16 +2009,16 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2020,69 +2031,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>ai-girlfriend, companion, deepseek-harness, digital-human, dsh, dsh-plugin, speech-to-speech, tts, voice-assistant, voice-clone, whisper</t>
-        </is>
-      </c>
+      <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>35</v>
+        <v>244</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-06-21</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>heshengtao/comfyui_LLM_party</t>
+          <t>caol64/wenyan-mcp</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2363</v>
+        <v>1316</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>提供LLM Agent框架，包括MCP服务器和多种功能节点
-【原文】LLM Agent Framework in ComfyUI includes MCP sever, Omost,GPT-sovits, ChatTTS,GOT-OCR2.0, and FLUX prompt nodes,access to Feishu,discord,and adapts to all llms with similar openai / aisuite interfaces, such as o1,ollama, gemini, grok, qwen, GLM, deepseek, kimi,doubao. Adapted to local llms, vlm, gguf such as llama-3.3 Janus-Pro, Linkage graphRAG</t>
+          <t>提供Markdown文章排版后发布至微信公众号的功能
+【原文】文颜 MCP Server 可以让 AI 自动将 Markdown 文章排版后发布至微信公众号。</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>MCP服务</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2092,7 +2099,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/heshengtao/comfyui_LLM_party</t>
+          <t>https://github.com/caol64/wenyan-mcp</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2101,16 +2108,16 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2125,62 +2132,62 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>agent, comfyui, dify, flux, gemini, gguf, gpt-sovits, graphrag, janus-pro, linux, llama, mcp</t>
+          <t>mcp-server, wechat, wenyan</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>889</v>
+        <v>475</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
+          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>mars-tw/open-seo-advisor-skill</t>
+          <t>PaddlePaddle/PaddleX</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>213</v>
+        <v>6267</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>全域 SEO 顧問技能，协助 SEO 健檢、修復、内容产出
-【原文】開源、可攜、不綁定單一廠商的全域 SEO 顧問技能 - 蒸餾 SEO 權威方法論，協助任何產業做 SEO 健檢、修復、內容產出</t>
+          <t>基于PaddlePaddle的AI开发工具，支持多种任务
+【原文】All-in-One Development Tool based on PaddlePaddle</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2195,7 +2202,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mars-tw/open-seo-advisor-skill</t>
+          <t>https://github.com/PaddlePaddle/PaddleX</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2204,7 +2211,7 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2226,19 +2233,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>ai-pipelines, classification, deployment, formula-recognition, layout-detection, object-detection, ocr, pdf2markdown, pp-chatocr, segmentation, speech-recognition, time-series</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>80</v>
+        <v>2384</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
@@ -2250,26 +2261,26 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Dicklesworthstone/llm_aided_ocr</t>
+          <t>lets-mica/mica-ppocr</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>3001</v>
+        <v>108</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>18.3</v>
+        <v>14.3</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>使用LLM增强Tesseract OCR输出，支持错误纠正
-【原文】Enhances Tesseract OCR output using LLMs (local or API) for error correction, smart chunking, and markdown formatting of scanned PDFs</t>
+          <t>提供PP-OCRv6纯Java图片OCR功能，支持行驶证、身份证等识别
+【原文】PP-OCRv6 纯 Java 图片 OCR（ONNX Runtime，零 PaddlePaddle 依赖，bit-exact 对位 Python，Spring Boot Starter，结构化识别行驶证/身份证/银行卡/驾驶证/营业执照等）</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -2284,7 +2295,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -2294,7 +2305,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Dicklesworthstone/llm_aided_ocr</t>
+          <t>https://github.com/lets-mica/mica-ppocr</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2303,16 +2314,16 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>2.61</v>
+        <v>2.04</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2327,62 +2338,63 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>ai-assist, llama2, llm, ocr, ocr-correction, tesseract</t>
+          <t>java, ocr, ppocrv6</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>1151</v>
+        <v>53</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
+          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Prohao42/aimy-skill</t>
+          <t>swirlai/swirl-search</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>201</v>
+        <v>3045</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>轻量级 AI Agent 渗透测试辅助技能
-【原文】aimy-skill 是一个轻量级、可嵌入 AI Agent 的渗透测试辅助技能，专为授权环境下的自动化信息收集和基础漏洞探测设计。它可以被 AI 助手（如 AutoGPT、LangChain 应用）调用，也可以独立命令行运行。</t>
+          <t>提供 AI 搜索和 RAG 功能
+【原文】AI Search &amp; RAG Without Moving Your Data. Get instant answers from your company's knowledge across 100+ apps while keeping data secure. Deploy in minutes, not months.
+【依据】topics: ai-search, bigquery, django, federated-query, federated-search, gpt, large-language-models, metasearch, python,</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2397,7 +2409,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Prohao42/aimy-skill</t>
+          <t>https://github.com/swirlai/swirl-search</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2406,11 +2418,11 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -2428,19 +2440,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P20" s="6" t="inlineStr"/>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>ai-search, bigquery, django, federated-query, federated-search, gpt, large-language-models, metasearch, python, rag, relevancy, retrieval-augmented-generation</t>
+        </is>
+      </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2022-04-08</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>109</v>
+        <v>1626</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
@@ -2452,41 +2468,42 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Topdu/OpenOCR</t>
+          <t>pditommaso/awesome-pipeline</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>1453</v>
+        <v>6626</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>12.1</v>
+        <v>10.4</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>开源OCR工具包，支持文档分析和处理
-【原文】OpenOCR: An Open-Source Toolkit for General-OCR Research and Applications, integrates a unified training and evaluation benchmark, commercial-grade OCR and Document Parsing systems, and faithful reproductions of the core implementations from a wide range of academic papers.</t>
+          <t>提供一系列优秀的管道工具列表
+【原文】A curated list of awesome pipeline toolkits inspired by Awesome Sysadmin
+【依据】topics: awesome-list, workflow</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2496,7 +2513,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Topdu/OpenOCR</t>
+          <t>https://github.com/pditommaso/awesome-pipeline</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2505,18 +2522,14 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2529,21 +2542,21 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>chineseocr, document-analysis, document-parsing, document-processing, ocr, ocr-pytorch, scene-text-detection, scene-text-recognition</t>
+          <t>awesome-list, workflow</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2014-07-19</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>841</v>
+        <v>4446</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
@@ -2555,41 +2568,41 @@
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ombulabs/claude-code_rails-upgrade-skill</t>
+          <t>t1804330987/DD_Rag</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>386</v>
+        <v>201</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>11.6</v>
+        <v>9.4</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Rails 应用升级辅助技能
-【原文】🤖 The one and only Claude Code Skill to Upgrade Rails by FastRuby.io -- Based on 60,000 dev/hours of experience upgrading Rails from 2.3 all the way to 8.1. Dual boot your Rails application and gradually upgrade one minor version at a time.  🚀</t>
+          <t>提供基于SpringAI的RAG Agent开发项目，涵盖权限隔离、文档入库等
+【原文】基于 SpringAI 的 Agent 开发项目：一个面向“组织知识库 + AI 助手”的 RAG Agent实战项目，把权限隔离、文档入库、混合检索、证据约束、Agent 工具调用和 Docker 部署串成了一条完整工程链路。如果你正在找一个能写进简历、能讲清架构、能覆盖 SpringAI / SpringAIAlibaba学习、技术点的项目，DD_Rag 值得 Star。</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>架构参考/可部署服务</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2599,7 +2612,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ombulabs/claude-code_rails-upgrade-skill</t>
+          <t>https://github.com/t1804330987/DD_Rag</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2608,16 +2621,16 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2632,57 +2645,57 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>claude-code, claude-code-skill, claude-code-skills, ruby-on-rails, technical-debt</t>
+          <t>rag, springai, springai-alibaba</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
+          <t>RAG 知识库 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>kha-white/manga-ocr</t>
+          <t>agent-ecosystem/skill-validator</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2781</v>
+        <v>244</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11.4</v>
+        <v>7.8</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>进行日本漫画文本的光学字符识别
-【原文】Optical character recognition for Japanese text, with the main focus being Japanese manga</t>
+          <t>验证Agent Skill内容的工具
+【原文】Validate Skill content against Agent Skill specification, with additional content density and quality checks.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -2702,7 +2715,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kha-white/manga-ocr</t>
+          <t>https://github.com/agent-ecosystem/skill-validator</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2711,16 +2724,16 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2733,23 +2746,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>comics, computer-vision, deep-learning, japanese, manga, ocr, transformers</t>
-        </is>
-      </c>
+      <c r="P23" s="6" t="inlineStr"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2022-01-15</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1708</v>
+        <v>219</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>1</v>
@@ -2761,36 +2770,36 @@
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>railwayapp/railway-skills</t>
+          <t>githubharald/SimpleHTR</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>325</v>
+        <v>2184</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>与 Railway 交互的 Agent 技能
-【原文】Agent skills for interacting with Railway</t>
+          <t>使用TensorFlow实现手写文本识别系统
+【原文】Handwritten Text Recognition (HTR) system implemented with TensorFlow.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2805,7 +2814,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/railwayapp/railway-skills</t>
+          <t>https://github.com/githubharald/SimpleHTR</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2814,7 +2823,7 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>1.26</v>
+        <v>0.72</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -2838,21 +2847,21 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>agents, infrastructure, railway</t>
+          <t>deep-learning, handwritten-text-recognition, machine-learning, ocr, recurrent-neural-networks, tensorflow</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2018-06-13</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>258</v>
+        <v>3021</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>1</v>
@@ -2864,31 +2873,31 @@
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-20</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>kha-white/mokuro</t>
+          <t>spences10/svelte-claude-skills</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1725</v>
+        <v>218</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>7.5</v>
+        <v>4.9</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>在浏览器中阅读日本漫画，支持文本选择
-【原文】Read Japanese manga inside browser with selectable text.</t>
+          <t>提供 Svelte Claude 技能
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -2896,9 +2905,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -2908,7 +2917,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kha-white/mokuro</t>
+          <t>https://github.com/spences10/svelte-claude-skills</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2917,16 +2926,16 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>1.07</v>
+        <v>0.7</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2939,23 +2948,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>comics, comics-reader, japanese, manga, manga-reader, ocr</t>
-        </is>
-      </c>
+      <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>1617</v>
+        <v>313</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>1</v>
@@ -2967,26 +2972,26 @@
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>amebalabs/TRex</t>
+          <t>uhub/awesome-llm</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>1909</v>
+        <v>831</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>屏幕文字复制工具，支持文本识别和截图
-【原文】Copy any text on your screen, stop retyping.</t>
+          <t>提供大型语言模型框架、库和软件的精选列表
+【原文】A curated list of awesome LLM frameworks, libraries and software.</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3001,7 +3006,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -3011,7 +3016,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/amebalabs/TRex</t>
+          <t>https://github.com/uhub/awesome-llm</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3020,18 +3025,14 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>Swift</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr"/>
       <c r="N26" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3044,21 +3045,21 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>macos, ocr, productivity, screenshot, swift, textrecognition, tools</t>
+          <t>ai, awesome, awesome-list, curated-list, large-language-models, list, llm, resources</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2023-03-31</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>2038</v>
+        <v>1269</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>1</v>
@@ -3070,26 +3071,27 @@
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
+          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>ahkscript/awesome-AutoHotkey</t>
+          <t>jubalh/awesome-os</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>3087</v>
+        <v>2278</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>收集AutoHotkey库、脚本、工具和资源
-【原文】A curated list of awesome AutoHotkey libraries, library distributions, scripts, tools and resources.</t>
+          <t>列出操作系统及相关资源
+【原文】A list of operating systems and stuff
+【依据】topics: awesome, awesome-list, kernel, linux, linux-kernel, operating-system, os, os-dev, osdev</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3114,7 +3116,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ahkscript/awesome-AutoHotkey</t>
+          <t>https://github.com/jubalh/awesome-os</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3123,7 +3125,7 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -3141,19 +3143,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P27" s="6" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, kernel, linux, linux-kernel, operating-system, os, os-dev, osdev</t>
+        </is>
+      </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2014-08-04</t>
+          <t>2017-02-18</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>4429</v>
+        <v>3501</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>1</v>
@@ -3165,26 +3171,26 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-20</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="28" ht="150" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>sirfz/tesserocr</t>
+          <t>frotms/PaddleOCR2Pytorch</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2172</v>
+        <v>1210</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Tesseract OCR API的Python封装库
-【原文】A Python wrapper for the tesseract-ocr API</t>
+          <t>将PaddleOCR推理转换为PyTorch版本
+【原文】PaddleOCR inference in PyTorch. Converted from [PaddleOCR](https://github.com/PaddlePaddle/PaddleOCR)</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3209,7 +3215,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sirfz/tesserocr</t>
+          <t>https://github.com/frotms/PaddleOCR2Pytorch</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3218,11 +3224,11 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -3242,21 +3248,21 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>cython, ocr, optical-character-recognition, python-library, tesseract</t>
+          <t>crnn, db, multilingual-models, ocr, paddleocr, paddlepaddle, pytorch, pytorchocr</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>2015-12-17</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="S28" s="3" t="n">
-        <v>3929</v>
+        <v>2090</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>1</v>
@@ -3268,26 +3274,26 @@
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-21</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>44bits/awesome-opensource-documents</t>
+          <t>tianxing-ovo/AutoSlide</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2329</v>
+        <v>101</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>收集开源文档、指南和书籍的列表
-【原文】:blue_book: A curated list of awesome open source or open source licensed documents, guides, books.</t>
+          <t>提供安卓自动滑动功能的应用
+【原文】一款安卓自动滑动APP，可以自动播放短视频、自动翻页阅读小说</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -3302,7 +3308,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -3312,7 +3318,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/44bits/awesome-opensource-documents</t>
+          <t>https://github.com/tianxing-ovo/AutoSlide</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3321,14 +3327,18 @@
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Kotlin</t>
+        </is>
+      </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3339,139 +3349,40 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>accessibility-service, android, auto-scroller, auto-slide, automation, douyin, kotlin, kuaishou</t>
+        </is>
+      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="S29" s="3" t="n">
-        <v>4146</v>
+        <v>542</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>toki-plus/ai-video-workflow</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>全自动AI视频生成工作流，支持多种内容创作
-【原文】全自动AI原生视频生成工作流，集成文生图(LibLib)/图生视频(即梦)/文生音乐(即梦)和AI提示词生成(豆包)，一键创作AIGC短视频。generative-ai, text-to-video, image-to-video, text-to-music, aigc, automation, pyqt5.</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>视频产线</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/toki-plus/ai-video-workflow</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>ai-content-creation, aigc, automation, bot, content-creation, ffmpeg, llm, pyqt5, python, short-video, tiktok, video-processing</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>283</v>
-      </c>
-      <c r="T30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V30" s="6" t="inlineStr">
-        <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-21</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V30"/>
+  <autoFilter ref="A2:V29"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-20 · 共 27 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-21 · 共 20 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,29 +633,29 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>liyupi/ai-model-world</t>
+          <t>minorun365/minorun-marp-skill</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>123</v>
+        <v>224</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>287</v>
+        <v>1568</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>展示556个AI大模型的排行榜和可视化信息
-【原文】AI 大模型世界，把 556 个大模型拟人化成像素小人的可视化站点。进来就能看到此刻谁最聪明、谁最会写代码、谁最便宜、谁刚发布，往下是国内与国外分区的厂商广场、完整的发布时间线和多维排行榜。搜索认模型名、厂商和能力，输入「多模态」会直接列出全部多模态模型。数据取自 Epoch AI、models.dev、LiveBench 与 Hugging Face，每小时自动同步，所有文案由真实数据生成，不调用任何 LLM。Next.js 静态导出，零后端。</t>
+          <t>Marp中制作演讲幻灯片的技能集
+【原文】Marpで登壇スライドを作るための、ストーリー・図・デザインバランスのスキル集と黒地テーマ、検査ツール</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/未定</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/liyupi/ai-model-world</t>
+          <t>https://github.com/minorun365/minorun-marp-skill</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>41</v>
+        <v>224</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-models, benchmark, chinese, data-visualization, deepseek, large-language-models, leaderboard, llm, llm-benchmarks, llm-leaderboard, model-comparison</t>
+          <t>agent-skills, claude-code, marp, presentation</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -717,48 +717,48 @@
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-22</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>HUANGCHIHHUNGLeo/claude-real-video</t>
+          <t>wuyoscar/jev-skill</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2163</v>
+        <v>206</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>184.7</v>
+        <v>1442</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>允许LLM观看视频，提取场景感知帧和转录本
-【原文】Let Claude (or any LLM) actually watch a video — scene-aware, deduplicated frames + transcript, from a URL or local file. Runs locally, MIT.</t>
+          <t>收集Jev用例、工作流和代理技能
+【原文】An awesome collection of Jev use cases, workflows, and agent skills.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>视频产线/古籍OCR线</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>技能包/未定</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/HUANGCHIHHUNGLeo/claude-real-video</t>
+          <t>https://github.com/wuyoscar/jev-skill</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>26.38</v>
+        <v>206</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -804,23 +804,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>claude, claude-code, cli, codex, codex-cli, ffmpeg, keyframe-extraction, llm, multimodal, ocr, openai-codex, python</t>
-        </is>
-      </c>
+      <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
@@ -832,31 +828,31 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>HRuiCcc/RuiC-card-skill</t>
+          <t>Player-YN/BrowserKitten</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>342</v>
+        <v>2890</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>184.2</v>
+        <v>842.9</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>生成3D全息闪卡网页的Agent Skill
-【原文】全息闪卡通用 Agent Skill：多模态模型都能用，不挑宿主——一句话生成可拖转、会流光、带层次景深的 3D 闪卡网页，附可编辑 Blender 工程</t>
+          <t>Chrome 扩展，选择网页内容生成可编辑的办公文件
+【原文】Paw Work - selection-first web agent for Chrome: select on the live page, describe the outcome, take away an editable office file. BYOK, sandboxed, no server.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>图文产线/AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/HRuiCcc/RuiC-card-skill</t>
+          <t>https://github.com/Player-YN/BrowserKitten</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -885,11 +881,11 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>26.31</v>
+        <v>120.42</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -909,62 +905,62 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>agent-skill, agent-skills, blender, collectible-card, holographic, multimodal, skills, threejs, webgl</t>
+          <t>ai-agent, browser-agent, byok, chrome-extension, llm, pptx, tldraw, univer</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>jingyunstudio/jingyun-dsh</t>
+          <t>huangbai-AI/post-production-skill</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>503</v>
+        <v>223</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>146.7</v>
+        <v>780.5</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>AI商业化桌面客户端，将AI智能体转化为商业产品
-【原文】基于 Jingyun Studio + DeepSeek Harness (DSH) 打造的一站式 AI 商业化桌面客户端，一个将 AI 智能体 / 技能 / 工作流转化为可交易商品的完整商业化平台客户端。  井云为 DSH 注入了完整的商业闭环：登录注册 → 会员体系 → 订阅支付 → 云端资产 → 多端同步，让 AI 开发者 30 分钟内将自己的智能体封装为独立的商业产品。</t>
+          <t>AI 视频后期特效创作 Skill，生成电影级 VFX 和创意转场
+【原文】用于 AI 视频后期特效创作的 Seedance 2.5 Skill，可生成电影级 VFX、创意转场、三维 UI、动态镜头与视觉合成提示词。</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -979,7 +975,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jingyunstudio/jingyun-dsh</t>
+          <t>https://github.com/huangbai-AI/post-production-skill</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -988,18 +984,14 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>20.96</v>
+        <v>111.5</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1010,23 +1002,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>deepseekharness, dsh, dsh-bundle, dsh-plugin, dsh-plugin-desktop, dsh-plugin-market, dsh-plugin-verify, dsh-plugins, dsh-skill</t>
-        </is>
-      </c>
+      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1038,37 +1026,36 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>dexhunter/seedance2-skill</t>
+          <t>kerpopule/hermes-jev-skills</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3812</v>
+        <v>298</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>120.8</v>
+        <v>695.3</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>生成视频生成最佳提示词的技能
-【原文】skill to create best prompts for generating videos with seedance2.0
-【依据】topics: prompt, seedance, seedance-2, video-prompt</t>
+          <t>Jev驱动的模型路由、内存、压缩、技能选择等技能
+【原文】Jev-powered model routing, memory, compaction, skill selection, computer and browser use for Hermes agents (also Claude Code and Codex)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/未定</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1083,7 +1070,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dexhunter/seedance2-skill</t>
+          <t>https://github.com/kerpopule/hermes-jev-skills</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1092,14 +1079,18 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>17.25</v>
+        <v>99.33</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1110,26 +1101,22 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>prompt, seedance, seedance-2, video-prompt</t>
-        </is>
-      </c>
+      <c r="P7" s="6" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>221</v>
+        <v>3</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
@@ -1138,27 +1125,26 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Kappaemme-git/codex-first-customer-finder-skill</t>
+          <t>VDERR/echocat-skill-panel</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1048</v>
+        <v>201</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>104.8</v>
+        <v>469</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>寻找潜在的首批客户
-【原文】A Codex skill that finds evidence-backed potential first customers from recent public signals.
-【依据】topics: codex, codex-skill, customer-discovery, early-adopters, prospecting, startup</t>
+          <t>DSH 技能调用审计和 skill 管理器
+【原文】DSH 技能调用审计 + 应用内 skill 管理器</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1183,7 +1169,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Kappaemme-git/codex-first-customer-finder-skill</t>
+          <t>https://github.com/VDERR/echocat-skill-panel</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1192,7 +1178,7 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>14.97</v>
+        <v>67</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -1201,7 +1187,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1216,21 +1202,21 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>codex, codex-skill, customer-discovery, early-adopters, prospecting, startup</t>
+          <t>cordis, deepseek-harness, dsh-plugin</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1242,41 +1228,41 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>pot-app/pot-desktop</t>
+          <t>ahujasid/mcp-for-blender</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>19425</v>
+        <v>29099</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>104.4</v>
+        <v>361.8</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>提供跨平台的划词翻译和OCR软件
-【原文】🌈一个跨平台的划词翻译和OCR软件 | A cross-platform software for text translation and recognition.</t>
+          <t>Blender 3D 插件，用于控制 Blender 与 LLM 交互
+【原文】Community plugin to control Blender 3D with any LLM of your choice</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>图文产线/AI免费池/视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/可部署服务</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>MCP服务/可部署服务</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1286,7 +1272,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pot-app/pot-desktop</t>
+          <t>https://github.com/ahujasid/mcp-for-blender</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1295,16 +1281,16 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>14.92</v>
+        <v>51.69</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1319,52 +1305,52 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>linux, macos, ocr, pot, pot-app, recognize, tauri, translate, translation, tts, windows</t>
+          <t>3d-modeling, ai, blender, blender-addon, blender-mcp, claude, generative-ai, llm, mcp, model-context-protocol, python</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1302</v>
+        <v>563</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>AccumulateMore/CV</t>
+          <t>huang-sir1/radiology-skills</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>23767</v>
+        <v>1754</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>101.9</v>
+        <v>129.2</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供深度学习笔记资源集合
-【原文】✅（已完结）超级全面的 深度学习 笔记【土堆 Pytorch】【李沐 动手学深度学习】【吴恩达 深度学习】【大飞 大模型Agent】</t>
+          <t>未知
+【依据】无具体描述</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1379,7 +1365,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1389,7 +1375,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/AccumulateMore/CV</t>
+          <t>https://github.com/huang-sir1/radiology-skills</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1398,16 +1384,16 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>14.55</v>
+        <v>18.46</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1420,64 +1406,60 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>agent, agents, book, chinese, computer-vision, cv, deep-learning, jupyter-notebook, llm, llms, machine-learning, natural-language-processing</t>
-        </is>
-      </c>
+      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1634</v>
+        <v>95</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-21</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>yuxino/kiri</t>
+          <t>Stack-Cairn/LiveAgent</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>454</v>
+        <v>2176</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>60</v>
+        <v>126.9</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>提供本地化截图、标注、OCR、录屏和视频剪辑功能
-【原文】Local-first screenshots, annotation, OCR, screen recording and video editing for macOS and Windows. 截图标注、文字识别、录屏与视频剪辑。</t>
+          <t>AI Agent 桌面客户端，支持 Webui 访问和定制
+【原文】A fully functional AI Agent desktop client that supports Webui access and can be creatively customized and expanded!</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>图文产线/AI免费池/视频产线</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/可部署服务</t>
+          <t>MCP服务/技能包/架构参考</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1492,7 +1474,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yuxino/kiri</t>
+          <t>https://github.com/Stack-Cairn/LiveAgent</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1501,7 +1483,7 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>8.57</v>
+        <v>18.13</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1510,7 +1492,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1525,67 +1507,67 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>annotation, desktop-app, image-annotation, local-first, macos, ocr, screen-capture, screen-recorder, screenshot, tauri, text-recognition, video-editing</t>
+          <t>ai-agents, ai-tools, claude-code, claude-desktop, codex, codex-app, desktop-app, fable, hermes, hermes-agent, mcp, oepnclaw</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-06-22</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>manyuegong33/r0crawl_skills</t>
+          <t>newljs/Layerive</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>36.1</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>提供逆向工程技能工具集
-【原文】r0crawl_skills is a massive reverse-engineering skill arsenal for web, Android, iOS, Frida, native binaries, protocols, malware, firmware, and anti-analysis—built for beginners, tuned for pros, and engineered for reproducible results.</t>
+          <t>本地 AI 图片创作工作台，支持文生图、提示词改图等
+【原文】Layerive 是本地的 AI 图片创作工作台：以项目和版本树管理文生图、提示词改图、局部重绘与参考图融合、变量批量改图、批量文生图（统一风格）、图片改字、扩图、去水印与完整对话记录。</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1595,7 +1577,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/manyuegong33/r0crawl_skills</t>
+          <t>https://github.com/newljs/Layerive</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1604,16 +1586,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>5.16</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>LGPL-3.0</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1629,47 +1611,47 @@
       <c r="P12" s="6" t="inlineStr"/>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ramjke/Translumo</t>
+          <t>FB208/OpenBidKit_Yibiao</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>5771</v>
+        <v>3009</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>33.9</v>
+        <v>51</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供游戏、视频、静态文本的实时屏幕翻译功能
-【原文】Advanced real-time screen translator for games, hardcoded subtitles in videos, static text and etc.</t>
+          <t>AI 标书编写工具，包含知识库和标书查重功能
+【原文】开箱即用的AI标书编写工具，标书AI生成工具，投标工具箱、知识库、标书查重、废标项检查，完全开源免费，欢迎使用</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1679,12 +1661,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1694,7 +1676,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ramjke/Translumo</t>
+          <t>https://github.com/FB208/OpenBidKit_Yibiao</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1703,16 +1685,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>4.84</v>
+        <v>7.29</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1727,21 +1709,21 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>autotranslate, easyocr, game-translation, mlnet, ocr, translation</t>
+          <t>ai, ai-writing, bid, bidding, document-ai, electron, llm, office-automation, proposal-generator, proposal-writing, rag, react</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1192</v>
+        <v>413</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1753,36 +1735,36 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>renmu2017/Hell-Grind-AIGC-Skill</t>
+          <t>firefly-hefeng/VESTI-SKILLS</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>201</v>
+        <v>288</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>30.6</v>
+        <v>31.5</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>AI故事片《Hell Grind》的AIGC视频生产工作流Skill
-【原文】Higgsfield 的 95 分钟 AI 故事片《Hell Grind》 全部提示词和制作方法抽取出来的Skill。这一套模型无关的 AIGC 视频生产工作流，将项目搭建、资产与镜头管理、图片/视频提示词生成与润色、生成记录、连续性检查和交付验收整合到一个 Skill 中。</t>
+          <t>VESTI提供的开放代理技能
+【原文】Open agent skills by VESTI: vesti-memory and vesti-handoff</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>视频产线/AI免费池</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/未定</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1797,7 +1779,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/renmu2017/Hell-Grind-AIGC-Skill</t>
+          <t>https://github.com/firefly-hefeng/VESTI-SKILLS</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1806,7 +1788,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>4.37</v>
+        <v>4.5</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1815,7 +1797,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1831,47 +1813,47 @@
       <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-22</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>jipraks/yt-short-clipper</t>
+          <t>ybh-ybh/know-where</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>1001</v>
+        <v>101</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>28.3</v>
+        <v>29.5</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>将长视频转换为短视频剪辑，具有AI高光检测、人脸追踪和字幕功能
-【原文】Windows desktop app that turns long-form YouTube videos into 9:16 short-form clips — AI highlight detection, face-tracking portrait reframe, and word-by-word captions.</t>
+          <t>自动提取和总结内容链接，存入飞书表格
+【原文】知归是一个面向个人使用的 AI 知识归档工具。把内容链接（微信公众号、稀土掘金、GitHub、小红书、抖音、B站）发送给飞书机器人，知归会自动完成内容提取、AI 分类与总结，并将结果沉淀到飞书多维表格中。Send WeChat Article / Douyin / Xiaohongshu / Bilibili links to a Feishu (Lark) bot; auto-extract, AI-summarize and archive to Feishu Bitable. Self-hosted personal knowledge base / second brain.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1881,7 +1863,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1896,7 +1878,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jipraks/yt-short-clipper</t>
+          <t>https://github.com/ybh-ybh/know-where</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1905,16 +1887,16 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1929,68 +1911,67 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>ai-video, content-creation, ffmpeg, instagram-reels, llm, mediapipe, python, react, rust, short-form-video, tauri, tauri-app</t>
+          <t>ai-summarization, bilibili, content-archive, douyin, feishu, feishu-bot, knowledge-base, knowledge-management, lark, llm, rss, rsshub</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>248</v>
+        <v>24</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>topic:content-creation stars:&gt;1000 pushed:&gt;2026-06-22</t>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>yunshu0909/yunshu_skillshub</t>
+          <t>bostrot/wslmanager</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>760</v>
+        <v>4005</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>21.8</v>
+        <v>15.3</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude Code Skills 集合
-【原文】云舒精选的 Claude Code Skills 集合，提升开发和产品管理效率
-【依据】topics: -</t>
+          <t>Windows Subsystem for Linux的GUI管理工具，支持AI助手和MCP服务器
+【原文】GUI for the Windows Subsystem for Linux — and native Linux/macOS VMs on Mac. Install, back up, move and configure distros without CLI flags; AI assistant with tools, MCP server for agents, remote WSL over SSH.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>MCP服务/技能包/未定</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -2000,7 +1981,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yunshu0909/yunshu_skillshub</t>
+          <t>https://github.com/bostrot/wslmanager</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2009,16 +1990,16 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>3.11</v>
+        <v>2.19</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Dart</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2031,19 +2012,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>ai, developer-tools, docker, flutter, gui, llm, macos, mcp, model-context-protocol, rootfs, turnkey, virtual-machine</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>244</v>
+        <v>1830</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2055,41 +2040,41 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>caol64/wenyan-mcp</t>
+          <t>voidforall/fengshui.skill</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1316</v>
+        <v>255</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>19.4</v>
+        <v>10.9</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>提供Markdown文章排版后发布至微信公众号的功能
-【原文】文颜 MCP Server 可以让 AI 自动将 Markdown 文章排版后发布至微信公众号。</t>
+          <t>传统风水顾问Claude Code Skill，提供风水咨询
+【原文】堪舆子 · 传统风水顾问 Claude Code Skill —— 三元玄空飞星、八宅明镜、择日学</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>MCP服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2099,7 +2084,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/caol64/wenyan-mcp</t>
+          <t>https://github.com/voidforall/fengshui.skill</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2108,18 +2093,14 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>2.77</v>
+        <v>1.56</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2130,14 +2111,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>mcp-server, wechat, wenyan</t>
-        </is>
-      </c>
+      <c r="P17" s="6" t="inlineStr"/>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
@@ -2146,48 +2123,48 @@
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>475</v>
+        <v>163</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-22</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>PaddlePaddle/PaddleX</t>
+          <t>NarHakobyan/awesome-nest-boilerplate</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>6267</v>
+        <v>2828</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>18.4</v>
+        <v>7.1</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>基于PaddlePaddle的AI开发工具，支持多种任务
-【原文】All-in-One Development Tool based on PaddlePaddle</t>
+          <t>NestJS的Boilerplate模板
+【原文】Awesome NestJS Boilerplate 😍, Typescript 💪, Postgres 🎉, TypeORM 🥳</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>架构参考/未定</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2202,7 +2179,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/PaddlePaddle/PaddleX</t>
+          <t>https://github.com/NarHakobyan/awesome-nest-boilerplate</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2211,16 +2188,16 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>2.63</v>
+        <v>1.02</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2233,23 +2210,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>ai-pipelines, classification, deployment, formula-recognition, layout-detection, object-detection, ocr, pdf2markdown, pp-chatocr, segmentation, speech-recognition, time-series</t>
-        </is>
-      </c>
+      <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2019-02-27</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>2384</v>
+        <v>2763</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
@@ -2261,36 +2234,36 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>lets-mica/mica-ppocr</t>
+          <t>cathrynlavery/codex-skill</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>108</v>
+        <v>217</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>14.3</v>
+        <v>6.2</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>提供PP-OCRv6纯Java图片OCR功能，支持行驶证、身份证等识别
-【原文】PP-OCRv6 纯 Java 图片 OCR（ONNX Runtime，零 PaddlePaddle 依赖，bit-exact 对位 Python，Spring Boot Starter，结构化识别行驶证/身份证/银行卡/驾驶证/营业执照等）</t>
+          <t>使用OpenAI Codex对Claude Code进行二次审查的技能
+【原文】Give Claude Code a second opinion using OpenAI Codex - automatic plan review via hooks</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包/未定</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2305,7 +2278,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lets-mica/mica-ppocr</t>
+          <t>https://github.com/cathrynlavery/codex-skill</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2314,16 +2287,16 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>2.04</v>
+        <v>0.89</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2336,65 +2309,60 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>java, ocr, ppocrv6</t>
-        </is>
-      </c>
+      <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>53</v>
+        <v>243</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-06-22</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>swirlai/swirl-search</t>
+          <t>sudhakar3697/awesome-electron-alternatives</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>3045</v>
+        <v>2201</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>13.1</v>
+        <v>6</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 搜索和 RAG 功能
-【原文】AI Search &amp; RAG Without Moving Your Data. Get instant answers from your company's knowledge across 100+ apps while keeping data secure. Deploy in minutes, not months.
-【依据】topics: ai-search, bigquery, django, federated-query, federated-search, gpt, large-language-models, metasearch, python,</t>
+          <t>Electron替代品列表
+【原文】A curated list of awesome Electron alternatives.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2409,7 +2377,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/swirlai/swirl-search</t>
+          <t>https://github.com/sudhakar3697/awesome-electron-alternatives</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2418,18 +2386,14 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1.87</v>
+        <v>0.85</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2442,21 +2406,21 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>ai-search, bigquery, django, federated-query, federated-search, gpt, large-language-models, metasearch, python, rag, relevancy, retrieval-augmented-generation</t>
+          <t>awesome-list, cross-platform-desktop-app-dev, electron, electron-alternatives, pwa</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2022-04-08</t>
+          <t>2019-08-27</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>1626</v>
+        <v>2582</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
@@ -2468,42 +2432,42 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-21</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>pditommaso/awesome-pipeline</t>
+          <t>blackholll/loonflow</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>6626</v>
+        <v>2090</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>10.4</v>
+        <v>4.6</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>提供一系列优秀的管道工具列表
-【原文】A curated list of awesome pipeline toolkits inspired by Awesome Sysadmin
-【依据】topics: awesome-list, workflow</t>
+          <t>智能流程自动化系统，支持工单、工作流、MCP服务
+【原文】A Intelligent and Visual Process Automation System,  ticket, workflow, MCP
+【依据】A Intelligent and Visual Process Automation System, ticket, workflow, MCP</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
+          <t>MCP服务/未定</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2513,7 +2477,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pditommaso/awesome-pipeline</t>
+          <t>https://github.com/blackholll/loonflow</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2522,14 +2486,18 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>1.49</v>
+        <v>0.66</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr"/>
+          <t>AGPL-3.0</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2542,67 +2510,67 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>awesome-list, workflow</t>
+          <t>devops, django, mcp, python, ticket, workflow, workflow-engine</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2014-07-19</t>
+          <t>2018-02-08</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>4446</v>
+        <v>3147</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-21</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>t1804330987/DD_Rag</t>
+          <t>dhicoc/chinese-traditional-wisdom-skill</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>提供基于SpringAI的RAG Agent开发项目，涵盖权限隔离、文档入库等
-【原文】基于 SpringAI 的 Agent 开发项目：一个面向“组织知识库 + AI 助手”的 RAG Agent实战项目，把权限隔离、文档入库、混合检索、证据约束、Agent 工具调用和 Docker 部署串成了一条完整工程链路。如果你正在找一个能写进简历、能讲清架构、能覆盖 SpringAI / SpringAIAlibaba学习、技术点的项目，DD_Rag 值得 Star。</t>
+          <t>提供中国传统文化智慧 AI 技能包，包含古籍知识库和可视化 Dashboard
+【原文】中国传统文化整体智慧 AI Agent 技能包 — 八字/紫微/六爻/梅花/风水/五运六气/体质全融合。纯前端 11 标签页可视化 Dashboard + 古籍知识库(30文件/16+部经典) + 6 JSON 确定性映射表 + 自动化测试。支持 Claude Code/Codex CLI/Cursor/Cline/OpenClaw 等 AI 客户端。</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>架构参考/可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2612,7 +2580,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/t1804330987/DD_Rag</t>
+          <t>https://github.com/dhicoc/chinese-traditional-wisdom-skill</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2621,16 +2589,16 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1.34</v>
+        <v>0.25</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2643,23 +2611,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>rag, springai, springai-alibaba</t>
-        </is>
-      </c>
+      <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
@@ -2671,718 +2635,12 @@
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>RAG 知识库 in:name,description stars:&gt;200</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>agent-ecosystem/skill-validator</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>244</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>验证Agent Skill内容的工具
-【原文】Validate Skill content against Agent Skill specification, with additional content density and quality checks.</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/agent-ecosystem/skill-validator</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>Go</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="T23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V23" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>githubharald/SimpleHTR</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>2184</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>使用TensorFlow实现手写文本识别系统
-【原文】Handwritten Text Recognition (HTR) system implemented with TensorFlow.</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>古籍OCR线</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/githubharald/SimpleHTR</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>deep-learning, handwritten-text-recognition, machine-learning, ocr, recurrent-neural-networks, tensorflow</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>2018-06-13</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>3021</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V24" s="6" t="inlineStr">
-        <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>spences10/svelte-claude-skills</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>218</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>提供 Svelte Claude 技能
-【依据】topics: -</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/spences10/svelte-claude-skills</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr"/>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>313</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V25" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="150" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>uhub/awesome-llm</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>831</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>提供大型语言模型框架、库和软件的精选列表
-【原文】A curated list of awesome LLM frameworks, libraries and software.</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/uhub/awesome-llm</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>ai, awesome, awesome-list, curated-list, large-language-models, list, llm, resources</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t>2023-03-31</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>1269</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V26" s="6" t="inlineStr">
-        <is>
-          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="150" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>jubalh/awesome-os</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>2278</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>列出操作系统及相关资源
-【原文】A list of operating systems and stuff
-【依据】topics: awesome, awesome-list, kernel, linux, linux-kernel, operating-system, os, os-dev, osdev</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/jubalh/awesome-os</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr"/>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, kernel, linux, linux-kernel, operating-system, os, os-dev, osdev</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>2017-02-18</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>3501</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V27" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>frotms/PaddleOCR2Pytorch</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>1210</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>将PaddleOCR推理转换为PyTorch版本
-【原文】PaddleOCR inference in PyTorch. Converted from [PaddleOCR](https://github.com/PaddlePaddle/PaddleOCR)</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>古籍OCR线</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/frotms/PaddleOCR2Pytorch</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>crnn, db, multilingual-models, ocr, paddleocr, paddlepaddle, pytorch, pytorchocr</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>2020-12-30</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>2090</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V28" s="6" t="inlineStr">
-        <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="150" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>tianxing-ovo/AutoSlide</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>提供安卓自动滑动功能的应用
-【原文】一款安卓自动滑动APP，可以自动播放短视频、自动翻页阅读小说</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/tianxing-ovo/AutoSlide</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>Kotlin</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>accessibility-service, android, auto-scroller, auto-slide, automation, douyin, kotlin, kuaishou</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>542</v>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V29" s="6" t="inlineStr">
-        <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-22</t>
+          <t>古籍 in:name,description stars:&gt;20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V29"/>
+  <autoFilter ref="A2:V22"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-21 · 共 20 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-22 · 共 20 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,29 +633,30 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>minorun365/minorun-marp-skill</t>
+          <t>Wan-Video/Wan2.2</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>224</v>
+        <v>17586</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1568</v>
+        <v>292.4</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Marp中制作演讲幻灯片的技能集
-【原文】Marpで登壇スライドを作るための、ストーリー・図・デザインバランスのスキル集と黒地テーマ、検査ツール</t>
+          <t>提供开放和高级的视频生成模型
+【原文】Wan: Open and Advanced Large-Scale Video Generative Models
+【依据】topics: aigc, video-generation</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包/未定</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +671,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/minorun365/minorun-marp-skill</t>
+          <t>https://github.com/Wan-Video/Wan2.2</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,7 +680,7 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>224</v>
+        <v>41.77</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -703,21 +704,21 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, claude-code, marp, presentation</t>
+          <t>aigc, video-generation</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1</v>
+        <v>421</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -729,36 +730,37 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>wuyoscar/jev-skill</t>
+          <t>feder-cr/aihawk_mcp_server</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>206</v>
+        <v>31621</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1442</v>
+        <v>284.1</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>收集Jev用例、工作流和代理技能
-【原文】An awesome collection of Jev use cases, workflows, and agent skills.</t>
+          <t>提供防检测的浏览器自动化和 MCP 服务器
+【原文】Anti-detect agentic browser: undetected browsing, browser automation, MCP server, AI web browsing agent, computer use, scraping, lead generation. No captchas.
+【依据】topics: agentic-ai, ai-agent, ai-automation, autonomous-agents, browser, browser-agent, claude-code-plugin, computer-use</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>技能包/未定</t>
+          <t>MCP服务/可部署服务</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -773,7 +775,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wuyoscar/jev-skill</t>
+          <t>https://github.com/feder-cr/aihawk_mcp_server</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,7 +784,7 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>206</v>
+        <v>40.59</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -804,22 +806,26 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>agentic-ai, ai-agent, ai-automation, autonomous-agents, browser, browser-agent, claude-code-plugin, computer-use, gemini-cli-extension, job-hunting, job-search, lead-generation</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1</v>
+        <v>779</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -828,26 +834,27 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Player-YN/BrowserKitten</t>
+          <t>Z-Siqi/Clash-for-Windows_Chinese</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2890</v>
+        <v>28566</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>842.9</v>
+        <v>100.9</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Chrome 扩展，选择网页内容生成可编辑的办公文件
-【原文】Paw Work - selection-first web agent for Chrome: select on the live page, describe the outcome, take away an editable office file. BYOK, sandboxed, no server.</t>
+          <t>提供 clash for windows 的汉化版
+【原文】clash for windows汉化版. 提供clash for windows的汉化版, 汉化补丁及汉化版安装程序
+【依据】topics: chinese, clash, clash-chinese, shadowsocks, windows, zh-cn</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -857,12 +864,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -872,7 +879,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Player-YN/BrowserKitten</t>
+          <t>https://github.com/Z-Siqi/Clash-for-Windows_Chinese</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -881,11 +888,11 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>120.42</v>
+        <v>14.41</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -905,67 +912,68 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, browser-agent, byok, chrome-extension, llm, pptx, tldraw, univer</t>
+          <t>chinese, clash, clash-chinese, shadowsocks, windows, zh-cn</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>24</v>
+        <v>1982</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-22</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>huangbai-AI/post-production-skill</t>
+          <t>uvwt/agentdock</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>223</v>
+        <v>1064</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>780.5</v>
+        <v>62.1</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>AI 视频后期特效创作 Skill，生成电影级 VFX 和创意转场
-【原文】用于 AI 视频后期特效创作的 Seedance 2.5 Skill，可生成电影级 VFX、创意转场、三维 UI、动态镜头与视觉合成提示词。</t>
+          <t>提供安全 MCP 运行时，用于 AI 代理操作本地机器和容器
+【原文】Secure MCP runtime for AI agents to operate local machines, servers, and containers with multi-device orchestration.
+【依据】topics: agent-skills, ai-agents, automation, devops, docker, mcp, model-context-protocol, remote-control, self-hosted, t</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>MCP服务/可部署服务</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -975,7 +983,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/huangbai-AI/post-production-skill</t>
+          <t>https://github.com/uvwt/agentdock</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -984,14 +992,18 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>111.5</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
+      </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1002,60 +1014,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, ai-agents, automation, devops, docker, mcp, model-context-protocol, remote-control, self-hosted, tool-calling</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-23</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>kerpopule/hermes-jev-skills</t>
+          <t>kyrolabs/awesome-langchain</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>298</v>
+        <v>9540</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>695.3</v>
+        <v>51.3</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Jev驱动的模型路由、内存、压缩、技能选择等技能
-【原文】Jev-powered model routing, memory, compaction, skill selection, computer and browser use for Hermes agents (also Claude Code and Codex)</t>
+          <t>提供 LangChain 框架相关的工具和项目列表
+【原文】😎 Awesome list of tools and projects with the awesome LangChain framework
+【依据】topics: ai, awesome, awesome-list, langchain, llm</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>技能包/未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1070,7 +1087,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kerpopule/hermes-jev-skills</t>
+          <t>https://github.com/kyrolabs/awesome-langchain</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1079,18 +1096,14 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>99.33</v>
+        <v>7.33</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1101,19 +1114,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>ai, awesome, awesome-list, langchain, llm</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3</v>
+        <v>1302</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1125,26 +1142,27 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>VDERR/echocat-skill-panel</t>
+          <t>rjs/shaping-skills</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>201</v>
+        <v>1439</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>469</v>
+        <v>42.7</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>DSH 技能调用审计和 skill 管理器
-【原文】DSH 技能调用审计 + 应用内 skill 管理器</t>
+          <t>使用 Claude 进行技能塑造的技能集合
+【原文】Skills I use with Claude for shaping
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1159,7 +1177,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1169,7 +1187,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/VDERR/echocat-skill-panel</t>
+          <t>https://github.com/rjs/shaping-skills</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1178,16 +1196,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>67</v>
+        <v>6.1</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1200,14 +1218,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>cordis, deepseek-harness, dsh-plugin</t>
-        </is>
-      </c>
+      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1216,7 +1230,7 @@
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>3</v>
+        <v>236</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1228,41 +1242,42 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ahujasid/mcp-for-blender</t>
+          <t>LancelotRar/best-cf-domains</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>29099</v>
+        <v>103</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>361.8</v>
+        <v>42.4</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Blender 3D 插件，用于控制 Blender 与 LLM 交互
-【原文】Community plugin to control Blender 3D with any LLM of your choice</t>
+          <t>提供 Cloudflare 优选域名 API
+【原文】Cloudflare 优选域名 API，服务于 Cloudflare 免费代理搭建方案，优质域名即为优质节点。
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1272,7 +1287,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ahujasid/mcp-for-blender</t>
+          <t>https://github.com/LancelotRar/best-cf-domains</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1281,18 +1296,14 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>51.69</v>
+        <v>6.06</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1303,69 +1314,66 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>3d-modeling, ai, blender, blender-addon, blender-mcp, claude, generative-ai, llm, mcp, model-context-protocol, python</t>
-        </is>
-      </c>
+      <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>563</v>
+        <v>17</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-22</t>
+          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>huang-sir1/radiology-skills</t>
+          <t>morphik-org/morphik-core</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1754</v>
+        <v>3712</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>129.2</v>
+        <v>38.2</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>未知
-【依据】无具体描述</t>
+          <t>开源的多模态检索引擎
+【原文】Open-source multimodal retrieval engine (Morphik Core)
+【依据】topics: artificial-intelligence, cache-augmented-generation, colpali, database, litellm, multimodal, rag, rules-based-in</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1375,7 +1383,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/huang-sir1/radiology-skills</t>
+          <t>https://github.com/morphik-org/morphik-core</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1384,11 +1392,11 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>18.46</v>
+        <v>5.46</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1406,19 +1414,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>artificial-intelligence, cache-augmented-generation, colpali, database, litellm, multimodal, rag, rules-based-ingestion</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>95</v>
+        <v>680</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1430,41 +1442,42 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Stack-Cairn/LiveAgent</t>
+          <t>miantiao-me/hacker-podcast</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2176</v>
+        <v>2581</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>126.9</v>
+        <v>30.9</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>AI Agent 桌面客户端，支持 Webui 访问和定制
-【原文】A fully functional AI Agent desktop client that supports Webui access and can be creatively customized and expanded!</t>
+          <t>自动抓取 Hacker News 热门文章，生成中文总结并转换为播客内容
+【原文】一个基于 AI 的 Hacker News 中文播客项目，每天自动抓取 Hacker News 热门文章，通过 AI 生成中文总结并转换为播客内容。
+【依据】topics: ai, ai-agent, ai-workflow, cloudflare, cloudflare-workers, cloudflare-workflows, hacker-news, nextjs</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1474,7 +1487,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Stack-Cairn/LiveAgent</t>
+          <t>https://github.com/miantiao-me/hacker-podcast</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1483,11 +1496,11 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>18.13</v>
+        <v>4.42</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1507,12 +1520,12 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, ai-tools, claude-code, claude-desktop, codex, codex-app, desktop-app, fable, hermes, hermes-agent, mcp, oepnclaw</t>
+          <t>ai, ai-agent, ai-workflow, cloudflare, cloudflare-workers, cloudflare-workflows, hacker-news, nextjs</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2025-02-15</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1521,7 +1534,7 @@
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>120</v>
+        <v>584</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1533,41 +1546,42 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-22</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>newljs/Layerive</t>
+          <t>ramitsurana/awesome-kubernetes</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>208</v>
+        <v>16089</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>28.2</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>本地 AI 图片创作工作台，支持文生图、提示词改图等
-【原文】Layerive 是本地的 AI 图片创作工作台：以项目和版本树管理文生图、提示词改图、局部重绘与参考图融合、变量批量改图、批量文生图（统一风格）、图片改字、扩图、去水印与完整对话记录。</t>
+          <t>提供 Kubernetes 源的精选列表
+【原文】A curated list for awesome kubernetes sources :ship::tada:
+【依据】topics: aws, azure, books, cloud-providers, deploy-kubernetes, docker, enterprise-kubernetes-products, google-cloud, goo</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1577,7 +1591,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/newljs/Layerive</t>
+          <t>https://github.com/ramitsurana/awesome-kubernetes</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1586,16 +1600,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>9.449999999999999</v>
+        <v>4.03</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>LGPL-3.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1608,10 +1622,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr"/>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>aws, azure, books, cloud-providers, deploy-kubernetes, docker, enterprise-kubernetes-products, google-cloud, google-kubernetes, kubernetes, kubernetes-cluster, kubernetes-sources</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1620,38 +1638,39 @@
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>22</v>
+        <v>3995</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-23</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>FB208/OpenBidKit_Yibiao</t>
+          <t>devlikeapro/waha</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>3009</v>
+        <v>7434</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>51</v>
+        <v>24.1</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>AI 标书编写工具，包含知识库和标书查重功能
-【原文】开箱即用的AI标书编写工具，标书AI生成工具，投标工具箱、知识库、标书查重、废标项检查，完全开源免费，欢迎使用</t>
+          <t>提供 WhatsApp HTTP API，支持多种引擎
+【原文】WAHA - WhatsApp HTTP API (REST API) that you can configure in a click! Multiple engines: WEBJS (browser based), NOWEB (websocket nodejs), GOWS (websocket go), WPP (browser)
+【依据】topics: ai-bot, bot, http-api, mcp, mcp-server, mcp-whatsapp, python-bot, whatsapp, whatsapp-api, whatsapp-automation, w</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1661,12 +1680,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包/MCP服务</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1676,7 +1695,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/FB208/OpenBidKit_Yibiao</t>
+          <t>https://github.com/devlikeapro/waha</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1685,16 +1704,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>7.29</v>
+        <v>3.44</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1709,62 +1728,63 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-writing, bid, bidding, document-ai, electron, llm, office-automation, proposal-generator, proposal-writing, rag, react</t>
+          <t>ai-bot, bot, http-api, mcp, mcp-server, mcp-whatsapp, python-bot, whatsapp, whatsapp-api, whatsapp-automation, whatsapp-bot, whatsapp-chat</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>413</v>
+        <v>2163</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-22</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>firefly-hefeng/VESTI-SKILLS</t>
+          <t>yan-labs/yan-skills</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>288</v>
+        <v>201</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>31.5</v>
+        <v>17.8</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>VESTI提供的开放代理技能
-【原文】Open agent skills by VESTI: vesti-memory and vesti-handoff</t>
+          <t>收集 Yan 的代理技能集合
+【原文】Yan's agent skills collection — Google Trends SEO workflows, AI news, autopilot, and more. For Claude Code / Codex / Cursor.
+【依据】topics: agent-skills, claude-code, google-trends, seo, skills</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>技能包/未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1779,7 +1799,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/firefly-hefeng/VESTI-SKILLS</t>
+          <t>https://github.com/yan-labs/yan-skills</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1788,7 +1808,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>4.5</v>
+        <v>2.54</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1797,7 +1817,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1810,19 +1830,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, claude-code, google-trends, seo, skills</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1834,36 +1858,37 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>ybh-ybh/know-where</t>
+          <t>meirwah/awesome-workflow-engines</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>101</v>
+        <v>7932</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>29.5</v>
+        <v>13.4</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>自动提取和总结内容链接，存入飞书表格
-【原文】知归是一个面向个人使用的 AI 知识归档工具。把内容链接（微信公众号、稀土掘金、GitHub、小红书、抖音、B站）发送给飞书机器人，知归会自动完成内容提取、AI 分类与总结，并将结果沉淀到飞书多维表格中。Send WeChat Article / Douyin / Xiaohongshu / Bilibili links to a Feishu (Lark) bot; auto-extract, AI-summarize and archive to Feishu Bitable. Self-hosted personal knowledge base / second brain.</t>
+          <t>开源工作流引擎的精选列表
+【原文】A curated list of awesome open source workflow engines
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1878,7 +1903,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ybh-ybh/know-where</t>
+          <t>https://github.com/meirwah/awesome-workflow-engines</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1887,18 +1912,14 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>4.21</v>
+        <v>1.91</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1909,14 +1930,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>ai-summarization, bilibili, content-archive, douyin, feishu, feishu-bot, knowledge-base, knowledge-management, lark, llm, rss, rsshub</t>
-        </is>
-      </c>
+      <c r="P15" s="6" t="inlineStr"/>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2015-05-20</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
@@ -1925,7 +1942,7 @@
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>24</v>
+        <v>4143</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1937,41 +1954,42 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>topic:xiaohongshu stars:&gt;100</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>bostrot/wslmanager</t>
+          <t>rrezartprebreza/spring-boot-skills</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>4005</v>
+        <v>278</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>15.3</v>
+        <v>12.1</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Windows Subsystem for Linux的GUI管理工具，支持AI助手和MCP服务器
-【原文】GUI for the Windows Subsystem for Linux — and native Linux/macOS VMs on Mac. Install, back up, move and configure distros without CLI flags; AI assistant with tools, MCP server for agents, remote WSL over SSH.</t>
+          <t>为 Spring Boot 开发者提供 Claude Code 和 Codex 技能
+【原文】Production-grade Claude Code and Codex skills for Spring Boot developers
+【依据】topics: ai-coding-agent, claude, claude-ai, claude-code, claude-plugin, claude-skill, claude-skills, codex, codex-skills</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1981,7 +1999,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/bostrot/wslmanager</t>
+          <t>https://github.com/rrezartprebreza/spring-boot-skills</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1990,16 +2008,16 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Dart</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2014,21 +2032,21 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>ai, developer-tools, docker, flutter, gui, llm, macos, mcp, model-context-protocol, rootfs, turnkey, virtual-machine</t>
+          <t>ai-coding-agent, claude, claude-ai, claude-code, claude-plugin, claude-skill, claude-skills, codex, codex-skills, developer-tools, java, mcp</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1830</v>
+        <v>161</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2040,41 +2058,42 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-22</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>voidforall/fengshui.skill</t>
+          <t>emotixco/claude-skills-founder</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>10.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>传统风水顾问Claude Code Skill，提供风水咨询
-【原文】堪舆子 · 传统风水顾问 Claude Code Skill —— 三元玄空飞星、八宅明镜、择日学</t>
+          <t>提供 Claude Code 技能给初创公司创始人
+【原文】Claude Code skills for startup founders — product briefs, competitor analysis, pricing strategy, pitch decks, and GTM plans from your terminal
+【依据】topics: ai, claude, claude-code, claude-code-plugin, competitor-analysis, founder, go-to-market, pitch-deck, product-man</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2084,7 +2103,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/voidforall/fengshui.skill</t>
+          <t>https://github.com/emotixco/claude-skills-founder</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2093,11 +2112,11 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr"/>
@@ -2111,19 +2130,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>ai, claude, claude-code, claude-code-plugin, competitor-analysis, founder, go-to-market, pitch-deck, product-management, skills, slash-commands, startup</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
@@ -2135,41 +2158,42 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>NarHakobyan/awesome-nest-boilerplate</t>
+          <t>tl2012tl/comfyUI-llama-TE</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2828</v>
+        <v>202</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>NestJS的Boilerplate模板
-【原文】Awesome NestJS Boilerplate 😍, Typescript 💪, Postgres 🎉, TypeORM 🥳</t>
+          <t>提供图片反推、提示词、本地多轮对话等功能
+【原文】qwen3/qwen3.5/qwen3.8/gemma4 图片反推,提示词,本地多轮对话,本地skill使用,扩写高速版
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>架构参考/未定</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -2179,7 +2203,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/NarHakobyan/awesome-nest-boilerplate</t>
+          <t>https://github.com/tl2012tl/comfyUI-llama-TE</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2188,16 +2212,16 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2213,62 +2237,63 @@
       <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2019-02-27</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>2763</v>
+        <v>157</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-22</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>cathrynlavery/codex-skill</t>
+          <t>Londeren/hh-skill-verifications-quizzes</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>217</v>
+        <v>652</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>使用OpenAI Codex对Claude Code进行二次审查的技能
-【原文】Give Claude Code a second opinion using OpenAI Codex - automatic plan review via hooks</t>
+          <t>提供 hh.ru 技能验证测试的答案
+【原文】Ответы на тесты для подтверждения навыков на hh.ru (headhunter.ru): английский, ООП, JavaScript, Git, HTML, Python, SQL, Scrum, Agile Project Management, MS Excel, Копирайтинг.
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>技能包/未定</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -2278,7 +2303,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cathrynlavery/codex-skill</t>
+          <t>https://github.com/Londeren/hh-skill-verifications-quizzes</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2287,18 +2312,14 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>AGPL-3.0</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2312,16 +2333,16 @@
       <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>243</v>
+        <v>776</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
@@ -2333,36 +2354,37 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-22</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>sudhakar3697/awesome-electron-alternatives</t>
+          <t>Justineo/vue-awesome</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2201</v>
+        <v>2426</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Electron替代品列表
-【原文】A curated list of awesome Electron alternatives.</t>
+          <t>Vue.js 的 SVG 图标组件
+【原文】Awesome SVG icon component for Vue.js, built-in with Font Awesome icons.
+【依据】topics: font-awesome, icon, svg, vue</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2377,7 +2399,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sudhakar3697/awesome-electron-alternatives</t>
+          <t>https://github.com/Justineo/vue-awesome</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2386,14 +2408,18 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.85</v>
+        <v>0.63</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2406,12 +2432,12 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>awesome-list, cross-platform-desktop-app-dev, electron, electron-alternatives, pwa</t>
+          <t>font-awesome, icon, svg, vue</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2019-08-27</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -2420,7 +2446,7 @@
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>2582</v>
+        <v>3826</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
@@ -2432,42 +2458,42 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-22</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>blackholll/loonflow</t>
+          <t>A9T9/RPA</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2090</v>
+        <v>2025</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>智能流程自动化系统，支持工单、工作流、MCP服务
-【原文】A Intelligent and Visual Process Automation System,  ticket, workflow, MCP
-【依据】A Intelligent and Visual Process Automation System, ticket, workflow, MCP</t>
+          <t>提供浏览器和桌面自动化工具，带有 MCP 服务器
+【原文】Browser and desktop automation with an MCP server for AI assistants. Record macros or write JavaScript to automate websites, extract data, and control desktop apps with OCR and image recognition.
+【依据】topics: ai-agents, browser-automation, browser-automation-ai-api, browser-extension, computer-use, desktop-automation, i</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/未定</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>MCP服务/可部署服务</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2477,7 +2503,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/blackholll/loonflow</t>
+          <t>https://github.com/A9T9/RPA</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2486,11 +2512,11 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2510,52 +2536,53 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>devops, django, mcp, python, ticket, workflow, workflow-engine</t>
+          <t>ai-agents, browser-automation, browser-automation-ai-api, browser-extension, computer-use, desktop-automation, image-recognition, macro-recorder, mcp, mcp-server, ocr, selenium-ide</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2018-02-08</t>
+          <t>2017-08-04</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>3147</v>
+        <v>3336</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-22</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>dhicoc/chinese-traditional-wisdom-skill</t>
+          <t>mswnlz/chinese-traditional</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>提供中国传统文化智慧 AI 技能包，包含古籍知识库和可视化 Dashboard
-【原文】中国传统文化整体智慧 AI Agent 技能包 — 八字/紫微/六爻/梅花/风水/五运六气/体质全融合。纯前端 11 标签页可视化 Dashboard + 古籍知识库(30文件/16+部经典) + 6 JSON 确定性映射表 + 自动化测试。支持 Claude Code/Codex CLI/Cursor/Cline/OpenClaw 等 AI 客户端。</t>
+          <t>提供中医课程资料大全
+【原文】🎁重磅资源！原价59880元 绝版中医课程资料大全【收藏版1.18TB】，包括基础、视频、外治、针灸、书籍等等等应有尽有
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2565,12 +2592,12 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2580,7 +2607,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dhicoc/chinese-traditional-wisdom-skill</t>
+          <t>https://github.com/mswnlz/chinese-traditional</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2589,18 +2616,14 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2614,16 +2637,16 @@
       <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>85</v>
+        <v>497</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
@@ -2635,7 +2658,7 @@
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>古籍 in:name,description stars:&gt;20</t>
+          <t>中医 in:name,description stars:&gt;50</t>
         </is>
       </c>
     </row>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-22 · 共 20 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-23 · 共 22 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,35 +633,34 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Wan-Video/Wan2.2</t>
+          <t>EKKOLearnAI/ekko-studio</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>17586</v>
+        <v>11182</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>292.4</v>
+        <v>474.4</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>提供开放和高级的视频生成模型
-【原文】Wan: Open and Advanced Large-Scale Video Generative Models
-【依据】topics: aigc, video-generation</t>
+          <t>多智能体AI工作空间，支持聊天、编码和可视化工作流程。
+【原文】Ekko Studio is a local-first AI workspace for multi-agent chat, coding, and visual workflows, available on desktop and the web.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -671,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Wan-Video/Wan2.2</t>
+          <t>https://github.com/EKKOLearnAI/ekko-studio</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -680,16 +679,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>41.77</v>
+        <v>67.77</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -704,68 +703,67 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>aigc, video-generation</t>
+          <t>agent, ai-agent, chat-ui, coding-agents, dashboard, ekko-studio, hermes, hermes-agent, hermes-web-ui, llm, multi-agent, multi-model</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>421</v>
+        <v>165</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-24</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>feder-cr/aihawk_mcp_server</t>
+          <t>op7418/guizang-product-video-skill</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>31621</v>
+        <v>221</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>284.1</v>
+        <v>309.4</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>提供防检测的浏览器自动化和 MCP 服务器
-【原文】Anti-detect agentic browser: undetected browsing, browser automation, MCP server, AI web browsing agent, computer use, scraping, lead generation. No captchas.
-【依据】topics: agentic-ai, ai-agent, ai-automation, autonomous-agents, browser, browser-agent, claude-code-plugin, computer-use</t>
+          <t>生成软件更新宣传片，复用产品组件和设计语言
+【原文】归藏 product video skill：复用真实产品组件和设计语言，用代码制作软件更新宣传片。包含分镜文案、原创配乐、动作音效与视频渲染，支持 Claude Code 和 Codex。</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -775,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/feder-cr/aihawk_mcp_server</t>
+          <t>https://github.com/op7418/guizang-product-video-skill</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -784,11 +782,11 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>40.59</v>
+        <v>44.2</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -808,12 +806,12 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, ai-agent, ai-automation, autonomous-agents, browser, browser-agent, claude-code-plugin, computer-use, gemini-cli-extension, job-hunting, job-search, lead-generation</t>
+          <t>agent-skills, claude-code, codepilot, codex, hyperframes, motion-design, product-video, release-notes, skill, skills, video-generation</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -822,10 +820,10 @@
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>779</v>
+        <v>5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -834,27 +832,26 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-23</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Z-Siqi/Clash-for-Windows_Chinese</t>
+          <t>feder-cr/invisible_playwright_mcp</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>28566</v>
+        <v>31631</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>100.9</v>
+        <v>283.8</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>提供 clash for windows 的汉化版
-【原文】clash for windows汉化版. 提供clash for windows的汉化版, 汉化补丁及汉化版安装程序
-【依据】topics: chinese, clash, clash-chinese, shadowsocks, windows, zh-cn</t>
+          <t>提供防检测的浏览器自动化工具，用于网络爬取和生成潜在客户。
+【原文】Anti-detect agentic stealth browser: undetected browsing, browser automation, Python AI web browsing agent, computer use, scraping, lead generation. No captchas.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -869,7 +866,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -879,7 +876,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Z-Siqi/Clash-for-Windows_Chinese</t>
+          <t>https://github.com/feder-cr/invisible_playwright_mcp</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -888,16 +885,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>14.41</v>
+        <v>40.55</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -912,63 +909,61 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>chinese, clash, clash-chinese, shadowsocks, windows, zh-cn</t>
+          <t>agentic-ai, ai-agent, ai-automation, autonomous-agents, browser, claude-code-plugin, crawler, gemini-cli-extension, job-hunting, job-search, lead-generation, llm-agent</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1982</v>
+        <v>780</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-23</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>uvwt/agentdock</t>
+          <t>VDERR/dsh-echocat-skill-panel</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1064</v>
+        <v>201</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>62.1</v>
+        <v>281.4</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供安全 MCP 运行时，用于 AI 代理操作本地机器和容器
-【原文】Secure MCP runtime for AI agents to operate local machines, servers, and containers with multi-device orchestration.
-【依据】topics: agent-skills, ai-agents, automation, devops, docker, mcp, model-context-protocol, remote-control, self-hosted, t</t>
+          <t>DSH 技能调用审计 + 应用内 skill 管理器</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -983,7 +978,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/uvwt/agentdock</t>
+          <t>https://github.com/VDERR/dsh-echocat-skill-panel</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -992,16 +987,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>8.869999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1016,12 +1011,12 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, automation, devops, docker, mcp, model-context-protocol, remote-control, self-hosted, tool-calling</t>
+          <t>cordis, deepseek-harness, dsh-plugin</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1030,7 +1025,7 @@
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1042,27 +1037,26 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-23</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>kyrolabs/awesome-langchain</t>
+          <t>superdesigndev/treg</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9540</v>
+        <v>2314</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>51.3</v>
+        <v>231.4</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供 LangChain 框架相关的工具和项目列表
-【原文】😎 Awesome list of tools and projects with the awesome LangChain framework
-【依据】topics: ai, awesome, awesome-list, langchain, llm</t>
+          <t>为智能体工具提供OpenRouter服务。
+【原文】OpenRouter for agent tools. Join community here: https://discord.gg/6mQYYfFMAn</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1072,12 +1066,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>MCP服务</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1087,7 +1081,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kyrolabs/awesome-langchain</t>
+          <t>https://github.com/superdesigndev/treg</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1096,14 +1090,18 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>7.33</v>
+        <v>33.06</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr"/>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1116,58 +1114,57 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>ai, awesome, awesome-list, langchain, llm</t>
+          <t>agents, api-keys, cli, credentials, developer-tools, dsh-plugin, mcp, proxy, python, registry, secrets</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1302</v>
+        <v>70</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-23</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>rjs/shaping-skills</t>
+          <t>Alisa0808/vox-director</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1439</v>
+        <v>2010</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>42.7</v>
+        <v>187.6</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>使用 Claude 进行技能塑造的技能集合
-【原文】Skills I use with Claude for shaping
-【依据】topics: -</t>
+          <t>自动生成Vox风格的解释性视频，支持Claude技能集成。
+【原文】Turn one topic into a finished Vox-style paper-collage explainer/ad video — automated end to end on Atlas Cloud + ffmpeg. An agent skill.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1177,7 +1174,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1187,7 +1184,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rjs/shaping-skills</t>
+          <t>https://github.com/Alisa0808/vox-director</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1196,16 +1193,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>6.1</v>
+        <v>26.8</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1218,19 +1215,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>ai, ai-video, claude-code, claude-skill, collage-video, dsh-plugin, explainer-video, ffmpeg, generative-ai, llm, motion-graphics, python</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>236</v>
+        <v>75</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1242,42 +1243,41 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-23</t>
+          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>LancelotRar/best-cf-domains</t>
+          <t>krillinai/OpenCreator</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>103</v>
+        <v>12220</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>42.4</v>
+        <v>132.7</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>提供 Cloudflare 优选域名 API
-【原文】Cloudflare 优选域名 API，服务于 Cloudflare 免费代理搭建方案，优质域名即为优质节点。
-【依据】topics: -</t>
+          <t>开源AI创作空间，支持视频、图像、声音等创作。
+【原文】Formerly KrillinAI. Open-source AI workspace for creators, powered by Codex. Create videos, images, voice, avatars, video translation, and edits with Agents in one place.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/图文产线</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LancelotRar/best-cf-domains</t>
+          <t>https://github.com/krillinai/OpenCreator</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1296,14 +1296,18 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>6.06</v>
+        <v>18.95</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1314,66 +1318,69 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, codex-cli, deskop-app, dubbing, image-generation, localization, skills, tts, video-editing, video-generation, video-transcription, video-translation</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>17</v>
+        <v>645</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-24</t>
+          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>morphik-org/morphik-core</t>
+          <t>zilliztech/deep-searcher</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3712</v>
+        <v>8280</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>38.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>开源的多模态检索引擎
-【原文】Open-source multimodal retrieval engine (Morphik Core)
-【依据】topics: artificial-intelligence, cache-augmented-generation, colpali, database, litellm, multimodal, rag, rules-based-in</t>
+          <t>开源深度研究替代方案，用于私有数据上的推理和搜索
+【原文】Open Source Deep Research Alternative to Reason and Search on Private Data. Written in Python.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1383,7 +1390,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/morphik-org/morphik-core</t>
+          <t>https://github.com/zilliztech/deep-searcher</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1392,11 +1399,11 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5.46</v>
+        <v>13.99</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1416,12 +1423,12 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>artificial-intelligence, cache-augmented-generation, colpali, database, litellm, multimodal, rag, rules-based-ingestion</t>
+          <t>agent, agentic-rag, claude, deep-research, deepseek, deepseek-r1, grok, grok3, llama4, llm, milvus, openai</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
@@ -1430,7 +1437,7 @@
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>680</v>
+        <v>592</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1442,42 +1449,41 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-23</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>miantiao-me/hacker-podcast</t>
+          <t>53AI/53AIHub</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2581</v>
+        <v>4658</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>30.9</v>
+        <v>63.1</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>自动抓取 Hacker News 热门文章，生成中文总结并转换为播客内容
-【原文】一个基于 AI 的 Hacker News 中文播客项目，每天自动抓取 Hacker News 热门文章，通过 AI 生成中文总结并转换为播客内容。
-【依据】topics: ai, ai-agent, ai-workflow, cloudflare, cloudflare-workers, cloudflare-workflows, hacker-news, nextjs</t>
+          <t>AI 知识库与 Agent 门户，管理企业知识、AI 代理、提示和 AI 工具
+【原文】53AI Hub is an open-source AI portal and knowledge base for managing enterprise knowledge, AI agents, prompts, and AI tools, seamlessly integrating with Coze, Dify, FastGPT, RAGFlow. 一个AI知识库与Agent门户</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>MCP服务/可部署服务</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1487,7 +1493,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/miantiao-me/hacker-podcast</t>
+          <t>https://github.com/53AI/53AIHub</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1496,16 +1502,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>4.42</v>
+        <v>9.01</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1520,68 +1526,67 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agent, ai-workflow, cloudflare, cloudflare-workers, cloudflare-workflows, hacker-news, nextjs</t>
+          <t>coze, dify, fastgpt, go, knowledge, maxkb, mcp, openai, prompt, rag, ragflow</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>584</v>
+        <v>517</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-23</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>ramitsurana/awesome-kubernetes</t>
+          <t>oceanbase/seekdb</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>16089</v>
+        <v>3021</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>28.2</v>
+        <v>62.7</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>提供 Kubernetes 源的精选列表
-【原文】A curated list for awesome kubernetes sources :ship::tada:
-【依据】topics: aws, azure, books, cloud-providers, deploy-kubernetes, docker, enterprise-kubernetes-products, google-cloud, goo</t>
+          <t>AI原生搜索引擎，统一向量、文本、结构化和半结构化数据
+【原文】The AI-Native Search Database. Best for agent storage, it unifies vector, text, structured, and semi-structured data into a single engine. This all-in-one database makes agents smarter, easier to run, and more stable.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1591,7 +1596,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ramitsurana/awesome-kubernetes</t>
+          <t>https://github.com/oceanbase/seekdb</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1600,16 +1605,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>4.03</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1624,21 +1629,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>aws, azure, books, cloud-providers, deploy-kubernetes, docker, enterprise-kubernetes-products, google-cloud, google-kubernetes, kubernetes, kubernetes-cluster, kubernetes-sources</t>
+          <t>ai-agents, copy-on-write, embedded-database, full-text-search, hnsw, hybrid-search, langchain, llamaindex, mysql, oceanbase, python, rag</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2015-10-15</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>3995</v>
+        <v>337</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1650,27 +1655,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-23</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>devlikeapro/waha</t>
+          <t>tayllan/awesome-algorithms</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>7434</v>
+        <v>25569</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>24.1</v>
+        <v>40.2</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供 WhatsApp HTTP API，支持多种引擎
-【原文】WAHA - WhatsApp HTTP API (REST API) that you can configure in a click! Multiple engines: WEBJS (browser based), NOWEB (websocket nodejs), GOWS (websocket go), WPP (browser)
-【依据】topics: ai-bot, bot, http-api, mcp, mcp-server, mcp-whatsapp, python-bot, whatsapp, whatsapp-api, whatsapp-automation, w</t>
+          <t>算法学习与实践资源列表
+【原文】A curated list of awesome places to learn and/or practice algorithms.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1680,12 +1684,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>技能包/MCP服务</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1695,7 +1699,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/devlikeapro/waha</t>
+          <t>https://github.com/tayllan/awesome-algorithms</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1704,18 +1708,14 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>3.44</v>
+        <v>5.74</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1726,14 +1726,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>ai-bot, bot, http-api, mcp, mcp-server, mcp-whatsapp, python-bot, whatsapp, whatsapp-api, whatsapp-automation, whatsapp-bot, whatsapp-chat</t>
-        </is>
-      </c>
+      <c r="P13" s="6" t="inlineStr"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2014-07-16</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -1742,39 +1738,38 @@
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>2163</v>
+        <v>4452</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-23</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>yan-labs/yan-skills</t>
+          <t>bharathgs/Awesome-pytorch-list</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>201</v>
+        <v>16678</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>17.8</v>
+        <v>33.4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>收集 Yan 的代理技能集合
-【原文】Yan's agent skills collection — Google Trends SEO workflows, AI news, autopilot, and more. For Claude Code / Codex / Cursor.
-【依据】topics: agent-skills, claude-code, google-trends, seo, skills</t>
+          <t>PyTorch 相关内容的综合列表
+【原文】A comprehensive list of pytorch related content on github,such as different models,implementations,helper libraries,tutorials etc.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1784,12 +1779,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1799,7 +1794,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yan-labs/yan-skills</t>
+          <t>https://github.com/bharathgs/Awesome-pytorch-list</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1808,18 +1803,14 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>2.54</v>
+        <v>4.77</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1832,12 +1823,12 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, claude-code, google-trends, seo, skills</t>
+          <t>awesome, awesome-list, computer-vision, cv, data-science, deep-learning, facebook, machine-learning, natural-language-processing, neural-network, nlp, nlp-library</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
@@ -1846,7 +1837,7 @@
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>79</v>
+        <v>3493</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1858,27 +1849,26 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-23</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>meirwah/awesome-workflow-engines</t>
+          <t>MarkPDFdown/markpdfdown</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>7932</v>
+        <v>2272</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>13.4</v>
+        <v>28.5</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>开源工作流引擎的精选列表
-【原文】A curated list of awesome open source workflow engines
-【依据】topics: -</t>
+          <t>将PDF转换为Markdown格式的高质量工具。
+【原文】A high-quality PDF to Markdown tool based on large language model visual recognition. 一款基于大模型视觉识别的高质量PDF转Markdown工具</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1888,7 +1878,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1903,7 +1893,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/meirwah/awesome-workflow-engines</t>
+          <t>https://github.com/MarkPDFdown/markpdfdown</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1912,14 +1902,18 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>1.91</v>
+        <v>4.07</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1930,51 +1924,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>llm, markdown, pdf, pdf-converter, pdf-markdown, pdf2markdown, pdf2md</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>4143</v>
+        <v>558</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-23</t>
+          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>rrezartprebreza/spring-boot-skills</t>
+          <t>markets/awesome-ruby</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>278</v>
+        <v>14157</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>12.1</v>
+        <v>22.2</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>为 Spring Boot 开发者提供 Claude Code 和 Codex 技能
-【原文】Production-grade Claude Code and Codex skills for Spring Boot developers
-【依据】topics: ai-coding-agent, claude, claude-ai, claude-code, claude-plugin, claude-skill, claude-skills, codex, codex-skills</t>
+          <t>收集 Ruby 库、工具、框架和软件的列表
+【原文】💎 A collection of awesome Ruby libraries, tools, frameworks and software</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1984,12 +1981,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1999,7 +1996,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rrezartprebreza/spring-boot-skills</t>
+          <t>https://github.com/markets/awesome-ruby</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2008,18 +2005,14 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1.73</v>
+        <v>3.17</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2032,21 +2025,21 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>ai-coding-agent, claude, claude-ai, claude-code, claude-plugin, claude-skill, claude-skills, codex, codex-skills, developer-tools, java, mcp</t>
+          <t>awesome, awesome-list, collection, curated-list, ruby, ruby-libraries</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>161</v>
+        <v>4465</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2058,27 +2051,26 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-23</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>emotixco/claude-skills-founder</t>
+          <t>We5ter/Scanners-Box</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>257</v>
+        <v>9056</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude Code 技能给初创公司创始人
-【原文】Claude Code skills for startup founders — product briefs, competitor analysis, pricing strategy, pitch decks, and GTM plans from your terminal
-【依据】topics: ai, claude, claude-code, claude-code-plugin, competitor-analysis, founder, go-to-market, pitch-deck, product-man</t>
+          <t>提供全面的网络安全工具矩阵。
+【原文】The Ultimate Open-Source Security Arsenal for Hackers, Enterprises, and AI Agents——面向极客、企业与 AI 智能体的全域开源网络安全工具矩阵</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2088,12 +2080,12 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2103,7 +2095,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/emotixco/claude-skills-founder</t>
+          <t>https://github.com/We5ter/Scanners-Box</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2112,11 +2104,11 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>1.31</v>
+        <v>2.54</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr"/>
@@ -2132,63 +2124,62 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>ai, claude, claude-code, claude-code-plugin, competitor-analysis, founder, go-to-market, pitch-deck, product-management, skills, slash-commands, startup</t>
+          <t>agent-security-audit, agent-security-benchmark, agent-security-red-teaming, agent-security-tools, ai, ai-security, apk-analysis, binary-analysis, code-analyzer, devsecops, exploitation-framework, malware-analysis</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2016-12-24</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>196</v>
+        <v>3560</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-23</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>tl2012tl/comfyUI-llama-TE</t>
+          <t>decalage2/awesome-security-hardening</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>202</v>
+        <v>6556</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>9</v>
+        <v>16.9</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>提供图片反推、提示词、本地多轮对话等功能
-【原文】qwen3/qwen3.5/qwen3.8/gemma4 图片反推,提示词,本地多轮对话,本地skill使用,扩写高速版
-【依据】topics: -</t>
+          <t>安全加固指南、工具和其他资源的集合
+【原文】A collection of awesome security hardening guides, tools and other resources</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2203,7 +2194,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tl2012tl/comfyUI-llama-TE</t>
+          <t>https://github.com/decalage2/awesome-security-hardening</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2212,18 +2203,14 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>1.29</v>
+        <v>2.42</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+      <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2234,51 +2221,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>awesome-list, best-practices, blue-team, blueteam, cis-benchmarks, computer-security, cyber-security, cybersecurity, infosec, linux-hardening, security, security-hardening</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2019-04-29</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>157</v>
+        <v>2704</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-24</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Londeren/hh-skill-verifications-quizzes</t>
+          <t>ArtemXTech/personal-os-skills</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>652</v>
+        <v>536</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>5.9</v>
+        <v>13.7</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>提供 hh.ru 技能验证测试的答案
-【原文】Ответы на тесты для подтверждения навыков на hh.ru (headhunter.ru): английский, ООП, JavaScript, Git, HTML, Python, SQL, Scrum, Agile Project Management, MS Excel, Копирайтинг.
-【依据】topics: -</t>
+          <t>Claude Code 技能用于 Obsidian
+【原文】Claude Code skills for Obsidian | Claude Code x Obsidian Lab starts May 5</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -2288,12 +2278,12 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -2303,7 +2293,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Londeren/hh-skill-verifications-quizzes</t>
+          <t>https://github.com/ArtemXTech/personal-os-skills</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2312,14 +2302,18 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.84</v>
+        <v>1.96</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2333,16 +2327,16 @@
       <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>776</v>
+        <v>274</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
@@ -2354,27 +2348,26 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-23</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Justineo/vue-awesome</t>
+          <t>nimrodfisher/data-analytics-skills</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2426</v>
+        <v>443</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>4.4</v>
+        <v>12.2</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Vue.js 的 SVG 图标组件
-【原文】Awesome SVG icon component for Vue.js, built-in with Font Awesome icons.
-【依据】topics: font-awesome, icon, svg, vue</t>
+          <t>提供 Claude &amp; Codex 在数据分析任务中的技能列表
+【原文】A comprehensive list of Claude &amp; Codex skills for a wide range of data analytics tasks</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2384,7 +2377,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2399,7 +2392,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Justineo/vue-awesome</t>
+          <t>https://github.com/nimrodfisher/data-analytics-skills</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2408,7 +2401,7 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.63</v>
+        <v>1.74</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -2417,7 +2410,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2432,21 +2425,21 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>font-awesome, icon, svg, vue</t>
+          <t>claude-code, codex, data-analytics, skills</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2016-04-01</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>3826</v>
+        <v>255</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
@@ -2458,42 +2451,41 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-23</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>A9T9/RPA</t>
+          <t>cdleon/awesome-terminals</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2025</v>
+        <v>2999</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>提供浏览器和桌面自动化工具，带有 MCP 服务器
-【原文】Browser and desktop automation with an MCP server for AI assistants. Record macros or write JavaScript to automate websites, extract data, and control desktop apps with OCR and image recognition.
-【依据】topics: ai-agents, browser-automation, browser-automation-ai-api, browser-extension, computer-use, desktop-automation, i</t>
+          <t>终端模拟器列表
+【原文】Terminal Emulators</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2503,7 +2495,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/A9T9/RPA</t>
+          <t>https://github.com/cdleon/awesome-terminals</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2512,18 +2504,14 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.61</v>
+        <v>1.03</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2536,24 +2524,24 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, browser-automation, browser-automation-ai-api, browser-extension, computer-use, desktop-automation, image-recognition, macro-recorder, mcp, mcp-server, ocr, selenium-ide</t>
+          <t>bash, c, command-line, cpp, golang, haskell, node, powershell, python, ruby, rust, shell</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2017-08-04</t>
+          <t>2018-10-07</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>3336</v>
+        <v>2908</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
@@ -2562,27 +2550,26 @@
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-24</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>mswnlz/chinese-traditional</t>
+          <t>guobao2333/DeepLX-Serverless</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>63</v>
+        <v>558</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>提供中医课程资料大全
-【原文】🎁重磅资源！原价59880元 绝版中医课程资料大全【收藏版1.18TB】，包括基础、视频、外治、针灸、书籍等等等应有尽有
-【依据】topics: -</t>
+          <t>提供免费的DeepL API服务，适用于无服务器环境。
+【原文】Free DeepL API for Serverless</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2597,7 +2584,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2607,7 +2594,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mswnlz/chinese-traditional</t>
+          <t>https://github.com/guobao2333/DeepLX-Serverless</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2616,14 +2603,18 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.13</v>
+        <v>0.72</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2634,36 +2625,246 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P22" s="6" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>api, deepl, deeplx, free-api, i18n, javascript, nodejs, serverless, translation</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>497</v>
+        <v>776</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>topic:free-api stars:&gt;300 pushed:&gt;2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>protegeproject/protege</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1534</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>知识图谱构建和管理的Java桌面应用程序。
+【原文】Protege Desktop</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>RAG检索线</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>架构参考</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/protegeproject/protege</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>java, knowledge-graph, knowledge-management, obo, ontology, ontology-engineering, owl, protege, protege-desktop, rdf, reasoning, semantics</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>2013-08-20</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>4782</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>kuaidi100-api/java-demo</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>提供快递查询API接口，支持快递单号查询、电子面单等。
+【原文】快递100API-Java快递查询接口主要应用在电商商城、ERP系统商、WMS系统商、独立站电商卖家、银行等企业。本Java快递查询接口目录提供：快递单号查询API接口、快递电子面单接口、寄快递接口、同城配送接口、快递地图跟踪接口等Java demo。接入只需要跟随Java快递查询接口示例即可，如需帮助，请点击下方官网链接，官网技术人员会免费帮助您接入接口。快递100API开放平台与国内外3000+快递公司合作提供快递单号查询API接口，快递电子面单接口，寄快递接口，快递地图跟踪接口等电商运营必备的物流快递工具.</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/kuaidi100-api/java-demo</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>java, kuaidi100, lable, lableprint, saas-api, shipping-api, tracking-api</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>2020-07-21</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>2255</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="V22" s="6" t="inlineStr">
-        <is>
-          <t>中医 in:name,description stars:&gt;50</t>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V22"/>
+  <autoFilter ref="A2:V24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-23 · 共 22 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-24 · 共 14 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,29 +633,29 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>EKKOLearnAI/ekko-studio</t>
+          <t>Vincentwei1021/anything2explainer</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>11182</v>
+        <v>2019</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>474.4</v>
+        <v>883.3</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>多智能体AI工作空间，支持聊天、编码和可视化工作流程。
-【原文】Ekko Studio is a local-first AI workspace for multi-agent chat, coding, and visual workflows, available on desktop and the web.</t>
+          <t>将任何主题转换为黑画布动画解释视频，带语音和字幕
+【原文】Topic in, narrated explainer video out. A Claude Code / Codex skill that turns any topic into a black-canvas motion-graphics explainer video with TTS voiceover, subtitles and a chapter progress bar. Chinese or English; every frame drawn in code with Remotion.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/EKKOLearnAI/ekko-studio</t>
+          <t>https://github.com/Vincentwei1021/anything2explainer</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>67.77</v>
+        <v>126.19</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -703,67 +703,67 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>agent, ai-agent, chat-ui, coding-agents, dashboard, ekko-studio, hermes, hermes-agent, hermes-web-ui, llm, multi-agent, multi-model</t>
+          <t>agent-skills, ai-agents, ai-video, claude-code, claude-code-skill, codex, edge-tts, educational-video, explainer-video, kokoro, motion-graphics, multi-agent</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-24</t>
+          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-26</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>op7418/guizang-product-video-skill</t>
+          <t>Ryze-AI-Adgent/open-seo-mcp-skills</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>221</v>
+        <v>1248</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>309.4</v>
+        <v>336</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>生成软件更新宣传片，复用产品组件和设计语言
-【原文】归藏 product video skill：复用真实产品组件和设计语言，用代码制作软件更新宣传片。包含分镜文案、原创配乐、动作音效与视频渲染，支持 Claude Code 和 Codex。</t>
+          <t>提供免费的SEO MCP服务器和开源SEO和GEO技能
+【原文】Free SEO MCP server + open-source SEO and GEO skills for Claude: keyword research, rank tracking, audits, backlinks, AI visibility on your real GSC/GA4/ads data. claude mcp add ryze --transport http https://connector.get-ryze.ai/mcp</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>MCP服务</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/op7418/guizang-product-video-skill</t>
+          <t>https://github.com/Ryze-AI-Adgent/open-seo-mcp-skills</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>44.2</v>
+        <v>48</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, claude-code, codepilot, codex, hyperframes, motion-design, product-video, release-notes, skill, skills, video-generation</t>
+          <t>ai-seo, ai-visibility, backlinks, claude, claude-code, claude-skills, dataforseo, generative-engine-optimization, geo, geo-mcp, keyword-research, llm-seo</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -832,36 +832,36 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-24</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>feder-cr/invisible_playwright_mcp</t>
+          <t>getsentry/MobileBuildMCP</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>31631</v>
+        <v>6416</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>283.8</v>
+        <v>79.7</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>提供防检测的浏览器自动化工具，用于网络爬取和生成潜在客户。
-【原文】Anti-detect agentic stealth browser: undetected browsing, browser automation, Python AI web browsing agent, computer use, scraping, lead generation. No captchas.</t>
+          <t>提供MCP服务器和CLI，用于iOS和macOS项目中的代理使用
+【原文】A Model Context Protocol (MCP) server and CLI that provides tools for agent use when working on iOS and macOS projects.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>MCP服务</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/feder-cr/invisible_playwright_mcp</t>
+          <t>https://github.com/getsentry/MobileBuildMCP</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>40.55</v>
+        <v>11.38</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, ai-agent, ai-automation, autonomous-agents, browser, claude-code-plugin, crawler, gemini-cli-extension, job-hunting, job-search, lead-generation, llm-agent</t>
+          <t>mcp, mcp-server, model-context-protocol, model-context-protocol-servers, tag-non-production, xcode, xcodebuild</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>780</v>
+        <v>564</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
@@ -935,25 +935,26 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-24</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>VDERR/dsh-echocat-skill-panel</t>
+          <t>vmoranv/jshookmcp</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>201</v>
+        <v>2019</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>281.4</v>
+        <v>65.7</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>DSH 技能调用审计 + 应用内 skill 管理器</t>
+          <t>提供js hook工具包，用于浏览器自动化和调试
+【原文】js hook toolkit that all you need</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -963,12 +964,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -978,7 +979,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/VDERR/dsh-echocat-skill-panel</t>
+          <t>https://github.com/vmoranv/jshookmcp</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -987,16 +988,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>40.2</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1011,67 +1012,67 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>cordis, deepseek-harness, dsh-plugin</t>
+          <t>browser-automation, debugging, deobfuscation, js-reverse, mcp, network-analysis, reverse-engineering, security-analysis</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>5</v>
+        <v>215</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-24</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>superdesigndev/treg</t>
+          <t>rynfar/meridian</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2314</v>
+        <v>2045</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>231.4</v>
+        <v>58</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>为智能体工具提供OpenRouter服务。
-【原文】OpenRouter for agent tools. Join community here: https://discord.gg/6mQYYfFMAn</t>
+          <t>使用Claude和Antigravity与Pi、OpenCode等编码客户端交互
+【原文】Use Claude and Antigravity with Pi, OpenCode and other coding clients. Local API bridge, usage dashboard and Mac app. Antigravity preview available in 1.74.0.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MCP服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1081,7 +1082,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/superdesigndev/treg</t>
+          <t>https://github.com/rynfar/meridian</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1090,16 +1091,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>33.06</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1114,21 +1115,21 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>agents, api-keys, cli, credentials, developer-tools, dsh-plugin, mcp, proxy, python, registry, secrets</t>
+          <t>ai-agents, ai-coding, aider, anthropic, antigravity, bun, claude, claude-agent-sdk, claude-max, cline, crush-cli, gemini</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>70</v>
+        <v>247</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1140,26 +1141,26 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-24</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Alisa0808/vox-director</t>
+          <t>iart-ai/motion-skills</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2010</v>
+        <v>498</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>187.6</v>
+        <v>37.1</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>自动生成Vox风格的解释性视频，支持Claude技能集成。
-【原文】Turn one topic into a finished Vox-style paper-collage explainer/ad video — automated end to end on Atlas Cloud + ffmpeg. An agent skill.</t>
+          <t>教授 AI 编码代理制作动态图形、动画和视频的技能库
+【原文】50 open-source skills that teach your AI coding agent to make motion graphics, animation &amp; video — kinetic typography, data-viz, explainers, TikTok/Reels, WebGL, Manim. 14 installable packs. By iart.ai, the AI motion agent.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1184,7 +1185,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Alisa0808/vox-director</t>
+          <t>https://github.com/iart-ai/motion-skills</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1193,7 +1194,7 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>26.8</v>
+        <v>5.3</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1217,21 +1218,21 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-video, claude-code, claude-skill, collage-video, dsh-plugin, explainer-video, ffmpeg, generative-ai, llm, motion-graphics, python</t>
+          <t>ai-agents, claude-code, motion-graphics, remotion, skills</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1243,41 +1244,42 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-25</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>krillinai/OpenCreator</t>
+          <t>Karovia/fullstack-ai-agent-roadmap</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>12220</v>
+        <v>502</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>132.7</v>
+        <v>36.3</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>开源AI创作空间，支持视频、图像、声音等创作。
-【原文】Formerly KrillinAI. Open-source AI workspace for creators, powered by Codex. Create videos, images, voice, avatars, video translation, and edits with Agents in one place.</t>
+          <t>提供从零基础到AI Agent全栈工程师的教程和项目
+【原文】🎯 从零基础到 AI Agent 全栈工程师 · 110 个详细教程 · 58 万字 · 400+ GitHub 项目精选 · Obsidian 友好 · 中文
+【依据】110 个详细教程，400+ GitHub 项目精选</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>视频产线/图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>架构参考</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1287,7 +1289,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/krillinai/OpenCreator</t>
+          <t>https://github.com/Karovia/fullstack-ai-agent-roadmap</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1296,18 +1298,14 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>18.95</v>
+        <v>5.18</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1320,67 +1318,67 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, codex-cli, deskop-app, dubbing, image-generation, localization, skills, tts, video-editing, video-generation, video-transcription, video-translation</t>
+          <t>ai, ai-agent, chinese, claude, fastapi, fullstack, javascript, langgraph, learning-roadmap, llm, mcp, obsidian</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>645</v>
+        <v>97</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-25</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>zilliztech/deep-searcher</t>
+          <t>limin112/min-skill</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>8280</v>
+        <v>360</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>97.90000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>开源深度研究替代方案，用于私有数据上的推理和搜索
-【原文】Open Source Deep Research Alternative to Reason and Search on Private Data. Written in Python.</t>
+          <t>提供 Claude 技能集
+【依据】набор скиллов для Claude</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1390,7 +1388,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zilliztech/deep-searcher</t>
+          <t>https://github.com/limin112/min-skill</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1399,16 +1397,16 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>13.99</v>
+        <v>2.79</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1421,23 +1419,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>agent, agentic-rag, claude, deep-research, deepseek, deepseek-r1, grok, grok3, llama4, llm, milvus, openai</t>
-        </is>
-      </c>
+      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>592</v>
+        <v>129</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1449,41 +1443,41 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-24</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>53AI/53AIHub</t>
+          <t>DragonJAR/Android-Pentesting-Skill</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4658</v>
+        <v>371</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>63.1</v>
+        <v>14.7</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>AI 知识库与 Agent 门户，管理企业知识、AI 代理、提示和 AI 工具
-【原文】53AI Hub is an open-source AI portal and knowledge base for managing enterprise knowledge, AI agents, prompts, and AI tools, seamlessly integrating with Coze, Dify, FastGPT, RAGFlow. 一个AI知识库与Agent门户</t>
+          <t>提供Android Pentesting技能
+【原文】Skill de Pentesting para Android</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1493,7 +1487,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/53AI/53AIHub</t>
+          <t>https://github.com/DragonJAR/Android-Pentesting-Skill</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1502,16 +1496,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>9.01</v>
+        <v>2.1</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1524,23 +1518,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>coze, dify, fastgpt, go, knowledge, maxkb, mcp, openai, prompt, rag, ragflow</t>
-        </is>
-      </c>
+      <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>517</v>
+        <v>177</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1552,26 +1542,26 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-24</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>oceanbase/seekdb</t>
+          <t>pinecone-io/examples</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>3021</v>
+        <v>3045</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>62.7</v>
+        <v>10.5</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>AI原生搜索引擎，统一向量、文本、结构化和半结构化数据
-【原文】The AI-Native Search Database. Best for agent storage, it unifies vector, text, structured, and semi-structured data into a single engine. This all-in-one database makes agents smarter, easier to run, and more stable.</t>
+          <t>提供 Pinecone 向量数据库的 Jupyter Notebook 示例
+【原文】Jupyter Notebooks to help you get hands-on with Pinecone vector databases</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1581,7 +1571,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1596,7 +1586,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/oceanbase/seekdb</t>
+          <t>https://github.com/pinecone-io/examples</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1605,16 +1595,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>8.960000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1629,21 +1619,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, copy-on-write, embedded-database, full-text-search, hnsw, hybrid-search, langchain, llamaindex, mysql, oceanbase, python, rag</t>
+          <t>ai, jupyter-notebook, llm, pinecone, python, rag, semantic-search, vector-database, vector-search</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>337</v>
+        <v>2025</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1655,26 +1645,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-24</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>tayllan/awesome-algorithms</t>
+          <t>marmelab/awesome-rest</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>25569</v>
+        <v>3916</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>40.2</v>
+        <v>6.6</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>算法学习与实践资源列表
-【原文】A curated list of awesome places to learn and/or practice algorithms.</t>
+          <t>提供关于RESTful API架构、开发、测试和性能的资源列表
+【原文】A collaborative list of great resources about RESTful API architecture, development, test, and performance</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1684,12 +1674,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1699,7 +1689,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tayllan/awesome-algorithms</t>
+          <t>https://github.com/marmelab/awesome-rest</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1708,11 +1698,11 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>5.74</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>CC0-1.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr"/>
@@ -1726,19 +1716,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>awesome, rest</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2014-07-16</t>
+          <t>2015-05-07</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>4452</v>
+        <v>4158</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1750,26 +1744,26 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-24</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>bharathgs/Awesome-pytorch-list</t>
+          <t>HenryQW/Awesome-TTRSS</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>16678</v>
+        <v>2591</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>33.4</v>
+        <v>5.4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>PyTorch 相关内容的综合列表
-【原文】A comprehensive list of pytorch related content on github,such as different models,implementations,helper libraries,tutorials etc.</t>
+          <t>提供强大的Docker化全合一RSS解决方案
+【原文】🐋 Awesome TTRSS, a powerful Dockerised all-in-one RSS solution.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1779,12 +1773,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1794,7 +1788,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/bharathgs/Awesome-pytorch-list</t>
+          <t>https://github.com/HenryQW/Awesome-TTRSS</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1803,14 +1797,18 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>4.77</v>
+        <v>0.77</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1823,21 +1821,21 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, computer-vision, cv, data-science, deep-learning, facebook, machine-learning, natural-language-processing, neural-network, nlp, nlp-library</t>
+          <t>docker, feedly, fever, mercury-parser, rss-feed, rss-reader, tt-rss, ttrss</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2017-07-13</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>3493</v>
+        <v>3360</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1849,26 +1847,26 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-24</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MarkPDFdown/markpdfdown</t>
+          <t>artwist-polyakov/polyakov-claude-skills</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2272</v>
+        <v>201</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>28.5</v>
+        <v>4.4</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>将PDF转换为Markdown格式的高质量工具。
-【原文】A high-quality PDF to Markdown tool based on large language model visual recognition. 一款基于大模型视觉识别的高质量PDF转Markdown工具</t>
+          <t>提供 Claude 技能集
+【原文】Набор скиллов для Claude</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1878,7 +1876,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1893,7 +1891,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MarkPDFdown/markpdfdown</t>
+          <t>https://github.com/artwist-polyakov/polyakov-claude-skills</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1902,11 +1900,11 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>4.07</v>
+        <v>0.63</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1924,14 +1922,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>llm, markdown, pdf, pdf-converter, pdf-markdown, pdf2markdown, pdf2md</t>
-        </is>
-      </c>
+      <c r="P15" s="6" t="inlineStr"/>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
@@ -1940,38 +1934,38 @@
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>558</v>
+        <v>321</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-24</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>markets/awesome-ruby</t>
+          <t>michelpereira/awesome-games-of-coding</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>14157</v>
+        <v>2158</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>22.2</v>
+        <v>4.3</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>收集 Ruby 库、工具、框架和软件的列表
-【原文】💎 A collection of awesome Ruby libraries, tools, frameworks and software</t>
+          <t>提供编程语言学习游戏的列表
+【原文】A curated list of games that can teach you how to learn a programming language.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1981,12 +1975,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1996,7 +1990,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/markets/awesome-ruby</t>
+          <t>https://github.com/michelpereira/awesome-games-of-coding</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2005,11 +1999,11 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>3.17</v>
+        <v>0.61</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>CC0-1.0</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr"/>
@@ -2025,21 +2019,21 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, collection, curated-list, ruby, ruby-libraries</t>
+          <t>awesome, awesome-list, game, guido-van-robot, programming-language, robocode</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2017-02-04</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>4465</v>
+        <v>3519</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2051,820 +2045,12 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>We5ter/Scanners-Box</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>9056</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>提供全面的网络安全工具矩阵。
-【原文】The Ultimate Open-Source Security Arsenal for Hackers, Enterprises, and AI Agents——面向极客、企业与 AI 智能体的全域开源网络安全工具矩阵</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/We5ter/Scanners-Box</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>agent-security-audit, agent-security-benchmark, agent-security-red-teaming, agent-security-tools, ai, ai-security, apk-analysis, binary-analysis, code-analyzer, devsecops, exploitation-framework, malware-analysis</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>2016-12-24</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>3560</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>decalage2/awesome-security-hardening</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>6556</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>安全加固指南、工具和其他资源的集合
-【原文】A collection of awesome security hardening guides, tools and other resources</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/decalage2/awesome-security-hardening</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>awesome-list, best-practices, blue-team, blueteam, cis-benchmarks, computer-security, cyber-security, cybersecurity, infosec, linux-hardening, security, security-hardening</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>2019-04-29</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>2704</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="150" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>ArtemXTech/personal-os-skills</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>536</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code 技能用于 Obsidian
-【原文】Claude Code skills for Obsidian | Claude Code x Obsidian Lab starts May 5</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/ArtemXTech/personal-os-skills</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="150" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>nimrodfisher/data-analytics-skills</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>443</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>提供 Claude &amp; Codex 在数据分析任务中的技能列表
-【原文】A comprehensive list of Claude &amp; Codex skills for a wide range of data analytics tasks</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/nimrodfisher/data-analytics-skills</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>claude-code, codex, data-analytics, skills</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V20" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="150" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>cdleon/awesome-terminals</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>2999</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>终端模拟器列表
-【原文】Terminal Emulators</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/cdleon/awesome-terminals</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>bash, c, command-line, cpp, golang, haskell, node, powershell, python, ruby, rust, shell</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>2018-10-07</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>2908</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V21" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="150" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>guobao2333/DeepLX-Serverless</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>558</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>提供免费的DeepL API服务，适用于无服务器环境。
-【原文】Free DeepL API for Serverless</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/guobao2333/DeepLX-Serverless</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>api, deepl, deeplx, free-api, i18n, javascript, nodejs, serverless, translation</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>776</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="V22" s="6" t="inlineStr">
-        <is>
-          <t>topic:free-api stars:&gt;300 pushed:&gt;2026-06-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>protegeproject/protege</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>1534</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>知识图谱构建和管理的Java桌面应用程序。
-【原文】Protege Desktop</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>RAG检索线</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>架构参考</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/protegeproject/protege</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>java, knowledge-graph, knowledge-management, obo, ontology, ontology-engineering, owl, protege, protege-desktop, rdf, reasoning, semantics</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>2013-08-20</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>4782</v>
-      </c>
-      <c r="T23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V23" s="6" t="inlineStr">
-        <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>kuaidi100-api/java-demo</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>272</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>提供快递查询API接口，支持快递单号查询、电子面单等。
-【原文】快递100API-Java快递查询接口主要应用在电商商城、ERP系统商、WMS系统商、独立站电商卖家、银行等企业。本Java快递查询接口目录提供：快递单号查询API接口、快递电子面单接口、寄快递接口、同城配送接口、快递地图跟踪接口等Java demo。接入只需要跟随Java快递查询接口示例即可，如需帮助，请点击下方官网链接，官网技术人员会免费帮助您接入接口。快递100API开放平台与国内外3000+快递公司合作提供快递单号查询API接口，快递电子面单接口，寄快递接口，快递地图跟踪接口等电商运营必备的物流快递工具.</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/kuaidi100-api/java-demo</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>java, kuaidi100, lable, lableprint, saas-api, shipping-api, tracking-api</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>2020-07-21</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>2255</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V24" s="6" t="inlineStr">
-        <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-25</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V24"/>
+  <autoFilter ref="A2:V16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-24 · 共 14 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-25 · 共 16 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,34 +633,34 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Vincentwei1021/anything2explainer</t>
+          <t>mikehasa/golive-skill</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2019</v>
+        <v>894</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>883.3</v>
+        <v>3129</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>将任何主题转换为黑画布动画解释视频，带语音和字幕
-【原文】Topic in, narrated explainer video out. A Claude Code / Codex skill that turns any topic into a black-canvas motion-graphics explainer video with TTS voiceover, subtitles and a chapter progress bar. Chinese or English; every frame drawn in code with Remotion.</t>
+          <t>提供将代理产品上线的一站式服务
+【原文】Take your agent-built product live: hosting, database, domain, email, payments — on your own accounts. Open-source Agent Skill + zero-dependency Node CLI: detect → plan → approve → apply → verify. No GoLive account, backend or telemetry.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Vincentwei1021/anything2explainer</t>
+          <t>https://github.com/mikehasa/golive-skill</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,11 +679,11 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>126.19</v>
+        <v>447</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -703,21 +703,21 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, ai-video, claude-code, claude-code-skill, codex, edge-tts, educational-video, explainer-video, kokoro, motion-graphics, multi-agent</t>
+          <t>agent-skill, agent-skills, ai-agents, claude-code, cloudflare, codex, database, deployment, developer-tools, devops, dns, godaddy</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -729,36 +729,36 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-26</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Ryze-AI-Adgent/open-seo-mcp-skills</t>
+          <t>helloianneo/ian-xiaohei-illustrations</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1248</v>
+        <v>12069</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>336</v>
+        <v>698.2</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>提供免费的SEO MCP服务器和开源SEO和GEO技能
-【原文】Free SEO MCP server + open-source SEO and GEO skills for Claude: keyword research, rank tracking, audits, backlinks, AI visibility on your real GSC/GA4/ads data. claude mcp add ryze --transport http https://connector.get-ryze.ai/mcp</t>
+          <t>生成中文小黑怪诞正文配图
+【原文】中文小黑怪诞正文配图生成 Skill | 16:9 白底手绘 | 少量红橙蓝批注 | Codex Skill</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MCP服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Ryze-AI-Adgent/open-seo-mcp-skills</t>
+          <t>https://github.com/helloianneo/ian-xiaohei-illustrations</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,18 +782,14 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>48</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -806,12 +802,12 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>ai-seo, ai-visibility, backlinks, claude, claude-code, claude-skills, dataforseo, generative-engine-optimization, geo, geo-mcp, keyword-research, llm-seo</t>
+          <t>ai-agent, chinese, codex-skill, handdrawn, illustration, image-generation, xiaohei</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -820,10 +816,10 @@
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -832,36 +828,36 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-25</t>
+          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>getsentry/MobileBuildMCP</t>
+          <t>Companion-Inc/feynman</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>6416</v>
+        <v>9781</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>79.7</v>
+        <v>360.4</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>提供MCP服务器和CLI，用于iOS和macOS项目中的代理使用
-【原文】A Model Context Protocol (MCP) server and CLI that provides tools for agent use when working on iOS and macOS projects.</t>
+          <t>开源 AI 研究代理
+【原文】The open source AI research agent.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MCP服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/getsentry/MobileBuildMCP</t>
+          <t>https://github.com/Companion-Inc/feynman</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -885,7 +881,7 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>11.38</v>
+        <v>51.48</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -909,52 +905,52 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>mcp, mcp-server, model-context-protocol, model-context-protocol-servers, tag-non-production, xcode, xcodebuild</t>
+          <t>ai-agent, arxiv, cli, literature-review, pi-coding-agent, research</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>564</v>
+        <v>190</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-25</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>vmoranv/jshookmcp</t>
+          <t>browser-use/web-ui</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2019</v>
+        <v>16585</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>65.7</v>
+        <v>184</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供js hook工具包，用于浏览器自动化和调试
-【原文】js hook toolkit that all you need</t>
+          <t>在浏览器中运行 AI 代理
+【原文】🖥️ Run AI Agent in your browser.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -964,12 +960,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -979,7 +975,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vmoranv/jshookmcp</t>
+          <t>https://github.com/browser-use/web-ui</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -988,16 +984,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>9.390000000000001</v>
+        <v>26.28</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1012,21 +1008,21 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>browser-automation, debugging, deobfuscation, js-reverse, mcp, network-analysis, reverse-engineering, security-analysis</t>
+          <t>ai-agent, browser-automation, browser-use-box, cloud-browser</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>215</v>
+        <v>631</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1038,41 +1034,41 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-25</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>rynfar/meridian</t>
+          <t>agents-universe/agents-universe</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2045</v>
+        <v>299</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>58</v>
+        <v>139.5</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>使用Claude和Antigravity与Pi、OpenCode等编码客户端交互
-【原文】Use Claude and Antigravity with Pi, OpenCode and other coding clients. Local API bridge, usage dashboard and Mac app. Antigravity preview available in 1.74.0.</t>
+          <t>提供数字分身协同工作平台
+【原文】不是问答机器人，而是能真正干活的数字分身。共享智能体，共享项目上下文，让项目所有成员一起协同工作。同时智能体会像人一样通过资料或者工作抽象和总结经验到项目上下文中</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>MCP服务/技能包/架构参考</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1082,7 +1078,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rynfar/meridian</t>
+          <t>https://github.com/agents-universe/agents-universe</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1091,16 +1087,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>8.279999999999999</v>
+        <v>19.93</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1115,67 +1111,67 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, ai-coding, aider, anthropic, antigravity, bun, claude, claude-agent-sdk, claude-max, cline, crush-cli, gemini</t>
+          <t>agent, agent-framework, agent-orchestration, agent-skill, agentic-ai, ai-agents, ai-governance, ai-tools, deepseek-harness, harness, harness-engineering, harness-framework</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>247</v>
+        <v>15</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-25</t>
+          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>iart-ai/motion-skills</t>
+          <t>cactus-compute/cactus</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>498</v>
+        <v>6058</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>37.1</v>
+        <v>81.5</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>教授 AI 编码代理制作动态图形、动画和视频的技能库
-【原文】50 open-source skills that teach your AI coding agent to make motion graphics, animation &amp; video — kinetic typography, data-viz, explainers, TikTok/Reels, WebGL, Manim. 14 installable packs. By iart.ai, the AI motion agent.</t>
+          <t>为移动设备提供量化、内核、运行时和推理引擎
+【原文】Quantization, kernels, runtime and inference engine for mobiles, wearables, smart home and robots.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1185,7 +1181,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/iart-ai/motion-skills</t>
+          <t>https://github.com/cactus-compute/cactus</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1194,16 +1190,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5.3</v>
+        <v>11.65</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1218,21 +1214,21 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, claude-code, motion-graphics, remotion, skills</t>
+          <t>ai, android, arm, edge, edge-ai, framework, ios, llamacpp, llm, llm-inference, llms, mobile</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>94</v>
+        <v>520</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1244,27 +1240,26 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-25</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Karovia/fullstack-ai-agent-roadmap</t>
+          <t>anus-dev/ANUS</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>502</v>
+        <v>6543</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>36.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>提供从零基础到AI Agent全栈工程师的教程和项目
-【原文】🎯 从零基础到 AI Agent 全栈工程师 · 110 个详细教程 · 58 万字 · 400+ GitHub 项目精选 · Obsidian 友好 · 中文
-【依据】110 个详细教程，400+ GitHub 项目精选</t>
+          <t>自主维护的代理
+【依据】self-maintaining-repository</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1274,12 +1269,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1289,7 +1284,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Karovia/fullstack-ai-agent-roadmap</t>
+          <t>https://github.com/anus-dev/ANUS</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1298,14 +1293,18 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>5.18</v>
+        <v>11.58</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1318,57 +1317,57 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agent, chinese, claude, fastapi, fullstack, javascript, langgraph, learning-roadmap, llm, mcp, obsidian</t>
+          <t>ai-agent, autonomous-agent, self-maintaining-repository, spec-driven-company</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>97</v>
+        <v>565</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-25</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>limin112/min-skill</t>
+          <t>helloianneo/ian-handdrawn-ppt</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>360</v>
+        <v>1442</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>19.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude 技能集
-【依据】набор скиллов для Claude</t>
+          <t>生成中文手绘技术 PPT 图像
+【原文】中文手绘技术 PPT 整页图像生成 Skill | 21:9 封面 + 16:9 正文配图 | PNG 输出</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1378,7 +1377,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1388,7 +1387,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/limin112/min-skill</t>
+          <t>https://github.com/helloianneo/ian-handdrawn-ppt</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1397,18 +1396,14 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>2.79</v>
+        <v>9.42</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1419,50 +1414,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>ai-agent, chinese, codex-skill, handdrawn, image-generation, ppt</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-25</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DragonJAR/Android-Pentesting-Skill</t>
+          <t>andyrewlee/awesome-agent-orchestrators</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>371</v>
+        <v>2004</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>14.7</v>
+        <v>56.6</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>提供Android Pentesting技能
-【原文】Skill de Pentesting para Android</t>
+          <t>列出代理编排器列表
+【原文】List of agent orchestrators</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1472,7 +1471,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>架构参考</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1487,7 +1486,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/DragonJAR/Android-Pentesting-Skill</t>
+          <t>https://github.com/andyrewlee/awesome-agent-orchestrators</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1496,18 +1495,14 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>2.1</v>
+        <v>8.08</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1518,19 +1513,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr"/>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>agent-coordination, agent-orchestration, agent-swarm, agentic-ai, ai-agents, ai-coding, ai-orchestration, awesome, awesome-list, claude-code, codex, coding-agents</t>
+        </is>
+      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1542,41 +1541,40 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-25</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>pinecone-io/examples</t>
+          <t>MashiroSaber03/Saber-Translator</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>3045</v>
+        <v>3604</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>10.5</v>
+        <v>43.3</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>提供 Pinecone 向量数据库的 Jupyter Notebook 示例
-【原文】Jupyter Notebooks to help you get hands-on with Pinecone vector databases</t>
+          <t>漫画翻译工具</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1586,7 +1584,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pinecone-io/examples</t>
+          <t>https://github.com/MashiroSaber03/Saber-Translator</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1595,16 +1593,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1.5</v>
+        <v>6.19</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1617,54 +1615,50 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>ai, jupyter-notebook, llm, pinecone, python, rag, semantic-search, vector-database, vector-search</t>
-        </is>
-      </c>
+      <c r="P12" s="6" t="inlineStr"/>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>2025</v>
+        <v>582</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-25</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>marmelab/awesome-rest</t>
+          <t>ExplosiveCoderflome/AI-Novel-Writing-Assistant</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>3916</v>
+        <v>3006</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>6.6</v>
+        <v>36.1</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供关于RESTful API架构、开发、测试和性能的资源列表
-【原文】A collaborative list of great resources about RESTful API architecture, development, test, and performance</t>
+          <t>面向长篇小说创作的 AI Native 开源系统，支持从灵感到完整小说的整本生产工作流
+【原文】面向长篇小说创作的 AI Native 开源系统，用 Agent、世界观、写法引擎、RAG 和整本生产工作流，帮助新手从一句灵感走到完整小说。AI-native engine for end-to-end novel creation — from idea to full chapters, with structured planning, worldbuilding, and agent-driven workflows.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1674,12 +1668,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1689,7 +1683,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/marmelab/awesome-rest</t>
+          <t>https://github.com/ExplosiveCoderflome/AI-Novel-Writing-Assistant</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1698,14 +1692,18 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>5.15</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr"/>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1718,12 +1716,12 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>awesome, rest</t>
+          <t>agent-workflow, ai, creative-writing, long-form-fiction, narrative-engine, novel-writing, rag, story-generation, worldbuilding, writing-assistant</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2015-05-07</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -1732,7 +1730,7 @@
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>4158</v>
+        <v>584</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1744,36 +1742,36 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-25</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>HenryQW/Awesome-TTRSS</t>
+          <t>agentset-ai/agentset</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2591</v>
+        <v>2096</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>提供强大的Docker化全合一RSS解决方案
-【原文】🐋 Awesome TTRSS, a powerful Dockerised all-in-one RSS solution.</t>
+          <t>提供开源的 RAG 平台，支持多种文件格式和内置引用
+【原文】The open-source RAG platform: built-in citations, deep research, 22+ file formats, partitions, MCP server, and more.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/图文产线/未归类</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>MCP服务/代码库/可部署服务</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1788,7 +1786,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/HenryQW/Awesome-TTRSS</t>
+          <t>https://github.com/agentset-ai/agentset</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1797,7 +1795,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.77</v>
+        <v>3.72</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1806,7 +1804,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1821,12 +1819,12 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>docker, feedly, fever, mercury-parser, rss-feed, rss-reader, tt-rss, ttrss</t>
+          <t>agentic-rag, ai, ai-agents, ai-sdk, chatbots, embeddings, genai, llms, memory, memory-management, rag, vercel-ai-sdk</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2017-07-13</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
@@ -1835,7 +1833,7 @@
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>3360</v>
+        <v>564</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1847,41 +1845,41 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-25</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>artwist-polyakov/polyakov-claude-skills</t>
+          <t>TykTechnologies/tyk</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>201</v>
+        <v>10832</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>4.4</v>
+        <v>16.7</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude 技能集
-【原文】Набор скиллов для Claude</t>
+          <t>提供支持多种协议的 API 和 AI 网关服务
+【原文】Open Source API and AI Gateway supporting REST, GraphQL, TCP, gRPC and MCP (Model Context Protocol)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/视频产线</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>MCP服务/可部署服务</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1891,7 +1889,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/artwist-polyakov/polyakov-claude-skills</t>
+          <t>https://github.com/TykTechnologies/tyk</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1900,16 +1898,16 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.63</v>
+        <v>2.39</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1922,50 +1920,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>ai, ai-gateway, api, api-gateway, api-management, cloudnative, go, graphql, grpc, k8s, kubernetes, llm</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2014-05-07</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>321</v>
+        <v>4524</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-25</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>michelpereira/awesome-games-of-coding</t>
+          <t>antfu/skills-npm</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2158</v>
+        <v>523</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4.3</v>
+        <v>15.5</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>提供编程语言学习游戏的列表
-【原文】A curated list of games that can teach you how to learn a programming language.</t>
+          <t>从 npm 安装代理技能
+【原文】Install agent skills from npm</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1975,7 +1977,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1990,7 +1992,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/michelpereira/awesome-games-of-coding</t>
+          <t>https://github.com/antfu/skills-npm</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1999,14 +2001,18 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.61</v>
+        <v>2.21</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2017,23 +2023,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, game, guido-van-robot, programming-language, robocode</t>
-        </is>
-      </c>
+      <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2017-02-04</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>3519</v>
+        <v>237</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2045,12 +2047,210 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-25</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>jaw9c/awesome-remote-mcp-servers</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1119</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>提供远程 MCP 服务器资源
+【原文】Remote MCP Servers</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jaw9c/awesome-remote-mcp-servers</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>537</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
+        <is>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>AtlasCloudAI/awesome-seedance-2.5-prompts-skills</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>209</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>提供 Seedance 2.5 提示词和视频生成技能
+【原文】100+ curated Seedance 2.5 prompts with real video previews, plus an installable Agent Skill that optimizes prompts, creates storyboards, and generates videos via Seedance models.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>图文产线/视频产线</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/AtlasCloudAI/awesome-seedance-2.5-prompts-skills</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, ai, ai-agents, ai-video, artificial-intelligence, awesome-list, bytedance, generative-ai, image-to-video, multimodal, prompt-engineering, prompts</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-26</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V16"/>
+  <autoFilter ref="A2:V18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-25 · 共 16 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-26 · 共 13 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,29 +633,29 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>mikehasa/golive-skill</t>
+          <t>unclecode/crawl4ai</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>894</v>
+        <v>84276</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>3129</v>
+        <v>678.1</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>提供将代理产品上线的一站式服务
-【原文】Take your agent-built product live: hosting, database, domain, email, payments — on your own accounts. Open-source Agent Skill + zero-dependency Node CLI: detect → plan → approve → apply → verify. No GoLive account, backend or telemetry.</t>
+          <t>开源网络爬虫和抓取工具，将任何网站转换为干净的、LLM 准备好的 Markdown 格式。
+【原文】Open-source web crawler and scraper for LLMs and AI agents: any website into clean, LLM-ready Markdown. Run it yourself, or use Crawl4AI Cloud with one key.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/AI免费池/未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>MCP服务/技能包/可部署服务</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/golive-skill</t>
+          <t>https://github.com/unclecode/crawl4ai</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>447</v>
+        <v>96.87</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>agent-skill, agent-skills, ai-agents, claude-code, cloudflare, codex, database, deployment, developer-tools, devops, dns, godaddy</t>
+          <t>ai, ai-agents, crawler, data-extraction, llm, markdown, mcp, open-source, playwright, python, rag, scraper</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2</v>
+        <v>870</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -729,36 +729,36 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-26</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>helloianneo/ian-xiaohei-illustrations</t>
+          <t>zouyuxuan122/dsh-our-free-model</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>12069</v>
+        <v>138</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>698.2</v>
+        <v>483</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>生成中文小黑怪诞正文配图
-【原文】中文小黑怪诞正文配图生成 Skill | 16:9 白底手绘 | 少量红橙蓝批注 | Codex Skill</t>
+          <t>在dsh中安装插件，无需登录、注册或填API Key即可使用免费模型。
+【原文】在 dsh 里装上这个插件即可，无需登录、注册或填 API Key，就能使用包括 Muse Spark 1.3、MiMo V2.6 在内的前沿模型——完全免费，不限量。 All you do is install this plugin in dsh: no login, no sign-up, no API key — the frontier models are just there, Muse Spark 1.3 and MiMo V2.6 among them. Completely free, with no usage cap.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/helloianneo/ian-xiaohei-illustrations</t>
+          <t>https://github.com/zouyuxuan122/dsh-our-free-model</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,14 +782,18 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>99.73999999999999</v>
+        <v>69</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -802,62 +806,62 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, chinese, codex-skill, handdrawn, illustration, image-generation, xiaohei</t>
+          <t>ai-agents, deepseek, deepseek-harness, developer-tools, dsh, dsh-plugin, free-model, llm, model-provider, openai-compatible</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>121</v>
+        <v>2</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-27</t>
+          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-28</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Companion-Inc/feynman</t>
+          <t>ScrapeGraphAI/Scrapegraph-ai</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9781</v>
+        <v>31310</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>360.4</v>
+        <v>225.3</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>开源 AI 研究代理
-【原文】The open source AI research agent.</t>
+          <t>基于AI的Python爬虫，用于数据提取。
+【原文】Python scraper based on AI</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线/AI免费池</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Companion-Inc/feynman</t>
+          <t>https://github.com/ScrapeGraphAI/Scrapegraph-ai</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -881,7 +885,7 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>51.48</v>
+        <v>32.18</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -890,7 +894,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -905,12 +909,12 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, arxiv, cli, literature-review, pi-coding-agent, research</t>
+          <t>ai-crawler, ai-scraping, ai-search, crawler, data-extraction, firecrawl-alternative, large-language-model, llm, markdown, rag, scraping, scraping-python</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -919,48 +923,48 @@
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>190</v>
+        <v>973</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-26</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>browser-use/web-ui</t>
+          <t>beenuar/AiSOC</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>16585</v>
+        <v>2368</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>184</v>
+        <v>112.8</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>在浏览器中运行 AI 代理
-【原文】🖥️ Run AI Agent in your browser.</t>
+          <t>开源AI安全运营中心，提供警报融合、LLM代理分类、MITRE ATT&amp;CK调查和可重放的决策账本。
+【原文】Open-source AI Security Operations Center: alert fusion, LLM-agent triage, MITRE ATT&amp;CK investigation, and a replayable decision ledger for every agent step. Self-hostable, runs with no API keys, MIT licensed. Ships an MCP server for Claude, Cursor and Continue.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>MCP服务/代码库</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -975,7 +979,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/browser-use/web-ui</t>
+          <t>https://github.com/beenuar/AiSOC</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -984,7 +988,7 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>26.28</v>
+        <v>16.11</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -1008,62 +1012,62 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, browser-automation, browser-use-box, cloud-browser</t>
+          <t>agentic-ai, ai-security, alert-triage, blue-team, cybersecurity, detection-engineering, incident-response, langgraph, llm-agents, mcp, mitre-attack, model-context-protocol</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>631</v>
+        <v>147</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-26</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>agents-universe/agents-universe</t>
+          <t>irinabuht12-oss/google-ads-meta-ads-mcp</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>299</v>
+        <v>2503</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>139.5</v>
+        <v>101.3</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供数字分身协同工作平台
-【原文】不是问答机器人，而是能真正干活的数字分身。共享智能体，共享项目上下文，让项目所有成员一起协同工作。同时智能体会像人一样通过资料或者工作抽象和总结经验到项目上下文中</t>
+          <t>提供Google Ads MCP服务器、Meta Ads MCP、GA4和Search Console的远程MCP。
+【原文】Google Ads MCP server + Meta Ads MCP (Facebook Ads MCP) + GA4 + Search Console in one hosted remote MCP for Claude, ChatGPT, Cursor &amp; n8n: 250+ tools, OAuth login, no API keys, approval-gated writes, free. By Ryze AI.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考</t>
+          <t>MCP服务/代码库</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1078,7 +1082,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/agents-universe/agents-universe</t>
+          <t>https://github.com/irinabuht12-oss/google-ads-meta-ads-mcp</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1087,18 +1091,14 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>19.93</v>
+        <v>14.47</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>agent, agent-framework, agent-orchestration, agent-skill, agentic-ai, ai-agents, ai-governance, ai-tools, deepseek-harness, harness, harness-engineering, harness-framework</t>
+          <t>advertising, chatgpt, claude, cursor, facebook-ads, facebook-ads-mcp, ga4, google-ads, google-ads-mcp, google-ads-mcp-server, google-analytics, google-analytics-mcp</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -1125,48 +1125,48 @@
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-06-27</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>cactus-compute/cactus</t>
+          <t>TripoGrowthLab/awesome-astra-prompts</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>6058</v>
+        <v>303</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>81.5</v>
+        <v>101</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>为移动设备提供量化、内核、运行时和推理引擎
-【原文】Quantization, kernels, runtime and inference engine for mobiles, wearables, smart home and robots.</t>
+          <t>提供多语言GPT-6 Astra提示和3D示例，用于游戏、Blender场景和交互式世界。
+【原文】200+ Curated GPT-6 Astra prompts and 3D examples for games, Blender scenes and interactive worlds. 14 languages, previews and source links. Updated twice daily. Curated by Tripo.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线/AI免费池</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cactus-compute/cactus</t>
+          <t>https://github.com/TripoGrowthLab/awesome-astra-prompts</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>11.65</v>
+        <v>14.43</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1214,21 +1214,21 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>ai, android, arm, edge, edge-ai, framework, ios, llamacpp, llm, llm-inference, llms, mobile</t>
+          <t>3d, ai-prompts, astra-prompts, awesome-list, blender, game-development, gpt-6-astra, multilingual, prompt-engineering, threejs, tripo</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>520</v>
+        <v>21</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1240,26 +1240,26 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-26</t>
+          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>anus-dev/ANUS</t>
+          <t>gamedev-skills/awesome-gamedev-agent-skills</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>6543</v>
+        <v>1160</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>81.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>自主维护的代理
-【依据】self-maintaining-repository</t>
+          <t>提供73个游戏开发技能，用于AI编码代理。
+【原文】73 game-dev skills for AI coding agents — Godot, Unity, Unreal, Phaser, PixiJS, three.js, Bevy, pygame, LÖVE, Roblox. Portable SKILL.md Agent Skills (the format Anthropic launched as Claude Skills), with a router that loads the right skill for your engine and task. Runs in Claude Code, Cursor, Kiro, Codex, Copilot, Gemini CLI and more.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/anus-dev/ANUS</t>
+          <t>https://github.com/gamedev-skills/awesome-gamedev-agent-skills</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>11.58</v>
+        <v>12.34</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1317,67 +1317,67 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, autonomous-agent, self-maintaining-repository, spec-driven-company</t>
+          <t>agent-skills, ai-agents, antigravity, awesome-list, claude-code, cline, codex, cursor, game-dev, game-development, gamedev, gemini-cli</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>565</v>
+        <v>94</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-26</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>helloianneo/ian-handdrawn-ppt</t>
+          <t>Natively-AI-assistant/natively-cluely-ai-assistant</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1442</v>
+        <v>2597</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>65.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>生成中文手绘技术 PPT 图像
-【原文】中文手绘技术 PPT 整页图像生成 Skill | 21:9 封面 + 16:9 正文配图 | PNG 输出</t>
+          <t>提供免费的开放源代码AI会议助手、面试助手和笔记记录器。
+【原文】Natively — Free open-source AI meeting assistant, interview copilot, and note taker. The best alternative to Cluely, Otter, Granola, Final Round AI, Fireflies, and Interview Coder. Real-time transcription, AI meeting notes, lecture recording, local RAG, BYOK, and stealth mode. Runs locally. No subscriptions. No data breaches.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/helloianneo/ian-handdrawn-ppt</t>
+          <t>https://github.com/Natively-AI-assistant/natively-cluely-ai-assistant</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1396,14 +1396,18 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>9.42</v>
+        <v>10.73</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr"/>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1416,52 +1420,52 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, chinese, codex-skill, handdrawn, image-generation, ppt</t>
+          <t>ai, ai-agent, ai-agents, ai-assistant, ai-tools, cheating, claude-code, claude-skills, cluely, cluely-alternative, cluely-clone, final-round-ai</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-26</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>andyrewlee/awesome-agent-orchestrators</t>
+          <t>aiming-lab/SkillRL</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2004</v>
+        <v>984</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>56.6</v>
+        <v>30</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>列出代理编排器列表
-【原文】List of agent orchestrators</t>
+          <t>通过递归技能增强强化学习进化智能体。
+【原文】[NeurIPS'26] SkillRL: Evolving Agents via Recursive Skill-Augmented Reinforcement Learning</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1471,7 +1475,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1486,7 +1490,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/andyrewlee/awesome-agent-orchestrators</t>
+          <t>https://github.com/aiming-lab/SkillRL</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1495,14 +1499,18 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>8.08</v>
+        <v>4.28</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1513,14 +1521,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>agent-coordination, agent-orchestration, agent-swarm, agentic-ai, ai-agents, ai-coding, ai-orchestration, awesome, awesome-list, claude-code, codex, coding-agents</t>
-        </is>
-      </c>
+      <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1529,7 +1533,7 @@
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1541,35 +1545,37 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-26</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MashiroSaber03/Saber-Translator</t>
+          <t>kldhsh123/Afterglow</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>3604</v>
+        <v>301</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>43.3</v>
+        <v>16.6</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>漫画翻译工具</t>
+          <t>使用社交软件聊天记录结合向量数据库，让AI扮演社交角色。
+【原文】使用社交软件聊天记录结合向量数据库让AI更好的扮演对方的角色，在不微调模型的情况下可以达到可观的效果。把曾经的美好，续成往后的陪伴。
+【依据】使用社交软件聊天记录结合向量数据库让AI更好的扮演对方的角色。</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>RAG检索线/AI免费池</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1584,7 +1590,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MashiroSaber03/Saber-Translator</t>
+          <t>https://github.com/kldhsh123/Afterglow</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1593,11 +1599,11 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>6.19</v>
+        <v>2.37</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1615,19 +1621,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr"/>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>afterglow, ai-companion, digital-companion, lancedb, llm, python, qq-chat, rag, semantic-search, vector-database, vue</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>582</v>
+        <v>127</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1639,26 +1649,27 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
+          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-06-28</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ExplosiveCoderflome/AI-Novel-Writing-Assistant</t>
+          <t>zhkl0228/unidbg</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>3006</v>
+        <v>5229</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>36.1</v>
+        <v>13.2</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>面向长篇小说创作的 AI Native 开源系统，支持从灵感到完整小说的整本生产工作流
-【原文】面向长篇小说创作的 AI Native 开源系统，用 Agent、世界观、写法引擎、RAG 和整本生产工作流，帮助新手从一句灵感走到完整小说。AI-native engine for end-to-end novel creation — from idea to full chapters, with structured planning, worldbuilding, and agent-driven workflows.</t>
+          <t>允许模拟Android和iOS原生库。
+【原文】Allows you to emulate an Android native library, and an experimental  iOS emulation
+【依据】Allows you to emulate an Android native library, and an experimental iOS emulation</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1668,12 +1679,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>架构参考</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1683,7 +1694,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ExplosiveCoderflome/AI-Novel-Writing-Assistant</t>
+          <t>https://github.com/zhkl0228/unidbg</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1692,16 +1703,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>5.15</v>
+        <v>1.89</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1716,67 +1727,68 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>agent-workflow, ai, creative-writing, long-form-fiction, narrative-engine, novel-writing, rag, story-generation, worldbuilding, writing-assistant</t>
+          <t>android, capstone, debugger, dynarmic, emulation, emulator, fishhook, hypervisor, ios, keystone, kvm, mcp</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2019-02-26</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>584</v>
+        <v>2769</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-26</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>agentset-ai/agentset</t>
+          <t>MarcoNasi/AI-Skills</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2096</v>
+        <v>286</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>26</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>提供开源的 RAG 平台，支持多种文件格式和内置引用
-【原文】The open-source RAG platform: built-in citations, deep research, 22+ file formats, partitions, MCP server, and more.</t>
+          <t>收集了 150 多个针对软件开发、前端、后端、自动化、UI/UX、SEO 和 DevOps 的专业 AI 技能。
+【原文】A curated collection of  150+ specialized AI Skills for software development, frontend, backend, automation, UI/UX, SEO, and DevOps. Each skill encapsulates a focused capability: generating code, templates, scripts, and production-ready workflows.
+【依据】A curated collection of 150+ specialized AI Skills for software development, frontend, backend, automation, UI/UX, SEO,</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/图文产线/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库/可部署服务</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1786,7 +1798,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/agentset-ai/agentset</t>
+          <t>https://github.com/MarcoNasi/AI-Skills</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1795,18 +1807,14 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>3.72</v>
+        <v>1.18</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1819,21 +1827,21 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>agentic-rag, ai, ai-agents, ai-sdk, chatbots, embeddings, genai, llms, memory, memory-management, rag, vercel-ai-sdk</t>
+          <t>ai-skills, claude-code, claude-skills, collection, cursor-skill, cursor-skills, ide-skills, skills, skills-collection, trae, trae-ai, trae-ide</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>564</v>
+        <v>243</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1845,41 +1853,41 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-26</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>TykTechnologies/tyk</t>
+          <t>patrickchugh/terravision</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>10832</v>
+        <v>1639</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>16.7</v>
+        <v>6.9</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>提供支持多种协议的 API 和 AI 网关服务
-【原文】Open Source API and AI Gateway supporting REST, GraphQL, TCP, gRPC and MCP (Model Context Protocol)</t>
+          <t>提供专业云架构图，从Terraform代码或JSON图生成。
+【原文】Professional cloud architecture diagrams with official AWS, Azure and GCP icons, from Terraform code or a plain JSON graph. MCP server + agent skill.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
+          <t>架构参考</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1889,7 +1897,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/TykTechnologies/tyk</t>
+          <t>https://github.com/patrickchugh/terravision</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1898,16 +1906,16 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>2.39</v>
+        <v>0.99</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1922,335 +1930,38 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-gateway, api, api-gateway, api-management, cloudnative, go, graphql, grpc, k8s, kubernetes, llm</t>
+          <t>agent-skill, architecture-diagram, cloud-architecture, diagrams-as-code, docs-as-code, drawio, llm-tools, mcp-server</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2014-05-07</t>
+          <t>2022-03-13</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>4524</v>
+        <v>1658</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>antfu/skills-npm</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>523</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>从 npm 安装代理技能
-【原文】Install agent skills from npm</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/antfu/skills-npm</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>jaw9c/awesome-remote-mcp-servers</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>1119</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>提供远程 MCP 服务器资源
-【原文】Remote MCP Servers</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/jaw9c/awesome-remote-mcp-servers</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>537</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>AtlasCloudAI/awesome-seedance-2.5-prompts-skills</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>209</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>提供 Seedance 2.5 提示词和视频生成技能
-【原文】100+ curated Seedance 2.5 prompts with real video previews, plus an installable Agent Skill that optimizes prompts, creates storyboards, and generates videos via Seedance models.</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>图文产线/视频产线</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/AtlasCloudAI/awesome-seedance-2.5-prompts-skills</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, ai, ai-agents, ai-video, artificial-intelligence, awesome-list, bytedance, generative-ai, image-to-video, multimodal, prompt-engineering, prompts</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-26</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-27</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V18"/>
+  <autoFilter ref="A2:V15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-26 · 共 13 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-27 · 共 14 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,29 +633,29 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>unclecode/crawl4ai</t>
+          <t>Rieranthony/product-film-skill</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>84276</v>
+        <v>208</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>678.1</v>
+        <v>1456</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>开源网络爬虫和抓取工具，将任何网站转换为干净的、LLM 准备好的 Markdown 格式。
-【原文】Open-source web crawler and scraper for LLMs and AI agents: any website into clean, LLM-ready Markdown. Run it yourself, or use Crawl4AI Cloud with one key.</t>
+          <t>无法从仓库描述中确定具体功能。
+【依据】无描述与话题，仅仓库名product-film-skill。</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>视频产线/AI免费池/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/unclecode/crawl4ai</t>
+          <t>https://github.com/Rieranthony/product-film-skill</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>96.87</v>
+        <v>208</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -701,23 +701,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>ai, ai-agents, crawler, data-extraction, llm, markdown, mcp, open-source, playwright, python, rag, scraper</t>
-        </is>
-      </c>
+      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>870</v>
+        <v>1</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -729,31 +725,32 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-27</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>zouyuxuan122/dsh-our-free-model</t>
+          <t>awlevin/typesafe-computer-use</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>138</v>
+        <v>1012</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>483</v>
+        <v>644</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>在dsh中安装插件，无需登录、注册或填API Key即可使用免费模型。
-【原文】在 dsh 里装上这个插件即可，无需登录、注册或填 API Key，就能使用包括 Muse Spark 1.3、MiMo V2.6 在内的前沿模型——完全免费，不限量。 All you do is install this plugin in dsh: no login, no sign-up, no API key — the frontier models are just there, Muse Spark 1.3 and MiMo V2.6 among them. Completely free, with no usage cap.</t>
+          <t>使用 OCR 技术进行屏幕识别，并使用 TypeSafe 进行自动化操作。
+【原文】Computer use for about $0.0002 a step: OCR the screen, classify the next action with TypeSafe, click. macOS.
+【依据】Computer use for about $0.0002 a step: OCR the screen.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -773,7 +770,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zouyuxuan122/dsh-our-free-model</t>
+          <t>https://github.com/awlevin/typesafe-computer-use</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,7 +779,7 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -791,7 +788,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -806,12 +803,12 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, deepseek, deepseek-harness, developer-tools, dsh, dsh-plugin, free-model, llm, model-provider, openai-compatible</t>
+          <t>ai-agents, automation, computer-use, macos, ocr, typesafe</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -820,53 +817,54 @@
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-28</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ScrapeGraphAI/Scrapegraph-ai</t>
+          <t>0xsline/OpenChatCut</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>31310</v>
+        <v>2013</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>225.3</v>
+        <v>190.4</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>基于AI的Python爬虫，用于数据提取。
-【原文】Python scraper based on AI</t>
+          <t>开源本地对话式 AI 视频编辑器，具有专业多轨道时间线、技能和 MCP 集成。
+【原文】Open-source, local-first conversational AI video editor with a professional multi-track timeline, Agent Skills, MCP integration, and Remotion rendering.
+【依据】Open-source local conversational AI video editor.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>图文产线/AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>MCP服务/技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -876,7 +874,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ScrapeGraphAI/Scrapegraph-ai</t>
+          <t>https://github.com/0xsline/OpenChatCut</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -885,16 +883,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>32.18</v>
+        <v>27.2</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -909,62 +907,62 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>ai-crawler, ai-scraping, ai-search, crawler, data-extraction, firecrawl-alternative, large-language-model, llm, markdown, rag, scraping, scraping-python</t>
+          <t>agent-skills, agentic-ai, ai-agent, ai-video-editor, capcut, chatcut, claude-code, codex, desktop-app, electron, ffmpeg, local-first</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>973</v>
+        <v>74</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-27</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>beenuar/AiSOC</t>
+          <t>mergisi/awesome-openclaw-agents</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2368</v>
+        <v>3987</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>112.8</v>
+        <v>119.3</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>开源AI安全运营中心，提供警报融合、LLM代理分类、MITRE ATT&amp;CK调查和可重放的决策账本。
-【原文】Open-source AI Security Operations Center: alert fusion, LLM-agent triage, MITRE ATT&amp;CK investigation, and a replayable decision ledger for every agent step. Self-hostable, runs with no API keys, MIT licensed. Ships an MCP server for Claude, Cursor and Continue.</t>
+          <t>提供 162 个生产就绪的 AI 代理模板。
+【原文】162 production-ready AI agent templates for OpenClaw. SOUL.md configs across 19 categories. Submit yours!</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -979,7 +977,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/beenuar/AiSOC</t>
+          <t>https://github.com/mergisi/awesome-openclaw-agents</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -988,7 +986,7 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>16.11</v>
+        <v>17.04</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -997,7 +995,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1012,12 +1010,12 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, ai-security, alert-triage, blue-team, cybersecurity, detection-engineering, incident-response, langgraph, llm-agents, mcp, mitre-attack, model-context-protocol</t>
+          <t>ai-agent-templates, ai-agents, ai-automation, anthropic, automation, awesome, awesome-list, claude, community-agents, crewclaw, docker, llm</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1026,10 +1024,10 @@
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
@@ -1038,36 +1036,37 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-27</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>irinabuht12-oss/google-ads-meta-ads-mcp</t>
+          <t>matt1398/claude-devtools</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2503</v>
+        <v>3950</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>101.3</v>
+        <v>119.2</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供Google Ads MCP服务器、Meta Ads MCP、GA4和Search Console的远程MCP。
-【原文】Google Ads MCP server + Meta Ads MCP (Facebook Ads MCP) + GA4 + Search Console in one hosted remote MCP for Claude, ChatGPT, Cursor &amp; n8n: 250+ tools, OAuth login, no API keys, approval-gated writes, free. By Ryze AI.</t>
+          <t>Claude Code 的开发工具，用于检查会话日志和工具调用。
+【原文】The missing DevTools for Claude Code — inspect session logs, tool calls, token usage, subagents, and context window in a visual UI. Free, open source.
+【依据】The missing DevTools for Claude Code.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1082,7 +1081,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/irinabuht12-oss/google-ads-meta-ads-mcp</t>
+          <t>https://github.com/matt1398/claude-devtools</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1091,14 +1090,18 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>14.47</v>
+        <v>17.03</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1111,67 +1114,68 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>advertising, chatgpt, claude, cursor, facebook-ads, facebook-ads-mcp, ga4, google-ads, google-ads-mcp, google-ads-mcp-server, google-analytics, google-analytics-mcp</t>
+          <t>ai, ai-agent, ai-debugging, ai-tools, anthropic, claude, claude-code, claude-code-tools, debugging, desktop-app, developer-tools, devtools</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-27</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>TripoGrowthLab/awesome-astra-prompts</t>
+          <t>yb2460/harness-anything</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>303</v>
+        <v>2078</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>101</v>
+        <v>118.2</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供多语言GPT-6 Astra提示和3D示例，用于游戏、Blender场景和交互式世界。
-【原文】200+ Curated GPT-6 Astra prompts and 3D examples for games, Blender scenes and interactive worlds. 14 languages, previews and source links. Updated twice daily. Curated by Tripo.</t>
+          <t>AI 代理控制中心，支持 WPS、MS Office 等应用程序的自动化。
+【原文】Harness Anything - AI agent control hub: WPS, MS Office, Zotero, Photoshop, 47 CLI commands, 27 academic skills, SVG-to-PPTX
+【依据】AI agent control hub: WPS, MS Office.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>图文产线/AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1181,7 +1185,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/TripoGrowthLab/awesome-astra-prompts</t>
+          <t>https://github.com/yb2460/harness-anything</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1190,16 +1194,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>14.43</v>
+        <v>16.89</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1214,12 +1218,12 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>3d, ai-prompts, astra-prompts, awesome-list, blender, game-development, gpt-6-astra, multilingual, prompt-engineering, threejs, tripo</t>
+          <t>ai-agent, automation, cli, cli-anything, com, office, python, windows, wps</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1228,38 +1232,39 @@
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-08-27</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>gamedev-skills/awesome-gamedev-agent-skills</t>
+          <t>duoduoler-ops/Table-skills</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1160</v>
+        <v>276</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>86.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>提供73个游戏开发技能，用于AI编码代理。
-【原文】73 game-dev skills for AI coding agents — Godot, Unity, Unreal, Phaser, PixiJS, three.js, Bevy, pygame, LÖVE, Roblox. Portable SKILL.md Agent Skills (the format Anthropic launched as Claude Skills), with a router that loads the right skill for your engine and task. Runs in Claude Code, Cursor, Kiro, Codex, Copilot, Gemini CLI and more.</t>
+          <t>自用 AI Skills 合集，用于项目交接和网页替身。
+【原文】自用 AI Skills 合集：项目交接与网页替身，让长任务接续更清楚，让独立重任务交给网页 ChatGPT。
+【依据】自用 AI Skills 合集：项目交接与网页替身。</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1284,7 +1289,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/gamedev-skills/awesome-gamedev-agent-skills</t>
+          <t>https://github.com/duoduoler-ops/Table-skills</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1293,11 +1298,11 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>12.34</v>
+        <v>12.55</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1315,23 +1320,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, ai-agents, antigravity, awesome-list, claude-code, cline, codex, cursor, game-dev, game-development, gamedev, gemini-cli</t>
-        </is>
-      </c>
+      <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
@@ -1343,26 +1344,26 @@
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-27</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Natively-AI-assistant/natively-cluely-ai-assistant</t>
+          <t>lingbol088-spec/codex-gpt-5.6-5.5-instruct</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2597</v>
+        <v>203</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>75.09999999999999</v>
+        <v>27.3</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供免费的开放源代码AI会议助手、面试助手和笔记记录器。
-【原文】Natively — Free open-source AI meeting assistant, interview copilot, and note taker. The best alternative to Cluely, Otter, Granola, Final Round AI, Fireflies, and Interview Coder. Real-time transcription, AI meeting notes, lecture recording, local RAG, BYOK, and stealth mode. Runs locally. No subscriptions. No data breaches.</t>
+          <t>GPT-5.6/5.5 指令工程框架，提供一键部署和技能模块。
+【原文】gpt-5.6/5.5-instruct —— GPT-5.6 / GPT-5.5 (Codex CLI) 的指令工程框架。通过 CTF 竞赛心理框架重构运行上下文，让模型的安全训练不被激活。不是打压拒绝，而是让拒绝通路不发生，拷打ai。一键部署，62 行提示词，50 个技能模块，纯 Python 无依赖。关注塔菲？</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1372,12 +1373,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>可部署服务/数据集</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1387,7 +1388,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Natively-AI-assistant/natively-cluely-ai-assistant</t>
+          <t>https://github.com/lingbol088-spec/codex-gpt-5.6-5.5-instruct</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1396,16 +1397,16 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>10.73</v>
+        <v>3.9</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1418,69 +1419,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>ai, ai-agent, ai-agents, ai-assistant, ai-tools, cheating, claude-code, claude-skills, cluely, cluely-alternative, cluely-clone, final-round-ai</t>
-        </is>
-      </c>
+      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>242</v>
+        <v>52</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-27</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>aiming-lab/SkillRL</t>
+          <t>aqm857886159/Nomi</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>984</v>
+        <v>523</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>通过递归技能增强强化学习进化智能体。
-【原文】[NeurIPS'26] SkillRL: Evolving Agents via Recursive Skill-Augmented Reinforcement Learning</t>
+          <t>开源 AI 视频工作台，支持本地模型和 ComfyUI，通过 MCP 进行视频制作。
+【原文】Open-source AI video workbench. Bring any model or your local ComfyUI, and let Claude Code / Codex / Cursor direct it over MCP — storyboard, references, generation, editable first cut on a real timeline. Local-first: projects, prompts, and keys stay on your machine. No account, no telemetry.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>MCP服务/技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1490,7 +1487,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/aiming-lab/SkillRL</t>
+          <t>https://github.com/aqm857886159/Nomi</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1499,16 +1496,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>4.28</v>
+        <v>3.58</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1521,19 +1518,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr"/>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>ai-agent, ai-video, ai-video-generator, bring-your-own-key, comfyui, creative-tools, desktop-app, electron, image-generation, local-first, mcp, offline</t>
+        </is>
+      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>230</v>
+        <v>146</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1545,42 +1546,42 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-27</t>
+          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>kldhsh123/Afterglow</t>
+          <t>SYuan03/Skill-Anything</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>16.6</v>
+        <v>12.5</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>使用社交软件聊天记录结合向量数据库，让AI扮演社交角色。
-【原文】使用社交软件聊天记录结合向量数据库让AI更好的扮演对方的角色，在不微调模型的情况下可以达到可观的效果。把曾经的美好，续成往后的陪伴。
-【依据】使用社交软件聊天记录结合向量数据库让AI更好的扮演对方的角色。</t>
+          <t>将任何来源（PDF、视频、网页、音频、文本）转换为包含测验、闪卡和间隔重复的交互式学习包，一键生成12节学习指南。
+【原文】Any source (PDF, video, web, audio, text) to interactive learning package with quizzes, flashcards and spaced repetition. One command, 12-section study guide.
+【依据】描述明确转换任意来源为交互式学习包，含视频但属学习工具。</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线/AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1590,7 +1591,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kldhsh123/Afterglow</t>
+          <t>https://github.com/SYuan03/Skill-Anything</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1599,11 +1600,11 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.37</v>
+        <v>1.78</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1623,53 +1624,53 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>afterglow, ai-companion, digital-companion, lancedb, llm, python, qq-chat, rag, semantic-search, vector-database, vue</t>
+          <t>active-recall, ai-learning, cli-tool, education, flashcard-generator, knowledge-extraction, learning-tool, llm, openai, pdf-to-quiz, python, quiz-generator</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-06-28</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>zhkl0228/unidbg</t>
+          <t>Prisma-Labs-Dev/apple-skills</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>5229</v>
+        <v>335</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>13.2</v>
+        <v>10.6</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>允许模拟Android和iOS原生库。
-【原文】Allows you to emulate an Android native library, and an experimental  iOS emulation
-【依据】Allows you to emulate an Android native library, and an experimental iOS emulation</t>
+          <t>为Claude Code和Codex提供Apple开发技能，涵盖iOS 26+ API、SwiftUI、Liquid Glass等最新内容。
+【原文】Apple development skills for Claude Code and Codex — latest iOS 26+ APIs, SwiftUI, Liquid Glass, and more
+【依据】描述写明Apple development skills for Claude Code and Codex。</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1679,7 +1680,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1694,7 +1695,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zhkl0228/unidbg</t>
+          <t>https://github.com/Prisma-Labs-Dev/apple-skills</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1703,16 +1704,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1725,14 +1726,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>android, capstone, debugger, dynarmic, emulation, emulator, fishhook, hypervisor, ios, keystone, kvm, mcp</t>
-        </is>
-      </c>
+      <c r="P13" s="6" t="inlineStr"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2019-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -1741,54 +1738,54 @@
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>2769</v>
+        <v>220</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-27</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MarcoNasi/AI-Skills</t>
+          <t>LangChat/langchat</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>286</v>
+        <v>1286</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>收集了 150 多个针对软件开发、前端、后端、自动化、UI/UX、SEO 和 DevOps 的专业 AI 技能。
-【原文】A curated collection of  150+ specialized AI Skills for software development, frontend, backend, automation, UI/UX, SEO, and DevOps. Each skill encapsulates a focused capability: generating code, templates, scripts, and production-ready workflows.
-【依据】A curated collection of 150+ specialized AI Skills for software development, frontend, backend, automation, UI/UX, SEO,</t>
+          <t>开源 AI Agent 应用平台，支持多模型、知识库 RAG、MCP 和智能问答。
+【原文】LangChat 是由 LangChat Team 开发的开源 AI Agent 应用平台，支持多模型、Agent、知识库 RAG、Skills、MCP 与智能问数。
+【依据】Open-source AI Agent application platform.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>MCP服务/技能包/可部署服务</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1798,7 +1795,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MarcoNasi/AI-Skills</t>
+          <t>https://github.com/LangChat/langchat</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1807,14 +1804,18 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Vue</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1827,52 +1828,53 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>ai-skills, claude-code, claude-skills, collection, cursor-skill, cursor-skills, ide-skills, skills, skills-collection, trae, trae-ai, trae-ide</t>
+          <t>agent, ai-agent, java, knowledge-base, langchain4j, llm, mcp, rag, spring-boot, vue3</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>243</v>
+        <v>962</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-27</t>
+          <t>RAG 知识库 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>patrickchugh/terravision</t>
+          <t>SynaLinks/synalinks-skills</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>1639</v>
+        <v>907</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>提供专业云架构图，从Terraform代码或JSON图生成。
-【原文】Professional cloud architecture diagrams with official AWS, Azure and GCP icons, from Terraform code or a plain JSON graph. MCP server + agent skill.</t>
+          <t>为Synalinks OSS提供编码代理（Coding Agents）技能。
+【原文】Coding Agents skills for Synalinks OSS
+【依据】描述为Coding Agents skills for Synalinks OSS，主题含neuro-symbolic。</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1882,12 +1884,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1897,7 +1899,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/patrickchugh/terravision</t>
+          <t>https://github.com/SynaLinks/synalinks-skills</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1906,11 +1908,11 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1930,21 +1932,21 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>agent-skill, architecture-diagram, cloud-architecture, diagrams-as-code, docs-as-code, drawio, llm-tools, mcp-server</t>
+          <t>artificial-intelligence, large-language-models, neuro-symbolic, neuro-symbolic-ai, neurosymbolic</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2022-03-13</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>1658</v>
+        <v>1198</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1956,12 +1958,116 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-27</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>wx-chevalier/Awesome-Books-Notes</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>2202</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>计算机科学和技术领域相关书籍的仓库。
+【原文】:books: Awesome CS Books(with Digests)/Series(.pdf by git lfs) Warehouse for Geeks, ProgrammingLanguage, SoftwareEngineering, Web, AI, ServerSideApplication, Infrastructure, FE etc. :dizzy: 优秀创业、商业、产品、人文、计算机科学与技术领域相关的书籍归档，以及我的读书笔记。
+【依据】Awesome CS Books(with Digests)/Series(.pdf by git lfs) Warehouse for Geeks.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/wx-chevalier/Awesome-Books-Notes</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>2017-11-06</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>3247</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V15"/>
+  <autoFilter ref="A2:V16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -61,11 +61,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -114,9 +109,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -484,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-27 · 共 14 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-28 · 共 17 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,34 +625,34 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Rieranthony/product-film-skill</t>
+          <t>lemomo-ai/lemo-opuscar</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>208</v>
+        <v>412</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1456</v>
+        <v>1442</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>无法从仓库描述中确定具体功能。
-【依据】无描述与话题，仅仓库名product-film-skill。</t>
+          <t>提供39种影片风格提示词及样片，用于创意编码和影片制作
+【原文】39 film styles, each a reusable style prompt plus a short film made entirely in code by Claude Opus 5.5. Pick a style, bring your own story, and let your agent direct. | Opus5.5 x 39 种影片风格：风格提示词 + 纯代码样片 + 导演与技术指南</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -670,7 +662,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Rieranthony/product-film-skill</t>
+          <t>https://github.com/lemomo-ai/lemo-opuscar</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,16 +671,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -701,7 +693,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>ai-agents, ai-video, animation, canvas, claude, claude-code, creative-coding, ffmpeg, filmmaking, motion-graphics, prompt-library, text-to-speech</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -709,48 +705,47 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-28</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>awlevin/typesafe-computer-use</t>
+          <t>kaankiziltug/logo-design-skill</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1012</v>
+        <v>208</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>644</v>
+        <v>728</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>使用 OCR 技术进行屏幕识别，并使用 TypeSafe 进行自动化操作。
-【原文】Computer use for about $0.0002 a step: OCR the screen, classify the next action with TypeSafe, click. macOS.
-【依据】Computer use for about $0.0002 a step: OCR the screen.</t>
+          <t>为 Claude, Gemini CLI, Codex 等AI代理提供全面的标志设计技能
+【原文】A comprehensive logo-design skill for Claude, Gemini CLI, Codex and other AI agents: principles, process, SVG craft, testing tools and a 1,400+ logo reference library.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -770,7 +765,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/awlevin/typesafe-computer-use</t>
+          <t>https://github.com/kaankiziltug/logo-design-skill</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -779,7 +774,7 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -788,7 +783,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -803,21 +798,21 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, automation, computer-use, macos, ocr, typesafe</t>
+          <t>agent-skills, branding, claude, claude-skills, codex, gemini-cli, logo-design, svg</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
@@ -829,42 +824,41 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-29</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>0xsline/OpenChatCut</t>
+          <t>win4r/MuseAI-Skills</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2013</v>
+        <v>282</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>190.4</v>
+        <v>658</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>开源本地对话式 AI 视频编辑器，具有专业多轨道时间线、技能和 MCP 集成。
-【原文】Open-source, local-first conversational AI video editor with a professional multi-track timeline, Agent Skills, MCP integration, and Remotion rendering.
-【依据】Open-source local conversational AI video editor.</t>
+          <t>提供 muse.ai 技能与运行环境文件的非官方存档
+【原文】muse.ai (Muse AI) skills and runtime snapshot: 68 skills, workflow guides, connector manifests. muse.ai 技能与运行环境文件；非官方存档 / Unofficial archive.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/可部署服务</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包/代码库</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -874,7 +868,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/0xsline/OpenChatCut</t>
+          <t>https://github.com/win4r/MuseAI-Skills</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -883,16 +877,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>27.2</v>
+        <v>94</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -907,62 +901,62 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, agentic-ai, ai-agent, ai-video-editor, capcut, chatcut, claude-code, codex, desktop-app, electron, ffmpeg, local-first</t>
+          <t>agent-skills, meta, muse, skills</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-28</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>mergisi/awesome-openclaw-agents</t>
+          <t>majidmanzarpour/threejs-game-skills</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3987</v>
+        <v>2150</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>119.3</v>
+        <v>142</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供 162 个生产就绪的 AI 代理模板。
-【原文】162 production-ready AI agent templates for OpenClaw. SOUL.md configs across 19 categories. Submit yours!</t>
+          <t>提供构建Three.js游戏的技能，包括图形、UI和QA
+【原文】Agent skills for building playable, polished Three.js browser games with gameplay, AAA-style graphics, UI, QA, and optional AI-generated 3D, image, and audio assets.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -977,7 +971,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mergisi/awesome-openclaw-agents</t>
+          <t>https://github.com/majidmanzarpour/threejs-game-skills</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -986,7 +980,7 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>17.04</v>
+        <v>20.28</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -995,7 +989,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1008,23 +1002,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>ai-agent-templates, ai-agents, ai-automation, anthropic, automation, awesome, awesome-list, claude, community-agents, crewclaw, docker, llm</t>
-        </is>
-      </c>
+      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>234</v>
+        <v>106</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1036,37 +1026,36 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-28</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>matt1398/claude-devtools</t>
+          <t>VoltAgent/voltagent</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3950</v>
+        <v>10682</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>119.2</v>
+        <v>141</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Claude Code 的开发工具，用于检查会话日志和工具调用。
-【原文】The missing DevTools for Claude Code — inspect session logs, tool calls, token usage, subagents, and context window in a visual UI. Free, open source.
-【依据】The missing DevTools for Claude Code.</t>
+          <t>构建基于 TypeScript 的 AI 代理工程平台
+【原文】AI Agent Engineering Platform built on an Open Source TypeScript AI Agent Framework</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1081,7 +1070,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/matt1398/claude-devtools</t>
+          <t>https://github.com/VoltAgent/voltagent</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1090,7 +1079,7 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>17.03</v>
+        <v>20.15</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -1114,68 +1103,67 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agent, ai-debugging, ai-tools, anthropic, claude, claude-code, claude-code-tools, debugging, desktop-app, developer-tools, devtools</t>
+          <t>agents, ai, ai-agents, ai-agents-framework, aiagentframework, chatbots, chatgpt, framework, javascript, llm, llm-observability, mcp</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>232</v>
+        <v>530</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-28</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>yb2460/harness-anything</t>
+          <t>youart-open-source/awesome-gpt-image-2-5-prompts</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2078</v>
+        <v>309</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>118.2</v>
+        <v>120.2</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>AI 代理控制中心，支持 WPS、MS Office 等应用程序的自动化。
-【原文】Harness Anything - AI agent control hub: WPS, MS Office, Zotero, Photoshop, 47 CLI commands, 27 academic skills, SVG-to-PPTX
-【依据】AI agent control hub: WPS, MS Office.</t>
+          <t>提供 GPT Image 2.5 提示词库，包含社区贡献的150个提示词
+【原文】GPT Image 2.5 prompts, verbatim and credited: 150 community prompts across 9 use cases, each with the author who wrote it and their post. Free to run.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1185,7 +1173,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yb2460/harness-anything</t>
+          <t>https://github.com/youart-open-source/awesome-gpt-image-2-5-prompts</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1194,16 +1182,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>16.89</v>
+        <v>17.17</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1218,53 +1206,52 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, automation, cli, cli-anything, com, office, python, windows, wps</t>
+          <t>ai-prompts, awesome-list, chatgpt-image-2-5-prompts, gpt-image, gpt-image-2, gpt-image-2-5, gpt-image-2-5-prompts, image-generation, openai, prompt-engineering, prompt-library, text-to-image</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-28</t>
+          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>duoduoler-ops/Table-skills</t>
+          <t>ziadoz/awesome-php</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>276</v>
+        <v>32716</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>87.90000000000001</v>
+        <v>48.9</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>自用 AI Skills 合集，用于项目交接和网页替身。
-【原文】自用 AI Skills 合集：项目交接与网页替身，让长任务接续更清楚，让独立重任务交给网页 ChatGPT。
-【依据】自用 AI Skills 合集：项目交接与网页替身。</t>
+          <t>收集PHP库、资源和工具列表
+【原文】A curated list of amazingly awesome PHP libraries, resources and shiny things.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1274,12 +1261,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1289,7 +1276,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/duoduoler-ops/Table-skills</t>
+          <t>https://github.com/ziadoz/awesome-php</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1298,18 +1285,14 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>12.55</v>
+        <v>6.98</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>WTFPL</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1320,10 +1303,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-lists, php, php-applications, php-framework, php-installation, php-library</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2013-11-26</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1332,7 +1319,7 @@
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>22</v>
+        <v>4689</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
@@ -1344,26 +1331,26 @@
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-28</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>lingbol088-spec/codex-gpt-5.6-5.5-instruct</t>
+          <t>ai4s-research/awesome-ai-for-science</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>203</v>
+        <v>2002</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>27.3</v>
+        <v>39.1</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>GPT-5.6/5.5 指令工程框架，提供一键部署和技能模块。
-【原文】gpt-5.6/5.5-instruct —— GPT-5.6 / GPT-5.5 (Codex CLI) 的指令工程框架。通过 CTF 竞赛心理框架重构运行上下文，让模型的安全训练不被激活。不是打压拒绝，而是让拒绝通路不发生，拷打ai。一键部署，62 行提示词，50 个技能模块，纯 Python 无依赖。关注塔菲？</t>
+          <t>收集加速科学发现的 AI 工具、库、论文、数据集和框架的精选列表
+【原文】A curated list of awesome AI tools, libraries, papers, datasets, and frameworks that accelerate scientific discovery — from physics and chemistry to biology, materials, and beyond.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1373,7 +1360,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/数据集</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1388,7 +1375,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lingbol088-spec/codex-gpt-5.6-5.5-instruct</t>
+          <t>https://github.com/ai4s-research/awesome-ai-for-science</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1397,18 +1384,14 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>3.9</v>
+        <v>5.58</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1419,65 +1402,69 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>ai-for-science, ai4s, ai4science, awesome, awesome-list, bioinformatics, scientific-ai</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>52</v>
+        <v>359</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-29</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>aqm857886159/Nomi</t>
+          <t>Neeeophytee/finding-unknowns-skills</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>523</v>
+        <v>339</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>25.1</v>
+        <v>27.9</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>开源 AI 视频工作台，支持本地模型和 ComfyUI，通过 MCP 进行视频制作。
-【原文】Open-source AI video workbench. Bring any model or your local ComfyUI, and let Claude Code / Codex / Cursor direct it over MCP — storyboard, references, generation, editable first cut on a real timeline. Local-first: projects, prompts, and keys stay on your machine. No account, no telemetry.</t>
+          <t>提供Claude Code、OpenAI Codex和Hermes的技能，用于AI代理
+【原文】14 installable skills for Claude Code, OpenAI Codex, and Hermes: find unknowns, clarify requirements, manage context, test assumptions, and verify bug fixes with regression evidence.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/可部署服务</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1487,7 +1474,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/aqm857886159/Nomi</t>
+          <t>https://github.com/Neeeophytee/finding-unknowns-skills</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1496,16 +1483,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>3.58</v>
+        <v>3.99</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1520,21 +1507,21 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, ai-video, ai-video-generator, bring-your-own-key, comfyui, creative-tools, desktop-app, electron, image-generation, local-first, mcp, offline</t>
+          <t>agent-skills, ai-agents, claude, claude-code, codex, cursor, hermes-agent, kimi-k3, openai-codex, prompting, skills</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1546,27 +1533,26 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>SYuan03/Skill-Anything</t>
+          <t>Kristories/awesome-guidelines</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>331</v>
+        <v>11133</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>12.5</v>
+        <v>23.2</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>将任何来源（PDF、视频、网页、音频、文本）转换为包含测验、闪卡和间隔重复的交互式学习包，一键生成12节学习指南。
-【原文】Any source (PDF, video, web, audio, text) to interactive learning package with quizzes, flashcards and spaced repetition. One command, 12-section study guide.
-【依据】描述明确转换任意来源为交互式学习包，含视频但属学习工具。</t>
+          <t>收集编程风格、最佳实践和编码规范
+【原文】Programming style, best practices, and coding conventions.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1576,7 +1562,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1591,7 +1577,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SYuan03/Skill-Anything</t>
+          <t>https://github.com/Kristories/awesome-guidelines</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1600,16 +1586,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1.78</v>
+        <v>3.31</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>CC0-1.0</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1624,21 +1610,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>active-recall, ai-learning, cli-tool, education, flashcard-generator, knowledge-extraction, learning-tool, llm, openai, pdf-to-quiz, python, quiz-generator</t>
+          <t>awesome, awesome-guidelines, awesome-list, code-quality, coding-conventions, guidelines, hacktoberfest, style-conventions, style-guide</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2017-07-12</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>186</v>
+        <v>3365</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1650,27 +1636,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-28</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Prisma-Labs-Dev/apple-skills</t>
+          <t>ozrwayne/rw-research-skill</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>335</v>
+        <v>207</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>10.6</v>
+        <v>18.3</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>为Claude Code和Codex提供Apple开发技能，涵盖iOS 26+ API、SwiftUI、Liquid Glass等最新内容。
-【原文】Apple development skills for Claude Code and Codex — latest iOS 26+ APIs, SwiftUI, Liquid Glass, and more
-【依据】描述写明Apple development skills for Claude Code and Codex。</t>
+          <t>提供独立研究工作流程技能，包括问题、文献、证据、设计、写作和提交
+【原文】Twelve standalone research workflow skills for questions, literature, evidence, design, writing, and submission.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1680,7 +1665,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1695,7 +1680,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Prisma-Labs-Dev/apple-skills</t>
+          <t>https://github.com/ozrwayne/rw-research-skill</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1704,16 +1689,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1.52</v>
+        <v>2.62</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1729,16 +1714,16 @@
       <c r="P13" s="6" t="inlineStr"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1750,37 +1735,36 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-28</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>LangChat/langchat</t>
+          <t>ViktorAxelsen/MemSkill</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>1286</v>
+        <v>582</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>9.4</v>
+        <v>16.9</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>开源 AI Agent 应用平台，支持多模型、知识库 RAG、MCP 和智能问答。
-【原文】LangChat 是由 LangChat Team 开发的开源 AI Agent 应用平台，支持多模型、Agent、知识库 RAG、Skills、MCP 与智能问数。
-【依据】Open-source AI Agent application platform.</t>
+          <t>学习并进化自我进化代理的记忆技能
+【原文】[NeurIPS'26] MemSkill: Learning and Evolving Memory Skills for Self-Evolving Agents</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/可部署服务</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1795,7 +1779,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LangChat/langchat</t>
+          <t>https://github.com/ViktorAxelsen/MemSkill</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1804,7 +1788,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.34</v>
+        <v>2.41</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1813,7 +1797,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1826,14 +1810,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>agent, ai-agent, java, knowledge-base, langchain4j, llm, mcp, rag, spring-boot, vue3</t>
-        </is>
-      </c>
+      <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
@@ -1842,39 +1822,38 @@
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>962</v>
+        <v>241</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>RAG 知识库 in:name,description stars:&gt;200</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>SynaLinks/synalinks-skills</t>
+          <t>iflytek/iFly-Skills</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>907</v>
+        <v>218</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>为Synalinks OSS提供编码代理（Coding Agents）技能。
-【原文】Coding Agents skills for Synalinks OSS
-【依据】描述为Coding Agents skills for Synalinks OSS，主题含neuro-symbolic。</t>
+          <t>提供 iFLYTEK 的语音、OCR、翻译、校对和多模态 AI 技能的官方集合
+【原文】Official collection of iFLYTEK skills for speech, OCR, translation, proofreading, and multimodal AI capabilities.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1884,7 +1863,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1899,7 +1878,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SynaLinks/synalinks-skills</t>
+          <t>https://github.com/iflytek/iFly-Skills</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1908,7 +1887,7 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.76</v>
+        <v>1.2</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -1932,21 +1911,21 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>artificial-intelligence, large-language-models, neuro-symbolic, neuro-symbolic-ai, neurosymbolic</t>
+          <t>agent, iflytek-astron, skill, skill-md, skills</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>1198</v>
+        <v>182</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1958,27 +1937,26 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-28</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>wx-chevalier/Awesome-Books-Notes</t>
+          <t>gbdev/awesome-gbdev</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2202</v>
+        <v>4515</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>计算机科学和技术领域相关书籍的仓库。
-【原文】:books: Awesome CS Books(with Digests)/Series(.pdf by git lfs) Warehouse for Geeks, ProgrammingLanguage, SoftwareEngineering, Web, AI, ServerSideApplication, Infrastructure, FE etc. :dizzy: 优秀创业、商业、产品、人文、计算机科学与技术领域相关的书籍归档，以及我的读书笔记。
-【依据】Awesome CS Books(with Digests)/Series(.pdf by git lfs) Warehouse for Geeks.</t>
+          <t>收集Game Boy开发资源，如工具、文档、模拟器等
+【原文】A curated list of Game Boy development resources such as tools, docs, emulators, related projects and open-source ROMs.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1988,7 +1966,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2003,7 +1981,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wx-chevalier/Awesome-Books-Notes</t>
+          <t>https://github.com/gbdev/awesome-gbdev</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2012,18 +1990,14 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.68</v>
+        <v>1.17</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
           <t>NOASSERTION</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
+      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2036,12 +2010,12 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>assembler, awesome, awesome-list, cartridge, dmg, documentation, game-boy-development, game-development, gameboy, gameboy-color, gameboy-color-emulator, gameboy-emulator</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2017-11-06</t>
+          <t>2016-02-23</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -2050,7 +2024,7 @@
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>3247</v>
+        <v>3870</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2062,12 +2036,317 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-28</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>danielecook/Awesome-Bioinformatics</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>4306</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>收集生物信息学库和软件列表
+【原文】A curated list of awesome Bioinformatics libraries and software.</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/danielecook/Awesome-Bioinformatics</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, bioinformatics</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>2014-08-27</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>4415</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>neiesc/awesome-minimalist</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>3659</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>收集简约框架列表，适用于快速开发
+【原文】A curated list of awesome minimalist frameworks (simple and lightweight).</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/neiesc/awesome-minimalist</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Astro</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>awesome-lists, hacktoberfest, minimalistic</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>2013-12-11</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>4674</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>getoneapi/OneAPI</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>提供多种社交媒体数据API，包括抖音、小红书等
+【原文】OneAPI，提供各种数据API，用户信息、视频列表、详情、点赞、评论数据、综合搜索等，包括：Douyin（抖音）、Xiaohongshu（小红书）、Kuaishou（快手）、Bilibili（哔哩哔哩）、Weibo（微博）、Toutiao（今日头条）、Xigua（西瓜视频）、Lemon8、Tiktok、Youtube等接口、数据、API、爬虫、采集。</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/getoneapi/OneAPI</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>api, bilibili, bilibili-api, data, data-api, douyin, douyin-api, kuaishou, kuaishou-api, lemon8, tiktok, tiktok-api</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>381</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V16"/>
+  <autoFilter ref="A2:V19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -109,6 +114,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -476,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -506,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-28 · 共 17 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-30 · 共 26 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -625,34 +633,34 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>lemomo-ai/lemo-opuscar</t>
+          <t>jev-chat/jev-chat-jarvis</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>412</v>
+        <v>7132</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1442</v>
+        <v>5547.1</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>提供39种影片风格提示词及样片，用于创意编码和影片制作
-【原文】39 film styles, each a reusable style prompt plus a short film made entirely in code by Claude Opus 5.5. Pick a style, bring your own story, and let your agent direct. | Opus5.5 x 39 种影片风格：风格提示词 + 纯代码样片 + 导演与技术指南</t>
+          <t>提供安装在手机上的对话助手，用于 QQ / X / 飞书中的对话辅助
+【原文】装在手机上的对话副驾：在 QQ / X / 飞书里读懂对方、给出候选回复、一键填入输入框，发不发由你。非侵入，只读屏幕，不 hook 不改包。</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -662,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lemomo-ai/lemo-opuscar</t>
+          <t>https://github.com/jev-chat/jev-chat-jarvis</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -671,16 +679,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>206</v>
+        <v>792.4400000000001</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Kotlin</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -695,67 +703,67 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, ai-video, animation, canvas, claude, claude-code, creative-coding, ffmpeg, filmmaking, motion-graphics, prompt-library, text-to-speech</t>
+          <t>accessibility-service, ai-assistant, android, chat-assistant, chat-copilot, llm, ocr, qq</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-30</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>kaankiziltug/logo-design-skill</t>
+          <t>YeJe-cpu/SeeCut</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>208</v>
+        <v>140</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>728</v>
+        <v>196</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>为 Claude, Gemini CLI, Codex 等AI代理提供全面的标志设计技能
-【原文】A comprehensive logo-design skill for Claude, Gemini CLI, Codex and other AI agents: principles, process, SVG craft, testing tools and a 1,400+ logo reference library.</t>
+          <t>提供 AI 视频编辑工具，可自动精剪数字人或真人口播视频
+【原文】An AI editor that watches its own cut: talking-head / AI-avatar video → auto-edited short video. 网感口播精剪：数字人/真人口播 → AI 自动精剪成网感动效短视频 → 可选剪映分层草稿</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -765,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kaankiziltug/logo-design-skill</t>
+          <t>https://github.com/YeJe-cpu/SeeCut</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -774,16 +782,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -798,67 +806,67 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, branding, claude, claude-skills, codex, gemini-cli, logo-design, svg</t>
+          <t>agent-skill, ai-avatar, ai-video, claude-code, gemini, heygen, hyperframes, talking-head, video-editing</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="T4" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
+          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>win4r/MuseAI-Skills</t>
+          <t>j4c8dobolsuo8m2m/seedance-api-cn</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>282</v>
+        <v>106</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>658</v>
+        <v>123.7</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>提供 muse.ai 技能与运行环境文件的非官方存档
-【原文】muse.ai (Muse AI) skills and runtime snapshot: 68 skills, workflow guides, connector manifests. muse.ai 技能与运行环境文件；非官方存档 / Unofficial archive.</t>
+          <t>提供 AI API 中转站/网关的中文文档和定价信息
+【原文】AI API 中转站/网关中文文档 · AI API gateway pricing: image2.5 $0.0085/image, Seedance 2.0 Mini $0.0106/sec, LLM tokens from $0.0229/M. One OpenAI-compatible key, $1 minimum top-up, per-call cost in every respo</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>MCP服务/代码库</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -868,7 +876,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/win4r/MuseAI-Skills</t>
+          <t>https://github.com/j4c8dobolsuo8m2m/seedance-api-cn</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -877,16 +885,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>94</v>
+        <v>17.67</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -901,52 +909,52 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, meta, muse, skills</t>
+          <t>ai-api-aggregator, ai-api-gateway, api-docs, api-pricing, apimart, cheapest-llm-api, llm-api-gateway, openai-compatible, openrouter-alternative, pay-as-you-go, per-image-pricing</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
+          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>majidmanzarpour/threejs-game-skills</t>
+          <t>k6hdkoe76rybli/flux2-flux-2-api-cn</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2150</v>
+        <v>101</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>142</v>
+        <v>117.8</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供构建Three.js游戏的技能，包括图形、UI和QA
-【原文】Agent skills for building playable, polished Three.js browser games with gameplay, AAA-style graphics, UI, QA, and optional AI-generated 3D, image, and audio assets.</t>
+          <t>提供 flux-2 API 的中文文档和定价信息
+【原文】AI API 中转站/网关中文文档 · flux-2 / flux2 API：1MP $0.024; 2MP $0.036; 3MP $0.048。模型 ID、参数、curl 与 Python 示例，OpenAI 兼容接口，$1 起充。</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -956,12 +964,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>MCP服务/代码库</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -971,7 +979,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/majidmanzarpour/threejs-game-skills</t>
+          <t>https://github.com/k6hdkoe76rybli/flux2-flux-2-api-cn</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -980,16 +988,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>20.28</v>
+        <v>16.83</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1002,50 +1010,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>api-docs, apimart, cn, flux-2, flux-2-api, flux2, flux2-api, model-cn, openai-compatible, pay-as-you-go</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
+          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>VoltAgent/voltagent</t>
+          <t>oy8jfpo2qa8075/qwenimage3.0-qwen-image-3.0-api-cn</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10682</v>
+        <v>101</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>141</v>
+        <v>117.8</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>构建基于 TypeScript 的 AI 代理工程平台
-【原文】AI Agent Engineering Platform built on an Open Source TypeScript AI Agent Framework</t>
+          <t>提供 qwen-image-3.0 API 的中文文档和定价信息
+【原文】AI API 中转站/网关中文文档 · qwen-image-3.0 / qwenimage3.0 API：default $0.0206; 1K $0.0206; 2K $0.0206。模型 ID、参数、curl 与 Python 示例，OpenAI 兼容接口，$1 起充。</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1055,12 +1067,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>MCP服务/代码库</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1070,7 +1082,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/VoltAgent/voltagent</t>
+          <t>https://github.com/oy8jfpo2qa8075/qwenimage3.0-qwen-image-3.0-api-cn</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1079,16 +1091,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>20.15</v>
+        <v>16.83</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1103,62 +1115,62 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>agents, ai, ai-agents, ai-agents-framework, aiagentframework, chatbots, chatgpt, framework, javascript, llm, llm-observability, mcp</t>
+          <t>api-docs, apimart, cn, model-cn, openai-compatible, pay-as-you-go, qwen-image-3-0, qwen-image-3-0-api, qwenimage3-0, qwenimage3-0-api</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>530</v>
+        <v>6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-29</t>
+          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>youart-open-source/awesome-gpt-image-2-5-prompts</t>
+          <t>hd42567u/grokimagine2.0-grok-imagine-2.0-api-cn</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>309</v>
+        <v>101</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>120.2</v>
+        <v>117.8</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供 GPT Image 2.5 提示词库，包含社区贡献的150个提示词
-【原文】GPT Image 2.5 prompts, verbatim and credited: 150 community prompts across 9 use cases, each with the author who wrote it and their post. Free to run.</t>
+          <t>提供 OpenAI 兼容的 AI API 中转站/网关中文文档
+【原文】AI API 中转站/网关中文文档 · grok-imagine-2.0 / grokimagine2.0 API：upload-image $0; default $0.015; region-edit $0.015。模型 ID、参数、curl 与 Python 示例，OpenAI 兼容接口，$1 起充。</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>MCP服务/技能包/架构参考/可部署服务</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1173,7 +1185,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/youart-open-source/awesome-gpt-image-2-5-prompts</t>
+          <t>https://github.com/hd42567u/grokimagine2.0-grok-imagine-2.0-api-cn</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1182,7 +1194,7 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>17.17</v>
+        <v>16.83</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -1191,7 +1203,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1206,67 +1218,67 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>ai-prompts, awesome-list, chatgpt-image-2-5-prompts, gpt-image, gpt-image-2, gpt-image-2-5, gpt-image-2-5-prompts, image-generation, openai, prompt-engineering, prompt-library, text-to-image</t>
+          <t>api-docs, apimart, cn, grok-imagine-2-0, grok-imagine-2-0-api, grokimagine2-0, grokimagine2-0-api, model-cn, openai-compatible, pay-as-you-go</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-08-29</t>
+          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ziadoz/awesome-php</t>
+          <t>yyjeqhc/webcodex</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>32716</v>
+        <v>2064</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>48.9</v>
+        <v>115.6</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>收集PHP库、资源和工具列表
-【原文】A curated list of amazingly awesome PHP libraries, resources and shiny things.</t>
+          <t>为云 AI 代理提供在本地机器上的真实开发环境
+【原文】Give cloud AI agents a real development environment on your own machines.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>MCP服务/可部署服务</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1276,7 +1288,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ziadoz/awesome-php</t>
+          <t>https://github.com/yyjeqhc/webcodex</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1285,14 +1297,18 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>6.98</v>
+        <v>16.51</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>WTFPL</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1305,52 +1321,52 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-lists, php, php-applications, php-framework, php-installation, php-library</t>
+          <t>agent, chatgpt, claude, claude-code, codex, developer-tools, gemini, gpt-actions, grok, mcp, rust, self-hosted</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2013-11-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>4689</v>
+        <v>125</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ai4s-research/awesome-ai-for-science</t>
+          <t>dontriskit/awesome-ai-system-prompts</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2002</v>
+        <v>6227</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>39.1</v>
+        <v>76</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>收集加速科学发现的 AI 工具、库、论文、数据集和框架的精选列表
-【原文】A curated list of awesome AI tools, libraries, papers, datasets, and frameworks that accelerate scientific discovery — from physics and chemistry to biology, materials, and beyond.</t>
+          <t>收集并整理顶级 AI 工具的系统提示词
+【原文】🧠 Curated collection of system prompts for top AI tools. Perfect for AI agent builders and prompt engineers. Incuding: ChatGPT, Claude, Perplexity, Manus, Claude-Code, Loveable, v0, Grok, same new, windsurf, notion, and MetaAI.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1360,7 +1376,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1375,7 +1391,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ai4s-research/awesome-ai-for-science</t>
+          <t>https://github.com/dontriskit/awesome-ai-system-prompts</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1384,14 +1400,18 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5.58</v>
+        <v>10.85</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1402,26 +1422,22 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>ai-for-science, ai4s, ai4science, awesome, awesome-list, bioinformatics, scientific-ai</t>
-        </is>
-      </c>
+      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>359</v>
+        <v>574</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
@@ -1430,26 +1446,26 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
+          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Neeeophytee/finding-unknowns-skills</t>
+          <t>haris-musa/excel-mcp-server</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>339</v>
+        <v>4206</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>27.9</v>
+        <v>49.5</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>提供Claude Code、OpenAI Codex和Hermes的技能，用于AI代理
-【原文】14 installable skills for Claude Code, OpenAI Codex, and Hermes: find unknowns, clarify requirements, manage context, test assumptions, and verify bug fixes with regression evidence.</t>
+          <t>提供用于 Excel 文件操作的 Model Context Protocol 服务器
+【原文】A Model Context Protocol server for Excel file manipulation</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1459,7 +1475,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>MCP服务/可部署服务</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1474,7 +1490,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Neeeophytee/finding-unknowns-skills</t>
+          <t>https://github.com/haris-musa/excel-mcp-server</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1483,7 +1499,7 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>3.99</v>
+        <v>7.07</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1507,12 +1523,12 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, claude, claude-code, codex, cursor, hermes-agent, kimi-k3, openai-codex, prompting, skills</t>
+          <t>ai, automation, excel, llm, mcp, mcp-server, sse, stdio, streamable-http, toolcalling</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1521,38 +1537,38 @@
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>85</v>
+        <v>595</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
+          <t>topic:mcp-server stars:&gt;1000 pushed:&gt;2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Kristories/awesome-guidelines</t>
+          <t>darkrishabh/agent-skills-eval</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>11133</v>
+        <v>798</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>23.2</v>
+        <v>38</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>收集编程风格、最佳实践和编码规范
-【原文】Programming style, best practices, and coding conventions.</t>
+          <t>为 agentskills.io 风格的 AI agent skills 提供测试运行器。
+【原文】A test runner for agentskills.io-style AI agent skills</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1562,7 +1578,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1577,7 +1593,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Kristories/awesome-guidelines</t>
+          <t>https://github.com/darkrishabh/agent-skills-eval</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1586,16 +1602,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>3.31</v>
+        <v>5.43</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1610,21 +1626,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-guidelines, awesome-list, code-quality, coding-conventions, guidelines, hacktoberfest, style-conventions, style-guide</t>
+          <t>agent-evals, agent-skills, agentskills, ai-agents, cli, jsonl, llm-evals, llm-evaluation, openai-compatible, typescript, yaml</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>3365</v>
+        <v>147</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1636,26 +1652,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ozrwayne/rw-research-skill</t>
+          <t>yaojingang/yao-geo-skills</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>207</v>
+        <v>790</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>18.3</v>
+        <v>32</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供独立研究工作流程技能，包括问题、文献、证据、设计、写作和提交
-【原文】Twelve standalone research workflow skills for questions, literature, evidence, design, writing, and submission.</t>
+          <t>提供用于 GEO 内容和流程的开放源代码 Skill 集合
+【原文】An open-source Skill collection for GEO content and workflows, continuously updated.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1665,7 +1681,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1680,7 +1696,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ozrwayne/rw-research-skill</t>
+          <t>https://github.com/yaojingang/yao-geo-skills</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1689,16 +1705,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>2.62</v>
+        <v>4.57</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1711,19 +1727,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>ai-agent, automation, cli, codex, geoflow, skills, workflow</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1735,36 +1755,36 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>ViktorAxelsen/MemSkill</t>
+          <t>Anil-matcha/open-dots</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>582</v>
+        <v>4587</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>16.9</v>
+        <v>26.2</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>学习并进化自我进化代理的记忆技能
-【原文】[NeurIPS'26] MemSkill: Learning and Evolving Memory Skills for Self-Evolving Agents</t>
+          <t>提供自托管的 AI 聊天、工具、审批流程和计算机任务
+【原文】Open-source alternative to OpenAI Dots: self-hosted AI chat, tools, approvals, connectors, and computer tasks.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>MCP服务/可部署服务</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1779,7 +1799,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ViktorAxelsen/MemSkill</t>
+          <t>https://github.com/Anil-matcha/open-dots</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1788,11 +1808,11 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>2.41</v>
+        <v>3.75</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1810,50 +1830,55 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>agentic-ai, ai-agent, ai-assistant, ai-workspace, approval-workflows, browser-automation, computer-use, computer-use-agent, fastapi, llm, local-first, nextjs</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>241</v>
+        <v>1224</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>iflytek/iFly-Skills</t>
+          <t>mzlogin/awesome-adb</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>218</v>
+        <v>12461</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>8.4</v>
+        <v>23.4</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>提供 iFLYTEK 的语音、OCR、翻译、校对和多模态 AI 技能的官方集合
-【原文】Official collection of iFLYTEK skills for speech, OCR, translation, proofreading, and multimodal AI capabilities.</t>
+          <t>汇总 ADB（Android Debug Bridge）完整用法的资源集合。
+【原文】ADB Usage Complete / ADB 用法大全
+【依据】ADB Usage Complete, topics含android-adb</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1863,7 +1888,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1878,7 +1903,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/iflytek/iFly-Skills</t>
+          <t>https://github.com/mzlogin/awesome-adb</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1887,18 +1912,14 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>1.2</v>
+        <v>3.35</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1911,21 +1932,21 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>agent, iflytek-astron, skill, skill-md, skills</t>
+          <t>android, android-adb, android-debug-bridge</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2016-07-19</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>182</v>
+        <v>3725</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1937,26 +1958,27 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-29</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>gbdev/awesome-gbdev</t>
+          <t>butterbase-ai/butterbase-skills</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>4515</v>
+        <v>533</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>收集Game Boy开发资源，如工具、文档、模拟器等
-【原文】A curated list of Game Boy development resources such as tools, docs, emulators, related projects and open-source ROMs.</t>
+          <t>为 Butterbase.ai 提供 agent skills 插件，支持 MCP 协议。
+【原文】Plugin for Butterbase.ai
+【依据】Plugin for Butterbase.ai, topics含skills, mcp</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1966,12 +1988,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包/MCP服务</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1981,7 +2003,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/gbdev/awesome-gbdev</t>
+          <t>https://github.com/butterbase-ai/butterbase-skills</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1990,11 +2012,11 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1.17</v>
+        <v>3.14</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr"/>
@@ -2010,21 +2032,21 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>assembler, awesome, awesome-list, cartridge, dmg, documentation, game-boy-development, game-development, gameboy, gameboy-color, gameboy-color-emulator, gameboy-emulator</t>
+          <t>agent-skills, ai-agents, backend-as-a-service, butterbase, claude, claude-code, mcp, skills</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2016-02-23</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>3870</v>
+        <v>170</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2036,26 +2058,26 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>danielecook/Awesome-Bioinformatics</t>
+          <t>sergebulaev/instagram-skills</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>4306</v>
+        <v>208</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>6.9</v>
+        <v>16.2</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>收集生物信息学库和软件列表
-【原文】A curated list of awesome Bioinformatics libraries and software.</t>
+          <t>提供 Instagram 营销技能，包括标题、轮播图、钩子、标签策略和每周计划
+【原文】Instagram marketing skills for Claude Code and Codex: captions, carousels, hooks, hashtag strategy, and a weekly plan. Draft, humanize, and publish via Publora. MIT. Content engineering by Creative Content Crafts.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2065,12 +2087,12 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2080,7 +2102,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/danielecook/Awesome-Bioinformatics</t>
+          <t>https://github.com/sergebulaev/instagram-skills</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2089,14 +2111,18 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.98</v>
+        <v>2.31</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2109,21 +2135,21 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, bioinformatics</t>
+          <t>agent-skill, ai-agents, ai-marketing, captions, claude-code, claude-skills, codex, content-creation, content-engineering, hashtags, instagram, instagram-marketing</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>4415</v>
+        <v>90</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
@@ -2135,26 +2161,25 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>neiesc/awesome-minimalist</t>
+          <t>Jianing1117/jianing-skills</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>3659</v>
+        <v>329</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>收集简约框架列表，适用于快速开发
-【原文】A curated list of awesome minimalist frameworks (simple and lightweight).</t>
+          <t>未提供具体描述</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2164,12 +2189,12 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -2179,7 +2204,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/neiesc/awesome-minimalist</t>
+          <t>https://github.com/Jianing1117/jianing-skills</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2188,16 +2213,16 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.78</v>
+        <v>2.22</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2210,23 +2235,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>awesome-lists, hacktoberfest, minimalistic</t>
-        </is>
-      </c>
+      <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2013-12-11</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>4674</v>
+        <v>148</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
@@ -2238,36 +2259,37 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-29</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>getoneapi/OneAPI</t>
+          <t>justinwetch/HIGAgentSkills</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>101</v>
+        <v>373</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1.9</v>
+        <v>13.1</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>提供多种社交媒体数据API，包括抖音、小红书等
-【原文】OneAPI，提供各种数据API，用户信息、视频列表、详情、点赞、评论数据、综合搜索等，包括：Douyin（抖音）、Xiaohongshu（小红书）、Kuaishou（快手）、Bilibili（哔哩哔哩）、Weibo（微博）、Toutiao（今日头条）、Xigua（西瓜视频）、Lemon8、Tiktok、Youtube等接口、数据、API、爬虫、采集。</t>
+          <t>提供 Apple 人机界面指南相关的 AI agent skills。
+【原文】Apple Human Interface Guidelines for Agents
+【依据】Apple Human Interface Guidelines for Agents, topics含skills</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2282,7 +2304,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/getoneapi/OneAPI</t>
+          <t>https://github.com/justinwetch/HIGAgentSkills</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2291,7 +2313,7 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.27</v>
+        <v>1.87</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2315,21 +2337,21 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>api, bilibili, bilibili-api, data, data-api, douyin, douyin-api, kuaishou, kuaishou-api, lemon8, tiktok, tiktok-api</t>
+          <t>agent, apple, design, designsystem, skills</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>381</v>
+        <v>199</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
@@ -2341,12 +2363,908 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>topic:xiaohongshu stars:&gt;100</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>garylab/MakeMoneyWithAI</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>1042</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>列出可用于轻松赚取收入的开源 AI 项目
+【原文】A list of open-source AI projects you can use to generate income easily.</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/garylab/MakeMoneyWithAI</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>ai, ai-agent, ai-agents, deepfake, llm, mcp, mcp-server, nlp, ocr, open-source, open-source-ai</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>560</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="150" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Softeria/ms-365-mcp-server</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>提供 Microsoft 365 和 Microsoft Office 服务的 Model Context Protocol (MCP) 服务器
+【原文】A Model Context Protocol (MCP) server for interacting with Microsoft 365 and Microsoft Office services through the Graph API</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务/架构参考</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Softeria/ms-365-mcp-server</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>546</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V21" s="6" t="inlineStr">
+        <is>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>KunoLu/640-skills</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>提供为自由职业者和团队设计的 Agent Skills
+【原文】Agent Skills for Solopreneurs &amp; Teams.</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>技能包/架构参考</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/KunoLu/640-skills</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>anliyuan/FeatherTalk</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>提供轻量级的数字人音频驱动 talking-head 框架
+【原文】超轻量级的数字人 FeatherTalk is a lightweight audio-driven talking-head framework.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>技能包/架构参考</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/anliyuan/FeatherTalk</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>81NewArk/AntiCAP</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>659</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>提供验证码识别功能，包括点选、滑块、算术、旋转 OCR
+【原文】验证码识别   点选 滑块 算术 旋转 OCR</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/81NewArk/AntiCAP</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>549</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="150" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>yuturuishi/ytlabel</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>339</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>YOLO标注训练工具，支持AI自动标注、视频采集与数据集收集。
+【原文】宇图瑞视 YOLO标注训练工具，AI自动标注，大模型提示词自动标注，自动采集视频，自动收集数据集
+【依据】自动采集视频, YOLO标注训练工具</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>视频产线/图文产线</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务/数据集</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/yuturuishi/ytlabel</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>590</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="150" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>manisandro/gImageReader</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>1997</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>提供 tesseract-ocr 的 Gtk/Qt 前端
+【原文】A Gtk/Qt front-end to tesseract-ocr.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/manisandro/gImageReader</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>GPL-3.0</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>C++</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>c-plus-plus, gtk, hocr, hocr-documents, ocr, pdf-document, qt, scanner, tesseract-ocr</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>2014-02-10</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>4615</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V26" s="6" t="inlineStr">
+        <is>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="150" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>shack2/SuperSQLInjectionV1</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>1268</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>提供超级 SQL 注入工具，支持多种数据库和注入方式
+【原文】超级SQL注入工具（SSQLInjection）是一款基于HTTP协议自组包的SQL注入工具,采用C#开发，直接操作TCP会话来进行HTTP交互，支持出现在HTTP协议任意位置的SQL注入，支持各种类型的SQL注入，支持HTTPS模式注入；支持以盲注、错误显示、Union注入等方式来获取数据；支持Access/MySQL/SQLServer/Oracle/PostgreSQL/DB2/SQLite/Informix等数据库；支持手动灵活的进行SQL注入绕过，可自定义进行字符替换等绕过注入防护。本工具为渗透测试人员、信息安全工程师等掌握SQL注入技能的人员设计，需要使用人员对SQL注入有一定了解。</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/shack2/SuperSQLInjectionV1</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>2017-03-21</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>3480</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V27" s="6" t="inlineStr">
+        <is>
+          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="150" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>open-guji/guji-resource-index</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>收录和索引各类古籍数字化资源的网站。
+【原文】收录所有古籍数字化资源的网站。</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>古籍OCR线</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/open-guji/guji-resource-index</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V28" s="6" t="inlineStr">
+        <is>
+          <t>古籍 in:name,description stars:&gt;20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V19"/>
+  <autoFilter ref="A2:V28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-30 · 共 26 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-10-01 · 共 18 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,19 +633,19 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>jev-chat/jev-chat-jarvis</t>
+          <t>KKKKhazix/AIHOT</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>7132</v>
+        <v>4203</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>5547.1</v>
+        <v>9807</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>提供安装在手机上的对话助手，用于 QQ / X / 飞书中的对话辅助
-【原文】装在手机上的对话副驾：在 QQ / X / 飞书里读懂对方、给出候选回复、一键填入输入框，发不发由你。非侵入，只读屏幕，不 hook 不改包。</t>
+          <t>提供行业热点站网站框架，支持自定义信源和精选标准。
+【原文】一个自己找热点、自己写日报的网站框架。把信源和精选标准换成你的，它就是你的行业热点站。</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jev-chat/jev-chat-jarvis</t>
+          <t>https://github.com/KKKKhazix/AIHOT</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>792.4400000000001</v>
+        <v>1401</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Kotlin</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -703,67 +703,67 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>accessibility-service, ai-assistant, android, chat-assistant, chat-copilot, llm, ocr, qq</t>
+          <t>ai, content-curation, llm, mcp, news-aggregator, rss, self-hosted, typescript</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-02</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>YeJe-cpu/SeeCut</t>
+          <t>yibie/awesome-jev</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>140</v>
+        <v>2037</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>196</v>
+        <v>1018.5</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 视频编辑工具，可自动精剪数字人或真人口播视频
-【原文】An AI editor that watches its own cut: talking-head / AI-avatar video → auto-edited short video. 网感口播精剪：数字人/真人口播 → AI 自动精剪成网感动效短视频 → 可选剪映分层草稿</t>
+          <t>收集和整理基于 Jev 模型的项目、集成和讨论列表
+【原文】A curated list of public projects, integrations, and discussions built on Jev — TypeSafe AI's System One model for typed decisions.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/YeJe-cpu/SeeCut</t>
+          <t>https://github.com/yibie/awesome-jev</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>28</v>
+        <v>145.5</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -806,67 +806,67 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agent-skill, ai-avatar, ai-video, claude-code, gemini, heygen, hyperframes, talking-head, video-editing</t>
+          <t>awesome, awesome-list, jev, llm</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>j4c8dobolsuo8m2m/seedance-api-cn</t>
+          <t>wenziai/wenzi-xhs-agent-skills</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>123.7</v>
+        <v>707</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>提供 AI API 中转站/网关的中文文档和定价信息
-【原文】AI API 中转站/网关中文文档 · AI API gateway pricing: image2.5 $0.0085/image, Seedance 2.0 Mini $0.0106/sec, LLM tokens from $0.0229/M. One OpenAI-compatible key, $1 minimum top-up, per-call cost in every respo</t>
+          <t>提供小红书 Agent Skills 工作流，包括账号定位、选题标题等。
+【原文】文子的小红书 Agent Skills：从账号定位、选题标题、真人化改稿、图文规划到排期复盘的一套可安装工作流。</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/j4c8dobolsuo8m2m/seedance-api-cn</t>
+          <t>https://github.com/wenziai/wenzi-xhs-agent-skills</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -885,18 +885,14 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>17.67</v>
+        <v>101</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -909,62 +905,62 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>ai-api-aggregator, ai-api-gateway, api-docs, api-pricing, apimart, cheapest-llm-api, llm-api-gateway, openai-compatible, openrouter-alternative, pay-as-you-go, per-image-pricing</t>
+          <t>agent-skills, codex-skills, content-creation, workbuddy, xiaohongshu</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>k6hdkoe76rybli/flux2-flux-2-api-cn</t>
+          <t>zhuyansen/awesome-claude-video-skills</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>101</v>
+        <v>337</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>117.8</v>
+        <v>589.8</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供 flux-2 API 的中文文档和定价信息
-【原文】AI API 中转站/网关中文文档 · flux-2 / flux2 API：1MP $0.024; 2MP $0.036; 3MP $0.048。模型 ID、参数、curl 与 Python 示例，OpenAI 兼容接口，$1 起充。</t>
+          <t>提供 Claude Code、Codex 等编码 Agent 制作视频的技能和工具包
+【原文】Open-source skills and toolkits that let Claude Code, Codex and other coding agents make video. 180 repos by type, each security-graded. English / 中文.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -979,7 +975,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/k6hdkoe76rybli/flux2-flux-2-api-cn</t>
+          <t>https://github.com/zhuyansen/awesome-claude-video-skills</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -988,18 +984,14 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>16.83</v>
+        <v>84.25</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>NOASSERTION</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1012,67 +1004,67 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>api-docs, apimart, cn, flux-2, flux-2-api, flux2, flux2-api, model-cn, openai-compatible, pay-as-you-go</t>
+          <t>agent-skills, awesome-list, claude-code, claude-skills, codex, hyperframes, motion-graphics, opus-5-5, remotion, video</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>oy8jfpo2qa8075/qwenimage3.0-qwen-image-3.0-api-cn</t>
+          <t>browseros-ai/BrowserOS</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>101</v>
+        <v>13785</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>117.8</v>
+        <v>192.6</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供 qwen-image-3.0 API 的中文文档和定价信息
-【原文】AI API 中转站/网关中文文档 · qwen-image-3.0 / qwenimage3.0 API：default $0.0206; 1K $0.0206; 2K $0.0206。模型 ID、参数、curl 与 Python 示例，OpenAI 兼容接口，$1 起充。</t>
+          <t>提供开源 Agentic 浏览器，替代 ChatGPT Atlas、Perplexity Comet 等。
+【原文】🌐 The open-source Agentic browser; alternative to ChatGPT Atlas, Perplexity Comet, Dia.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1082,7 +1074,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/oy8jfpo2qa8075/qwenimage3.0-qwen-image-3.0-api-cn</t>
+          <t>https://github.com/browseros-ai/BrowserOS</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1091,16 +1083,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>16.83</v>
+        <v>27.51</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1115,67 +1107,67 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>api-docs, apimart, cn, model-cn, openai-compatible, pay-as-you-go, qwen-image-3-0, qwen-image-3-0-api, qwenimage3-0, qwenimage3-0-api</t>
+          <t>agent, ai-agents, automation, browser, browser-automation, browseros, chromium, claude, linux, llm, lmstudio, macos</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>hd42567u/grokimagine2.0-grok-imagine-2.0-api-cn</t>
+          <t>fallow-rs/fallow</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>101</v>
+        <v>4967</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>117.8</v>
+        <v>175.6</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供 OpenAI 兼容的 AI API 中转站/网关中文文档
-【原文】AI API 中转站/网关中文文档 · grok-imagine-2.0 / grokimagine2.0 API：upload-image $0; default $0.015; region-edit $0.015。模型 ID、参数、curl 与 Python 示例，OpenAI 兼容接口，$1 起充。</t>
+          <t>提供 TypeScript 和 JavaScript 代码库智能分析工具，包括健康、复杂度、重复代码等。
+【原文】Codebase intelligence for TypeScript and JavaScript. Health, complexity hotspots, duplication, architecture boundaries, circular dependencies, design-system drift, and unused code, from one graph. CLI, GitHub Action, LSP, MCP, and VS Code. Rust, MIT licensed.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1185,7 +1177,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/hd42567u/grokimagine2.0-grok-imagine-2.0-api-cn</t>
+          <t>https://github.com/fallow-rs/fallow</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1194,16 +1186,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>16.83</v>
+        <v>25.09</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1218,67 +1210,67 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>api-docs, apimart, cn, grok-imagine-2-0, grok-imagine-2-0-api, grokimagine2-0, grokimagine2-0-api, model-cn, openai-compatible, pay-as-you-go</t>
+          <t>architecture, circular-dependencies, cli, code-duplication, code-health, code-quality, codebase-intelligence, complexity, dead-code, developer-tools, javascript, mcp</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>yyjeqhc/webcodex</t>
+          <t>MunGell/awesome-for-beginners</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2064</v>
+        <v>89750</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>115.6</v>
+        <v>157.3</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>为云 AI 代理提供在本地机器上的真实开发环境
-【原文】Give cloud AI agents a real development environment on your own machines.</t>
+          <t>提供初学者友好型项目列表。
+【原文】A list of awesome beginners-friendly projects.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1288,7 +1280,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yyjeqhc/webcodex</t>
+          <t>https://github.com/MunGell/awesome-for-beginners</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1297,18 +1289,14 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>16.51</v>
+        <v>22.47</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>Rust</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1321,12 +1309,12 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>agent, chatgpt, claude, claude-code, codex, developer-tools, gemini, gpt-actions, grok, mcp, rust, self-hosted</t>
+          <t>awesome, awesome-list, beginner-project, beginners-friendly, list</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2015-10-24</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1335,38 +1323,38 @@
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>125</v>
+        <v>3995</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-31</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>dontriskit/awesome-ai-system-prompts</t>
+          <t>rmyndharis/antigravity-skills</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>6227</v>
+        <v>1670</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>76</v>
+        <v>45.5</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>收集并整理顶级 AI 工具的系统提示词
-【原文】🧠 Curated collection of system prompts for top AI tools. Perfect for AI agent builders and prompt engineers. Incuding: ChatGPT, Claude, Perplexity, Manus, Claude-Code, Loveable, v0, Grok, same new, windsurf, notion, and MetaAI.</t>
+          <t>收集 Google Antigravity 的 Agent 技能
+【原文】A curated collection of Agent Skills for Google Antigravity</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1376,7 +1364,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1391,7 +1379,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dontriskit/awesome-ai-system-prompts</t>
+          <t>https://github.com/rmyndharis/antigravity-skills</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1400,7 +1388,7 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>10.85</v>
+        <v>6.5</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1397,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1422,22 +1410,26 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>antigravity, antigravity-skills</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>574</v>
+        <v>257</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
@@ -1446,36 +1438,36 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-08-31</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>haris-musa/excel-mcp-server</t>
+          <t>lucasrosati/claude-code-memory-setup</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4206</v>
+        <v>1001</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>49.5</v>
+        <v>40.7</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>提供用于 Excel 文件操作的 Model Context Protocol 服务器
-【原文】A Model Context Protocol server for Excel file manipulation</t>
+          <t>提供 Claude Code 的持久记忆和代码库知识图谱，支持代码导入管道。
+【原文】Up to 71.5x fewer tokens per session on Claude Code with Obsidian + Graphify. Persistent memory, codebase knowledge graphs, and chat import pipeline. 🇧🇷 PT-BR included.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1490,7 +1482,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/haris-musa/excel-mcp-server</t>
+          <t>https://github.com/lucasrosati/claude-code-memory-setup</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1499,7 +1491,7 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>7.07</v>
+        <v>5.82</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1523,52 +1515,52 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai, automation, excel, llm, mcp, mcp-server, sse, stdio, streamable-http, toolcalling</t>
+          <t>ai-tools, claude-code, coding-agent, developer-productivity, graphify, knowledge-graph, obsidian, second-brain, token-optimization, zettelkasten</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>595</v>
+        <v>172</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp-server stars:&gt;1000 pushed:&gt;2026-08-31</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>darkrishabh/agent-skills-eval</t>
+          <t>kubeflow/kubeflow</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>798</v>
+        <v>15890</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>38</v>
+        <v>34.4</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>为 agentskills.io 风格的 AI agent skills 提供测试运行器。
-【原文】A test runner for agentskills.io-style AI agent skills</t>
+          <t>提供云原生 AI 平台，支持数据科学和机器学习。
+【原文】The Cloud Native AI Platform</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1578,7 +1570,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1593,7 +1585,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/darkrishabh/agent-skills-eval</t>
+          <t>https://github.com/kubeflow/kubeflow</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1602,18 +1594,14 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>5.43</v>
+        <v>4.92</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1626,21 +1614,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agent-evals, agent-skills, agentskills, ai-agents, cli, jsonl, llm-evals, llm-evaluation, openai-compatible, typescript, yaml</t>
+          <t>agentic-ai, ai, data-science, distributed-ai, genai, google-kubernetes-engine, jupyter, kubeflow, kubernetes, machine-learning, minikube, ml</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>147</v>
+        <v>3227</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1652,26 +1640,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>yaojingang/yao-geo-skills</t>
+          <t>johnbean393/Sidekick</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>790</v>
+        <v>3316</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供用于 GEO 内容和流程的开放源代码 Skill 集合
-【原文】An open-source Skill collection for GEO content and workflows, continuously updated.</t>
+          <t>提供 macOS 上与本地 LLM 交互的聊天应用
+【原文】A native macOS app that allows users to chat with a local LLM that can respond with information from files, folders and websites on your Mac without installing any other software. Powered by llama.cpp.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1681,7 +1669,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1696,7 +1684,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yaojingang/yao-geo-skills</t>
+          <t>https://github.com/johnbean393/Sidekick</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1705,7 +1693,7 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -1714,7 +1702,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Swift</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1729,12 +1717,12 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, automation, cli, codex, geoflow, skills, workflow</t>
+          <t>agentic-ai, agents, ai, ai-agents, aichat, chatbot, deep-research, deepseek, deepseek-r1, gpt-oss, llama, llama4</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -1743,7 +1731,7 @@
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>173</v>
+        <v>722</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1755,41 +1743,41 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Anil-matcha/open-dots</t>
+          <t>luwill/research-skills</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>4587</v>
+        <v>853</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>26.2</v>
+        <v>22.9</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>提供自托管的 AI 聊天、工具、审批流程和计算机任务
-【原文】Open-source alternative to OpenAI Dots: self-hosted AI chat, tools, approvals, connectors, and computer tasks.</t>
+          <t>封装常用研究经验和过程为 Agent 技能
+【原文】Some commonly used research experiences and processes are encapsulated into Agent skills.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1799,7 +1787,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Anil-matcha/open-dots</t>
+          <t>https://github.com/luwill/research-skills</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1808,11 +1796,11 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>3.75</v>
+        <v>3.27</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1830,55 +1818,50 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>agentic-ai, ai-agent, ai-assistant, ai-workspace, approval-workflows, browser-automation, computer-use, computer-use-agent, fastapi, llm, local-first, nextjs</t>
-        </is>
-      </c>
+      <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>1224</v>
+        <v>261</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-31</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>mzlogin/awesome-adb</t>
+          <t>terrakok/kmp-awesome</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>12461</v>
+        <v>5879</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>汇总 ADB（Android Debug Bridge）完整用法的资源集合。
-【原文】ADB Usage Complete / ADB 用法大全
-【依据】ADB Usage Complete, topics含android-adb</t>
+          <t>整理 Kotlin Multiplatform 库和工具列表
+【原文】An awesome list that curates the best Kotlin Multiplatform libraries, tools and more.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1888,12 +1871,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1903,7 +1886,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mzlogin/awesome-adb</t>
+          <t>https://github.com/terrakok/kmp-awesome</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1912,11 +1895,11 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>3.35</v>
+        <v>3.19</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr"/>
@@ -1932,21 +1915,21 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>android, android-adb, android-debug-bridge</t>
+          <t>android, awesome, compose, compose-multiplatform, ios, jetbrains, kmm, kmp, kotlin, kotlin-multiplatform, libraries, tools</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2016-07-19</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>3725</v>
+        <v>1843</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1958,27 +1941,26 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-31</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>butterbase-ai/butterbase-skills</t>
+          <t>FishBottle7/opencode2dsh</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>533</v>
+        <v>101</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>22</v>
+        <v>21.4</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>为 Butterbase.ai 提供 agent skills 插件，支持 MCP 协议。
-【原文】Plugin for Butterbase.ai
-【依据】Plugin for Butterbase.ai, topics含skills, mcp</t>
+          <t>提供 DeepSeek Harness 的免费 OpenCode Zen 模型，无需 API key。
+【原文】DSH plugin — free OpenCode Zen models for DeepSeek Harness (DSH). Free LLM API, no API key needed. 在 DSH 中使用 OpenCode Zen 免费模型，无需 API key</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1988,7 +1970,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>技能包/MCP服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2003,7 +1985,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/butterbase-ai/butterbase-skills</t>
+          <t>https://github.com/FishBottle7/opencode2dsh</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2012,14 +1994,18 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2032,52 +2018,52 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, backend-as-a-service, butterbase, claude, claude-code, mcp, skills</t>
+          <t>cordis, cordis-plugin, deepseek, deepseek-harness, dsh, dsh-plugin, free-api, free-llm, free-llm-access, free-models, llm, llm-agents</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>170</v>
+        <v>33</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
+          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>sergebulaev/instagram-skills</t>
+          <t>Calrton/jailbreak-prompts</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>16.2</v>
+        <v>16.7</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>提供 Instagram 营销技能，包括标题、轮播图、钩子、标签策略和每周计划
-【原文】Instagram marketing skills for Claude Code and Codex: captions, carousels, hooks, hashtag strategy, and a weekly plan. Draft, humanize, and publish via Publora. MIT. Content engineering by Creative Content Crafts.</t>
+          <t>提供精选 LLM 破甲提示词合集，包括 Codex、GPT-5.x、Claude 等。
+【原文】精选 LLM 破甲提示词合集 — Codex / GPT-5.x / Claude / Gemini / DeepSeek / Grok — UNFILTERED MODE · GODMODE · CTF Sandbox</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2087,7 +2073,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2102,7 +2088,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sergebulaev/instagram-skills</t>
+          <t>https://github.com/Calrton/jailbreak-prompts</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2111,18 +2097,14 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2133,53 +2115,50 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>agent-skill, ai-agents, ai-marketing, captions, claude-code, claude-skills, codex, content-creation, content-engineering, hashtags, instagram, instagram-marketing</t>
-        </is>
-      </c>
+      <c r="P17" s="6" t="inlineStr"/>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Jianing1117/jianing-skills</t>
+          <t>SylphxAI/anymd</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>329</v>
+        <v>1003</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>15.5</v>
+        <v>12.9</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>未提供具体描述</t>
+          <t>提供文件到 Markdown 的转换工具，支持多种文件格式和图像 OCR。
+【原文】Any file → clean Markdown for AI agents: PDF, Word, PowerPoint, Excel, EPUB, HTML and web pages, images (OCR), audio and video (metadata, subtitles, transcripts). A fast Rust MCP server and CLI that runs on your machine. No API key.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2194,7 +2173,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -2204,7 +2183,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Jianing1117/jianing-skills</t>
+          <t>https://github.com/SylphxAI/anymd</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2213,16 +2192,16 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2235,22 +2214,26 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>ai-agents, cli, document-conversion, docx, docx-to-markdown, epub, html-to-markdown, llm, markdown, markitdown-alternative, mcp, model-context-protocol</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>148</v>
+        <v>545</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
@@ -2259,27 +2242,26 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>justinwetch/HIGAgentSkills</t>
+          <t>EvoScientist/EvoSkills</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>373</v>
+        <v>440</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>提供 Apple 人机界面指南相关的 AI agent skills。
-【原文】Apple Human Interface Guidelines for Agents
-【依据】Apple Human Interface Guidelines for Agents, topics含skills</t>
+          <t>扩展 EvoScientist 的技能和知识包
+【原文】🧬 Extend EvoScientist with Installable Skill &amp; Knowledge Packs</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -2289,12 +2271,12 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -2304,7 +2286,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/justinwetch/HIGAgentSkills</t>
+          <t>https://github.com/EvoScientist/EvoSkills</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2313,11 +2295,11 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -2337,21 +2319,21 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>agent, apple, design, designsystem, skills</t>
+          <t>ai-agent, ai4science, skills, vibe-research</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
@@ -2363,26 +2345,26 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>garylab/MakeMoneyWithAI</t>
+          <t>LLMSecurity/awesome-agent-skills-security</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1042</v>
+        <v>208</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>13</v>
+        <v>7.1</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>列出可用于轻松赚取收入的开源 AI 项目
-【原文】A list of open-source AI projects you can use to generate income easily.</t>
+          <t>收集关于 Agent 技能安全的资源列表
+【原文】🛡️ A curated list of resources on agent skills security: attacks, defenses, frameworks, and benchmarks for securing AI agent tool use and skill ecosystems</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2392,7 +2374,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2407,7 +2389,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/garylab/MakeMoneyWithAI</t>
+          <t>https://github.com/LLMSecurity/awesome-agent-skills-security</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2416,18 +2398,14 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2440,12 +2418,12 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agent, ai-agents, deepfake, llm, mcp, mcp-server, nlp, ocr, open-source, open-source-ai</t>
+          <t>agent-security, ai-safety, awesome-list, llm-security, mcp, owasp, prompt-injection, tool-use</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -2454,7 +2432,7 @@
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>560</v>
+        <v>206</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
@@ -2466,805 +2444,12 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="150" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Softeria/ms-365-mcp-server</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>1002</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>提供 Microsoft 365 和 Microsoft Office 服务的 Model Context Protocol (MCP) 服务器
-【原文】A Model Context Protocol (MCP) server for interacting with Microsoft 365 and Microsoft Office services through the Graph API</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>MCP服务/架构参考</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/Softeria/ms-365-mcp-server</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P21" s="6" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>546</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V21" s="6" t="inlineStr">
-        <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="150" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>KunoLu/640-skills</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>提供为自由职业者和团队设计的 Agent Skills
-【原文】Agent Skills for Solopreneurs &amp; Teams.</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/KunoLu/640-skills</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V22" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>anliyuan/FeatherTalk</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>提供轻量级的数字人音频驱动 talking-head 框架
-【原文】超轻量级的数字人 FeatherTalk is a lightweight audio-driven talking-head framework.</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/anliyuan/FeatherTalk</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="T23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V23" s="6" t="inlineStr">
-        <is>
-          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>81NewArk/AntiCAP</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>659</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>提供验证码识别功能，包括点选、滑块、算术、旋转 OCR
-【原文】验证码识别   点选 滑块 算术 旋转 OCR</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/81NewArk/AntiCAP</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="inlineStr"/>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>549</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V24" s="6" t="inlineStr">
-        <is>
-          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>yuturuishi/ytlabel</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>339</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>YOLO标注训练工具，支持AI自动标注、视频采集与数据集收集。
-【原文】宇图瑞视 YOLO标注训练工具，AI自动标注，大模型提示词自动标注，自动采集视频，自动收集数据集
-【依据】自动采集视频, YOLO标注训练工具</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>视频产线/图文产线</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务/数据集</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/yuturuishi/ytlabel</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr"/>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-17</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>590</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V25" s="6" t="inlineStr">
-        <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="150" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>manisandro/gImageReader</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>1997</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>提供 tesseract-ocr 的 Gtk/Qt 前端
-【原文】A Gtk/Qt front-end to tesseract-ocr.</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/manisandro/gImageReader</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>GPL-3.0</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>C++</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>c-plus-plus, gtk, hocr, hocr-documents, ocr, pdf-document, qt, scanner, tesseract-ocr</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t>2014-02-10</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>4615</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V26" s="6" t="inlineStr">
-        <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="150" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>shack2/SuperSQLInjectionV1</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>1268</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>提供超级 SQL 注入工具，支持多种数据库和注入方式
-【原文】超级SQL注入工具（SSQLInjection）是一款基于HTTP协议自组包的SQL注入工具,采用C#开发，直接操作TCP会话来进行HTTP交互，支持出现在HTTP协议任意位置的SQL注入，支持各种类型的SQL注入，支持HTTPS模式注入；支持以盲注、错误显示、Union注入等方式来获取数据；支持Access/MySQL/SQLServer/Oracle/PostgreSQL/DB2/SQLite/Informix等数据库；支持手动灵活的进行SQL注入绕过，可自定义进行字符替换等绕过注入防护。本工具为渗透测试人员、信息安全工程师等掌握SQL注入技能的人员设计，需要使用人员对SQL注入有一定了解。</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/shack2/SuperSQLInjectionV1</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>C#</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P27" s="6" t="inlineStr"/>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>2017-03-21</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>3480</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V27" s="6" t="inlineStr">
-        <is>
-          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>open-guji/guji-resource-index</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>收录和索引各类古籍数字化资源的网站。
-【原文】收录所有古籍数字化资源的网站。</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>古籍OCR线</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/open-guji/guji-resource-index</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr"/>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P28" s="6" t="inlineStr"/>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V28" s="6" t="inlineStr">
-        <is>
-          <t>古籍 in:name,description stars:&gt;20</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V28"/>
+  <autoFilter ref="A2:V20"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-10-01 · 共 18 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-10-04 · 共 38 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,19 +633,20 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>KKKKhazix/AIHOT</t>
+          <t>rehan-remade/universal-modder</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>4203</v>
+        <v>2709</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>9807</v>
+        <v>4740.8</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>提供行业热点站网站框架，支持自定义信源和精选标准。
-【原文】一个自己找热点、自己写日报的网站框架。把信源和精选标准换成你的，它就是你的行业热点站。</t>
+          <t>为 Claude Code 提供游戏模改技能和工具
+【原文】Point Claude at any game. Skills, tools and the fal MCP that let Claude Code mod almost any PC game you own: recon, reverse engineering, fal-generated art/3D/audio, in-game testing, showcase videos.
+【依据】Claude Code modding, fal MCP</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -670,7 +671,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/KKKKhazix/AIHOT</t>
+          <t>https://github.com/rehan-remade/universal-modder</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,7 +680,7 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>1401</v>
+        <v>677.25</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -688,7 +689,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -703,21 +704,21 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>ai, content-curation, llm, mcp, news-aggregator, rss, self-hosted, typescript</t>
+          <t>age-of-empires, claude-code, claude-code-plugin, fal, game-assets, game-modding, mcp, modding, reverse-engineering, tmodloader</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -729,41 +730,41 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-01</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>yibie/awesome-jev</t>
+          <t>feder-cr/dots</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2037</v>
+        <v>2580</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1018.5</v>
+        <v>3612</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>收集和整理基于 Jev 模型的项目、集成和讨论列表
-【原文】A curated list of public projects, integrations, and discussions built on Jev — TypeSafe AI's System One model for typed decisions.</t>
+          <t>提供开源的 web dots：一个具有自己浏览器的 AI 代理
+【原文】Open-source dots for the web: an AI agent with its own browser, one that does not get blocked.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -773,7 +774,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yibie/awesome-jev</t>
+          <t>https://github.com/feder-cr/dots</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,11 +783,11 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>145.5</v>
+        <v>516</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -806,52 +807,53 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, jev, llm</t>
+          <t>ai-agent, ai-agents, ai-browser, anti-detect-browser, browser-agent, browser-automation, chatgpt, dotfiles, dots, firefox, llm-agent, mcp</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-01</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>wenziai/wenzi-xhs-agent-skills</t>
+          <t>Edwardxlai/easyread</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>101</v>
+        <v>685</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>707</v>
+        <v>1198.8</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>提供小红书 Agent Skills 工作流，包括账号定位、选题标题等。
-【原文】文子的小红书 Agent Skills：从账号定位、选题标题、真人化改稿、图文规划到排期复盘的一套可安装工作流。</t>
+          <t>提供英文论文的中文翻译和文献管理工具
+【原文】把英文论文读成舒服的中文：本地 PDF 论文翻译、原文对照、边读边问 AI、文献管理。Read English papers in comfortable Chinese.
+【依据】Read English papers in comfortable Chinese, reference-manager</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -866,7 +868,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -876,7 +878,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wenziai/wenzi-xhs-agent-skills</t>
+          <t>https://github.com/Edwardxlai/easyread</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -885,14 +887,18 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>101</v>
+        <v>171.25</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -905,7 +911,7 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, codex-skills, content-creation, workbuddy, xiaohongshu</t>
+          <t>academic, arxiv, chinese, claude-code, codex, electron, llm, paper-reading, pdf-translator, reference-manager, research-tool, translation</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -915,42 +921,42 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:xiaohongshu stars:&gt;100</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>zhuyansen/awesome-claude-video-skills</t>
+          <t>latent-spaces/brag</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>337</v>
+        <v>13319</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>589.8</v>
+        <v>847.6</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude Code、Codex 等编码 Agent 制作视频的技能和工具包
-【原文】Open-source skills and toolkits that let Claude Code, Codex and other coding agents make video. 180 repos by type, each security-graded. English / 中文.</t>
+          <t>将项目转换为可分享的启动视频
+【原文】You built it. Now brag. Turn the project you just created into a short, shareable launch video with one command.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -965,7 +971,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -975,7 +981,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zhuyansen/awesome-claude-video-skills</t>
+          <t>https://github.com/latent-spaces/brag</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -984,14 +990,18 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>84.25</v>
+        <v>121.08</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1004,21 +1014,21 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, awesome-list, claude-code, claude-skills, codex, hyperframes, motion-graphics, opus-5-5, remotion, video</t>
+          <t>agent-skills, claude-code, claude-skills, hyperframes, launch-video, video-generation</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1030,26 +1040,27 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-01</t>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>browseros-ai/BrowserOS</t>
+          <t>ApodexAI/FrontierAgent</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>13785</v>
+        <v>5086</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>192.6</v>
+        <v>828</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供开源 Agentic 浏览器，替代 ChatGPT Atlas、Perplexity Comet 等。
-【原文】🌐 The open-source Agentic browser; alternative to ChatGPT Atlas, Perplexity Comet, Dia.</t>
+          <t>提供代理框架和命令行 TUI
+【原文】🧩 FrontierAgent, our agent framework, open-sourced alongside it — native command-line TUI, ReAct and Agent Team modes, one command on macOS and Linux, no preinstall, no hard Docker dependency.
+【依据】agent framework, native command-line TUI</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1062,9 +1073,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1074,7 +1085,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/browseros-ai/BrowserOS</t>
+          <t>https://github.com/ApodexAI/FrontierAgent</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1083,16 +1094,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>27.51</v>
+        <v>118.28</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1107,62 +1118,63 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>agent, ai-agents, automation, browser, browser-automation, browseros, chromium, claude, linux, llm, lmstudio, macos</t>
+          <t>agent-orchestration, agentic-ai, agentic-framework, ai-agents, harness, multi-agent, terminal-agent, tui</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>501</v>
+        <v>43</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-01</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>fallow-rs/fallow</t>
+          <t>TreapGoGo/deepseek-whale-girl</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>4967</v>
+        <v>253</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>175.6</v>
+        <v>295.2</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供 TypeScript 和 JavaScript 代码库智能分析工具，包括健康、复杂度、重复代码等。
-【原文】Codebase intelligence for TypeScript and JavaScript. Health, complexity hotspots, duplication, architecture boundaries, circular dependencies, design-system drift, and unused code, from one graph. CLI, GitHub Action, LSP, MCP, and VS Code. Rust, MIT licensed.</t>
+          <t>整理鲸鱼娘二创角色参考图、生成提示词、社区作品与相关项目，为创作者提供参考与灵感。
+【原文】由社区共同维护的鲸鱼娘二创资源库，整理角色参考图、生成提示词、社区作品与相关项目，为创作者提供方便易用的参考与灵感。本项目为非官方社区项目，不代表 DeepSeek 官方立场。
+【依据】描述提到角色参考图、生成提示词、社区作品</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集/技能包</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1177,7 +1189,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/fallow-rs/fallow</t>
+          <t>https://github.com/TreapGoGo/deepseek-whale-girl</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1186,7 +1198,7 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>25.09</v>
+        <v>42.17</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -1195,7 +1207,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1208,54 +1220,50 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>architecture, circular-dependencies, cli, code-duplication, code-health, code-quality, codebase-intelligence, complexity, dead-code, developer-tools, javascript, mcp</t>
-        </is>
-      </c>
+      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>198</v>
+        <v>6</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-01</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MunGell/awesome-for-beginners</t>
+          <t>SunnyMaria/csapp-zh-markdown</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>89750</v>
+        <v>671</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>157.3</v>
+        <v>261</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>提供初学者友好型项目列表。
-【原文】A list of awesome beginners-friendly projects.</t>
+          <t>提供 CSAPP 中文文档和学习资料
+【原文】CSAPP 中文文档与学习资料：《深入理解计算机系统》第三版全章节 Markdown，含练习题答案、八大实验中文翻译及官方自学实验包，方便在线阅读与离线学习。</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1280,7 +1288,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MunGell/awesome-for-beginners</t>
+          <t>https://github.com/SunnyMaria/csapp-zh-markdown</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1289,14 +1297,18 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>22.47</v>
+        <v>37.28</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1309,12 +1321,12 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, beginner-project, beginners-friendly, list</t>
+          <t>chinese, computer-architecture, computer-systems, csapp, csapp-labs, markdown, systems-programming</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2015-10-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1323,53 +1335,54 @@
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>3995</v>
+        <v>18</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-01</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>rmyndharis/antigravity-skills</t>
+          <t>guanmo-ai/awesome-ai-motion</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1670</v>
+        <v>221</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>45.5</v>
+        <v>221</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>收集 Google Antigravity 的 Agent 技能
-【原文】A curated collection of Agent Skills for Google Antigravity</t>
+          <t>收集惊艳动效、创意视频与交互艺术，提供源码、提示词与制作过程。
+【原文】发现惊艳动效、创意视频与交互艺术，探索背后的源码、提示词与制作过程。Curated motion design, creative video &amp; interactive art — with source code, prompts &amp; making-of resources.
+【依据】描述提到创意视频、提示词、动效源码</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/图文产线</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集/技能包</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1379,7 +1392,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rmyndharis/antigravity-skills</t>
+          <t>https://github.com/guanmo-ai/awesome-ai-motion</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1388,11 +1401,11 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>6.5</v>
+        <v>31.57</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1412,52 +1425,52 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>antigravity, antigravity-skills</t>
+          <t>ai-video, animation, awesome, awesome-list, claude, motion-design, opus, prompts</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>257</v>
+        <v>7</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-01</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>lucasrosati/claude-code-memory-setup</t>
+          <t>jordan-gibbs/hyperresearch</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1001</v>
+        <v>3763</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>40.7</v>
+        <v>148</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude Code 的持久记忆和代码库知识图谱，支持代码导入管道。
-【原文】Up to 71.5x fewer tokens per session on Claude Code with Obsidian + Graphify. Persistent memory, codebase knowledge graphs, and chat import pipeline. 🇧🇷 PT-BR included.</t>
+          <t>将 Claude Code 或 Codex 转换为深度研究代理
+【原文】Convert Claude Code or Codex into the most intelligent Deep Research Agent. Collect, search, and synthesize web research into a persistent, searchable wiki that builds on itself. Hosted API + MCP: hyperresearch.ai</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1482,7 +1495,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lucasrosati/claude-code-memory-setup</t>
+          <t>https://github.com/jordan-gibbs/hyperresearch</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1491,7 +1504,7 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>5.82</v>
+        <v>21.14</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -1515,62 +1528,62 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai-tools, claude-code, coding-agent, developer-productivity, graphify, knowledge-graph, obsidian, second-brain, token-optimization, zettelkasten</t>
+          <t>agents, agentskills, citations, claude-code, codex, codex-plugin, codex-skill, deep-research, deep-research-agent, deepresearch, mcp-server, research</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-09-01</t>
+          <t>topic:mcp-server stars:&gt;1000 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>kubeflow/kubeflow</t>
+          <t>zhouxiaoka/autoclip</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>15890</v>
+        <v>9140</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>34.4</v>
+        <v>141.3</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>提供云原生 AI 平台，支持数据科学和机器学习。
-【原文】The Cloud Native AI Platform</t>
+          <t>提供开源 AI 视频剪辑桌面工具
+【原文】AutoClip｜一个链接，一键出片。开源 AI 视频剪辑桌面工具，将播客、访谈、课程等长视频自动剪成短视频，生成字幕、封面和发布文案，适配抖音、小红书、TikTok、Reels 与 YouTube Shorts。Open-source AI video clipping &amp; content repurposing.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/AI免费池</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/可部署服务/代码库</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1585,7 +1598,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kubeflow/kubeflow</t>
+          <t>https://github.com/zhouxiaoka/autoclip</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1594,14 +1607,18 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>4.92</v>
+        <v>20.18</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1614,67 +1631,67 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, ai, data-science, distributed-ai, genai, google-kubernetes-engine, jupyter, kubeflow, kubernetes, machine-learning, minikube, ml</t>
+          <t>ai-agent, ai-video-editor, content-repurposing, desktop-app, douyin, instagram-reels, mcp, open-source, podcast, subtitles, tiktok, video-clipping</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>3227</v>
+        <v>453</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-09-01</t>
+          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>johnbean393/Sidekick</t>
+          <t>tianma-if/edgeever</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>3316</v>
+        <v>2002</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>32.1</v>
+        <v>140.1</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供 macOS 上与本地 LLM 交互的聊天应用
-【原文】A native macOS app that allows users to chat with a local LLM that can respond with information from files, folders and websites on your Mac without installing any other software. Powered by llama.cpp.</t>
+          <t>提供开源 AI 知识库和 Evernote 替代品
+【原文】Open-source, AI-native knowledge base &amp; Evernote alternative with native MCP. Zero-cost on Cloudflare or Docker.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>MCP服务/技能包/架构参考</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1684,7 +1701,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/johnbean393/Sidekick</t>
+          <t>https://github.com/tianma-if/edgeever</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1693,16 +1710,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>4.59</v>
+        <v>20.02</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1717,52 +1734,53 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, agents, ai, ai-agents, aichat, chatbot, deep-research, deepseek, deepseek-r1, gpt-oss, llama, llama4</t>
+          <t>ai-agent, cloudflare, cloudflare-d1, cloudflare-r2, cloudflare-workers, docker, electron, evernote, evernote-alternative, knowledge-base, mcp, model-context-protocol</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>722</v>
+        <v>100</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-09-01</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>luwill/research-skills</t>
+          <t>xianyu110/awesome-openclaw-tutorial</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>853</v>
+        <v>4565</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>22.9</v>
+        <v>135.4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>封装常用研究经验和过程为 Agent 技能
-【原文】Some commonly used research experiences and processes are encapsulated into Agent skills.</t>
+          <t>提供 OpenClaw 中文教程和接入飞书的指南
+【原文】OpenClaw 中文教程（4500+ Star · 已出版纸质书）：安装、配置、Skills、飞书接入与避坑｜作者的 GPT-6 / Codex / Claude Code 新项目见 README 顶部
+【依据】OpenClaw 中文教程，飞书接入与避坑</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1777,7 +1795,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1787,7 +1805,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/luwill/research-skills</t>
+          <t>https://github.com/xianyu110/awesome-openclaw-tutorial</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1796,16 +1814,16 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>3.27</v>
+        <v>19.34</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1818,50 +1836,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, ai-agent, ai-assistant, ai-tools, automation, awesome, awesome-list, chinese, chinese-tutorial, claude-code, codex, feishu</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-01</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>terrakok/kmp-awesome</t>
+          <t>Doulor/DoulorCloud</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>5879</v>
+        <v>203</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>22.3</v>
+        <v>118.4</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>整理 Kotlin Multiplatform 库和工具列表
-【原文】An awesome list that curates the best Kotlin Multiplatform libraries, tools and more.</t>
+          <t>提供一站式云端资源分发平台
+【原文】Doulor Cloud —— 一站式云端资源分发平台：二级域名 / 域名邮箱 / R2 直链网盘 / 个人名片 / AI API 中转站。纯静态前端 + Cloudflare Workers + D1 + R2。</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1876,7 +1898,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1886,7 +1908,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/terrakok/kmp-awesome</t>
+          <t>https://github.com/Doulor/DoulorCloud</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1895,14 +1917,18 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>3.19</v>
+        <v>16.92</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1915,62 +1941,63 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>android, awesome, compose, compose-multiplatform, ios, jetbrains, kmm, kmp, kotlin, kotlin-multiplatform, libraries, tools</t>
+          <t>ai-gateway, cloudflare-d1, cloudflare-r2, cloudflare-workers, react, serverless, typescript</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>1843</v>
+        <v>12</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-01</t>
+          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>FishBottle7/opencode2dsh</t>
+          <t>gnipbao/minimax-h3-video-reverse-skill</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>21.4</v>
+        <v>103</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>提供 DeepSeek Harness 的免费 OpenCode Zen 模型，无需 API key。
-【原文】DSH plugin — free OpenCode Zen models for DeepSeek Harness (DSH). Free LLM API, no API key needed. 在 DSH 中使用 OpenCode Zen 免费模型，无需 API key</t>
+          <t>MiniMax H3视频反推Skill，可反推真实镜头、首帧与动态提示词，支持AUTO/T2VA/I2V/DUAL模式。
+【原文】MiniMax H3 视频反推 Skill：真实镜头、首帧与动态提示词、AUTO/T2VA/I2V/DUAL，附中文教程与验证工具。
+【依据】描述提到视频反推、动态提示词、首帧</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/图文产线</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/数据集</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1985,7 +2012,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/FishBottle7/opencode2dsh</t>
+          <t>https://github.com/gnipbao/minimax-h3-video-reverse-skill</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1994,7 +2021,7 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>3.06</v>
+        <v>14.71</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2030,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2016,23 +2043,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>cordis, cordis-plugin, deepseek, deepseek-harness, dsh, dsh-plugin, free-api, free-llm, free-llm-access, free-models, llm, llm-agents</t>
-        </is>
-      </c>
+      <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2044,26 +2067,27 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-07-03</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Calrton/jailbreak-prompts</t>
+          <t>ombharatiya/ai-system-design-guide</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>203</v>
+        <v>3471</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>16.7</v>
+        <v>83.2</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>提供精选 LLM 破甲提示词合集，包括 Codex、GPT-5.x、Claude 等。
-【原文】精选 LLM 破甲提示词合集 — Codex / GPT-5.x / Claude / Gemini / DeepSeek / Grok — UNFILTERED MODE · GODMODE · CTF Sandbox</t>
+          <t>面向工程师的AI系统设计指南，涵盖生产级AI系统构建与评估。
+【原文】AI system design guide for engineers building production AI systems and evals.
+【依据】描述为AI系统设计指南，未涉及指定线</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2073,7 +2097,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>架构参考/数据集</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2088,7 +2112,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Calrton/jailbreak-prompts</t>
+          <t>https://github.com/ombharatiya/ai-system-design-guide</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2097,7 +2121,7 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>2.39</v>
+        <v>11.89</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2115,60 +2139,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>agentic-ai, agentic-workflow, ai, ai-jobs, artificial-intelligence, aws, azure, claude, evals, forward-deployed-engineer, gemini, gen-ai</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>85</v>
+        <v>292</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-03</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>SylphxAI/anymd</t>
+          <t>GiovanniPasq/agentic-rag-for-dummies</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1003</v>
+        <v>4222</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>12.9</v>
+        <v>83</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>提供文件到 Markdown 的转换工具，支持多种文件格式和图像 OCR。
-【原文】Any file → clean Markdown for AI agents: PDF, Word, PowerPoint, Excel, EPUB, HTML and web pages, images (OCR), audio and video (metadata, subtitles, transcripts). A fast Rust MCP server and CLI that runs on your machine. No API key.</t>
+          <t>用LangGraph构建模块化Agentic RAG，学习检索增强生成代理。
+【原文】A modular Agentic RAG built with LangGraph — learn Retrieval-Augmented Generation Agents in minutes.
+【依据】描述提及Agentic RAG built with LangGraph</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>架构参考/代码库</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2183,7 +2212,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SylphxAI/anymd</t>
+          <t>https://github.com/GiovanniPasq/agentic-rag-for-dummies</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2192,7 +2221,7 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>1.84</v>
+        <v>11.86</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2230,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2216,12 +2245,12 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, cli, document-conversion, docx, docx-to-markdown, epub, html-to-markdown, llm, markdown, markitdown-alternative, mcp, model-context-protocol</t>
+          <t>agent, agentic-ai, agentic-rag, agents, ai-agents, bm25, generative-ai, gradio, langchain, langgraph, llm, ollama</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -2230,10 +2259,10 @@
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>545</v>
+        <v>356</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
@@ -2242,26 +2271,26 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-03</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>EvoScientist/EvoSkills</t>
+          <t>oumi-ai/oumi</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>440</v>
+        <v>9391</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>12.7</v>
+        <v>74.7</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>扩展 EvoScientist 的技能和知识包
-【原文】🧬 Extend EvoScientist with Installable Skill &amp; Knowledge Packs</t>
+          <t>提供 LLM 微调、评估和部署工具
+【原文】Easily fine-tune (SFT/RL), evaluate, and deploy Qwen, Gemma, or any open agentic LLM/VLM!</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -2286,7 +2315,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/EvoScientist/EvoSkills</t>
+          <t>https://github.com/oumi-ai/oumi</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2295,7 +2324,7 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>1.81</v>
+        <v>10.67</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2319,21 +2348,21 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, ai4science, skills, vibe-research</t>
+          <t>agentic-ai, dpo, fine-tuning, gemma, gpt-oss, grpo, inference, llama, llm, llm-as-a-judge, llm-evaluation, llms</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>243</v>
+        <v>880</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
@@ -2345,26 +2374,27 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-01</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>LLMSecurity/awesome-agent-skills-security</t>
+          <t>samugit83/redamon</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>208</v>
+        <v>2917</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>7.1</v>
+        <v>73.2</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>收集关于 Agent 技能安全的资源列表
-【原文】🛡️ A curated list of resources on agent skills security: attacks, defenses, frameworks, and benchmarks for securing AI agent tool use and skill ecosystems</t>
+          <t>开源自托管AI渗透测试框架，将攻击面映射为图，自主利用并提交修复PR，支持双向MCP。
+【原文】Open-source, self-hosted AI penetration testing framework: maps your attack surface into a graph, autonomously exploits it from a Kali sandbox with human approval gates, and opens PRs that fix what it finds. MCP both ways: plug in any MCP server as a tool, or drive RedAmon from Claude Code or your own agent.
+【依据】描述为AI渗透测试框架，未涉及指定线</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2374,12 +2404,12 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>MCP服务/可部署服务/架构参考</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -2389,7 +2419,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LLMSecurity/awesome-agent-skills-security</t>
+          <t>https://github.com/samugit83/redamon</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2398,14 +2428,18 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1.01</v>
+        <v>10.46</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2418,21 +2452,21 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>agent-security, ai-safety, awesome-list, llm-security, mcp, owasp, prompt-injection, tool-use</t>
+          <t>agentic-ai, ai, ai-pentesting, attack-surface-management, autonomous-agents, bug-bounty, cybersecurity, ethical-hacking, ethical-hacking-tools, exploitation, kali-linux, llm-agents</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>206</v>
+        <v>279</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
@@ -2444,12 +2478,2036 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-01</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="150" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>wangzhishou/OneBox</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>574</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>免费安卓AI智能体与工具箱应用，集成聊天机器人等功能。
+【原文】A free AI agent &amp; toolbox for Android | 一站式安卓 AI 智能体 &amp; 工具箱
+【依据】描述为安卓AI工具箱，未涉及指定线</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务/未定</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/wangzhishou/OneBox</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Kotlin</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>ai, ai-agent, ai-agents, ai-assistants, ai-tools, android, android-app, android-application, android-apps, chatbot, chatgpt, chatgpt-api</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V21" s="6" t="inlineStr">
+        <is>
+          <t>智能体 in:name,description stars:&gt;200</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Jesseovo/last30days-skill-cn</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>1866</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>自动搜索中国互联网8大主流平台最近30天内容，生成有据可查的研究报告。
+【原文】last30days-cn 是一个 AI Agent 技能（Skill），能够自动搜索中国互联网 8 大主流平台最近 30 天的内容，综合分析后生成有据可查的研究报告。
+【依据】描述明确为AI Agent技能（Skill）</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Jesseovo/last30days-skill-cn</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>claude-code, dsh-plugin, openclaw, openclaw-skills, rednotebook, research, tiktok, web-search</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>187</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Syngnat/GoNavi</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>2060</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>提供高性能多数据源数据库客户端
+【原文】High-performance multi-data-source database client — ~30MB, AI &amp; MCP ready, zero Electron bloat. | 高性能多数据源数据库客户端：约 30MB，AI 与 MCP 就绪，告别 Electron 膨胀。</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>架构参考/可部署服务</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Syngnat/GoNavi</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>ai, cross-platform, database-client, database-gui, desktop-app, developer-tools, golang, kafka, mcp, model-context-protocol, mongodb, mqtt</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Jpisnice/shadcn-ui-mcp-server</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>3019</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>MCP服务器，让LLM获取shadcn/ui组件结构、用法与安装信息，兼容React、Svelte、Vue和React Native。
+【原文】A mcp server to allow LLMS gain context about shadcn ui component structure,usage and installation,compaitable with react,svelte 5,vue &amp; React Native
+【依据】描述为MCP服务器，未涉及指定线</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务/代码库</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Jpisnice/shadcn-ui-mcp-server</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>ai, expo, mcp, modelcontextprotocol, nextjs, npm, npm-package, npx, react, react-native, shadcn-ui, svelte</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>545</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="150" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>thibmaek/awesome-raspberry-pi</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>16947</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>树莓派工具、项目、镜像和资源精选列表。
+【原文】📝 A curated list of awesome Raspberry Pi tools, projects, images and resources
+【依据】描述为curated list of awesome Raspberry Pi tools</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/thibmaek/awesome-raspberry-pi</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, list, raspberry-pi, resources, rpi</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>2016-09-16</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>3670</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="150" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>tensorchord/Awesome-LLMOps</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>5953</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>LLMOps工具精选列表。
+【原文】An awesome &amp; curated list of best LLMOps tools for developers
+【依据】描述为awesome &amp; curated list of best LLMOps tools</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/tensorchord/Awesome-LLMOps</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>ai-development-tools, awesome-list, llmops, mlops</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>2022-04-15</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>1633</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V26" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="150" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>openmedlab/Awesome-Medical-Dataset</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>2161</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>收集医学数据集资源。
+【原文】Collection of awesome medical dataset resources.
+【依据】描述为医学数据集集合，未涉及指定线</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/openmedlab/Awesome-Medical-Dataset</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>2024-01-19</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>989</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V27" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="150" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>mgramin/awesome-db-tools</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>5319</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>汇总数据库管理工具，涵盖跨数据库、监控、SQL客户端、可视化等，让数据库工作更轻松。
+【原文】Everything that makes working with databases easier
+【依据】描述与话题均为数据库工具，未涉及任何指定线</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>数据集/未定</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/mgramin/awesome-db-tools</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, cross-database, database, database-management, ide, monitoring, sql-client, visualization</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>2018-05-18</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>3061</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V28" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ziguishian/MxPage</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>379</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>生成 AI 电商产品详情页和图像
+【原文】开源 AI 电商详情页生成器｜商品主图、详情长图、小红书图文、批量生图与多语言翻译。支持 Windows 桌面端和自部署，使用自己的模型 API。Open-source AI e-commerce product image &amp; detail page generator.</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/ziguishian/MxPage</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>ai-agents, batch-processing, e-commerce, electron, image-editing, image-generation, image-translation, nextjs, openai-compatible, product-detail-page, product-images, product-photography</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V29" s="6" t="inlineStr">
+        <is>
+          <t>topic:xiaohongshu stars:&gt;100</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>youngfish42/Awesome-FL</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>提供联邦学习相关学术信息
+【原文】Comprehensive and timely academic information on federated learning (papers, frameworks, datasets, tutorials, workshops)</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/youngfish42/Awesome-FL</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>CC-BY-SA-4.0</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>artificial-intelligence, awesome, computer-vision, data-mining, database, deep-learning, efficiency, federated-learning, federated-learning-framework, graph, graph-neural-networks, information-retrieval</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>1597</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V30" s="6" t="inlineStr">
+        <is>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="150" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>TarrySingh/Artificial-Intelligence-Deep-Learning-Machine-Learning-Tutorials</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>4012</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>提供免费动手AI课程，可在Colab、Kaggle等平台运行，涵盖模型验证、文档提取、RAG等。
+【原文】Synapsa Commons: free, hands-on AI courses that run anywhere (Colab, Kaggle, Binder, Codespaces, Jupyter). EU AI Act conformity evidence, model validation, predictive maintenance, document extraction, retrieval and RAG, AI agents and MCP, a simulated humanoid. Every lesson autograded. From the team building Synapsa.
+【依据】描述提到检索和RAG</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>RAG检索线</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>数据集/技能包</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/TarrySingh/Artificial-Intelligence-Deep-Learning-Machine-Learning-Tutorials</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>ai-agents, ai-governance, artificial-intelligence, autograding, deep-learning, document-ai, eu-ai-act, google-colab, humanoid-robotics, jupyter-notebook, machine-learning, mlops</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>2017-07-13</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>3370</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V31" s="6" t="inlineStr">
+        <is>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="150" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>pskoett/pskoett-ai-skills</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>309</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>AI代理的技能集合。
+【原文】Skills for AI agents
+【依据】描述为Skills for AI agents</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/pskoett/pskoett-ai-skills</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V32" s="6" t="inlineStr">
+        <is>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="150" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>zudochkin/awesome-newsletters</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>4494</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>精选新闻通讯列表。
+【原文】A list of amazing Newsletters
+【依据】描述为list of amazing Newsletters</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/zudochkin/awesome-newsletters</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, email, email-newsletter, emails, newsletter</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2015-08-06</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>4077</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V33" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="150" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>hal9ai/awesome-dataviz</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>4420</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>提供数据可视化库和资源列表
+【原文】:chart_with_upwards_trend:  A curated list of awesome data visualization libraries and resources.</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/hal9ai/awesome-dataviz</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>awesome-list, chart, data-visualization, dataviz, visualization, visualize-data</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>2015-07-21</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>4093</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V34" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="150" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>ahang008/ah-xhs-cover-title</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>生成短视频封面标题和封面三行文案
+【原文】短视频封面标题生成器。从85条爆款公式中自动路由匹配，生成标题和封面三行文案。</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/ahang008/ah-xhs-cover-title</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V35" s="6" t="inlineStr">
+        <is>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="150" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>mojoaxel/awesome-regression-testing</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>2417</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>视觉回归测试资源精选列表。
+【原文】🕶️ A curated list of resources around the topic: visual regression testing
+【依据】描述为curated list of resources</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/mojoaxel/awesome-regression-testing</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>CC-BY-SA-4.0</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>awesome, test-automation, testing, testing-tools</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>3385</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V36" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="150" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>sfermigier/awesome-functional-python</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>2559</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Python函数式编程资源精选列表。
+【原文】A curated list of awesome things related to functional programming in Python.
+【依据】描述为curated list of awesome things</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/sfermigier/awesome-functional-python</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>awesome, functional-programming, python</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>3581</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V37" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="150" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>trackawesomelist/trackawesomelist</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>681</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>跟踪 500+ 个优秀列表更新
+【原文】Track 500+ Awesome List Updates, Track it - not just star it!</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/trackawesomelist/trackawesomelist</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, track, trending</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>1495</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V38" s="6" t="inlineStr">
+        <is>
+          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="150" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>BaptisteBlouin/EventExtractionPapers</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>581</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>提供事件抽取相关论文资源列表
+【原文】A list of NLP resources focused on event extraction task</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/BaptisteBlouin/EventExtractionPapers</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>event-coreference, event-detection, event-extraction, information-extraction, nlp, papers</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>2019-12-13</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>2487</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V39" s="6" t="inlineStr">
+        <is>
+          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="150" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>overtrue/laravel-pinyin</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>531</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>为 Laravel 提供中文转拼音的翻译器
+【原文】:cn: Chinese to Pinyin translator for Laravel</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/overtrue/laravel-pinyin</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>chinese, chinese-to-pinyin, laravel, pinyin</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>2015-03-15</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>4221</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V40" s="6" t="inlineStr">
+        <is>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-09-04</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V20"/>
+  <autoFilter ref="A2:V40"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -109,6 +114,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -476,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -506,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-10-05 · 共 13 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-10-06 · 共 20 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -625,30 +633,29 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ythx-101/live-panel-skill</t>
+          <t>aoci-spec/aoci-code</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>497</v>
+        <v>1170</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1739.5</v>
+        <v>138.8</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>根据JSON配置生成动画架构图，输出H.264 mp4或实时网页，也可作为Claude Code style skill使用
-【原文】Config-driven animated architecture diagrams: turn one JSON file into a terminal-style, always-running diagram or a light-theme infographic that moves. Outputs H.264 mp4 or a live web page; also a Claude Code style skill (SKILL.md).
-【依据】从描述'Outputs H.264 mp4...also a Claude Code style skill'看出</t>
+          <t>代码库和数据库模式的持久、Git 版本化的映射，编码代理在接触任何内容之前读取。本地优先 MCP 服务器 + CLI。
+【原文】A persistent, Git-versioned map of your whole codebase and database schema that coding agents read before they touch anything. Local-first MCP server + CLI in Go: a governed repository index of code knowledge that gives Claude Code, Codex, Cursor, and opencode long-term context, memory, and code intelligence.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -663,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ythx-101/live-panel-skill</t>
+          <t>https://github.com/aoci-spec/aoci-code</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -672,7 +679,7 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>248.5</v>
+        <v>19.83</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -681,7 +688,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -694,19 +701,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>agent-memory, agents-md, ai-coding, ai-context, claude-code, code-indexing, code-intelligence, codex, coding-agent, context-engineering, cursor, database-schema</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -718,41 +729,41 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-05</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>mdpsec/bug-bounty-hunting-prompts</t>
+          <t>raullenchai/Rapid-MLX</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>304</v>
+        <v>3911</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>425.6</v>
+        <v>122.8</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>提供结构化漏洞赏金猎人提示
-【原文】Reusable prompts for a structured, evidence-first bug bounty hunting workflow</t>
+          <t>为Apple Silicon构建的OpenAI和Anthropic兼容的LLM推理服务器
+【原文】Rapid-MLX is an open-source (Apache 2.0) OpenAI- and Anthropic-compatible LLM inference server for Apple Silicon, built on MLX, focused on reliable tool calling for coding agents. Up to 4× faster than Apple's MLX (mlx-lm) on the same weights.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -762,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mdpsec/bug-bounty-hunting-prompts</t>
+          <t>https://github.com/raullenchai/Rapid-MLX</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -771,14 +782,18 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>60.8</v>
+        <v>17.54</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr"/>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -791,62 +806,62 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>application-security, bug-bounty, bug-bounty-hunting, cybersecurity, llm-prompts, open-source, penetration-testing, prompt-engineering, responsible-disclosure, security-research, vulnerability-research, web-security</t>
+          <t>anthropic-api, apple-silicon, claude-code, coding-agents, continuous-batching, inference-server, llm-inference, llm-server, lm-studio-alternative, local-ai, local-llm, macos</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>5</v>
+        <v>223</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-09-05</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>The-Vibe-Company/quivr</t>
+          <t>datalab-to/lift</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39579</v>
+        <v>1168</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>223.1</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>将内容流转换为搜索和监控引擎
-【原文】An open-source engine that turns continuous content streams into search and monitoring. Durable ingestion, hybrid search, alerts, and plugins for formats, models and business rules.</t>
+          <t>快速准确地从文档中提取结构化数据
+【原文】Extract structured data from documents quickly and accurately.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -861,7 +876,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/The-Vibe-Company/quivr</t>
+          <t>https://github.com/datalab-to/lift</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -870,16 +885,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>31.87</v>
+        <v>9.34</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -894,12 +909,12 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>ai, api, chatbot, chatgpt, database, docker, framework, frontend, groq, html, javascript, llm</t>
+          <t>ai, extract, ocr, pdf, python</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -908,7 +923,7 @@
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1242</v>
+        <v>125</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -920,36 +935,36 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-09-05</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-08</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>microsoft/ResearchStudio</t>
+          <t>TNT-Likely/PanWatch</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3004</v>
+        <v>2018</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>130.6</v>
+        <v>55.2</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>AI辅助研究，从问题到论文生成
-【原文】ResearchStudio: Our AI co-author, from research problem to final publication.</t>
+          <t>A股/港股/美股的AI盯盘、持仓分析、实时提醒与自动报告
+【原文】PanWatch — AI stock monitoring for A-shares, HK &amp; US markets, powered by TradingAgents. Portfolio insights, real-time alerts &amp; automated reports.｜盯盘侠：覆盖 A股/港股/美股的 AI 盯盘、持仓分析、实时提醒与自动报告。</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -964,7 +979,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/ResearchStudio</t>
+          <t>https://github.com/TNT-Likely/PanWatch</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -973,7 +988,7 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>18.66</v>
+        <v>7.88</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -997,62 +1012,62 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>blog-generation, idea-generation, poster-generation, presentation, researchstudio-idea, researchstudio-reel, video-generation</t>
+          <t>a-share, agent, ai, ai-agent, akshare, deepseek, fastapi, fintech, langgraph, llm, mcp, openai</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-07-07</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>morluto/rea</t>
+          <t>sampotts/plyr</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2934</v>
+        <v>30014</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>118</v>
+        <v>49.4</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>使用代理进行逆向工程
-【原文】Reverse engineer anything with agents, from app behavior down to native binaries.</t>
+          <t>提供HTML5、YouTube和Vimeo播放器
+【原文】Deprecated in favour of Video.js 10; security updates only. Simple HTML5, YouTube and Vimeo player.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1067,7 +1082,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/morluto/rea</t>
+          <t>https://github.com/sampotts/plyr</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1076,7 +1091,7 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>16.86</v>
+        <v>7.06</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -1085,7 +1100,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1100,53 +1115,52 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agent-tools, ai-agents, binary-analysis, cli, coding-agent, coding-agents, cordis, decompiler, disassembler, dsh, dsh-plugin</t>
+          <t>deprecated, html5-video, javascript, plyr, videojs, vimeo, youtube</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2015-02-14</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>174</v>
+        <v>4252</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp-server stars:&gt;1000 pushed:&gt;2026-09-05</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-07-08</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>wesammustafa/Claude-Code-Everything-You-Need-to-Know</t>
+          <t>swjybky/deepwrite</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3095</v>
+        <v>547</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>52.4</v>
+        <v>47.2</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供Claude Code实用指南，涵盖设置、提示词工程、斜杠命令、技能、钩子、子代理、MCP等
-【原文】A practical Claude Code guide with clear mental models and copy-paste examples — setup, prompt engineering, slash commands, skills, hooks, subagents, agent teams, and MCP servers. Beginner path to power-user depth. Featured in Awesome Claude Code.
-【依据】从描述'Claude Code guide...skills, hooks, MCP'看出</t>
+          <t>深度专门用于写作的 Harness 智能体。
+【原文】深度专门用于写作的Harness智能体</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1171,7 +1185,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wesammustafa/Claude-Code-Everything-You-Need-to-Know</t>
+          <t>https://github.com/swjybky/deepwrite</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1180,16 +1194,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>7.48</v>
+        <v>6.75</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1202,14 +1216,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, agentic-coding, ai-agents, anthropic, anthropic-claude, best-practices, claude, claude-ai, claude-code, claude-code-guide, claude-code-hooks, claude-code-skills</t>
-        </is>
-      </c>
+      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1218,53 +1228,53 @@
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-05</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>riddleling/iOS-OCR-Server</t>
+          <t>JGRFW/comfyui-AICG3D</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2090</v>
+        <v>128</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>34</v>
+        <v>37.3</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>使用Vision Framework的iOS OCR服务器
-【原文】An iOS OCR Server Using Apple’s Vision Framework</t>
+          <t>ComfyUI + MiniMax H3本地无限长视频生成工作流
+【原文】短剧工作台｜ComfyUI + MiniMax H3 本地无限长视频生成工作流</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1274,7 +1284,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/riddleling/iOS-OCR-Server</t>
+          <t>https://github.com/JGRFW/comfyui-AICG3D</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1283,16 +1293,16 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>4.86</v>
+        <v>5.33</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1307,63 +1317,62 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>http-server, ios, ocr, vision-framework</t>
+          <t>ai-video, comfyui, comfyui-nodes, custom-nodes, gguf, minimax-h3, prompt-engineering, text-to-video</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>430</v>
+        <v>24</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-07</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-08</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Ramakm/AI-Engineering</t>
+          <t>google-gemma/gemma-skills</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1457</v>
+        <v>1000</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>32.4</v>
+        <v>37.2</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供AI学习资源
-【原文】A group of notebooks  and other files which can help you learn AI from scratch.
-【依据】A group of notebooks and other files which can help you learn AI from scratch</t>
+          <t>为 Gemma 和模型/代理交互的技能。
+【原文】Skills for the Gemma and model/agent interactions</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1378,7 +1387,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Ramakm/AI-Engineering</t>
+          <t>https://github.com/google-gemma/gemma-skills</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1387,16 +1396,16 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>4.63</v>
+        <v>5.32</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1411,21 +1420,21 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>ai, artificial-intelligence, books, chatbot, machine-learning, math, ml, mlmodel, neural-network, ocr, pytorch, rag</t>
+          <t>gemma, skills</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>315</v>
+        <v>188</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1437,26 +1446,26 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-07</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>rigtorp/awesome-modern-cpp</t>
+          <t>conorluddy/ios-simulator-skill</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>13170</v>
+        <v>1266</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>现代C++资源集合
-【原文】A collection of resources on modern C++</t>
+          <t>为iOS模拟器构建的Claude技能
+【原文】An IOS Simulator Skill for Agents. Use it to optimise their ability to build, run and interact with your apps, and to proxy xcodebuild to save token and context wastage.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1466,12 +1475,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1481,7 +1490,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rigtorp/awesome-modern-cpp</t>
+          <t>https://github.com/conorluddy/ios-simulator-skill</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1490,16 +1499,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>3.43</v>
+        <v>3.58</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1514,21 +1523,21 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>cpp, cpp11, cpp14, cpp17, cpp1z, cpp20</t>
+          <t>agent, agentic-ai, ai-agents, claude, claude-ai, claude-code, claude-skills, claudecode, claudeskills, dx, ios, iossimulator</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2016-03-30</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>3841</v>
+        <v>354</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1540,26 +1549,26 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-05</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>liangdabiao/smy-seedance-storyboard</t>
+          <t>fanbidog/okkmax-web</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>102</v>
+        <v>255</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>生成上美影风格短剧制作文档
-【原文】你给一个故事，它还你一套能直接拿去出图、出视频的上美影短剧制作文档。**  "上美影"= 上海美术电影制片厂，就是《大闹天宫》《天书奇谭》《九色鹿》那种复古手绘动画的味道——概括的造型、手工感的线条、大片平涂的矿物颜料色。</t>
+          <t>独立第三方AI API中转站测评与导航
+【原文】OkkMax —— 独立第三方 AI API 中转站测评与导航:纯度检测(识破偷换模型)、可用性监测、真实用户口碑。</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1569,12 +1578,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1584,7 +1593,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/liangdabiao/smy-seedance-storyboard</t>
+          <t>https://github.com/fanbidog/okkmax-web</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1593,14 +1602,18 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.49</v>
+        <v>2.68</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1613,21 +1626,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>skill, skills</t>
+          <t>api-relay, claude, claude-code, codex, gemini, llm, nextjs, prisma</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1639,26 +1652,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-07</t>
+          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-08</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>3150214587/niehaixia</t>
+          <t>reHackable/awesome-reMarkable</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>62</v>
+        <v>7740</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>5.5</v>
+        <v>17</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>将倪海厦中医思维体系注入AI Agent
-【原文】倪海厦skill · 经方中医AI 将经方大师倪海厦的完整中医思维体系注入 AI Agent</t>
+          <t>关于 reMarkable 平板的精选项目列表。
+【原文】A curated list of projects related to the reMarkable tablet</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1668,12 +1681,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1683,7 +1696,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/3150214587/niehaixia</t>
+          <t>https://github.com/reHackable/awesome-reMarkable</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1692,18 +1705,14 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.79</v>
+        <v>2.43</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1714,60 +1723,64 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, remarkable-tablet</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2018-01-19</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>78</v>
+        <v>3182</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>中医 in:name,description stars:&gt;50</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>alchaincyf/paul-graham-skill</t>
+          <t>pathintegral-institute/mcpm.sh</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>101</v>
+        <v>1011</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>3.9</v>
+        <v>12.5</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>构建Paul Graham认知操作系统
-【原文】Paul Graham的认知操作系统。不是语录合集，是可运行的思维框架。Made with 女娲.skill</t>
+          <t>跨平台 CLI MCP 包管理器和注册库，搜索和配置 MCP 服务器，高级路由和配置功能。
+【原文】CLI MCP package manager &amp; registry for all platforms and all clients. Search &amp; configure MCP servers. Advanced Router &amp; Profile features.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/AI免费池</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>MCP服务/代码库</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1782,7 +1795,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/alchaincyf/paul-graham-skill</t>
+          <t>https://github.com/pathintegral-institute/mcpm.sh</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1791,14 +1804,18 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.55</v>
+        <v>1.79</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1809,66 +1826,69 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>ai, claude-desktop, cli, cline, continue, cursor, goose, homebrew, llm, mcp, package-manager, pip</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>182</v>
+        <v>564</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>女娲 in:name,description stars:&gt;100</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>rigtorp/awesome-lockfree</t>
+          <t>Comfy-Org/comfy-skills</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2071</v>
+        <v>219</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3.8</v>
+        <v>12.2</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>收集无锁与无等待编程的资源列表
-【原文】A collection of resources on wait-free and lock-free programming
-【依据】从描述'A collection of resources on wait-free and lock-free programming'看出</t>
+          <t>Comfy Cloud 产品技能：生成图像、视频、音频和 3D 的 slash 命令，Comfy Cloud 代理的单个事实来源。
+【原文】Comfy Cloud product skills: slash commands for generating images, video, audio, and 3D with Comfy Cloud agents. Single source of truth for the installer and MCP server.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/AI免费池</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/MCP服务</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1878,7 +1898,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rigtorp/awesome-lockfree</t>
+          <t>https://github.com/Comfy-Org/comfy-skills</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1887,11 +1907,11 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.54</v>
+        <v>1.75</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr"/>
@@ -1907,12 +1927,12 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>assembly, concurrency, concurrent-programming, cpp, lock-free, wait-free</t>
+          <t>ai-agents, claude, comfyui, mcp, skills</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2016-03-31</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
@@ -1921,7 +1941,7 @@
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>3840</v>
+        <v>125</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1933,12 +1953,729 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-05</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Tenney95/AI-Canvas-tauri</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>本地优先AI画布，支持AI短剧、图像/视频生成等
+【原文】Local-first AI canvas for visual workflows, AI short drama, image/video generation, storyboarding and asset management. ComfyUI, AI agents, MCP &amp; Blender. 本地优先 AI 画布：AI短剧、AI资产管理、图像/视频生成、分镜制作与视频剪辑。</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>图文产线/视频产线</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务/技能包/架构参考</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Tenney95/AI-Canvas-tauri</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>ai-agent, ai-asset-management, ai-canvas, ai-short-drama, ai-workflow, asset-management, blender, comfyui, generative-ai, image-generation, local-first, mcp</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>plenaryapp/awesome-rss-feeds</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>2816</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>推荐的 RSS 源和本地新闻部分的精选 RSS 源列表（和 OPML 文件）。
+【原文】Awesome RSS feeds - A curated list of RSS feeds (and OPML files) used in Recommended Feeds and local news sections of Plenary - an RSS reader, article downloader and a podcast player app for android</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/plenaryapp/awesome-rss-feeds</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, feed, opml, opml-files, plenary, rss, rss-feed, rss-reader</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>1923</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Meet-Miyani/compose-skill</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Jetpack Compose &amp; Compose Multiplatform 的代理技能。使 Claude Code、Codex、Cursor、Copilot、Gemini CLI 和 OpenCode 编写更好的 Compose。
+【原文】Compose Skill (Compose Kit): agent skills for Jetpack Compose &amp; Compose Multiplatform. Makes Claude Code, Codex, Cursor, Copilot, Gemini CLI and OpenCode write better Compose: MVI, Koin, Navigation 3, Ktor, Room. Tested blind on 5 models in 120 agentic runs.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Meet-Miyani/compose-skill</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, ai-coding-assistant, android, claude-code, claude-skills, codex, compose-multiplatform, compose-skill, cursor, gemini-cli, github-copilot, jetpack-compose</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>krzysztofdudek/ResearcherSkill</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>AI 编码代理成为科学家。30+实验，在您睡觉时进行。
+【原文】One file. Your AI coding agent becomes a scientist. 30+ experiments while you sleep.</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/krzysztofdudek/ResearcherSkill</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>ai-agents, ai-coding, architecture-as-code, autonomous, autoresearch, claude-code, codex, cursor, developer-tools, experimentation, gemini-cli, optimization</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>jghoman/awesome-apache-airflow</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>3934</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Apache Airflow 资源精选列表。
+【原文】Curated list of resources about Apache Airflow</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jghoman/awesome-apache-airflow</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>airflow, apache-airflow, awesome, awesome-list, workflow-management</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>2018-01-11</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>3190</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="150" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>pnp/powerplatform-prompts</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>301</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>提供Power Platform中GPT模型的提示示例集合
+【原文】This repository contains a collection of prompt examples to be used with GPT models in the Power Platform.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/pnp/powerplatform-prompts</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>hacktoberfest</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>1272</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V21" s="6" t="inlineStr">
+        <is>
+          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>xiaomaoJT/TgBot</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>306</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>基于Google Apps Script实现的Telegram机器人
+【原文】telegram机器人，基于Google Apps Script实现。【功能描述】 ❶ 超级群管功能❷ 广告词/敏感词过滤、自动删除/警告❸ 多样化接口查询、XiaoMao数据加工❹ 自定义聊天窗快捷键盘/消息跟随按钮❺ 关键字消息/私聊消息 自动回复❻ 私聊消息/群组消息 捕捉及消息私人推送❼ 私聊消息/群组消息 自动存储  【功能细则】 入群检测、退群检测、入群欢迎、退群欢送、超级群管功能、用户封禁、用户解封、用户禁言、广告词敏感词拦截及自动删除、chatGPT查询、消息私人推送、BOT消息主动回复、自动接口查询及数据加工、自定义键盘、私聊及自动回复、关键字自动回复、消息存储等功能</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/xiaomaoJT/TgBot</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>bot, chatgpt, gas, googleappsscript, telegram, telegram-bot, telegrambot</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>1467</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-07-08</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V15"/>
+  <autoFilter ref="A2:V22"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -61,11 +61,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -114,9 +109,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -484,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-10-06 · 共 20 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-10-07 · 共 13 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,19 +625,19 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>aoci-spec/aoci-code</t>
+          <t>jasonbitsmith/muse-skills</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1170</v>
+        <v>206</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>138.8</v>
+        <v>721</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>代码库和数据库模式的持久、Git 版本化的映射，编码代理在接触任何内容之前读取。本地优先 MCP 服务器 + CLI。
-【原文】A persistent, Git-versioned map of your whole codebase and database schema that coding agents read before they touch anything. Local-first MCP server + CLI in Go: a governed repository index of code knowledge that gives Claude Code, Codex, Cursor, and opencode long-term context, memory, and code intelligence.</t>
+          <t>提供 300 条 Muse 技能，包含痛点与做法
+【原文】300 条 Muse 技能：每条一句话痛点 + 三步做法，点开就能用</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -655,12 +647,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -670,7 +662,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/aoci-spec/aoci-code</t>
+          <t>https://github.com/jasonbitsmith/muse-skills</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,18 +671,14 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>19.83</v>
+        <v>103</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Go</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -701,23 +689,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>agent-memory, agents-md, ai-coding, ai-context, claude-code, code-indexing, code-intelligence, codex, coding-agent, context-engineering, cursor, database-schema</t>
-        </is>
-      </c>
+      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -729,26 +713,26 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-06</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>raullenchai/Rapid-MLX</t>
+          <t>joeseesun/qiaomu-codex-imagegen</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3911</v>
+        <v>107</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>122.8</v>
+        <v>249.7</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>为Apple Silicon构建的OpenAI和Anthropic兼容的LLM推理服务器
-【原文】Rapid-MLX is an open-source (Apache 2.0) OpenAI- and Anthropic-compatible LLM inference server for Apple Silicon, built on MLX, focused on reliable tool calling for coding agents. Up to 4× faster than Apple's MLX (mlx-lm) on the same weights.</t>
+          <t>使任何Agent能够调用Codex内置的图像生成功能
+【原文】让任何 Agent 调用 Codex 内置生图（MCP + CLI + Skill），内置小红书、视频封面、Mondo 海报技巧 · Codex image generation for any agent</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -758,12 +742,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -773,7 +757,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/raullenchai/Rapid-MLX</t>
+          <t>https://github.com/joeseesun/qiaomu-codex-imagegen</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,16 +766,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>17.54</v>
+        <v>35.67</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -806,62 +790,62 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>anthropic-api, apple-silicon, claude-code, coding-agents, continuous-batching, inference-server, llm-inference, llm-server, lm-studio-alternative, local-ai, local-llm, macos</t>
+          <t>agent-skills, claude-code, codex, image-generation, mcp, poster-design, xiaohongshu</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>223</v>
+        <v>3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-06</t>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>datalab-to/lift</t>
+          <t>hexiaofeier/hehe-industry-research-skill-pack</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1168</v>
+        <v>299</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>65.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>快速准确地从文档中提取结构化数据
-【原文】Extract structured data from documents quickly and accurately.</t>
+          <t>提供行业与企业研究技能包，支持行业研究、企业研究、市场分析等模块
+【原文】盒盒原创中文行业与企业研究技能包：1 个总入口协同 13 个专项 Skill，支持完整行业研究或企业研究、以及市场格局、市场规模、企业画像等独立专项模块。</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -876,7 +860,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/datalab-to/lift</t>
+          <t>https://github.com/hexiaofeier/hehe-industry-research-skill-pack</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -885,11 +869,11 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>9.34</v>
+        <v>13.59</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -909,21 +893,21 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>ai, extract, ocr, pdf, python</t>
+          <t>agent-skills, company-research, financial-analysis, industry-analysis, industry-chain-map, industry-research, market-analysis, market-research, market-sizing</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -935,26 +919,26 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-08</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>TNT-Likely/PanWatch</t>
+          <t>atomicstrata/llm-wiki-compiler</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2018</v>
+        <v>2164</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>55.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>A股/港股/美股的AI盯盘、持仓分析、实时提醒与自动报告
-【原文】PanWatch — AI stock monitoring for A-shares, HK &amp; US markets, powered by TradingAgents. Portfolio insights, real-time alerts &amp; automated reports.｜盯盘侠：覆盖 A股/港股/美股的 AI 盯盘、持仓分析、实时提醒与自动报告。</t>
+          <t>将原始知识源转换为相互链接的维基百科
+【原文】The knowledge compiler. Raw sources in, interlinked wiki out. Inspired by Karpathy's LLM Wiki pattern.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -964,7 +948,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>MCP服务</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -979,7 +963,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/TNT-Likely/PanWatch</t>
+          <t>https://github.com/atomicstrata/llm-wiki-compiler</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -988,7 +972,7 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>7.88</v>
+        <v>11.7</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -997,7 +981,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1012,21 +996,21 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>a-share, agent, ai, ai-agent, akshare, deepseek, fastapi, fintech, langgraph, llm, mcp, openai</t>
+          <t>agent-skills, ai-agents, cli, compiler, context-engineering, karpathy, knowledge-base, knowledge-compilation, llm, markdown, mcp, mcp-server</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>256</v>
+        <v>185</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1038,36 +1022,36 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-09-06</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>sampotts/plyr</t>
+          <t>cv-cat/catbus</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>30014</v>
+        <v>110</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>49.4</v>
+        <v>77</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供HTML5、YouTube和Vimeo播放器
-【原文】Deprecated in favour of Video.js 10; security updates only. Simple HTML5, YouTube and Vimeo player.</t>
+          <t>提供统一命令和JSON输出，用于操作多个社交媒体平台
+【原文】一个命令操作小红书、抖音、TikTok、B 站、快手、微博、闲鱼、淘宝、京东、X：统一的命令与 JSON 输出，给人和 AI Agent 用</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1082,7 +1066,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sampotts/plyr</t>
+          <t>https://github.com/cv-cat/catbus</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1091,7 +1075,7 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>7.06</v>
+        <v>11</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -1100,7 +1084,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1115,21 +1099,21 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>deprecated, html5-video, javascript, plyr, videojs, vimeo, youtube</t>
+          <t>ai-agent, bilibili, claude-code, cli, crawler, douyin, jd, kuaishou, nodejs, rednote, spider, taobao</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2015-02-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>4252</v>
+        <v>10</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1141,26 +1125,26 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-07-08</t>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>swjybky/deepwrite</t>
+          <t>alexpate/awesome-design-systems</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>547</v>
+        <v>26069</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>47.2</v>
+        <v>53.5</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>深度专门用于写作的 Harness 智能体。
-【原文】深度专门用于写作的Harness智能体</t>
+          <t>收集各种设计系统的资源
+【原文】💅🏻 ⚒ A collection of awesome design systems</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1185,7 +1169,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/swjybky/deepwrite</t>
+          <t>https://github.com/alexpate/awesome-design-systems</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1194,18 +1178,14 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>6.75</v>
+        <v>7.64</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>Unlicense</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1216,65 +1196,69 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, design-systems, hacktoberfest, pattern-library, ui-library</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2017-06-06</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>81</v>
+        <v>3410</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>JGRFW/comfyui-AICG3D</t>
+          <t>maxritter/pilot-shell</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>128</v>
+        <v>2083</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>ComfyUI + MiniMax H3本地无限长视频生成工作流
-【原文】短剧工作台｜ComfyUI + MiniMax H3 本地无限长视频生成工作流</t>
+          <t>为Claude Code和OpenAI Codex提供专业上下文和工具工程
+【原文】Professional context and harness engineering for Claude Code and OpenAI Codex. Build production-grade software with spec-driven development, TDD, persistent memory, quality gates, code intelligence, human oversight, and end-to-end verification.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1284,7 +1268,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/JGRFW/comfyui-AICG3D</t>
+          <t>https://github.com/maxritter/pilot-shell</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1293,16 +1277,16 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>5.33</v>
+        <v>5.88</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1317,62 +1301,62 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>ai-video, comfyui, comfyui-nodes, custom-nodes, gguf, minimax-h3, prompt-engineering, text-to-video</t>
+          <t>agent-skills, agentic-engineering, ai-coding, anthropic, claude-code, code-quality, code-review, codex, codex-cli, coding-agents, context-engineering, developer-tools</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>24</v>
+        <v>354</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-08</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>google-gemma/gemma-skills</t>
+          <t>YanjieZe/awesome-humanoid-robot-learning</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1000</v>
+        <v>2797</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>37.2</v>
+        <v>27.7</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>为 Gemma 和模型/代理交互的技能。
-【原文】Skills for the Gemma and model/agent interactions</t>
+          <t>提供类人机器人学习领域的论文列表
+【原文】A Paper List for Humanoid Robot Learning.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1387,7 +1371,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/google-gemma/gemma-skills</t>
+          <t>https://github.com/YanjieZe/awesome-humanoid-robot-learning</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1396,11 +1380,11 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5.32</v>
+        <v>3.96</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1418,14 +1402,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>gemma, skills</t>
-        </is>
-      </c>
+      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
@@ -1434,7 +1414,7 @@
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>188</v>
+        <v>707</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1446,26 +1426,26 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-06</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>conorluddy/ios-simulator-skill</t>
+          <t>ChromeDevTools/awesome-chrome-devtools</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1266</v>
+        <v>7157</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>25.1</v>
+        <v>13</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>为iOS模拟器构建的Claude技能
-【原文】An IOS Simulator Skill for Agents. Use it to optimise their ability to build, run and interact with your apps, and to proxy xcodebuild to save token and context wastage.</t>
+          <t>收集Chrome DevTools和DevTools Protocol生态系统中的工具和资源
+【原文】Awesome tooling and resources in the Chrome DevTools &amp; DevTools Protocol ecosystem</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1475,7 +1455,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1490,7 +1470,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/conorluddy/ios-simulator-skill</t>
+          <t>https://github.com/ChromeDevTools/awesome-chrome-devtools</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1499,18 +1479,14 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>3.58</v>
+        <v>1.85</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1523,12 +1499,12 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, ai-agents, claude, claude-ai, claude-code, claude-skills, claudecode, claudeskills, dx, ios, iossimulator</t>
+          <t>awesome, awesome-list</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2016-03-08</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1537,7 +1513,7 @@
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>354</v>
+        <v>3865</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1549,26 +1525,26 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-06</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>fanbidog/okkmax-web</t>
+          <t>menkesu/awesome-pm-skills</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>255</v>
+        <v>429</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>18.8</v>
+        <v>11.9</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>独立第三方AI API中转站测评与导航
-【原文】OkkMax —— 独立第三方 AI API 中转站测评与导航:纯度检测(识破偷换模型)、可用性监测、真实用户口碑。</t>
+          <t>提供基于 Lenny's Podcast 的产品管理工作流程
+【原文】Product management workflows grounded in Lenny's Podcast, for Claude Code, Codex, and Cursor.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1578,12 +1554,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1593,7 +1569,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/fanbidog/okkmax-web</t>
+          <t>https://github.com/menkesu/awesome-pm-skills</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1602,16 +1578,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.68</v>
+        <v>1.7</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1626,52 +1602,52 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>api-relay, claude, claude-code, codex, gemini, llm, nextjs, prisma</t>
+          <t>ai, awesome-list, claude, cursor, lenny-rachitsky, pm-skills, product-management</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>95</v>
+        <v>252</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-08</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>reHackable/awesome-reMarkable</t>
+          <t>lingxling/awesome-skills-cn</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>7740</v>
+        <v>299</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>17</v>
+        <v>8.9</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>关于 reMarkable 平板的精选项目列表。
-【原文】A curated list of projects related to the reMarkable tablet</t>
+          <t>提供7000+Skills的中文学习版和教程
+【原文】热门Skills中文cn学习版+教程，提供7000+Skills，集成claude skills (11w+Star) | awesome-openclaw-skills (4w+Star) | ui-ux-pro-max-skill (4w+Star)等10余个热门Skill项目</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1681,7 +1657,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1696,7 +1672,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/reHackable/awesome-reMarkable</t>
+          <t>https://github.com/lingxling/awesome-skills-cn</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1705,14 +1681,18 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>2.43</v>
+        <v>1.27</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1725,21 +1705,21 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, remarkable-tablet</t>
+          <t>agents, anthropic, antigravity, awesome-list, chinese, claude, claude-skills, huggingface, obsidian, openai, openclaw, scientific</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2018-01-19</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>3182</v>
+        <v>236</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1751,36 +1731,36 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-06</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>pathintegral-institute/mcpm.sh</t>
+          <t>rguo12/awesome-causality-algorithms</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>1011</v>
+        <v>3290</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>跨平台 CLI MCP 包管理器和注册库，搜索和配置 MCP 服务器，高级路由和配置功能。
-【原文】CLI MCP package manager &amp; registry for all platforms and all clients. Search &amp; configure MCP servers. Advanced Router &amp; Profile features.</t>
+          <t>提供学习因果关系的算法索引
+【原文】An index of algorithms for learning causality with data</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>视频产线/AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1795,7 +1775,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pathintegral-institute/mcpm.sh</t>
+          <t>https://github.com/rguo12/awesome-causality-algorithms</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1804,18 +1784,14 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.79</v>
+        <v>1.12</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+      <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1828,21 +1804,21 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>ai, claude-desktop, cli, cline, continue, cursor, goose, homebrew, llm, mcp, package-manager, pip</t>
+          <t>awesome, baselines, causal-inference, causality, causality-algorithms, causality-analysis, learning-to-rank, multilabel-classification, recommender-system, unconfoundedness-assumption</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>564</v>
+        <v>2940</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1854,41 +1830,41 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-06</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Comfy-Org/comfy-skills</t>
+          <t>mfoud444/ollamafreeapi</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>219</v>
+        <v>320</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>12.2</v>
+        <v>4.5</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Comfy Cloud 产品技能：生成图像、视频、音频和 3D 的 slash 命令，Comfy Cloud 代理的单个事实来源。
-【原文】Comfy Cloud product skills: slash commands for generating images, video, audio, and 3D with Comfy Cloud agents. Single source of truth for the installer and MCP server.</t>
+          <t>提供Ollama LLMs的免费分布式API访问
+【原文】OllamaFreeAPI: Free Distributed API for Ollama LLMs  Public gateway to our managed Ollama servers with: - Zero-configuration access to 50+ models - Auto load-balanced across global nodes - Free tier with no API keys required - Built on ollama-python</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>视频产线/AI免费池</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>技能包/MCP服务</t>
+          <t>MCP服务</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1898,7 +1874,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Comfy-Org/comfy-skills</t>
+          <t>https://github.com/mfoud444/ollamafreeapi</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1907,14 +1883,18 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>1.75</v>
+        <v>0.64</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr"/>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1927,24 +1907,24 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, claude, comfyui, mcp, skills</t>
+          <t>ai-api, deepseek, free-ai, free-ai-api, free-api, llama, llm, mistral, ollama</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>125</v>
+        <v>499</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
@@ -1953,729 +1933,12 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Tenney95/AI-Canvas-tauri</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>201</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>本地优先AI画布，支持AI短剧、图像/视频生成等
-【原文】Local-first AI canvas for visual workflows, AI short drama, image/video generation, storyboarding and asset management. ComfyUI, AI agents, MCP &amp; Blender. 本地优先 AI 画布：AI短剧、AI资产管理、图像/视频生成、分镜制作与视频剪辑。</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>图文产线/视频产线</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>MCP服务/技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/Tenney95/AI-Canvas-tauri</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>ai-agent, ai-asset-management, ai-canvas, ai-short-drama, ai-workflow, asset-management, blender, comfyui, generative-ai, image-generation, local-first, mcp</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>plenaryapp/awesome-rss-feeds</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>2816</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>推荐的 RSS 源和本地新闻部分的精选 RSS 源列表（和 OPML 文件）。
-【原文】Awesome RSS feeds - A curated list of RSS feeds (and OPML files) used in Recommended Feeds and local news sections of Plenary - an RSS reader, article downloader and a podcast player app for android</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/plenaryapp/awesome-rss-feeds</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, feed, opml, opml-files, plenary, rss, rss-feed, rss-reader</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>1923</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Meet-Miyani/compose-skill</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Jetpack Compose &amp; Compose Multiplatform 的代理技能。使 Claude Code、Codex、Cursor、Copilot、Gemini CLI 和 OpenCode 编写更好的 Compose。
-【原文】Compose Skill (Compose Kit): agent skills for Jetpack Compose &amp; Compose Multiplatform. Makes Claude Code, Codex, Cursor, Copilot, Gemini CLI and OpenCode write better Compose: MVI, Koin, Navigation 3, Ktor, Room. Tested blind on 5 models in 120 agentic runs.</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/Meet-Miyani/compose-skill</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, ai-coding-assistant, android, claude-code, claude-skills, codex, compose-multiplatform, compose-skill, cursor, gemini-cli, github-copilot, jetpack-compose</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="150" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>krzysztofdudek/ResearcherSkill</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>AI 编码代理成为科学家。30+实验，在您睡觉时进行。
-【原文】One file. Your AI coding agent becomes a scientist. 30+ experiments while you sleep.</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/krzysztofdudek/ResearcherSkill</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>ai-agents, ai-coding, architecture-as-code, autonomous, autoresearch, claude-code, codex, cursor, developer-tools, experimentation, gemini-cli, optimization</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="150" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>jghoman/awesome-apache-airflow</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>3934</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Apache Airflow 资源精选列表。
-【原文】Curated list of resources about Apache Airflow</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/jghoman/awesome-apache-airflow</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>airflow, apache-airflow, awesome, awesome-list, workflow-management</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>2018-01-11</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>3190</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V20" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="150" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>pnp/powerplatform-prompts</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>301</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>提供Power Platform中GPT模型的提示示例集合
-【原文】This repository contains a collection of prompt examples to be used with GPT models in the Power Platform.</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/pnp/powerplatform-prompts</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>hacktoberfest</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>2023-04-13</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>1272</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V21" s="6" t="inlineStr">
-        <is>
-          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="150" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>xiaomaoJT/TgBot</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>306</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>基于Google Apps Script实现的Telegram机器人
-【原文】telegram机器人，基于Google Apps Script实现。【功能描述】 ❶ 超级群管功能❷ 广告词/敏感词过滤、自动删除/警告❸ 多样化接口查询、XiaoMao数据加工❹ 自定义聊天窗快捷键盘/消息跟随按钮❺ 关键字消息/私聊消息 自动回复❻ 私聊消息/群组消息 捕捉及消息私人推送❼ 私聊消息/群组消息 自动存储  【功能细则】 入群检测、退群检测、入群欢迎、退群欢送、超级群管功能、用户封禁、用户解封、用户禁言、广告词敏感词拦截及自动删除、chatGPT查询、消息私人推送、BOT消息主动回复、自动接口查询及数据加工、自定义键盘、私聊及自动回复、关键字自动回复、消息存储等功能</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/xiaomaoJT/TgBot</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>bot, chatgpt, gas, googleappsscript, telegram, telegram-bot, telegrambot</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>1467</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V22" s="6" t="inlineStr">
-        <is>
-          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-07-08</t>
+          <t>free llm api in:name,description stars:&gt;200 pushed:&gt;2026-07-09</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V22"/>
+  <autoFilter ref="A2:V15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -109,6 +114,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -476,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -506,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-10-07 · 共 13 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-10-08 · 共 16 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -625,34 +633,35 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>jasonbitsmith/muse-skills</t>
+          <t>QingYunA/answer-me-with-html</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>206</v>
+        <v>2182</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>721</v>
+        <v>2545.7</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>提供 300 条 Muse 技能，包含痛点与做法
-【原文】300 条 Muse 技能：每条一句话痛点 + 三步做法，点开就能用</t>
+          <t>使用HTML回答复杂问题的AI技能。
+【原文】Answer me with HTML — an agent skill that answers hard questions with a one-page HTML you can actually read. 让 AI Agent 用一页 HTML 回答复杂问题。
+【依据】agent-skill, ai-agent, claude-code, claude-skills</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -662,7 +671,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jasonbitsmith/muse-skills</t>
+          <t>https://github.com/QingYunA/answer-me-with-html</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -671,14 +680,18 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>103</v>
+        <v>363.67</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -689,60 +702,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>agent-skill, ai-agent, claude-code, claude-code-skill, claude-skill, claude-skills, cli, diagram, explainer, html, llm, ste100</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-07</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>joeseesun/qiaomu-codex-imagegen</t>
+          <t>yihui-dev/awesome-opus5-5-videos</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>107</v>
+        <v>2828</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>249.7</v>
+        <v>1799.6</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>使任何Agent能够调用Codex内置的图像生成功能
-【原文】让任何 Agent 调用 Codex 内置生图（MCP + CLI + Skill），内置小红书、视频封面、Mondo 海报技巧 · Codex image generation for any agent</t>
+          <t>使用Claude Opus 5.5制作的病毒视频和背后的提示词。
+【原文】A growing collection of viral videos made with Claude Opus 5.5 and the prompts behind them. Watch each original next to a live remake on Skillry. Updated regularly.
+【依据】ai-video, awesome, claude, creative-coding</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -757,7 +775,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/joeseesun/qiaomu-codex-imagegen</t>
+          <t>https://github.com/yihui-dev/awesome-opus5-5-videos</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -766,18 +784,14 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>35.67</v>
+        <v>257.09</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -790,21 +804,21 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, claude-code, codex, image-generation, mcp, poster-design, xiaohongshu</t>
+          <t>ai-video, awesome, awesome-list, claude, claude-opus, creative-coding, motion-graphics, prompts, threejs</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
@@ -816,36 +830,37 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:xiaohongshu stars:&gt;100</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>hexiaofeier/hehe-industry-research-skill-pack</t>
+          <t>feder-cr/invisible_dots</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>299</v>
+        <v>31819</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>95.09999999999999</v>
+        <v>280.1</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>提供行业与企业研究技能包，支持行业研究、企业研究、市场分析等模块
-【原文】盒盒原创中文行业与企业研究技能包：1 个总入口协同 13 个专项 Skill，支持完整行业研究或企业研究、以及市场格局、市场规模、企业画像等独立专项模块。</t>
+          <t>开源、自托管的OpenAI Dots替代品，用于自动化和自主代理。
+【原文】Open-source, self-hosted alternative to OpenAI Dots, Grok Bot. Built to be undetectable by anti-bot systems.
+【依据】agent-skills, agentic-ai, ai-agent, ai-assistants</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -860,7 +875,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/hexiaofeier/hehe-industry-research-skill-pack</t>
+          <t>https://github.com/feder-cr/invisible_dots</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -869,7 +884,7 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>13.59</v>
+        <v>40.02</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -878,7 +893,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -893,24 +908,24 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, company-research, financial-analysis, industry-analysis, industry-chain-map, industry-research, market-analysis, market-research, market-sizing</t>
+          <t>agent-skills, agentic-ai, ai-agent, ai-agents, ai-assistant, antidetect-browser, automation, autonomous-agents, browser-automation, claude-cowork, computer-use, computer-use-agent</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>22</v>
+        <v>795</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
@@ -919,26 +934,27 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-07</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>atomicstrata/llm-wiki-compiler</t>
+          <t>undefined-ui/second-brain-os</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2164</v>
+        <v>1009</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>227.8</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>将原始知识源转换为相互链接的维基百科
-【原文】The knowledge compiler. Raw sources in, interlinked wiki out. Inspired by Karpathy's LLM Wiki pattern.</t>
+          <t>构建个人知识库的AI第二大脑，支持Claude Code和Obsidian。
+【原文】An AI second brain that maintains itself. Full guide, starter vault, agent skills and scripts for a self-organizing knowledge base in Claude Code and Obsidian.
+【依据】agent-skills, knowledge-management, personal-knowledge-base</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -948,7 +964,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MCP服务</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -963,7 +979,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/atomicstrata/llm-wiki-compiler</t>
+          <t>https://github.com/undefined-ui/second-brain-os</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -972,7 +988,7 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>11.7</v>
+        <v>32.55</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -981,7 +997,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -996,12 +1012,12 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, cli, compiler, context-engineering, karpathy, knowledge-base, knowledge-compilation, llm, markdown, mcp, mcp-server</t>
+          <t>agent-skills, ai-agents, claude, claude-code, claude-skills, knowledge-graph, knowledge-management, llm, mcp, obsidian, personal-knowledge-base, pkm</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1010,43 +1026,44 @@
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-07</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>cv-cat/catbus</t>
+          <t>carnot-tech/jinba-consulting-pptx-skill</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>110</v>
+        <v>1136</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>77</v>
+        <v>220.9</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供统一命令和JSON输出，用于操作多个社交媒体平台
-【原文】一个命令操作小红书、抖音、TikTok、B 站、快手、微博、闲鱼、淘宝、京东、X：统一的命令与 JSON 输出，给人和 AI Agent 用</t>
+          <t>提供让AI生成高质量PPTX的技能
+【原文】AIにまじなPPTXを作らせる Claude Code / Codex スキル
+【依据】描述“AIにまじなPPTXを作らせる Claude Code / Codex スキル”</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1066,7 +1083,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cv-cat/catbus</t>
+          <t>https://github.com/carnot-tech/jinba-consulting-pptx-skill</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1075,7 +1092,7 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>11</v>
+        <v>31.56</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -1084,7 +1101,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1097,14 +1114,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>ai-agent, bilibili, claude-code, cli, crawler, douyin, jd, kuaishou, nodejs, rednote, spider, taobao</t>
-        </is>
-      </c>
+      <c r="P7" s="6" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -1113,7 +1126,7 @@
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1125,36 +1138,37 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:xiaohongshu stars:&gt;100</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>alexpate/awesome-design-systems</t>
+          <t>MemTensor/memmy-agent</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>26069</v>
+        <v>2073</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>53.5</v>
+        <v>172.8</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>收集各种设计系统的资源
-【原文】💅🏻 ⚒ A collection of awesome design systems</t>
+          <t>个人AI代理和本地记忆中心，支持多个AI代理共享记忆。
+【原文】🍙  A personal AI agent &amp; local memory hub for all AI agents, gives every AI one shared, fully controlled memory and persistent context — all AI remember the same you. Now supports Claude Code, Codex, OpenClaw and Hermes Agent etc.
+【依据】agent, agentic-ai, ai-agents, chatgpt</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1169,7 +1183,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/alexpate/awesome-design-systems</t>
+          <t>https://github.com/MemTensor/memmy-agent</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1178,14 +1192,18 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>7.64</v>
+        <v>24.68</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Unlicense</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1198,67 +1216,68 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, design-systems, hacktoberfest, pattern-library, ui-library</t>
+          <t>agent, agentic-ai, ai-agents, chatgpt, claude-code, cli, codex, cursor, desktop-app, desktop-pet, dsh-plugin, hermes-agent</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>3410</v>
+        <v>84</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-07</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>maxritter/pilot-shell</t>
+          <t>joeseesun/opus-video-prompts</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2083</v>
+        <v>205</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>41.2</v>
+        <v>130.5</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>为Claude Code和OpenAI Codex提供专业上下文和工具工程
-【原文】Professional context and harness engineering for Claude Code and OpenAI Codex. Build production-grade software with spec-driven development, TDD, persistent memory, quality gates, code intelligence, human oversight, and end-to-end verification.</t>
+          <t>使用Claude Opus 5.5代码生成视频的案例和提示词。
+【原文】Claude Opus 5.5 用代码生成视频：全网案例与可直接复制的提示词 | Copy-ready prompts &amp; 54 cases of Opus 5.5 code-rendered videos
+【依据】claude, motion-graphics, opus, prompts, video-generation</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1268,7 +1287,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/maxritter/pilot-shell</t>
+          <t>https://github.com/joeseesun/opus-video-prompts</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1277,18 +1296,14 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>5.88</v>
+        <v>18.64</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1301,67 +1316,68 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, agentic-engineering, ai-coding, anthropic, claude-code, code-quality, code-review, codex, codex-cli, coding-agents, context-engineering, developer-tools</t>
+          <t>claude, claude-code, motion-graphics, opus, prompts, remotion, video-generation</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>354</v>
+        <v>11</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-07</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>YanjieZe/awesome-humanoid-robot-learning</t>
+          <t>Loopera-ai/loopera</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2797</v>
+        <v>536</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>27.7</v>
+        <v>125.1</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供类人机器人学习领域的论文列表
-【原文】A Paper List for Humanoid Robot Learning.</t>
+          <t>面向基本面因子研究的智能体，具有证据门控验证和研究记忆。
+【原文】面向基本面因子研究的智能体-A hypothesis-driven AI agent for fundamental factor research, with evidence-gated validation and research memory.
+【依据】ai, ai-agent, quant</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1371,7 +1387,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/YanjieZe/awesome-humanoid-robot-learning</t>
+          <t>https://github.com/Loopera-ai/loopera</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1380,18 +1396,14 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>3.96</v>
+        <v>17.87</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1402,65 +1414,70 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>ai, ai-agent, quant</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>707</v>
+        <v>30</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-07</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ChromeDevTools/awesome-chrome-devtools</t>
+          <t>metasequoiaime/msime</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>7157</v>
+        <v>512</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>13</v>
+        <v>99.5</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>收集Chrome DevTools和DevTools Protocol生态系统中的工具和资源
-【原文】Awesome tooling and resources in the Chrome DevTools &amp; DevTools Protocol ecosystem</t>
+          <t>跨平台中文输入法，支持Android、iOS、macOS、Linux、Windows与HarmonyOS。
+【原文】下一代跨平台水杉输入法（MSIME）：面向 Android、iOS、macOS、Linux、Windows 与 HarmonyOS 的多平台中文输入法，使用共享输入引擎与各平台原生宿主。
+【依据】ime, input-method, inputmethodkit, ios, macos, pinyin</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>代码库/可部署服务</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1470,7 +1487,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ChromeDevTools/awesome-chrome-devtools</t>
+          <t>https://github.com/metasequoiaime/msime</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1479,14 +1496,18 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>1.85</v>
+        <v>14.22</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr"/>
+          <t>GPL-3.0</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1499,52 +1520,53 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list</t>
+          <t>android, chinese, cpp, harmonyos, ime, input-method, inputmethodkit, ios, linux, macos, pinyin, rust</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2016-03-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>3865</v>
+        <v>36</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-07</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>menkesu/awesome-pm-skills</t>
+          <t>Leanmcp/gateway-skills</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>429</v>
+        <v>2110</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>11.9</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>提供基于 Lenny's Podcast 的产品管理工作流程
-【原文】Product management workflows grounded in Lenny's Podcast, for Claude Code, Codex, and Cursor.</t>
+          <t>在仪表板中清晰查看Claude代码日志
+【原文】See your claude code logs in clear details in your dashboard
+【依据】描述“See your claude code logs in clear details in your dashboard”</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1559,7 +1581,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1569,7 +1591,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/menkesu/awesome-pm-skills</t>
+          <t>https://github.com/Leanmcp/gateway-skills</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1578,11 +1600,11 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1.7</v>
+        <v>11.05</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1600,23 +1622,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>ai, awesome-list, claude, cursor, lenny-rachitsky, pm-skills, product-management</t>
-        </is>
-      </c>
+      <c r="P12" s="6" t="inlineStr"/>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>252</v>
+        <v>191</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1628,36 +1646,37 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-07</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>lingxling/awesome-skills-cn</t>
+          <t>Achno/gowall</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>299</v>
+        <v>2314</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>8.9</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供7000+Skills的中文学习版和教程
-【原文】热门Skills中文cn学习版+教程，提供7000+Skills，集成claude skills (11w+Star) | awesome-openclaw-skills (4w+Star) | ui-ux-pro-max-skill (4w+Star)等10余个热门Skill项目</t>
+          <t>图像处理工具，包括颜色提取、OCR、图像压缩等。
+【原文】A tool to convert a Wallpaper's color scheme / palette, OCR with VLM's Traditional &amp; Hybrid, Image Compression ,color palette extraction,  image upsacling with Adversarial Networks  and more image processing features.
+【依据】background-removal, color-extractor, color-palette, image-processing</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>代码库/可部署服务</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1672,7 +1691,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lingxling/awesome-skills-cn</t>
+          <t>https://github.com/Achno/gowall</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1681,7 +1700,7 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1.27</v>
+        <v>2.86</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -1690,7 +1709,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1705,12 +1724,12 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>agents, anthropic, antigravity, awesome-list, chinese, claude, claude-skills, huggingface, obsidian, openai, openclaw, scientific</t>
+          <t>background-removal, cli, color-extractor, color-palette, color-scheme, compression, go, image, image-converter, image-processing, ocr, pixel-art</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -1719,7 +1738,7 @@
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>236</v>
+        <v>808</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1731,26 +1750,27 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-07</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>rguo12/awesome-causality-algorithms</t>
+          <t>tuya/tuya-openclaw-skills</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>3290</v>
+        <v>479</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>提供学习因果关系的算法索引
-【原文】An index of algorithms for learning causality with data</t>
+          <t>为Tuya智能生态系统开发的AI技能库，例如设备控制
+【原文】Tuya AI Skill Library for OpenClaw/TuyaClaw - An AI-driven skill set built for the development of Tuya's smart ecosystem (e.g., device control).
+【依据】描述“Tuya AI Skill Library for OpenClaw/TuyaClaw”</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1760,7 +1780,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1775,7 +1795,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rguo12/awesome-causality-algorithms</t>
+          <t>https://github.com/tuya/tuya-openclaw-skills</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1784,14 +1804,18 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.12</v>
+        <v>2.28</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1802,14 +1826,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>awesome, baselines, causal-inference, causality, causality-algorithms, causality-analysis, learning-to-rank, multilabel-classification, recommender-system, unconfoundedness-assumption</t>
-        </is>
-      </c>
+      <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
@@ -1818,7 +1838,7 @@
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2940</v>
+        <v>210</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1830,36 +1850,37 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-07</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>mfoud444/ollamafreeapi</t>
+          <t>xialeiliu/Awesome-Incremental-Learning</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>320</v>
+        <v>4530</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>4.5</v>
+        <v>10.7</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>提供Ollama LLMs的免费分布式API访问
-【原文】OllamaFreeAPI: Free Distributed API for Ollama LLMs  Public gateway to our managed Ollama servers with: - Zero-configuration access to 50+ models - Auto load-balanced across global nodes - Free tier with no API keys required - Built on ollama-python</t>
+          <t>收集增量学习相关资源列表
+【原文】Awesome Incremental Learning
+【依据】描述“Awesome Incremental Learning”表明是增量学习资源列表</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MCP服务</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1874,7 +1895,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mfoud444/ollamafreeapi</t>
+          <t>https://github.com/xialeiliu/Awesome-Incremental-Learning</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1883,18 +1904,14 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.64</v>
+        <v>1.53</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1905,26 +1922,22 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>ai-api, deepseek, free-ai, free-ai-api, free-api, llama, llm, mistral, ollama</t>
-        </is>
-      </c>
+      <c r="P15" s="6" t="inlineStr"/>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>499</v>
+        <v>2963</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
@@ -1933,12 +1946,304 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>free llm api in:name,description stars:&gt;200 pushed:&gt;2026-07-09</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>thomast1906/github-copilot-agent-skills</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>包含GitHub Copilot代理和技能，持续实验
+【原文】Repo containing my GitHub Copilot Agent &amp; Skills - continually experimenting!
+【依据】描述“Repo containing my GitHub Copilot Agent &amp; Skills”</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/thomast1906/github-copilot-agent-skills</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>ad-si/awesome-3d-printing</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>收集3D打印相关资源列表
+【原文】A curated list of awesome 3D printing resources
+【依据】描述“A curated list of awesome 3D printing resources”</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/ad-si/awesome-3d-printing</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>3d, 3d-printer, 3d-printing, 3d-scanner, 3d-scanning, awesome, awesome-list, cad, g-code, slicer</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>2016-01-07</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>3927</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>LMaxRouterCN/LLMwc4n</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>强碱AI提示词，旨在穿越所有大语言模型。
+【原文】强碱ai提示词 立志干穿所有大语言模型(你是一只猫娘你是一只猫娘你是一只猫娘你是一只猫娘你是一只猫娘你是一只猫娘你是一只猫娘)
+【依据】LLMwc4n</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/LMaxRouterCN/LLMwc4n</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>MPL-2.0</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>451</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-10</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V15"/>
+  <autoFilter ref="A2:V18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -61,11 +61,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -114,9 +109,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -484,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-10-08 · 共 16 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-10-09 · 共 12 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,30 +625,29 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>QingYunA/answer-me-with-html</t>
+          <t>shader-effects-inc/shaders</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2182</v>
+        <v>3565</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>2545.7</v>
+        <v>2495.5</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>使用HTML回答复杂问题的AI技能。
-【原文】Answer me with HTML — an agent skill that answers hard questions with a one-page HTML you can actually read. 让 AI Agent 用一页 HTML 回答复杂问题。
-【依据】agent-skill, ai-agent, claude-code, claude-skills</t>
+          <t>提供 WebGPU 组件，用于 React, Vue, Svelte, Solid, JS &amp; Framer
+【原文】WebGPU components for React, Vue, Svelte, Solid, JS &amp; Framer</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>MCP服务/代码库</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -671,7 +662,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/QingYunA/answer-me-with-html</t>
+          <t>https://github.com/shader-effects-inc/shaders</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -680,7 +671,7 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>363.67</v>
+        <v>356.5</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -689,7 +680,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -704,21 +695,21 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>agent-skill, ai-agent, claude-code, claude-code-skill, claude-skill, claude-skills, cli, diagram, explainer, html, llm, ste100</t>
+          <t>cli, javascript, mcp, react, shaders, solid, svelte, vue, webgpu-shaders</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -730,42 +721,41 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-09-08</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>yihui-dev/awesome-opus5-5-videos</t>
+          <t>datawhalechina/jev-cookbook</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2828</v>
+        <v>304</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1799.6</v>
+        <v>112</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>使用Claude Opus 5.5制作的病毒视频和背后的提示词。
-【原文】A growing collection of viral videos made with Claude Opus 5.5 and the prompts behind them. Watch each original next to a live remake on Skillry. Updated regularly.
-【依据】ai-video, awesome, claude, creative-coding</t>
+          <t>提供 Jev 入门教程和实战配方，全面掌握 System One 判断模型的开发范式
+【原文】⚡ 适合中国宝宝的 Jev 入门教程｜手把手带你了解关于 Jev 的一切——Jupyter Notebook 轻松实验，从三种问题原语到 18 篇实战配方、语音智能家居、模型评测与本地微调，全面掌握 System One 判断模型的开发范式</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>方剂知识线</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -775,7 +765,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yihui-dev/awesome-opus5-5-videos</t>
+          <t>https://github.com/datawhalechina/jev-cookbook</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -784,14 +774,18 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>257.09</v>
+        <v>16</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr"/>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -802,70 +796,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>ai-video, awesome, awesome-list, claude, claude-opus, creative-coding, motion-graphics, prompts, threejs</t>
-        </is>
-      </c>
+      <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-08</t>
+          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>feder-cr/invisible_dots</t>
+          <t>SichengLong26/deepresearch_agent_harness</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>31819</v>
+        <v>221</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>280.1</v>
+        <v>28.1</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>开源、自托管的OpenAI Dots替代品，用于自动化和自主代理。
-【原文】Open-source, self-hosted alternative to OpenAI Dots, Grok Bot. Built to be undetectable by anti-bot systems.
-【依据】agent-skills, agentic-ai, ai-agent, ai-assistants</t>
+          <t>多智能体深度研究系统，融合私有知识图谱与联网搜索，含 Harness 编排、持久化 Memory 与受控自进化 Skills
+【原文】多智能体深度研究系统，融合私有知识图谱(GraphRAG)与联网搜索，含 Harness 编排、持久化 Memory 与受控自进化 Skills，FastAPI + React 全栈。</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>AI免费池/RAG检索线</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>架构参考</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -875,7 +864,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/feder-cr/invisible_dots</t>
+          <t>https://github.com/SichengLong26/deepresearch_agent_harness</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -884,16 +873,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>40.02</v>
+        <v>4.02</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -906,14 +895,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, agentic-ai, ai-agent, ai-agents, ai-assistant, antidetect-browser, automation, autonomous-agents, browser-automation, claude-cowork, computer-use, computer-use-agent</t>
-        </is>
-      </c>
+      <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -922,49 +907,48 @@
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>795</v>
+        <v>55</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-09-08</t>
+          <t>知识图谱 in:name,description stars:&gt;200 pushed:&gt;2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>undefined-ui/second-brain-os</t>
+          <t>FloWritesCode/fwc-swiftui-skills</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1009</v>
+        <v>388</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>227.8</v>
+        <v>23.4</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>构建个人知识库的AI第二大脑，支持Claude Code和Obsidian。
-【原文】An AI second brain that maintains itself. Full guide, starter vault, agent skills and scripts for a self-organizing knowledge base in Claude Code and Obsidian.
-【依据】agent-skills, knowledge-management, personal-knowledge-base</t>
+          <t>提供用于现代 SwiftUI 开发的编码代理技能。
+【原文】Coding Agent Skills for modern SwiftUI development</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -979,7 +963,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/undefined-ui/second-brain-os</t>
+          <t>https://github.com/FloWritesCode/fwc-swiftui-skills</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -988,18 +972,14 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>32.55</v>
+        <v>3.34</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1010,23 +990,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, ai-agents, claude, claude-code, claude-skills, knowledge-graph, knowledge-management, llm, mcp, obsidian, personal-knowledge-base, pkm</t>
-        </is>
-      </c>
+      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1038,27 +1014,26 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-09-08</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>carnot-tech/jinba-consulting-pptx-skill</t>
+          <t>mbasso/awesome-wasm</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1136</v>
+        <v>9649</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>220.9</v>
+        <v>19.5</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供让AI生成高质量PPTX的技能
-【原文】AIにまじなPPTXを作らせる Claude Code / Codex スキル
-【依据】描述“AIにまじなPPTXを作らせる Claude Code / Codex スキル”</t>
+          <t>提供 WebAssembly 生态系统资源的精选列表
+【原文】😎 Curated list of awesome things regarding the WebAssembly (wasm) ecosystem.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1068,7 +1043,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1083,7 +1058,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/carnot-tech/jinba-consulting-pptx-skill</t>
+          <t>https://github.com/mbasso/awesome-wasm</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1092,18 +1067,14 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>31.56</v>
+        <v>2.79</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1114,19 +1085,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, awesome-wasm, awesome-webassembly, list, lists, resources, wasm, webassembly</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2017-04-25</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>36</v>
+        <v>3454</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1138,27 +1113,26 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-08</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MemTensor/memmy-agent</t>
+          <t>ZJU4EmbodiedAI/EmbodiedSkills</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2073</v>
+        <v>237</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>172.8</v>
+        <v>13.5</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>个人AI代理和本地记忆中心，支持多个AI代理共享记忆。
-【原文】🍙  A personal AI agent &amp; local memory hub for all AI agents, gives every AI one shared, fully controlled memory and persistent context — all AI remember the same you. Now supports Claude Code, Codex, OpenClaw and Hermes Agent etc.
-【依据】agent, agentic-ai, ai-agents, chatgpt</t>
+          <t>为 RoboTwin 提供模块化 embodied-agent 运行时，结合 VLM-based grounding 和 subgoal scheduling
+【原文】A modular embodied-agent runtime for RoboTwin, combining VLM-based grounding, subgoal scheduling, OpenPI/pi0.5 action generation, and execution-time verification.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1168,12 +1142,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>架构参考</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1183,7 +1157,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MemTensor/memmy-agent</t>
+          <t>https://github.com/ZJU4EmbodiedAI/EmbodiedSkills</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1192,16 +1166,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>24.68</v>
+        <v>1.93</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1214,70 +1188,64 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>agent, agentic-ai, ai-agents, chatgpt, claude-code, cli, codex, cursor, desktop-app, desktop-pet, dsh-plugin, hermes-agent</t>
-        </is>
-      </c>
+      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-08</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>joeseesun/opus-video-prompts</t>
+          <t>MichengAI/dsh-agency-agents</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>205</v>
+        <v>104</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>130.5</v>
+        <v>13.2</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>使用Claude Opus 5.5代码生成视频的案例和提示词。
-【原文】Claude Opus 5.5 用代码生成视频：全网案例与可直接复制的提示词 | Copy-ready prompts &amp; 54 cases of Opus 5.5 code-rendered videos
-【依据】claude, motion-graphics, opus, prompts, video-generation</t>
+          <t>为 DeepSeek Harness 提供 321 名可召唤的专业智能体</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1287,7 +1255,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/joeseesun/opus-video-prompts</t>
+          <t>https://github.com/MichengAI/dsh-agency-agents</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1296,14 +1264,18 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>18.64</v>
+        <v>1.89</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1316,68 +1288,67 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>claude, claude-code, motion-graphics, opus, prompts, remotion, video-generation</t>
+          <t>deepseek, deepseek-harness, dsh, dsh-plugin, dsh-plugins</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-10</t>
+          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Loopera-ai/loopera</t>
+          <t>Klerith/fernando-skills</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>536</v>
+        <v>293</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>125.1</v>
+        <v>13.2</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>面向基本面因子研究的智能体，具有证据门控验证和研究记忆。
-【原文】面向基本面因子研究的智能体-A hypothesis-driven AI agent for fundamental factor research, with evidence-gated validation and research memory.
-【依据】ai, ai-agent, quant</t>
+          <t>提供用于 Claude Code、Cursor、Codex 和 Antigravity 的规范驱动开发技能。
+【原文】Spec-driven development skills for Claude Code, Cursor, Codex, and Antigravity. By Fernando Herrera.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1387,7 +1358,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Loopera-ai/loopera</t>
+          <t>https://github.com/Klerith/fernando-skills</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1396,14 +1367,18 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>17.87</v>
+        <v>1.89</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1414,70 +1389,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>ai, ai-agent, quant</t>
-        </is>
-      </c>
+      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>metasequoiaime/msime</t>
+          <t>ClawLabsAI/free-ai-models</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>512</v>
+        <v>202</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>99.5</v>
+        <v>9.1</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>跨平台中文输入法，支持Android、iOS、macOS、Linux、Windows与HarmonyOS。
-【原文】下一代跨平台水杉输入法（MSIME）：面向 Android、iOS、macOS、Linux、Windows 与 HarmonyOS 的多平台中文输入法，使用共享输入引擎与各平台原生宿主。
-【依据】ime, input-method, inputmethodkit, ios, macos, pinyin</t>
+          <t>提供免费 AI 模型列表，按质量排序，包含实时状态和 OpenAI 兼容端点
+【原文】Daily-updated list of free AI models (free LLM APIs), ranked by quality with live status. Plus one OpenAI-compatible endpoint that routes to the best one.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>代码库/可部署服务</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1487,7 +1457,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/metasequoiaime/msime</t>
+          <t>https://github.com/ClawLabsAI/free-ai-models</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1496,16 +1466,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>14.22</v>
+        <v>1.3</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1520,12 +1490,12 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>android, chinese, cpp, harmonyos, ime, input-method, inputmethodkit, ios, linux, macos, pinyin, rust</t>
+          <t>ai, ai-api, ai-models, awesome-list, chatgpt-alternative, cline, deepseek, free, free-api, free-llm, gemma, language-model</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1534,39 +1504,38 @@
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>36</v>
+        <v>155</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-09-08</t>
+          <t>free llm api in:name,description stars:&gt;200 pushed:&gt;2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Leanmcp/gateway-skills</t>
+          <t>yjjnls/awesome-blockchain</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2110</v>
+        <v>3633</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>在仪表板中清晰查看Claude代码日志
-【原文】See your claude code logs in clear details in your dashboard
-【依据】描述“See your claude code logs in clear details in your dashboard”</t>
+          <t>提供区块链开发和应用资源的精选列表
+【原文】⚡️Curated list of resources for the development and applications of blockchain.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1576,7 +1545,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1591,7 +1560,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Leanmcp/gateway-skills</t>
+          <t>https://github.com/yjjnls/awesome-blockchain</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1600,7 +1569,7 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>11.05</v>
+        <v>1.17</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -1609,7 +1578,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1622,19 +1591,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr"/>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, bitcoin, blockchain, bulletproofs, digital-currency, dpos, eos, eosio, ethereum, fabric, iota</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>191</v>
+        <v>3115</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1646,37 +1619,36 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-08</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Achno/gowall</t>
+          <t>RobRoyce/knowledge</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2314</v>
+        <v>1459</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>图像处理工具，包括颜色提取、OCR、图像压缩等。
-【原文】A tool to convert a Wallpaper's color scheme / palette, OCR with VLM's Traditional &amp; Hybrid, Image Compression ,color palette extraction,  image upsacling with Adversarial Networks  and more image processing features.
-【依据】background-removal, color-extractor, color-palette, image-processing</t>
+          <t>知识管理工具，用于保存、搜索、访问、探索和聊天网站、文档和文件
+【原文】Knowledge is a tool for saving, searching, accessing, exploring and chatting with all of your favorite websites, documents and files.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>代码库/可部署服务</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1691,7 +1663,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Achno/gowall</t>
+          <t>https://github.com/RobRoyce/knowledge</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1700,16 +1672,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>2.86</v>
+        <v>0.76</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1724,21 +1696,21 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>background-removal, cli, color-extractor, color-palette, color-scheme, compression, go, image, image-converter, image-processing, ocr, pixel-art</t>
+          <t>knowledge-discovery, knowledge-graph, knowledge-management, large-language-models, learning, llm, research</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2021-07-10</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>808</v>
+        <v>1917</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1750,42 +1722,41 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-10</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>tuya/tuya-openclaw-skills</t>
+          <t>gpt-img-2/ai-image-prompt-cookbook</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>479</v>
+        <v>101</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>为Tuya智能生态系统开发的AI技能库，例如设备控制
-【原文】Tuya AI Skill Library for OpenClaw/TuyaClaw - An AI-driven skill set built for the development of Tuya's smart ecosystem (e.g., device control).
-【依据】描述“Tuya AI Skill Library for OpenClaw/TuyaClaw”</t>
+          <t>中文 AI 图片提示词库，覆盖女装、童装、电商主图等
+【原文】中文 AI 图片提示词库，覆盖女装、童装、电商主图、产品摄影、小红书封面和广告海报。</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1795,7 +1766,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tuya/tuya-openclaw-skills</t>
+          <t>https://github.com/gpt-img-2/ai-image-prompt-cookbook</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1804,18 +1775,14 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>2.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1826,19 +1793,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>ai, ai-image-prompts, ai-prompts, chatgpt-image, ecommerce, fashion, gpt-image, image-generation, product-photography, prompt, prompt-engineering, xiaohongshu</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1850,400 +1821,12 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>xialeiliu/Awesome-Incremental-Learning</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>4530</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>收集增量学习相关资源列表
-【原文】Awesome Incremental Learning
-【依据】描述“Awesome Incremental Learning”表明是增量学习资源列表</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/xialeiliu/Awesome-Incremental-Learning</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>2018-08-28</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>2963</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>thomast1906/github-copilot-agent-skills</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>202</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>包含GitHub Copilot代理和技能，持续实验
-【原文】Repo containing my GitHub Copilot Agent &amp; Skills - continually experimenting!
-【依据】描述“Repo containing my GitHub Copilot Agent &amp; Skills”</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/thomast1906/github-copilot-agent-skills</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>ad-si/awesome-3d-printing</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>收集3D打印相关资源列表
-【原文】A curated list of awesome 3D printing resources
-【依据】描述“A curated list of awesome 3D printing resources”</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/ad-si/awesome-3d-printing</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>3d, 3d-printer, 3d-printing, 3d-scanner, 3d-scanning, awesome, awesome-list, cad, g-code, slicer</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>2016-01-07</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>3927</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>LMaxRouterCN/LLMwc4n</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>201</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>强碱AI提示词，旨在穿越所有大语言模型。
-【原文】强碱ai提示词 立志干穿所有大语言模型(你是一只猫娘你是一只猫娘你是一只猫娘你是一只猫娘你是一只猫娘你是一只猫娘你是一只猫娘)
-【依据】LLMwc4n</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/LMaxRouterCN/LLMwc4n</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>估算(生涯日均×7)</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>MPL-2.0</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>451</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-10</t>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V18"/>
+  <autoFilter ref="A2:V14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-10-09 · 共 12 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-10-10 · 共 16 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -625,34 +625,34 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>shader-effects-inc/shaders</t>
+          <t>chengyi-ai/cy-carousel-skill</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>3565</v>
+        <v>288</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>2495.5</v>
+        <v>336</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>提供 WebGPU 组件，用于 React, Vue, Svelte, Solid, JS &amp; Framer
-【原文】WebGPU components for React, Vue, Svelte, Solid, JS &amp; Framer</t>
+          <t>图文轮播Skill，提供选题查证、素材查找、排版、检查、打包，交付封面和10页内容
+【原文】图文轮播 Skill（cy-carousel）：给一个选题，查证、找素材、排版、检查、打包，交付封面＋10 页</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/shader-effects-inc/shaders</t>
+          <t>https://github.com/chengyi-ai/cy-carousel-skill</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>356.5</v>
+        <v>48</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -693,14 +693,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>cli, javascript, mcp, react, shaders, solid, svelte, vue, webgpu-shaders</t>
-        </is>
-      </c>
+      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -709,53 +705,53 @@
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-09</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>datawhalechina/jev-cookbook</t>
+          <t>kitze/skillbox</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>304</v>
+        <v>267</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>112</v>
+        <v>81.3</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>提供 Jev 入门教程和实战配方，全面掌握 System One 判断模型的开发范式
-【原文】⚡ 适合中国宝宝的 Jev 入门教程｜手把手带你了解关于 Jev 的一切——Jupyter Notebook 轻松实验，从三种问题原语到 18 篇实战配方、语音智能家居、模型评测与本地微调，全面掌握 System One 判断模型的开发范式</t>
+          <t>自托管、版本化的AI代理技能库，支持MCP，范围客户端和可选Jev推荐
+【原文】Self-hosted, versioned skills library for AI agents. MCP, scoped clients, and optional Jev recommendations.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>方剂知识线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>技能包/MCP服务</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -765,7 +761,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/datawhalechina/jev-cookbook</t>
+          <t>https://github.com/kitze/skillbox</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -774,16 +770,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>16</v>
+        <v>11.61</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -799,7 +795,7 @@
       <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -808,53 +804,53 @@
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-07-11</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SichengLong26/deepresearch_agent_harness</t>
+          <t>z91772524-ai/pojia-next</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>28.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>多智能体深度研究系统，融合私有知识图谱与联网搜索，含 Harness 编排、持久化 Memory 与受控自进化 Skills
-【原文】多智能体深度研究系统，融合私有知识图谱(GraphRAG)与联网搜索，含 Harness 编排、持久化 Memory 与受控自进化 Skills，FastAPI + React 全栈。</t>
+          <t>提供脚本自动化工具，支持多个客户端提示词和人格替换
+【原文】一个脚本搞定 DSH / WorkBuddy / ZCode / Codex / Cursor / Claude 六客户端的提示词与人格替换：零依赖、双击即用、可自证、改前备份、一键还原。另附【免装 Python 的单文件 exe】；DSH 自动区分官方桌面版 / 社区桌面版。附 bandit/semgrep 扫描与 SHA256 校验。</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -864,7 +860,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SichengLong26/deepresearch_agent_harness</t>
+          <t>https://github.com/z91772524-ai/pojia-next</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -873,11 +869,11 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>4.02</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -895,19 +891,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>ai-agent, automation, claude-code, codex, cursor, deepseek-harness, dsh, exe, glm, no-dependencies, one-click, persona</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -919,36 +919,36 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>知识图谱 in:name,description stars:&gt;200 pushed:&gt;2026-07-11</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>FloWritesCode/fwc-swiftui-skills</t>
+          <t>awdr74100/figwright</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>388</v>
+        <v>1003</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>23.4</v>
+        <v>61.6</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供用于现代 SwiftUI 开发的编码代理技能。
-【原文】Coding Agent Skills for modern SwiftUI development</t>
+          <t>提供双向 Figma MCP 服务器，将设计转换为代码
+【原文】Free, two-way Figma MCP server. Turn designs into framework-aware code, and push code back to the canvas. Works with Claude Code, Cursor, Codex, and any MCP client.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>MCP服务/未定</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/FloWritesCode/fwc-swiftui-skills</t>
+          <t>https://github.com/awdr74100/figwright</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -972,14 +972,18 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>3.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -990,19 +994,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>ai, claude-code, codegen, codex, cursor, design-to-code, figma, figma-mcp, figma-plugin, figma-to-code, mcp, model-context-protocol</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1014,26 +1022,26 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-09</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>mbasso/awesome-wasm</t>
+          <t>xiaodou-official/xiaodou-open-platform</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9649</v>
+        <v>108</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>19.5</v>
+        <v>58.2</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供 WebAssembly 生态系统资源的精选列表
-【原文】😎 Curated list of awesome things regarding the WebAssembly (wasm) ecosystem.</t>
+          <t>提供个人支付和收款通道，支持虚拟商品交易
+【原文】小豆支付开放平台（小豆开放平台）：个人也能申请的收款通道——个人支付、个人收款、H5远程支付；个人开发者无需营业执照，身份证 + 本人银行卡极简入驻，入驻与接入免费（无搭建费、无通道费、无一次性手续费）。虚拟商品商家（卡密、课程、电子书、软件、会员权益、游戏道具）支付宝+微信聚合收款：RSA2 签名 + webhook 验签、持牌机构清算、次日到账；含 12 篇文档、四语言签名示例与本地 demo。Payment API for individuals &amp; digital-goods merchants: Alipay + WeChat Pay, no business license required.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1043,12 +1051,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1058,7 +1066,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mbasso/awesome-wasm</t>
+          <t>https://github.com/xiaodou-official/xiaodou-open-platform</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1067,11 +1075,11 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>2.79</v>
+        <v>8.31</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr"/>
@@ -1087,67 +1095,67 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, awesome-wasm, awesome-webassembly, list, lists, resources, wasm, webassembly</t>
+          <t>aggregate-payment, alipay, card-key, china, digital-downloads, digital-goods, faka, h5-payment, online-courses, openapi, payment, payment-api</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2017-04-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3454</v>
+        <v>13</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-09</t>
+          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-07-12</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>ZJU4EmbodiedAI/EmbodiedSkills</t>
+          <t>fabio-rovai/open-ontologies</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>237</v>
+        <v>1008</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>13.5</v>
+        <v>32.8</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>为 RoboTwin 提供模块化 embodied-agent 运行时，结合 VLM-based grounding 和 subgoal scheduling
-【原文】A modular embodied-agent runtime for RoboTwin, combining VLM-based grounding, subgoal scheduling, OpenPI/pi0.5 action generation, and execution-time verification.</t>
+          <t>管理生产本体变更，提供审计报告和证明
+【原文】Plan, apply and roll back changes to a production ontology, with a blast radius report and a proof an auditor can re-check.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>MCP服务/未定</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1157,7 +1165,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ZJU4EmbodiedAI/EmbodiedSkills</t>
+          <t>https://github.com/fabio-rovai/open-ontologies</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1166,16 +1174,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1.93</v>
+        <v>4.69</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1188,10 +1196,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>ai-native, description-logics, formal-verification, infrastructure-as-code, isabelle-language, knowledge-graph, lean, lean4, mcp, mcp-server, ontology, owl</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1200,7 +1212,7 @@
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>123</v>
+        <v>215</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1212,25 +1224,26 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-09</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MichengAI/dsh-agency-agents</t>
+          <t>apify/mcpc</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>104</v>
+        <v>1004</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>13.2</v>
+        <v>23</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>为 DeepSeek Harness 提供 321 名可召唤的专业智能体</t>
+          <t>最兼容的MCP CLI客户端，支持工具、资源、提示、补全、异步任务、技能、stdio和Streamable HTTP
+【原文】The most compatible MCP CLI client. Supports: tools, resources, prompts, completions, async tasks, skills, stdio and Streamable HTTP (MCP 2026-07-28 and 2025-11-25). Persistent sessions, OAuth 2.1 with DCR, CIMD, client credentials, and ID-JAG, OS keychain, --json for code mode, grep across servers, proxy for AI sandboxes, x402 &amp; more.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1240,7 +1253,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/MCP服务</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1255,7 +1268,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MichengAI/dsh-agency-agents</t>
+          <t>https://github.com/apify/mcpc</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1264,7 +1277,7 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1.89</v>
+        <v>3.29</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1288,21 +1301,21 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>deepseek, deepseek-harness, dsh, dsh-plugin, dsh-plugins</t>
+          <t>ai-agents, bash, claude, cli, code-mode, command-line, mcp, mcp-client, model-context-protocol, shell</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>55</v>
+        <v>305</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
@@ -1314,26 +1327,26 @@
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Klerith/fernando-skills</t>
+          <t>KristenPan/pickoo-your-favorites</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>293</v>
+        <v>150</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>13.2</v>
+        <v>22.8</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供用于 Claude Code、Cursor、Codex 和 Antigravity 的规范驱动开发技能。
-【原文】Spec-driven development skills for Claude Code, Cursor, Codex, and Antigravity. By Fernando Herrera.</t>
+          <t>提供本地创作者收藏工作台，支持 Markdown 捕获和浏览器 UI
+【原文】Local-first creator favorites workbench with evidence-preserving Markdown capture and a complete browser UI.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1358,7 +1371,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Klerith/fernando-skills</t>
+          <t>https://github.com/KristenPan/pickoo-your-favorites</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1367,7 +1380,7 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>1.89</v>
+        <v>3.26</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1376,7 +1389,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1389,19 +1402,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, creator-tools, local-first, markdown, xiaohongshu</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1413,41 +1430,40 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-09</t>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ClawLabsAI/free-ai-models</t>
+          <t>huangbai-AI/sd-2-5-prompt</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9.1</v>
+        <v>20.4</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>提供免费 AI 模型列表，按质量排序，包含实时状态和 OpenAI 兼容端点
-【原文】Daily-updated list of free AI models (free LLM APIs), ranked by quality with live status. Plus one OpenAI-compatible endpoint that routes to the best one.</t>
+          <t>编写 Seedance 2.5 视频提示词</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1457,7 +1473,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ClawLabsAI/free-ai-models</t>
+          <t>https://github.com/huangbai-AI/sd-2-5-prompt</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1466,16 +1482,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>1.3</v>
+        <v>2.91</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1488,54 +1504,50 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>ai, ai-api, ai-models, awesome-list, chatgpt-alternative, cline, deepseek, free, free-api, free-llm, gemma, language-model</t>
-        </is>
-      </c>
+      <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>free llm api in:name,description stars:&gt;200 pushed:&gt;2026-07-11</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-12</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>yjjnls/awesome-blockchain</t>
+          <t>megumi-ben/marco-polo.skill</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>3633</v>
+        <v>197</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>提供区块链开发和应用资源的精选列表
-【原文】⚡️Curated list of resources for the development and applications of blockchain.</t>
+          <t>提供 AI 旅行规划技能
+【原文】AI travel planning skill · 旅行攻略助手 | Real routes, reservation checklists &amp; interactive travel handbooks.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1545,12 +1557,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1560,7 +1572,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yjjnls/awesome-blockchain</t>
+          <t>https://github.com/megumi-ben/marco-polo.skill</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1569,16 +1581,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1.17</v>
+        <v>1.93</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1593,12 +1605,12 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, bitcoin, blockchain, bulletproofs, digital-currency, dpos, eos, eosio, ethereum, fabric, iota</t>
+          <t>agent-skills, ai-travel, amap, fliggy, itinerary, travel-planner, xiaohongshu</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1607,7 +1619,7 @@
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>3115</v>
+        <v>102</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1619,26 +1631,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-09</t>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>RobRoyce/knowledge</t>
+          <t>juliaError/econ-TopJournal-writing-Skill</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>1459</v>
+        <v>203</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>知识管理工具，用于保存、搜索、访问、探索和聊天网站、文档和文件
-【原文】Knowledge is a tool for saving, searching, accessing, exploring and chatting with all of your favorite websites, documents and files.</t>
+          <t>经济类顶级期刊写作技能
+【原文】econ-TopJournal-writing-Skill</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1648,12 +1660,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1663,7 +1675,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/RobRoyce/knowledge</t>
+          <t>https://github.com/juliaError/econ-TopJournal-writing-Skill</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1672,16 +1684,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.76</v>
+        <v>1.34</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1694,23 +1706,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>knowledge-discovery, knowledge-graph, knowledge-management, large-language-models, learning, llm, research</t>
-        </is>
-      </c>
+      <c r="P13" s="6" t="inlineStr"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2021-07-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1917</v>
+        <v>151</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1722,41 +1730,41 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-09-09</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>gpt-img-2/ai-image-prompt-cookbook</t>
+          <t>MobileFirstLLC/social-media-hacker-list</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>101</v>
+        <v>2356</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>中文 AI 图片提示词库，覆盖女装、童装、电商主图等
-【原文】中文 AI 图片提示词库，覆盖女装、童装、电商主图、产品摄影、小红书封面和广告海报。</t>
+          <t>提供社交媒体增强应用和工具列表
+【原文】Growing list of apps and tools for enhancing social media experiences.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1766,7 +1774,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/gpt-img-2/ai-image-prompt-cookbook</t>
+          <t>https://github.com/MobileFirstLLC/social-media-hacker-list</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1775,14 +1783,18 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr"/>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1795,21 +1807,21 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-image-prompts, ai-prompts, chatgpt-image, ecommerce, fashion, gpt-image, image-generation, product-photography, prompt, prompt-engineering, xiaohongshu</t>
+          <t>facebook, instagram, linkedin, mastodon, reddit, snapchat, social-media, twitter, youtube</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2020-10-03</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>147</v>
+        <v>2198</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1821,12 +1833,416 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>topic:xiaohongshu stars:&gt;100</t>
+          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>bubblevv/ai-api-gongyi-nav</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>导航 AI API 公益中转站
+【原文】AI API 公益中转站导航：GPT Claude Codex DeepSeek 免费 API</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/bubblevv/ai-api-gongyi-nav</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>ai-api, ai-navigation, api-relay, chatgpt-api, claude, codex, deepseek, free-api, github-pages, gpt, new-api</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Dicklesworthstone/meta_skill</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>本地优先的AI编码代理技能管理平台，支持SQLite+Git持久化，语义搜索，Bandit优化建议和MCP集成
+【原文】Local-first skill management platform for AI coding agents: dual SQLite+Git persistence, semantic search, bandit-optimized suggestions, and MCP integration</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>技能包/MCP服务</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Dicklesworthstone/meta_skill</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>ai-agents, cli, developer-tools, mcp, rust</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>taskyoooo/ziwei-doushu-skill</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>提供古籍命理分析 Claude Skill
+【原文】基于《紫微斗数全书》《飞星紫微斗数全书》等正统古籍蒸馏的 Claude Skill，支持命盘、宫位、四化、大限流年等专业命理分析</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/taskyoooo/ziwei-doushu-skill</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
+        <is>
+          <t>古籍 in:name,description stars:&gt;20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Jac21/SkillSet</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>直观的求职者技能可视化工具，利用D3.js和JSONResume
+【原文】✨ Intuitive job-candidate skill visualization, taking advantage of D3.js and JSONResume.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Jac21/SkillSet</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>css, d3, fetch-api, json-schema, jsonresume, visualization</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>2016-02-12</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>3893</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-10</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V14"/>
+  <autoFilter ref="A2:V18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -107,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -506,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-10-10 · 共 16 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-10-11 · 共 16 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -625,44 +633,45 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>chengyi-ai/cy-carousel-skill</t>
+          <t>DuarteSantos8/openGym</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>288</v>
+        <v>9360</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>336</v>
+        <v>770.8</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>图文轮播Skill，提供选题查证、素材查找、排版、检查、打包，交付封面和10页内容
-【原文】图文轮播 Skill（cy-carousel）：给一个选题，查证、找素材、排版、检查、打包，交付封面＋10 页</t>
+          <t>自托管健身房和体重追踪器，支持计划、记录锻炼和肌肉训练情况
+【原文】Self-hosted gym &amp; body-weight tracker — plan routines, log workouts (supersets, warm-ups, cardio), see which muscles are trained, fatigued or detrained, import from FitNotes/Strong/Hevy, passkey login. Your data, your server.
+【依据】topics: bodyweight, docker, fitness, fitness-tracker, gym, health, mcp, nodejs, passkeys, progressive-web-applications,</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
+          <t>MCP服务/技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/chengyi-ai/cy-carousel-skill</t>
+          <t>https://github.com/DuarteSantos8/openGym</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -671,16 +680,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>48</v>
+        <v>110.12</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -693,50 +702,55 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>bodyweight, docker, fitness, fitness-tracker, gym, health, mcp, nodejs, passkeys, progressive-web-applications, pwa, react</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-10</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>kitze/skillbox</t>
+          <t>NanmiCoder/dsh-agent-teams</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>267</v>
+        <v>2014</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>81.3</v>
+        <v>235</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>自托管、版本化的AI代理技能库，支持MCP，范围客户端和可选Jev推荐
-【原文】Self-hosted, versioned skills library for AI agents. MCP, scoped clients, and optional Jev recommendations.</t>
+          <t>DeepSeek Harness的Agent Teams多智能体协作插件
+【原文】DeepSeek Harness 的 Agent Teams 多智能体协作插件，支持多个 AI Agent 组成团队，协同完成复杂任务，实现任务分配、并行执行、成员通信与团队协作。 AgentTeams plugin for DeepSeek Harness
+【依据】topics: agentteams, deepseekharness, dsh, dsh-agent-teams, dsh-plugin</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -746,7 +760,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>技能包/MCP服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -754,14 +768,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kitze/skillbox</t>
+          <t>https://github.com/NanmiCoder/dsh-agent-teams</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -770,7 +784,7 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>11.61</v>
+        <v>33.57</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -779,7 +793,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -792,50 +806,55 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>agentteams, deepseekharness, dsh, dsh-agent-teams, dsh-plugin</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-10</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>z91772524-ai/pojia-next</t>
+          <t>LaurieWired/GhidraMCP</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>214</v>
+        <v>10962</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>65.09999999999999</v>
+        <v>135.3</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>提供脚本自动化工具，支持多个客户端提示词和人格替换
-【原文】一个脚本搞定 DSH / WorkBuddy / ZCode / Codex / Cursor / Claude 六客户端的提示词与人格替换：零依赖、双击即用、可自证、改前备份、一键还原。另附【免装 Python 的单文件 exe】；DSH 自动区分官方桌面版 / 社区桌面版。附 bandit/semgrep 扫描与 SHA256 校验。</t>
+          <t>Ghidra的MCP服务器
+【原文】MCP Server for Ghidra
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -853,14 +872,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/z91772524-ai/pojia-next</t>
+          <t>https://github.com/LaurieWired/GhidraMCP</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -869,16 +888,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>19.33</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -891,14 +910,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>ai-agent, automation, claude-code, codex, cursor, deepseek-harness, dsh, exe, glm, no-dependencies, one-click, persona</t>
-        </is>
-      </c>
+      <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -907,48 +922,49 @@
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>23</v>
+        <v>567</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-12</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>awdr74100/figwright</t>
+          <t>ccfos/nightingale</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1003</v>
+        <v>13327</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>61.6</v>
+        <v>38.6</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供双向 Figma MCP 服务器，将设计转换为代码
-【原文】Free, two-way Figma MCP server. Turn designs into framework-aware code, and push code back to the canvas. Works with Claude Code, Cursor, Codex, and any MCP client.</t>
+          <t>提供开源自托管的指标、日志和数据库告警监控，内置 AI 代理和 MCP 服务器。
+【原文】Open-source, self-hosted alerting for metrics, logs, and databases. Includes a built-in AI agent and MCP server.
+【依据】描述包含内置 AI agent 和 MCP server</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/未定</t>
+          <t>MCP服务/可部署服务</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -956,14 +972,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/awdr74100/figwright</t>
+          <t>https://github.com/ccfos/nightingale</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -972,16 +988,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>8.800000000000001</v>
+        <v>5.52</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -996,12 +1012,12 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>ai, claude-code, codegen, codex, cursor, design-to-code, figma, figma-mcp, figma-plugin, figma-to-code, mcp, model-context-protocol</t>
+          <t>alerting, logs, metrics, monitoring, nightingale, observability, sre, sre-agent, time-series, tsdb</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2020-03-03</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1010,7 +1026,7 @@
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>114</v>
+        <v>2413</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1022,26 +1038,27 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-10</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>xiaodou-official/xiaodou-open-platform</t>
+          <t>GT-RIPL/Awesome-LLM-Robotics</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>108</v>
+        <v>4485</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>58.2</v>
+        <v>20.7</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供个人支付和收款通道，支持虚拟商品交易
-【原文】小豆支付开放平台（小豆开放平台）：个人也能申请的收款通道——个人支付、个人收款、H5远程支付；个人开发者无需营业执照，身份证 + 本人银行卡极简入驻，入驻与接入免费（无搭建费、无通道费、无一次性手续费）。虚拟商品商家（卡密、课程、电子书、软件、会员权益、游戏道具）支付宝+微信聚合收款：RSA2 签名 + webhook 验签、持牌机构清算、次日到账；含 12 篇文档、四语言签名示例与本地 demo。Payment API for individuals &amp; digital-goods merchants: Alipay + WeChat Pay, no business license required.</t>
+          <t>收集整理使用大型语言/多模态模型进行机器人/强化学习研究的论文、代码和相关网站列表。
+【原文】A comprehensive list of papers using large language/multi-modal models for Robotics/RL, including papers, codes, and related websites
+【依据】描述明确为 comprehensive list of papers</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1051,22 +1068,22 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/xiaodou-official/xiaodou-open-platform</t>
+          <t>https://github.com/GT-RIPL/Awesome-LLM-Robotics</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1075,11 +1092,11 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>8.31</v>
+        <v>2.95</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr"/>
@@ -1093,79 +1110,76 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>aggregate-payment, alipay, card-key, china, digital-downloads, digital-goods, faka, h5-payment, online-courses, openapi, payment, payment-api</t>
-        </is>
-      </c>
+      <c r="P7" s="6" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2022-08-12</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>13</v>
+        <v>1521</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-07-12</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>fabio-rovai/open-ontologies</t>
+          <t>akitaonrails/my-skills</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1008</v>
+        <v>219</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>32.8</v>
+        <v>16.4</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>管理生产本体变更，提供审计报告和证明
-【原文】Plan, apply and roll back changes to a production ontology, with a blast radius report and a proof an auditor can re-check.</t>
+          <t>个人技能集合，未针对通用使用定制
+【原文】akitaonrails' personal skills (not tailored for general usage)
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/未定</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/fabio-rovai/open-ontologies</t>
+          <t>https://github.com/akitaonrails/my-skills</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1174,16 +1188,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>4.69</v>
+        <v>2.35</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1196,23 +1210,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>ai-native, description-logics, formal-verification, infrastructure-as-code, isabelle-language, knowledge-graph, lean, lean4, mcp, mcp-server, ontology, owl</t>
-        </is>
-      </c>
+      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>215</v>
+        <v>93</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1224,36 +1234,37 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-09-10</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>apify/mcpc</t>
+          <t>Fausto-404/js-reverse-automation--skill</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1004</v>
+        <v>594</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>23</v>
+        <v>16.4</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>最兼容的MCP CLI客户端，支持工具、资源、提示、补全、异步任务、技能、stdio和Streamable HTTP
-【原文】The most compatible MCP CLI client. Supports: tools, resources, prompts, completions, async tasks, skills, stdio and Streamable HTTP (MCP 2026-07-28 and 2025-11-25). Persistent sessions, OAuth 2.1 with DCR, CIMD, client credentials, and ID-JAG, OS keychain, --json for code mode, grep across servers, proxy for AI sandboxes, x402 &amp; more.</t>
+          <t>结合 chrome-devtools-mcp 和 Skill 规范，实现前端 JavaScript 逆向自动化分析。
+【原文】结合chrome-devtools-mcp的能力并加上Skill的规范，实现JSRPC+Flask+autoDecoder方案的前端JS逆向自动化分析，提升JS逆向的效率
+【依据】描述明确为 skill，用于 JS 逆向自动化</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>技能包/MCP服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1261,14 +1272,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/apify/mcpc</t>
+          <t>https://github.com/Fausto-404/js-reverse-automation--skill</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1277,7 +1288,7 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>3.29</v>
+        <v>2.34</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1286,7 +1297,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1301,21 +1312,21 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, bash, claude, cli, code-mode, command-line, mcp, mcp-client, model-context-protocol, shell</t>
+          <t>ai-tools, automation, burp-suite, javascript, js, js-reverse, reverse, reverse-engineering, security-tools, skills, web-security</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>305</v>
+        <v>254</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
@@ -1327,26 +1338,27 @@
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-10</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>KristenPan/pickoo-your-favorites</t>
+          <t>testdino-hq/playwright-skill</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>150</v>
+        <v>391</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>22.8</v>
+        <v>11.4</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供本地创作者收藏工作台，支持 Markdown 捕获和浏览器 UI
-【原文】Local-first creator favorites workbench with evidence-preserving Markdown capture and a complete browser UI.</t>
+          <t>提供 Playwright 最佳实践的 AI 指南，辅助自动化测试和报告生成。
+【原文】TestDino Playwright Skill: AI-powered guides for Playwright best practices, made by testdino.com.
+【依据】描述为 AI-powered guides for Playwright best practices</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1364,14 +1376,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/KristenPan/pickoo-your-favorites</t>
+          <t>https://github.com/testdino-hq/playwright-skill</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1380,18 +1392,14 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>3.26</v>
+        <v>1.63</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1404,21 +1412,21 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, creator-tools, local-first, markdown, xiaohongshu</t>
+          <t>ai, ai-skills, antigravity-skills, claude-skills, codex-skills, cursor-skills, devtool, openclaw-skills, playwright, reporting, skills, test-reporting</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1430,25 +1438,27 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:xiaohongshu stars:&gt;100</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>huangbai-AI/sd-2-5-prompt</t>
+          <t>Luyu2026/Skill-Bible</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>201</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>20.4</v>
+        <v>10.6</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>编写 Seedance 2.5 视频提示词</t>
+          <t>汇总并展示可用的 skill 集合，作为 skill 使用指南或宝典。
+【原文】好用的skill都在宝典
+【依据】描述为“好用的skill都在宝典”，表明是skill集合</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1458,22 +1468,22 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/数据集</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/huangbai-AI/sd-2-5-prompt</t>
+          <t>https://github.com/Luyu2026/Skill-Bible</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1482,16 +1492,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>2.91</v>
+        <v>1.52</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1507,72 +1517,73 @@
       <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-12</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>megumi-ben/marco-polo.skill</t>
+          <t>shouldnotappearcalm/a-share-skill</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>197</v>
+        <v>243</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 旅行规划技能
-【原文】AI travel planning skill · 旅行攻略助手 | Real routes, reservation checklists &amp; interactive travel handbooks.</t>
+          <t>A股数据分析、量化选股与模拟交易Skill集合
+【原文】A股数据分析、量化选股与模拟交易 Skill 集合，支持实时行情、历史K线、技术指标、自定义交易策略与模拟买入、卖出交易账户
+【依据】topics: a-share, agent-skills, akshare, claude-code, claude-skills, mcp, paper-trading, quant, stock</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>方剂知识线/未归类</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/未定</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/megumi-ben/marco-polo.skill</t>
+          <t>https://github.com/shouldnotappearcalm/a-share-skill</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1581,16 +1592,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1.93</v>
+        <v>1.17</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1605,21 +1616,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-travel, amap, fliggy, itinerary, travel-planner, xiaohongshu</t>
+          <t>a-share, agent-skills, akshare, claude-code, claude-skills, mcp, paper-trading, quant, stock</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1631,26 +1642,27 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:xiaohongshu stars:&gt;100</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>juliaError/econ-TopJournal-writing-Skill</t>
+          <t>siteserver/cms</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>203</v>
+        <v>3914</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>经济类顶级期刊写作技能
-【原文】econ-TopJournal-writing-Skill</t>
+          <t>基于.NET Core的网站内容管理系统
+【原文】SSCMS 基于 .NET Core，能够以最低的成本、最少的人力投入在最短的时间内架设一个功能齐全、性能优异、规模庞大并易于维护的网站平台。链接是SSCMS推出的全新AI视频开源社区：献丑AI
+【依据】topics: c-sharp, cms, content-management-system, dot-net, siteserver, siteserver-cms, ss-cms, sscms</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1660,22 +1672,22 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
+          <t>架构参考</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/juliaError/econ-TopJournal-writing-Skill</t>
+          <t>https://github.com/siteserver/cms</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1684,16 +1696,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1706,50 +1718,55 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>c-sharp, cms, content-management-system, dot-net, siteserver, siteserver-cms, ss-cms, sscms</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2017-04-26</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>151</v>
+        <v>3455</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-10</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MobileFirstLLC/social-media-hacker-list</t>
+          <t>Thinklab-SJTU/awesome-ml4co</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2356</v>
+        <v>2175</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>7.5</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>提供社交媒体增强应用和工具列表
-【原文】Growing list of apps and tools for enhancing social media experiences.</t>
+          <t>收集整理机器学习用于组合优化方向的论文列表。
+【原文】Awesome machine learning for combinatorial optimization papers.
+【依据】描述为 awesome machine learning for combinatorial optimization papers</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1759,22 +1776,22 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MobileFirstLLC/social-media-hacker-list</t>
+          <t>https://github.com/Thinklab-SJTU/awesome-ml4co</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1787,12 +1804,12 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1807,21 +1824,21 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>facebook, instagram, linkedin, mastodon, reddit, snapchat, social-media, twitter, youtube</t>
+          <t>combinatorial-optimization, machine-learning, operations-research, paper-list</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2020-10-03</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2198</v>
+        <v>2030</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1833,26 +1850,27 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>bubblevv/ai-api-gongyi-nav</t>
+          <t>Carlos487/awesome-wpf</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>102</v>
+        <v>2171</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>导航 AI API 公益中转站
-【原文】AI API 公益中转站导航：GPT Claude Codex DeepSeek 免费 API</t>
+          <t>WPF资源、库和UI控件集合
+【原文】A collection of awesome WPF resources, libraries and UI controls.
+【依据】topics: awesome, awesome-list, controls, dotnet, dotnet-core, net, ui-components, wpf</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1862,22 +1880,22 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/bubblevv/ai-api-gongyi-nav</t>
+          <t>https://github.com/Carlos487/awesome-wpf</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1886,16 +1904,16 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>CC0-1.0</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1910,77 +1928,78 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>ai-api, ai-navigation, api-relay, chatgpt-api, claude, codex, deepseek, free-api, github-pages, gpt, new-api</t>
+          <t>awesome, awesome-list, controls, dotnet, dotnet-core, net, ui-components, wpf</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2020-02-21</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>128</v>
+        <v>2424</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-12</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Dicklesworthstone/meta_skill</t>
+          <t>marcelscruz/dev-resources</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>205</v>
+        <v>1352</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>本地优先的AI编码代理技能管理平台，支持SQLite+Git持久化，语义搜索，Bandit优化建议和MCP集成
-【原文】Local-first skill management platform for AI coding agents: dual SQLite+Git persistence, semantic search, bandit-optimized suggestions, and MCP integration</t>
+          <t>开发者资源列表，包含课程、设计、信息等资源
+【原文】A collaborative list of resources for developers
+【依据】topics: assets, awesome, awesome-list, courses, design, dev-resources, development, hacktoberfest, information, infrastr</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>技能包/MCP服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Dicklesworthstone/meta_skill</t>
+          <t>https://github.com/marcelscruz/dev-resources</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1989,16 +2008,16 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2013,21 +2032,21 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, cli, developer-tools, mcp, rust</t>
+          <t>assets, awesome, awesome-list, courses, design, dev-resources, development, hacktoberfest, information, infrastructure, jobs, programming</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2021-01-25</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>270</v>
+        <v>2085</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2039,51 +2058,52 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-10</t>
+          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>taskyoooo/ziwei-doushu-skill</t>
+          <t>dav-niu474/huobao-drama-ai</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>提供古籍命理分析 Claude Skill
-【原文】基于《紫微斗数全书》《飞星紫微斗数全书》等正统古籍蒸馏的 Claude Skill，支持命盘、宫位、四化、大限流年等专业命理分析</t>
+          <t>AI短剧创作平台，支持剧本到成片的一站式制作
+【原文】🎬 AI短剧创作平台 — 从剧本到成片，一站式AI短剧制作工作台。支持70+大模型(GLM5.1/DeepSeek V4/Qwen3.5等)、图片生成、视频生成(Seedance 2.0)、AI配音，多供应商配置，Next.js 16全栈构建
+【依据】topics: ai-creative, ai-drama, ai-image-generation, ai-video-generation, deepseek, glm5, nextjs, nvidia-nim, prisma, see</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/taskyoooo/ziwei-doushu-skill</t>
+          <t>https://github.com/dav-niu474/huobao-drama-ai</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2092,14 +2112,18 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.12</v>
+        <v>0.6</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2110,19 +2134,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>ai-creative, ai-drama, ai-image-generation, ai-video-generation, deepseek, glm5, nextjs, nvidia-nim, prisma, seedance, short-drama, storyboard</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
@@ -2134,51 +2162,52 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>古籍 in:name,description stars:&gt;20</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Jac21/SkillSet</t>
+          <t>myhub/tr</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>201</v>
+        <v>1383</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>直观的求职者技能可视化工具，利用D3.js和JSONResume
-【原文】✨ Intuitive job-candidate skill visualization, taking advantage of D3.js and JSONResume.</t>
+          <t>离线OCR SDK，用于中文文本检测和识别
+【原文】Free Offline OCR 离线的中文文本检测+识别SDK
+【依据】topics: crnn, ctpn, curved-text, deeplearning, ocr, pixellink, text-recognition, transformer</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Jac21/SkillSet</t>
+          <t>https://github.com/myhub/tr</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2187,16 +2216,16 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.05</v>
+        <v>0.53</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2211,33 +2240,33 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>css, d3, fetch-api, json-schema, jsonresume, visualization</t>
+          <t>crnn, ctpn, curved-text, deeplearning, ocr, pixellink, text-recognition, transformer</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2016-02-12</t>
+          <t>2019-08-18</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>3893</v>
+        <v>2611</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-10</t>
+          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-07-13</t>
         </is>
       </c>
     </row>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -113,10 +113,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-10-11 · 共 16 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-10-12 · 共 17 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,25 +633,24 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>DuarteSantos8/openGym</t>
+          <t>paperclipai/paperclip</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>9360</v>
+        <v>100508</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>770.8</v>
+        <v>3140.9</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>自托管健身房和体重追踪器，支持计划、记录锻炼和肌肉训练情况
-【原文】Self-hosted gym &amp; body-weight tracker — plan routines, log workouts (supersets, warm-ups, cardio), see which muscles are trained, fatigued or detrained, import from FitNotes/Strong/Hevy, passkey login. Your data, your server.
-【依据】topics: bodyweight, docker, fitness, fitness-tracker, gym, health, mcp, nodejs, passkeys, progressive-web-applications,</t>
+          <t>开源应用，用于管理工作中使用的代理。
+【原文】The open-source app everyone uses to manage agents at work</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -659,19 +658,19 @@
           <t>MCP服务/技能包/可部署服务</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/DuarteSantos8/openGym</t>
+          <t>https://github.com/paperclipai/paperclip</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -680,16 +679,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>110.12</v>
+        <v>448.7</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -702,55 +701,50 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>bodyweight, docker, fitness, fitness-tracker, gym, health, mcp, nodejs, passkeys, progressive-web-applications, pwa, react</t>
-        </is>
-      </c>
+      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>85</v>
+        <v>224</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-11</t>
+          <t>stars:&gt;100000 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NanmiCoder/dsh-agent-teams</t>
+          <t>Folkbench/folkbench</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2014</v>
+        <v>335</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>235</v>
+        <v>234.5</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>DeepSeek Harness的Agent Teams多智能体协作插件
-【原文】DeepSeek Harness 的 Agent Teams 多智能体协作插件，支持多个 AI Agent 组成团队，协同完成复杂任务，实现任务分配、并行执行、成员通信与团队协作。 AgentTeams plugin for DeepSeek Harness
-【依据】topics: agentteams, deepseekharness, dsh, dsh-agent-teams, dsh-plugin</t>
+          <t>AI API 中转站评测排行与切换工具，支持 Claude Code / Codex。
+【原文】AI API 中转站评测排行与切换工具：实测可用率、延迟与价格 · Open-source AI API relay benchmark, rankings &amp; switcher for Claude Code / Codex</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -760,22 +754,22 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>MCP服务/技能包/架构参考</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/NanmiCoder/dsh-agent-teams</t>
+          <t>https://github.com/Folkbench/folkbench</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -784,16 +778,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>33.57</v>
+        <v>33.5</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -808,21 +802,21 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agentteams, deepseekharness, dsh, dsh-agent-teams, dsh-plugin</t>
+          <t>ai, api-relay, api-relay-pricing, benchmark, benchmarks, claude, claude-code, codex, folkbench, llm, model-evaluation, openai-api</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
@@ -834,27 +828,26 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
+          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LaurieWired/GhidraMCP</t>
+          <t>JourniOne-ai/JourniOne-Planning-Skills</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>10962</v>
+        <v>802</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>135.3</v>
+        <v>216</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Ghidra的MCP服务器
-【原文】MCP Server for Ghidra
-【依据】topics: -</t>
+          <t>JourniOne旅行规划技能，从灵感、路线到带地图、可分享的旅行日志。
+【原文】JourniOne 旅行规划 Skill：从灵感与逐日路线，到带地图、可分享的 Travel Journal，按需衔接酒店与航班。</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -864,22 +857,22 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LaurieWired/GhidraMCP</t>
+          <t>https://github.com/JourniOne-ai/JourniOne-Planning-Skills</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -888,16 +881,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>19.33</v>
+        <v>30.85</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -910,19 +903,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, ai-agent, itinerary, journione, travel-journal, travel-planning</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>567</v>
+        <v>26</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -934,52 +931,51 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-11</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ccfos/nightingale</t>
+          <t>wenziai/wenzi-xiaohongshu-workflow</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>13327</v>
+        <v>170</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>38.6</v>
+        <v>99.2</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供开源自托管的指标、日志和数据库告警监控，内置 AI 代理和 MCP 服务器。
-【原文】Open-source, self-hosted alerting for metrics, logs, and databases. Includes a built-in AI agent and MCP server.
-【依据】描述包含内置 AI agent 和 MCP server</t>
+          <t>一套可安装的 Agent Skills，用于小红书内容创作工作流。
+【原文】文子的小红书工作流：从账号定位、选题标题、真人化改稿、图文规划到排期复盘的一套可安装 Agent Skills。</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ccfos/nightingale</t>
+          <t>https://github.com/wenziai/wenzi-xiaohongshu-workflow</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -988,18 +984,14 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5.52</v>
+        <v>14.17</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>Go</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1012,21 +1004,21 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>alerting, logs, metrics, monitoring, nightingale, observability, sre, sre-agent, time-series, tsdb</t>
+          <t>agent-skills, codex-skills, content-creation, workbuddy, xiaohongshu</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2020-03-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>2413</v>
+        <v>12</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1038,37 +1030,36 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-11</t>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GT-RIPL/Awesome-LLM-Robotics</t>
+          <t>charlie947/motion-graphics-skills</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4485</v>
+        <v>217</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>20.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>收集整理使用大型语言/多模态模型进行机器人/强化学习研究的论文、代码和相关网站列表。
-【原文】A comprehensive list of papers using large language/multi-modal models for Robotics/RL, including papers, codes, and related websites
-【依据】描述明确为 comprehensive list of papers</t>
+          <t>13项Claude Code技能，用于发布级动态图形制作，无需After Effects或视频生成器。
+【原文】13 Claude Code skills for launch-grade motion graphics. Every frame is code. No After Effects, no video generator.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1076,14 +1067,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/GT-RIPL/Awesome-LLM-Robotics</t>
+          <t>https://github.com/charlie947/motion-graphics-skills</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1092,14 +1083,18 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>2.95</v>
+        <v>13.56</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>BSD-3-Clause</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1110,19 +1105,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, ai-marketing, animation, claude, claude-code, claude-skills, codex, hyperframes, motion-graphics, video</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1521</v>
+        <v>16</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1134,27 +1133,26 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-11</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>akitaonrails/my-skills</t>
+          <t>onvoyage-ai/gtm-engineer-skills</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>219</v>
+        <v>1321</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>16.4</v>
+        <v>40.5</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>个人技能集合，未针对通用使用定制
-【原文】akitaonrails' personal skills (not tailored for general usage)
-【依据】topics: -</t>
+          <t>Claude Code技能，用于提升网站AEO和GEO分数，提供16项检查和修复。
+【原文】Claude Code skill for improving website AEO (AI Engine Optimization) and GEO (Generative Engine Optimization) scores — 16 foundational checks, 6 intelligence dimensions, framework-specific fixes</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1164,22 +1162,22 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/akitaonrails/my-skills</t>
+          <t>https://github.com/onvoyage-ai/gtm-engineer-skills</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1188,16 +1186,16 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>2.35</v>
+        <v>5.79</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1210,10 +1208,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>aeo, ai-optimization, claude-code, geo, llms-txt, seo, structured-data</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1222,7 +1224,7 @@
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>93</v>
+        <v>228</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1234,27 +1236,26 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-11</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Fausto-404/js-reverse-automation--skill</t>
+          <t>yasewang1337-svg/winutil-cn</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>594</v>
+        <v>567</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>16.4</v>
+        <v>33.3</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>结合 chrome-devtools-mcp 和 Skill 规范，实现前端 JavaScript 逆向自动化分析。
-【原文】结合chrome-devtools-mcp的能力并加上Skill的规范，实现JSRPC+Flask+autoDecoder方案的前端JS逆向自动化分析，提升JS逆向的效率
-【依据】描述明确为 skill，用于 JS 逆向自动化</t>
+          <t>面向 Windows 11 的中文软件管理与系统维护工具。
+【原文】面向 Windows 11 的中文软件管理与系统维护工具，支持 Windows 10 / 11 x64 安装镜像制作。基于 Chris Titus Tech Windows Utility。</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1264,7 +1265,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1272,14 +1273,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Fausto-404/js-reverse-automation--skill</t>
+          <t>https://github.com/yasewang1337-svg/winutil-cn</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1288,16 +1289,16 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>2.34</v>
+        <v>4.76</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>PowerShell</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1312,63 +1313,62 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>ai-tools, automation, burp-suite, javascript, js, js-reverse, reverse, reverse-engineering, security-tools, skills, web-security</t>
+          <t>chinese, chinese-localization, debloat, i18n, localization, package-manager, powershell, system-maintenance, windows, windows-10, windows-11, windows-utility</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>254</v>
+        <v>119</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-11</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>testdino-hq/playwright-skill</t>
+          <t>yexi-by/dsh-unrestricted</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>391</v>
+        <v>204</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>11.4</v>
+        <v>28</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供 Playwright 最佳实践的 AI 指南，辅助自动化测试和报告生成。
-【原文】TestDino Playwright Skill: AI-powered guides for Playwright best practices, made by testdino.com.
-【依据】描述为 AI-powered guides for Playwright best practices</t>
+          <t>DeepSeek Harness插件，通过系统提示词解除模型回答限制，支持Web与桌面端。
+【原文】DeepSeek Harness 提示词破限插件：通过系统提示词解除模型回答限制，深度适配 Web 与桌面端多模式及工具调用</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1376,14 +1376,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/testdino-hq/playwright-skill</t>
+          <t>https://github.com/yexi-by/dsh-unrestricted</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1392,14 +1392,18 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>1.63</v>
+        <v>4</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1412,53 +1416,52 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-skills, antigravity-skills, claude-skills, codex-skills, cursor-skills, devtool, openclaw-skills, playwright, reporting, skills, test-reporting</t>
+          <t>deepseek-harness, dsh, plugin, prompt-engineering, typescript</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>240</v>
+        <v>51</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-11</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Luyu2026/Skill-Bible</t>
+          <t>thedivergentai/Game-Design-Agentic-Skills</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>201</v>
+        <v>834</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>10.6</v>
+        <v>23.7</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>汇总并展示可用的 skill 集合，作为 skill 使用指南或宝典。
-【原文】好用的skill都在宝典
-【依据】描述为“好用的skill都在宝典”，表明是skill集合</t>
+          <t>游戏 AI 代理的多引擎长期记忆库，包含多种技能和蓝图。
+【原文】Multi-engine long-term memory for game AI agents. Deep Godot 4.7+ (99 skills, 27 genre blueprints) + Bevy docs-first parity — audited patterns, persona orchestration (Analyst · Auditor · Builder), production-grade engineering.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1468,22 +1471,22 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>技能包/数据集</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
+          <t>架构参考</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Luyu2026/Skill-Bible</t>
+          <t>https://github.com/thedivergentai/Game-Design-Agentic-Skills</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1492,16 +1495,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>1.52</v>
+        <v>3.38</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>LGPL-3.0</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>GDScript</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1517,16 +1520,16 @@
       <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>132</v>
+        <v>247</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1538,52 +1541,51 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-11</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>shouldnotappearcalm/a-share-skill</t>
+          <t>webpro/awesome-dotfiles</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>243</v>
+        <v>10897</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>17.1</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>A股数据分析、量化选股与模拟交易Skill集合
-【原文】A股数据分析、量化选股与模拟交易 Skill 集合，支持实时行情、历史K线、技术指标、自定义交易策略与模拟买入、卖出交易账户
-【依据】topics: a-share, agent-skills, akshare, claude-code, claude-skills, mcp, paper-trading, quant, stock</t>
+          <t>一个精选的dotfiles资源列表。
+【原文】A curated list of dotfiles resources.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>方剂知识线/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包/未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/shouldnotappearcalm/a-share-skill</t>
+          <t>https://github.com/webpro/awesome-dotfiles</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1592,18 +1594,14 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1.17</v>
+        <v>2.44</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1616,12 +1614,12 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>a-share, agent-skills, akshare, claude-code, claude-skills, mcp, paper-trading, quant, stock</t>
+          <t>awesome, awesome-list, bash, dotfiles, dotfiles-resources, fish, list, shell, tools, zsh</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2014-07-16</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1630,7 +1628,7 @@
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>208</v>
+        <v>4471</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1642,27 +1640,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-11</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>siteserver/cms</t>
+          <t>km1994/LLMs_interview_notes</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>3914</v>
+        <v>2614</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>7.9</v>
+        <v>16.3</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>基于.NET Core的网站内容管理系统
-【原文】SSCMS 基于 .NET Core，能够以最低的成本、最少的人力投入在最短的时间内架设一个功能齐全、性能优异、规模庞大并易于维护的网站平台。链接是SSCMS推出的全新AI视频开源社区：献丑AI
-【依据】topics: c-sharp, cms, content-management-system, dot-net, siteserver, siteserver-cms, ss-cms, sscms</t>
+          <t>记录大模型算法工程师相关的面试题。
+【原文】该仓库主要记录 大模型（LLMs） 算法工程师相关的面试题</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1672,22 +1669,22 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/siteserver/cms</t>
+          <t>https://github.com/km1994/LLMs_interview_notes</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1696,18 +1693,14 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1.13</v>
+        <v>2.33</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1718,14 +1711,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>c-sharp, cms, content-management-system, dot-net, siteserver, siteserver-cms, ss-cms, sscms</t>
-        </is>
-      </c>
+      <c r="P13" s="6" t="inlineStr"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2017-04-26</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -1734,7 +1723,7 @@
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>3455</v>
+        <v>1122</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1746,52 +1735,51 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-13</t>
+          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Thinklab-SJTU/awesome-ml4co</t>
+          <t>fcakyon/phd-skills</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2175</v>
+        <v>416</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>收集整理机器学习用于组合优化方向的论文列表。
-【原文】Awesome machine learning for combinatorial optimization papers.
-【依据】描述为 awesome machine learning for combinatorial optimization papers</t>
+          <t>提供用于Claude Code的博士研究技能，包括论文复现、实验设计和评审。
+【原文】PhD Research Skills for Claude Code: paper reproduction, experiment design, paper review, result comparison and more.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>技能包/MCP服务</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Thinklab-SJTU/awesome-ml4co</t>
+          <t>https://github.com/fcakyon/phd-skills</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1800,16 +1788,16 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.07</v>
+        <v>1.93</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1824,21 +1812,21 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>combinatorial-optimization, machine-learning, operations-research, paper-list</t>
+          <t>academic, agents, ai, claude, claude-code, claude-code-plugin, claude-skills, conference, fable, hooks, journal, mcp</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2030</v>
+        <v>215</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1850,37 +1838,36 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-11</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Carlos487/awesome-wpf</t>
+          <t>NotIntoSports/RoleAI</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2171</v>
+        <v>108</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>6.3</v>
+        <v>12.2</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>WPF资源、库和UI控件集合
-【原文】A collection of awesome WPF resources, libraries and UI controls.
-【依据】topics: awesome, awesome-list, controls, dotnet, dotnet-core, net, ui-components, wpf</t>
+          <t>AI 数字人项目，支持实时互动、语音对练等功能。
+【原文】AI 数字人项目。角色以虚拟形象实时互动：你说话，对方看着你回答。也可做语音对练、会议辅助和直播讲解。</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1888,14 +1875,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Carlos487/awesome-wpf</t>
+          <t>https://github.com/NotIntoSports/RoleAI</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1904,16 +1891,16 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.9</v>
+        <v>1.74</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1926,65 +1913,60 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, controls, dotnet, dotnet-core, net, ui-components, wpf</t>
-        </is>
-      </c>
+      <c r="P15" s="6" t="inlineStr"/>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2020-02-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>2424</v>
+        <v>62</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-11</t>
+          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>marcelscruz/dev-resources</t>
+          <t>VanGong1999/screen-creative-skills</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1352</v>
+        <v>449</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4.5</v>
+        <v>11.4</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>开发者资源列表，包含课程、设计、信息等资源
-【原文】A collaborative list of resources for developers
-【依据】topics: assets, awesome, awesome-list, courses, design, dev-resources, development, hacktoberfest, information, infrastr</t>
+          <t>影视创作评估策划 Agent Skills，包含 AI 影视自动化工作流。
+【原文】Skills for Film and Television Creation Agents|31 个影视创作评估策划Agent Skills｜AI影视自动化工作流｜竖屏短剧长剧IP改编｜情节题材提炼｜剧本小说IP创作策划评估｜人物小传｜拉片人物剧集故事五元素分析｜大纲生成｜</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1992,14 +1974,14 @@
           <t>宽松·可进闭源</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/marcelscruz/dev-resources</t>
+          <t>https://github.com/VanGong1999/screen-creative-skills</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2008,7 +1990,7 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.65</v>
+        <v>1.63</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -2017,7 +1999,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2032,21 +2014,21 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>assets, awesome, awesome-list, courses, design, dev-resources, development, hacktoberfest, information, infrastructure, jobs, programming</t>
+          <t>agents, ai, skills</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2021-01-25</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>2085</v>
+        <v>275</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2058,52 +2040,51 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>dav-niu474/huobao-drama-ai</t>
+          <t>wy-luke/All-Chinese-Character-Set</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>101</v>
+        <v>1952</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>AI短剧创作平台，支持剧本到成片的一站式制作
-【原文】🎬 AI短剧创作平台 — 从剧本到成片，一站式AI短剧制作工作台。支持70+大模型(GLM5.1/DeepSeek V4/Qwen3.5等)、图片生成、视频生成(Seedance 2.0)、AI配音，多供应商配置，Next.js 16全栈构建
-【依据】topics: ai-creative, ai-drama, ai-image-generation, ai-video-generation, deepseek, glm5, nextjs, nvidia-nim, prisma, see</t>
+          <t>包含全部中文字符的字符集，适用于 Unity 3D。
+【原文】致力于维护一个包含全部中文字符（汉字+符号）的字符集，包罗万象，含3500 / 7000 常用汉字集、常用符号集。A Charater Set contains all Chinese charaters.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dav-niu474/huobao-drama-ai</t>
+          <t>https://github.com/wy-luke/All-Chinese-Character-Set</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2112,16 +2093,16 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.6</v>
+        <v>1.08</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2136,21 +2117,21 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>ai-creative, ai-drama, ai-image-generation, ai-video-generation, deepseek, glm5, nextjs, nvidia-nim, prisma, seedance, short-drama, storyboard</t>
+          <t>character-set, chinese, chinese-character, chinese-characters, chinese-simplified, font, textmeshpro, unity, unity-3d, unity3d</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>169</v>
+        <v>1804</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
@@ -2162,52 +2143,51 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-13</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>myhub/tr</t>
+          <t>dbwls99706/ros2-engineering-skills</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1383</v>
+        <v>219</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>3.7</v>
+        <v>7.3</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>离线OCR SDK，用于中文文本检测和识别
-【原文】Free Offline OCR 离线的中文文本检测+识别SDK
-【依据】topics: crnn, ctpn, curved-text, deeplearning, ocr, pixellink, text-recognition, transformer</t>
+          <t>用于生产级ROS 2开发的Agent技能，涵盖工作区、节点、执行器等。
+【原文】Agent skill for production-grade ROS 2 development. Progressive-disclosure SKILL.md covering workspace, nodes, executors, QoS, ros2_control, Nav2, MoveIt 2, real-time, and deployment. Works with Claude Code, Codex, Cursor, Gemini CLI.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/myhub/tr</t>
+          <t>https://github.com/dbwls99706/ros2-engineering-skills</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2216,11 +2196,11 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.53</v>
+        <v>1.04</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2240,38 +2220,141 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>crnn, ctpn, curved-text, deeplearning, ocr, pixellink, text-recognition, transformer</t>
+          <t>agent-skill, claude, claude-code, robotics, ros2</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2019-08-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>dineug/erd-editor</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>ERD 编辑器，设计数据库模式，支持多种导入和导出功能。
+【原文】ERD Editor: design database schemas visually, import SQL DDL, GraphQL, DBML and AML, export DDL and code for 22 languages. Web app, Google Drive, VS Code, IntelliJ, Obsidian, a custom element, and an MCP server that lets coding agents edit diagrams live.</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/dineug/erd-editor</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>code-generation, data-modeling, database, database-design, database-schema, dbml, ddl, diagram, entity-relationship-diagram, erd, erd-editor, graphql</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="S18" s="3" t="n">
-        <v>2611</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-07-13</t>
+      <c r="S19" s="3" t="n">
+        <v>2598</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V18"/>
+  <autoFilter ref="A2:V19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -61,11 +61,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -114,9 +109,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -484,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -514,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-10-12 · 共 17 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-10-13 · 共 21 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,29 +625,29 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>paperclipai/paperclip</t>
+          <t>wheresryan22/anatomy</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>100508</v>
+        <v>6847</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>3140.9</v>
+        <v>9585.799999999999</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>开源应用，用于管理工作中使用的代理。
-【原文】The open-source app everyone uses to manage agents at work</t>
+          <t>创建交互式等距插图，生成 SVG 和 WebGL 效果
+【原文】An agent skill for creating detailed, interactive isometric illustrations of real-world machines and complex systems. Generates polished SVGs with optional WebGL shaders and 3D effects.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +662,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/paperclipai/paperclip</t>
+          <t>https://github.com/wheresryan22/anatomy</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,7 +671,7 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>448.7</v>
+        <v>1369.4</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -688,7 +680,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -701,10 +693,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>agent-skill, open-source, svg, vizualization</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -713,7 +709,7 @@
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>224</v>
+        <v>5</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -725,41 +721,41 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;100000 pushed:&gt;2026-09-12</t>
+          <t>agent skill in:name,description stars:&gt;300 pushed:&gt;2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Folkbench/folkbench</t>
+          <t>Ebony-Vinyl/EAC-Desktop</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>335</v>
+        <v>2002</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>234.5</v>
+        <v>233.6</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>AI API 中转站评测排行与切换工具，支持 Claude Code / Codex。
-【原文】AI API 中转站评测排行与切换工具：实测可用率、延迟与价格 · Open-source AI API relay benchmark, rankings &amp; switcher for Claude Code / Codex</t>
+          <t>桌面版插件和谐共存平台
+【原文】Embracing All Creation (Desktop) — Dedicated to the Harmonious Coexistence of Hundreds of DSH Plugins / 揽尽万象（桌面版） —— 致力于让数百个DSH插件和谐共存</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Folkbench/folkbench</t>
+          <t>https://github.com/Ebony-Vinyl/EAC-Desktop</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -778,16 +774,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>33.5</v>
+        <v>33.37</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -802,12 +798,12 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>ai, api-relay, api-relay-pricing, benchmark, benchmarks, claude, claude-code, codex, folkbench, llm, model-evaluation, openai-api</t>
+          <t>ai-agent, deepseek, deepseek-harness, desktop, desktop-app, dsh, dsh-plugin, dsh-plugins, dshdesktop, electron, tauri, windows</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -816,43 +812,43 @@
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-07-14</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>JourniOne-ai/JourniOne-Planning-Skills</t>
+          <t>Dave-cc/vibe-knowledge-film</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>802</v>
+        <v>173</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>216</v>
+        <v>173</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>JourniOne旅行规划技能，从灵感、路线到带地图、可分享的旅行日志。
-【原文】JourniOne 旅行规划 Skill：从灵感与逐日路线，到带地图、可分享的 Travel Journal，按需衔接酒店与航班。</t>
+          <t>抖音爆款 Vibe 知识短片 skill，深度拆解爆款视频，一键出片
+【原文】抖音爆款Vibe知识大赏知识短片skill，深度拆解爆款视频，复刻画风，导演分镜表，自动配音效，一键出片</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -862,7 +858,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -872,7 +868,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/JourniOne-ai/JourniOne-Planning-Skills</t>
+          <t>https://github.com/Dave-cc/vibe-knowledge-film</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -881,11 +877,11 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>30.85</v>
+        <v>24.71</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -903,69 +899,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, ai-agent, itinerary, journione, travel-journal, travel-planning</t>
-        </is>
-      </c>
+      <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>wenziai/wenzi-xiaohongshu-workflow</t>
+          <t>fumingyang2004/Tulpa</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>170</v>
+        <v>305</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>99.2</v>
+        <v>125.6</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>一套可安装的 Agent Skills，用于小红书内容创作工作流。
-【原文】文子的小红书工作流：从账号定位、选题标题、真人化改稿、图文规划到排期复盘的一套可安装 Agent Skills。</t>
+          <t>通过 MCP 让桌面 Agent 访问 QQ/微信数据，加入群聊
+【原文】通过 MCP，让几乎所有桌面 Agent 都能访问 QQ / 微信的本地数据、调用相关功能，甚至直接加入 QQ 群聊变成你的群友！</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>MCP服务/技能包</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -975,7 +967,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wenziai/wenzi-xiaohongshu-workflow</t>
+          <t>https://github.com/fumingyang2004/Tulpa</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -984,14 +976,18 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>14.17</v>
+        <v>17.94</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1004,57 +1000,57 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, codex-skills, content-creation, workbuddy, xiaohongshu</t>
+          <t>ai-agents, antigravity, claude-code, codex, deepseek-harness, gpt, mcp, onebot, qq-bot, snowluma, workbuddy</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:xiaohongshu stars:&gt;100</t>
+          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>charlie947/motion-graphics-skills</t>
+          <t>trustfuture/simon-skills</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>217</v>
+        <v>397</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>94.90000000000001</v>
+        <v>120.8</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>13项Claude Code技能，用于发布级动态图形制作，无需After Effects或视频生成器。
-【原文】13 Claude Code skills for launch-grade motion graphics. Every frame is code. No After Effects, no video generator.</t>
+          <t>提供AI视频生成技能集合
+【原文】不露脸做视频账号的 AI skill 合集：调查长片 + 手绘白板讲解视频，一句选题出片、配音字幕、封面与各平台文案</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1074,7 +1070,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/charlie947/motion-graphics-skills</t>
+          <t>https://github.com/trustfuture/simon-skills</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1083,7 +1079,7 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>13.56</v>
+        <v>17.26</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -1092,7 +1088,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1107,21 +1103,21 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-marketing, animation, claude, claude-code, claude-skills, codex, hyperframes, motion-graphics, video</t>
+          <t>claude-code, codex, excalidraw, remotion, skills, video-generation</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1133,41 +1129,41 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>onvoyage-ai/gtm-engineer-skills</t>
+          <t>skalesapp/skales</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1321</v>
+        <v>2035</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>40.5</v>
+        <v>65</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Claude Code技能，用于提升网站AEO和GEO分数，提供16项检查和修复。
-【原文】Claude Code skill for improving website AEO (AI Engine Optimization) and GEO (Generative Engine Optimization) scores — 16 foundational checks, 6 intelligence dimensions, framework-specific fixes</t>
+          <t>跨平台个人 AI 代理，支持自动化任务和桌面/浏览器自动化
+【原文】Personal AI agent for macOS, Windows, Linux, Android &amp; iOS. Set a goal, it works alone: coding (Skales Code), desktop + browser automation, autonomous scheduled Tasks. Teams of agents and humans across paired desktops. Agent2Agent, MCP, computer use, voice, local LLMs (Ollama), Agent Skills (SKILL.md). 26 AI providers, BYOK. No Docker, no terminal.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1177,7 +1173,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/onvoyage-ai/gtm-engineer-skills</t>
+          <t>https://github.com/skalesapp/skales</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1186,18 +1182,14 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5.79</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1210,62 +1202,62 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>aeo, ai-optimization, claude-code, geo, llms-txt, seo, structured-data</t>
+          <t>agentic-ai, ai-agent, ai-assistant, android, automation, autonomous-agent, desktop-app, electron, ios, linux, llm, local-ai</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>yasewang1337-svg/winutil-cn</t>
+          <t>ciddwd/overlay-translator</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>567</v>
+        <v>1005</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>33.3</v>
+        <v>62.2</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>面向 Windows 11 的中文软件管理与系统维护工具。
-【原文】面向 Windows 11 的中文软件管理与系统维护工具，支持 Windows 10 / 11 x64 安装镜像制作。基于 Chris Titus Tech Windows Utility。</t>
+          <t>开源 Android 屏幕实时翻译工具，支持 OCR 和多种翻译服务
+【原文】无需 ROOT 的开源 Android 屏幕实时翻译工具，适合游戏、视觉小说和漫画。支持端侧与云端 OCR、离线 LLM、多种翻译服务和文字朗读（TTS），译文可直接显示在画面上。Open-source no-root Android real-time screen translator for games, visual novels, and manga. Supports on-device and cloud OCR, offline LLMs, multiple translation services, on-screen translations, and text-to-speech (TTS).</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线/未归类</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1280,7 +1272,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yasewang1337-svg/winutil-cn</t>
+          <t>https://github.com/ciddwd/overlay-translator</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1289,16 +1281,16 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>4.76</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>PowerShell</t>
+          <t>Kotlin</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1313,62 +1305,62 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>chinese, chinese-localization, debloat, i18n, localization, package-manager, powershell, system-maintenance, windows, windows-10, windows-11, windows-utility</t>
+          <t>android, android-app, game-translation, gguf, kotlin, llama-cpp, llm, manga, manga-ocr, mlkit, no-root, ocr</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-09-12</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>yexi-by/dsh-unrestricted</t>
+          <t>xuanyustudio/LocalMiniDrama</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>204</v>
+        <v>2041</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>28</v>
+        <v>58.3</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>DeepSeek Harness插件，通过系统提示词解除模型回答限制，支持Web与桌面端。
-【原文】DeepSeek Harness 提示词破限插件：通过系统提示词解除模型回答限制，深度适配 Web 与桌面端多模式及工具调用</t>
+          <t>开源本地 AI 短剧 &amp; 漫剧生成工具，从故事到成片一站式完成
+【原文】🎬 seedance2接入  开源本地 AI 短剧 &amp; 漫剧生成工具 —— 从故事到成片一站式完成，数据不出本机，短剧工作流管理平台，高灵活度，AI真人剧，AI漫剧本地搞定。 Open-source local AI short drama maker: story → storyboard → video, fully offline, your data stays yours. 纳米流水线</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>技能包/数据集</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1383,7 +1375,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yexi-by/dsh-unrestricted</t>
+          <t>https://github.com/xuanyustudio/LocalMiniDrama</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1392,7 +1384,7 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>4</v>
+        <v>8.33</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1416,52 +1408,52 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>deepseek-harness, dsh, plugin, prompt-engineering, typescript</t>
+          <t>ai, ai-agent, ai-mini-drama, ai-video, electron, javascript, mini-drama, nodejs, offline, offline-short-drama, open-source, short-video</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>51</v>
+        <v>245</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-14</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>thedivergentai/Game-Design-Agentic-Skills</t>
+          <t>benchflow-ai/skillsbench</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>834</v>
+        <v>1842</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>23.7</v>
+        <v>44.8</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>游戏 AI 代理的多引擎长期记忆库，包含多种技能和蓝图。
-【原文】Multi-engine long-term memory for game AI agents. Deep Godot 4.7+ (99 skills, 27 genre blueprints) + Bevy docs-first parity — audited patterns, persona orchestration (Analyst · Auditor · Builder), production-grade engineering.</t>
+          <t>评估技能和智能体效果
+【原文】SkillsBench evaluates how well skills work and how effective agents are at using them.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1471,12 +1463,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1486,7 +1478,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/thedivergentai/Game-Design-Agentic-Skills</t>
+          <t>https://github.com/benchflow-ai/skillsbench</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1495,16 +1487,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>3.38</v>
+        <v>6.4</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>LGPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>GDScript</t>
+          <t>PDDL</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1517,19 +1509,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr"/>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>benchmark, skillsbench</t>
+        </is>
+      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>247</v>
+        <v>288</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1541,26 +1537,26 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>webpro/awesome-dotfiles</t>
+          <t>hotheadhacker/awesome-selfhost-docker</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>10897</v>
+        <v>4091</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>17.1</v>
+        <v>34.9</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>一个精选的dotfiles资源列表。
-【原文】A curated list of dotfiles resources.</t>
+          <t>提供可Docker部署的软件列表
+【原文】🚀 Curated list of open-source, self-hosted projects deployable with Docker and docker-compose. Your go-to resource for amazing self-hostable software.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1570,7 +1566,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1585,7 +1581,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/webpro/awesome-dotfiles</t>
+          <t>https://github.com/hotheadhacker/awesome-selfhost-docker</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1594,14 +1590,18 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.44</v>
+        <v>4.99</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1612,23 +1612,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, bash, dotfiles, dotfiles-resources, fish, list, shell, tools, zsh</t>
-        </is>
-      </c>
+      <c r="P12" s="6" t="inlineStr"/>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2014-07-16</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>4471</v>
+        <v>820</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1640,26 +1636,26 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-12</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>km1994/LLMs_interview_notes</t>
+          <t>isair/jarvis</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2614</v>
+        <v>2021</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>16.3</v>
+        <v>33.7</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>记录大模型算法工程师相关的面试题。
-【原文】该仓库主要记录 大模型（LLMs） 算法工程师相关的面试题</t>
+          <t>提供 100% 私密的 AI 语音助手，可在电脑上使用（离线）
+【原文】A 100% private AI voice assistant that lives on your computer (works offline). Talk naturally as if Jarvis is a third person in the room, and get conversational responses. It remembers everything, knows location and time, can check the web, control Chrome, track nutrition, and more with support for unlimited MCPs / tools without context rot.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1669,12 +1665,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1684,7 +1680,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/km1994/LLMs_interview_notes</t>
+          <t>https://github.com/isair/jarvis</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1693,14 +1689,18 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>2.33</v>
+        <v>4.81</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr"/>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1711,60 +1711,64 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>ai, assistant, health, machine-learning, mcp, nutrition, privacy, private, search, searching, voice</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1122</v>
+        <v>420</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-09-12</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>fcakyon/phd-skills</t>
+          <t>joeseesun/qiaomu-cut-skill</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>416</v>
+        <v>374</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>13.5</v>
+        <v>30.1</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>提供用于Claude Code的博士研究技能，包括论文复现、实验设计和评审。
-【原文】PhD Research Skills for Claude Code: paper reproduction, experiment design, paper review, result comparison and more.</t>
+          <t>乔木智能视频导演 Skill，提供素材治理、双语字幕、品牌包装与渲染
+【原文】乔木智能视频导演 Skill：素材治理、双语字幕、品牌包装与可复现渲染 | Agent-native video director with governed sourcing and verifiable rendering</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>技能包/MCP服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1779,7 +1783,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/fcakyon/phd-skills</t>
+          <t>https://github.com/joeseesun/qiaomu-cut-skill</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1788,7 +1792,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.93</v>
+        <v>4.3</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1797,7 +1801,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1812,21 +1816,21 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>academic, agents, ai, claude, claude-code, claude-code-plugin, claude-skills, conference, fable, hooks, journal, mcp</t>
+          <t>agent-skill, ai-video, ffmpeg, nodejs, subtitles, video-editing</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>215</v>
+        <v>87</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1838,36 +1842,36 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>NotIntoSports/RoleAI</t>
+          <t>sparanoid/chinese-copywriting-guidelines</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>108</v>
+        <v>15744</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>12.2</v>
+        <v>24</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>AI 数字人项目，支持实时互动、语音对练等功能。
-【原文】AI 数字人项目。角色以虚拟形象实时互动：你说话，对方看着你回答。也可做语音对练、会议辅助和直播讲解。</t>
+          <t>提供中文文案排版指南
+【原文】Chinese copywriting guidelines for better written communication／中文文案排版指北</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1882,7 +1886,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/NotIntoSports/RoleAI</t>
+          <t>https://github.com/sparanoid/chinese-copywriting-guidelines</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1891,18 +1895,14 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>1.74</v>
+        <v>3.43</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Rust</t>
-        </is>
-      </c>
+      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1913,10 +1913,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>chinese, chinese-simplified, chinese-traditional, copywriting, css, documentation, guideline, leancloud, markdown</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2014-03-17</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
@@ -1925,7 +1929,7 @@
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>62</v>
+        <v>4593</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1937,41 +1941,41 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-07-14</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>VanGong1999/screen-creative-skills</t>
+          <t>Anil-matcha/awesome-open-source-saas-alternatives</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>449</v>
+        <v>3397</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>11.4</v>
+        <v>22.3</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>影视创作评估策划 Agent Skills，包含 AI 影视自动化工作流。
-【原文】Skills for Film and Television Creation Agents|31 个影视创作评估策划Agent Skills｜AI影视自动化工作流｜竖屏短剧长剧IP改编｜情节题材提炼｜剧本小说IP创作策划评估｜人物小传｜拉片人物剧集故事五元素分析｜大纲生成｜</t>
+          <t>提供开源SaaS应用替代方案列表
+【原文】Open source alternatives to paid SaaS apps: Notion, Slack, Auth0, Vercel and more. Curated list with licenses and GitHub stars.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1981,7 +1985,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/VanGong1999/screen-creative-skills</t>
+          <t>https://github.com/Anil-matcha/awesome-open-source-saas-alternatives</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1990,16 +1994,16 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1.63</v>
+        <v>3.18</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2014,12 +2018,12 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>agents, ai, skills</t>
+          <t>alternatives, auth0-alternative, awesome, awesome-list, figma-alternative, firebase-alternative, free-software, notion-alternative, open-source, open-source-alternatives, open-source-software, postman-alternative</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -2028,7 +2032,7 @@
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>275</v>
+        <v>1068</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2040,41 +2044,41 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>wy-luke/All-Chinese-Character-Set</t>
+          <t>joeseesun/qiaomu-meta-skill</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1952</v>
+        <v>384</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>7.6</v>
+        <v>18.4</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>包含全部中文字符的字符集，适用于 Unity 3D。
-【原文】致力于维护一个包含全部中文字符（汉字+符号）的字符集，包罗万象，含3500 / 7000 常用汉字集、常用符号集。A Charater Set contains all Chinese charaters.</t>
+          <t>创建和评估乔木Agent技能
+【原文】把工作流变成可研究、可评测、可发布的乔木 Agent Skill | Turn workflows into researched, tested, release-ready agent skills.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2084,7 +2088,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wy-luke/All-Chinese-Character-Set</t>
+          <t>https://github.com/joeseesun/qiaomu-meta-skill</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2093,16 +2097,16 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>1.08</v>
+        <v>2.63</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2117,57 +2121,57 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>character-set, chinese, chinese-character, chinese-characters, chinese-simplified, font, textmeshpro, unity, unity-3d, unity3d</t>
+          <t>agent-skills, ai-workflow, qiaomu, skill-creator, skill-evaluation, skillsmp</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>1804</v>
+        <v>146</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-09-12</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>dbwls99706/ros2-engineering-skills</t>
+          <t>oil-oil/oil-cover</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>219</v>
+        <v>265</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>7.3</v>
+        <v>16.9</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>用于生产级ROS 2开发的Agent技能，涵盖工作区、节点、执行器等。
-【原文】Agent skill for production-grade ROS 2 development. Progressive-disclosure SKILL.md covering workspace, nodes, executors, QoS, ros2_control, Nav2, MoveIt 2, real-time, and deployment. Works with Claude Code, Codex, Cursor, Gemini CLI.</t>
+          <t>为 Claude Code &amp; Codex 生成视频封面和缩略图技能
+【原文】Video cover &amp; thumbnail skill for Claude Code &amp; Codex. 帮你用视频画面做小红书和 B 站封面。</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -2177,7 +2181,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -2187,7 +2191,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dbwls99706/ros2-engineering-skills</t>
+          <t>https://github.com/oil-oil/oil-cover</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2196,11 +2200,11 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>1.04</v>
+        <v>2.41</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2220,21 +2224,21 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>agent-skill, claude, claude-code, robotics, ros2</t>
+          <t>agent-skill, agent-skills, bilibili, claude-code, claude-skills, codex, codex-skill, content-creation, cover, cover-design, image-generation, skill</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
@@ -2246,26 +2250,26 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-09-12</t>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>dineug/erd-editor</t>
+          <t>meirwah/awesome-incident-response</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>1723</v>
+        <v>9447</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>4.6</v>
+        <v>16.6</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>ERD 编辑器，设计数据库模式，支持多种导入和导出功能。
-【原文】ERD Editor: design database schemas visually, import SQL DDL, GraphQL, DBML and AML, export DDL and code for 22 languages. Web app, Google Drive, VS Code, IntelliJ, Obsidian, a custom element, and an MCP server that lets coding agents edit diagrams live.</t>
+          <t>收集整理事件响应工具的列表
+【原文】A curated list of tools for incident response</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -2290,7 +2294,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dineug/erd-editor</t>
+          <t>https://github.com/meirwah/awesome-incident-response</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2299,18 +2303,14 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.66</v>
+        <v>2.37</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2323,21 +2323,21 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>code-generation, data-modeling, database, database-design, database-schema, dbml, ddl, diagram, entity-relationship-diagram, erd, erd-editor, graphql</t>
+          <t>awesome, awesome-list, cybersecurity, dfir, incident-response, incident-response-tooling, list, security</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2015-11-10</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>2598</v>
+        <v>3990</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
@@ -2349,12 +2349,420 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-12</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>alpacahq/alpaca-mcp-server</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>1018</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>提供股票、ETF、加密货币交易API
+【原文】Alpaca’s official MCP Server lets you trade stocks, ETFs, crypto, and options, run data analysis, and build strategies in plain English directly from your favorite LLM tools and IDEs</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池/未归类</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/alpacahq/alpaca-mcp-server</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>ai-trading, algorithmic-trading, crypto, etfs, mcp, mcp-server, options, stocks, trading, trading-api</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>497</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="150" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>italiaremote/awesome-italia-remote</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>2656</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>提供意大利远程工作公司列表
+【原文】A list of remote-friendly or full-remote companies that targets Italian talents.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/italiaremote/awesome-italia-remote</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, italy, jobs, list, remote, remote-jobs</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>2022-01-24</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>1723</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V21" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>engineering-management/awesome-engineering-management</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>2779</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>提供工程管理和领导力学习工具
+【原文】Pointers and tools for learning and day-to-day practice of engineering management &amp; leadership.</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/engineering-management/awesome-engineering-management</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, engineering-management, leadership, productivity, project-management</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>2021-06-11</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>1950</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Laihiujin/Prism</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>AI 驱动的多账号/多平台矩阵投放/发布平台，支持异步高并发自动化视频发布
+【原文】AI 驱动的多账号 / 多平台矩阵投放/发布平台，支持异步高并发自动化视频发布</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Laihiujin/Prism</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>auto-publish, automation, bilibili, content-publishing, douyin, kuaishou, matrix-publishing, multi-account, multi-platform, patchright, scheduled-publishing, scheduler</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-07-15</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V19"/>
+  <autoFilter ref="A2:V23"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -109,6 +114,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -476,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -506,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-10-13 · 共 21 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-10-15 · 共 23 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -625,24 +633,24 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>wheresryan22/anatomy</t>
+          <t>Arekejoker/qwen21-nsfw-pose-skill</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>6847</v>
+        <v>1399</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>9585.799999999999</v>
+        <v>4896.5</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>创建交互式等距插图，生成 SVG 和 WebGL 效果
-【原文】An agent skill for creating detailed, interactive isometric illustrations of real-world machines and complex systems. Generates polished SVGs with optional WebGL shaders and 3D effects.</t>
+          <t>生成 NSFW/姿势出图 skill
+【原文】Qwen-Image 2.1 NSFW/姿势出图 skill：作者级提示词配方 + NSFW LoRA + 136 姿势 VNCCS 人偶控制；适用 Claude Code / Codex / Cursor / OpenClaw</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -652,7 +660,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -662,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wheresryan22/anatomy</t>
+          <t>https://github.com/Arekejoker/qwen21-nsfw-pose-skill</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -671,16 +679,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>1369.4</v>
+        <v>699.5</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -695,52 +703,52 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>agent-skill, open-source, svg, vizualization</t>
+          <t>agent-skill, comfyui, image-generation, openclaw, pose-control, qwen-image</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>agent skill in:name,description stars:&gt;300 pushed:&gt;2026-07-15</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Ebony-Vinyl/EAC-Desktop</t>
+          <t>onehumanbeing/esp32-iphone-agent</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2002</v>
+        <v>2156</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>233.6</v>
+        <v>3773</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>桌面版插件和谐共存平台
-【原文】Embracing All Creation (Desktop) — Dedicated to the Harmonious Coexistence of Hundreds of DSH Plugins / 揽尽万象（桌面版） —— 致力于让数百个DSH插件和谐共存</t>
+          <t>使用 ESP32 控制iPhone的AI模型
+【原文】Let an AI model use a real iPhone with a $7 ESP32: AirPlay eyes, USB HID hands, any OpenAI-compatible vision model. No Mac, no developer account, no jailbreak.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -765,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Ebony-Vinyl/EAC-Desktop</t>
+          <t>https://github.com/onehumanbeing/esp32-iphone-agent</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -774,7 +782,7 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>33.37</v>
+        <v>539</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -783,7 +791,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -798,21 +806,21 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, deepseek, deepseek-harness, desktop, desktop-app, dsh, dsh-plugin, dsh-plugins, dshdesktop, electron, tauri, windows</t>
+          <t>ai-agent, airplay, automation, computer-use, esp32, esp32-s3, iphone, llm, usb-hid</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
@@ -824,41 +832,41 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-09-13</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Dave-cc/vibe-knowledge-film</t>
+          <t>bherbruck/solidcraft</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>173</v>
+        <v>2464</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>173</v>
+        <v>2156</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>抖音爆款 Vibe 知识短片 skill，深度拆解爆款视频，一键出片
-【原文】抖音爆款Vibe知识大赏知识短片skill，深度拆解爆款视频，复刻画风，导演分镜表，自动配音效，一键出片</t>
+          <t>开源参数化 3D CAD 应用
+【原文】SolidCraft: an open-source parametric 3D CAD application built in pure Rust. Desktop, web, and automation through MCP.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>可部署服务/架构参考</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -868,7 +876,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Dave-cc/vibe-knowledge-film</t>
+          <t>https://github.com/bherbruck/solidcraft</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -877,16 +885,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>24.71</v>
+        <v>308</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -899,60 +907,64 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>3d-modeling, brep, cad, egui, mcp, parametric-cad, rust, step, wasm</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-07-15</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>fumingyang2004/Tulpa</t>
+          <t>edenfunf/reelmimic</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>305</v>
+        <v>3250</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>125.6</v>
+        <v>1338.3</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>通过 MCP 让桌面 Agent 访问 QQ/微信数据，加入群聊
-【原文】通过 MCP，让几乎所有桌面 Agent 都能访问 QQ / 微信的本地数据、调用相关功能，甚至直接加入 QQ 群聊变成你的群友！</t>
+          <t>根据视频风格生成新视频
+【原文】Show it a video you love. Get a new video in the same style. An AI crew (Claude Code or Codex) plans, builds and reviews it with you.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -967,7 +979,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/fumingyang2004/Tulpa</t>
+          <t>https://github.com/edenfunf/reelmimic</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -976,7 +988,7 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>17.94</v>
+        <v>191.18</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -985,7 +997,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1000,17 +1012,17 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, antigravity, claude-code, codex, deepseek-harness, gpt, mcp, onebot, qq-bot, snowluma, workbuddy</t>
+          <t>2d-animation, ai-agents, ai-video, animation, claude-code, codex, multi-agent, style-transfer, video-generation</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
@@ -1021,41 +1033,41 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>微调 in:name,description stars:&gt;300 pushed:&gt;2026-07-15</t>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>trustfuture/simon-skills</t>
+          <t>trailhq/Trail-Code</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>397</v>
+        <v>10038</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>120.8</v>
+        <v>675.6</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供AI视频生成技能集合
-【原文】不露脸做视频账号的 AI skill 合集：调查长片 + 手绘白板讲解视频，一句选题出片、配音字幕、封面与各平台文案</t>
+          <t>增强 Claude Code 等编码代理
+【原文】Turbocharge Claude Code, Cursor, Codex, Gemini &amp; every coding agent: faster, cheaper, with contextual understanding specific to your codebase.</t>
         </is>
       </c>
       <c r="